--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -5057,14 +5057,18 @@
       <c r="B5" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>158</v>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>PRJ-2025-042</t>
+        </is>
       </c>
       <c r="D5" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>160</v>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
       </c>
       <c r="AA5" s="3" t="s">
         <v>6</v>
@@ -5074,8 +5078,10 @@
       <c r="B6" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>158</v>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Aufbau Gemeindezentrum Beispielstadt</t>
+        </is>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -5087,14 +5093,18 @@
       <c r="B7" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>158</v>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Beispiel Hilfswerk e.V.</t>
+        </is>
       </c>
       <c r="D7" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>158</v>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
       <c r="AA7" s="3" t="s">
         <v>8</v>
@@ -5104,8 +5114,10 @@
       <c r="B8" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>158</v>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>01.01.2025 - 31.12.2027</t>
+        </is>
       </c>
       <c r="D8" s="4" t="s">
         <v>165</v>
@@ -5121,14 +5133,18 @@
       <c r="B9" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>158</v>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>PRJ-2022-017</t>
+        </is>
       </c>
       <c r="D9" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>158</v>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
       <c r="AA9" s="3" t="s">
         <v>10</v>
@@ -5138,14 +5154,14 @@
       <c r="B10" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>158</v>
+      <c r="C10" s="10">
+        <v>45657</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>158</v>
+      <c r="E10" s="11">
+        <v>125</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>11</v>
@@ -5155,14 +5171,14 @@
       <c r="B11" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>158</v>
+      <c r="C11" s="12">
+        <v>200000</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>158</v>
+      <c r="E11" s="13">
+        <v>1600</v>
       </c>
       <c r="AA11" s="3" t="s">
         <v>12</v>
@@ -5172,14 +5188,14 @@
       <c r="B12" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>158</v>
+      <c r="C12" s="10">
+        <v>45658</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>158</v>
+      <c r="E12" s="11">
+        <v>125</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>13</v>
@@ -5189,14 +5205,14 @@
       <c r="B13" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>158</v>
+      <c r="C13" s="12">
+        <v>200000</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>158</v>
+      <c r="E13" s="13">
+        <v>1600</v>
       </c>
       <c r="AA13" s="3" t="s">
         <v>14</v>
@@ -5212,8 +5228,10 @@
         <v>175</v>
       </c>
       <c r="C15" s="14"/>
-      <c r="D15" s="15" t="s">
-        <v>176</v>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
       </c>
       <c r="E15" s="16" t="s">
         <v>177</v>
@@ -5225,8 +5243,10 @@
     <row r="16" ht="22" customHeight="true">
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
-      <c r="D16" s="15" t="s">
-        <v>176</v>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
       </c>
       <c r="E16" s="16" t="s">
         <v>178</v>
@@ -5238,8 +5258,10 @@
     <row r="17" ht="22" customHeight="true">
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="15" t="s">
-        <v>176</v>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
       </c>
       <c r="E17" s="16" t="s">
         <v>179</v>
@@ -5251,8 +5273,10 @@
     <row r="18" ht="22" customHeight="true">
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="15" t="s">
-        <v>176</v>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
       </c>
       <c r="E18" s="16" t="s">
         <v>180</v>
@@ -5264,8 +5288,10 @@
     <row r="19" ht="22" customHeight="true">
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="15" t="s">
-        <v>176</v>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
       </c>
       <c r="E19" s="16" t="s">
         <v>181</v>
@@ -5277,8 +5303,10 @@
     <row r="20" ht="22" customHeight="true">
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
-      <c r="D20" s="15" t="s">
-        <v>176</v>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
       </c>
       <c r="E20" s="16" t="s">
         <v>182</v>
@@ -5290,8 +5318,10 @@
     <row r="21" ht="22" customHeight="true">
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
-      <c r="D21" s="15" t="s">
-        <v>176</v>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
       </c>
       <c r="E21" s="16" t="s">
         <v>183</v>
@@ -13525,7 +13555,7 @@
         <v>311</v>
       </c>
       <c r="C34" s="129">
-        <v>125000</v>
+        <v>325000</v>
       </c>
       <c r="D34" s="130" t="str">
         <f>=IF(C34=0, 0, IF(ROUND(SUM(C35:C36), 2)=0, ROUND(D31 - 0, 2), ROUND(C34 / ROUND(SUM(C34:C36), 2) * D31, 2)))</f>
@@ -13535,7 +13565,7 @@
         <v>311</v>
       </c>
       <c r="J34" s="129">
-        <v>175000</v>
+        <v>375000</v>
       </c>
       <c r="K34" s="130" t="str">
         <f>=IF(J34=0, 0, IF(ROUND(SUM(J35:J36), 2)=0, ROUND(K31 - 0, 2), ROUND(J34 / ROUND(SUM(J34:J36), 2) * K31, 2)))</f>

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
   <si>
     <t xml:space="preserve">  DASHBOARD (v1.0)</t>
   </si>
@@ -1112,16 +1112,10 @@
     <t>Saldo des Vorprojekts</t>
   </si>
   <si>
-    <t>KMW</t>
-  </si>
-  <si>
     <t>Gesamteinnahmen in Periode</t>
   </si>
   <si>
     <t>Einnahmen (Durchschnittskurs)</t>
-  </si>
-  <si>
-    <t>Projektpartner</t>
   </si>
   <si>
     <t>Gesamt (Durchschnittskurs)</t>
@@ -7236,55 +7230,55 @@
   <sheetData>
     <row r="3">
       <c r="H3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="O3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="V3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AC3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AJ3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AQ3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AX3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BE3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BL3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BS3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BZ3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="CG3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="CN3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="CU3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="DB3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="DI3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="DP3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4">
@@ -8424,7 +8418,7 @@
         <f>=ROUND(IF(Saldovortrag_EUR="",0,Saldovortrag_EUR),2)</f>
       </c>
       <c r="I11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_1,2)</f>
@@ -8439,7 +8433,7 @@
         <f>=ROUND(FB_SaldoEUR_1,2)</f>
       </c>
       <c r="P11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Q11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_2,2)</f>
@@ -8454,7 +8448,7 @@
         <f>=ROUND(FB_SaldoEUR_2,2)</f>
       </c>
       <c r="W11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="X11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_3,2)</f>
@@ -8469,7 +8463,7 @@
         <f>=ROUND(FB_SaldoEUR_3,2)</f>
       </c>
       <c r="AD11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AE11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_4,2)</f>
@@ -8484,7 +8478,7 @@
         <f>=ROUND(FB_SaldoEUR_4,2)</f>
       </c>
       <c r="AK11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AL11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_5,2)</f>
@@ -8499,7 +8493,7 @@
         <f>=ROUND(FB_SaldoEUR_5,2)</f>
       </c>
       <c r="AR11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AS11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_6,2)</f>
@@ -8514,7 +8508,7 @@
         <f>=ROUND(FB_SaldoEUR_6,2)</f>
       </c>
       <c r="AY11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AZ11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_7,2)</f>
@@ -8529,7 +8523,7 @@
         <f>=ROUND(FB_SaldoEUR_7,2)</f>
       </c>
       <c r="BF11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="BG11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_8,2)</f>
@@ -8544,7 +8538,7 @@
         <f>=ROUND(FB_SaldoEUR_8,2)</f>
       </c>
       <c r="BM11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="BN11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_9,2)</f>
@@ -8559,7 +8553,7 @@
         <f>=ROUND(FB_SaldoEUR_9,2)</f>
       </c>
       <c r="BT11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="BU11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_10,2)</f>
@@ -8574,7 +8568,7 @@
         <f>=ROUND(FB_SaldoEUR_10,2)</f>
       </c>
       <c r="CA11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="CB11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_11,2)</f>
@@ -8589,7 +8583,7 @@
         <f>=ROUND(FB_SaldoEUR_11,2)</f>
       </c>
       <c r="CH11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="CI11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_12,2)</f>
@@ -8604,7 +8598,7 @@
         <f>=ROUND(FB_SaldoEUR_12,2)</f>
       </c>
       <c r="CO11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="CP11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_13,2)</f>
@@ -8619,7 +8613,7 @@
         <f>=ROUND(FB_SaldoEUR_13,2)</f>
       </c>
       <c r="CV11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="CW11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_14,2)</f>
@@ -8634,7 +8628,7 @@
         <f>=ROUND(FB_SaldoEUR_14,2)</f>
       </c>
       <c r="DC11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="DD11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_15,2)</f>
@@ -8649,7 +8643,7 @@
         <f>=ROUND(FB_SaldoEUR_15,2)</f>
       </c>
       <c r="DJ11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="DK11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_16,2)</f>
@@ -8664,7 +8658,7 @@
         <f>=ROUND(FB_SaldoEUR_16,2)</f>
       </c>
       <c r="DQ11" s="143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="DR11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_17,2)</f>
@@ -14546,7 +14540,7 @@
         <f>=ROUND(IFERROR(D43/E43,0),6)</f>
       </c>
       <c r="I43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J43" s="161" t="s">
         <v>158</v>
@@ -14561,7 +14555,7 @@
         <f>=ROUND(IFERROR(K43/L43,0),6)</f>
       </c>
       <c r="P43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Q43" s="161" t="s">
         <v>158</v>
@@ -14576,7 +14570,7 @@
         <f>=ROUND(IFERROR(R43/S43,0),6)</f>
       </c>
       <c r="W43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="X43" s="161" t="s">
         <v>158</v>
@@ -14591,7 +14585,7 @@
         <f>=ROUND(IFERROR(Y43/Z43,0),6)</f>
       </c>
       <c r="AD43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AE43" s="161" t="s">
         <v>158</v>
@@ -14606,7 +14600,7 @@
         <f>=ROUND(IFERROR(AF43/AG43,0),6)</f>
       </c>
       <c r="AK43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AL43" s="161" t="s">
         <v>158</v>
@@ -14621,7 +14615,7 @@
         <f>=ROUND(IFERROR(AM43/AN43,0),6)</f>
       </c>
       <c r="AR43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AS43" s="161" t="s">
         <v>158</v>
@@ -14636,7 +14630,7 @@
         <f>=ROUND(IFERROR(AT43/AU43,0),6)</f>
       </c>
       <c r="AY43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AZ43" s="161" t="s">
         <v>158</v>
@@ -14651,7 +14645,7 @@
         <f>=ROUND(IFERROR(BA43/BB43,0),6)</f>
       </c>
       <c r="BF43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="BG43" s="161" t="s">
         <v>158</v>
@@ -14666,7 +14660,7 @@
         <f>=ROUND(IFERROR(BH43/BI43,0),6)</f>
       </c>
       <c r="BM43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="BN43" s="161" t="s">
         <v>158</v>
@@ -14681,7 +14675,7 @@
         <f>=ROUND(IFERROR(BO43/BP43,0),6)</f>
       </c>
       <c r="BT43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="BU43" s="161" t="s">
         <v>158</v>
@@ -14696,7 +14690,7 @@
         <f>=ROUND(IFERROR(BV43/BW43,0),6)</f>
       </c>
       <c r="CA43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="CB43" s="161" t="s">
         <v>158</v>
@@ -14711,7 +14705,7 @@
         <f>=ROUND(IFERROR(CC43/CD43,0),6)</f>
       </c>
       <c r="CH43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="CI43" s="161" t="s">
         <v>158</v>
@@ -14726,7 +14720,7 @@
         <f>=ROUND(IFERROR(CJ43/CK43,0),6)</f>
       </c>
       <c r="CO43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="CP43" s="161" t="s">
         <v>158</v>
@@ -14741,7 +14735,7 @@
         <f>=ROUND(IFERROR(CQ43/CR43,0),6)</f>
       </c>
       <c r="CV43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="CW43" s="161" t="s">
         <v>158</v>
@@ -14756,7 +14750,7 @@
         <f>=ROUND(IFERROR(CX43/CY43,0),6)</f>
       </c>
       <c r="DC43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="DD43" s="161" t="s">
         <v>158</v>
@@ -14771,7 +14765,7 @@
         <f>=ROUND(IFERROR(DE43/DF43,0),6)</f>
       </c>
       <c r="DJ43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="DK43" s="161" t="s">
         <v>158</v>
@@ -14786,7 +14780,7 @@
         <f>=ROUND(IFERROR(DL43/DM43,0),6)</f>
       </c>
       <c r="DQ43" s="160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="DR43" s="161" t="s">
         <v>158</v>
@@ -14806,7 +14800,7 @@
         <v>199</v>
       </c>
       <c r="C44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="D44" s="167">
         <v>1250000</v>
@@ -14821,7 +14815,7 @@
         <v>199</v>
       </c>
       <c r="J44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="K44" s="167">
         <v>1000000</v>
@@ -14836,7 +14830,7 @@
         <v>199</v>
       </c>
       <c r="Q44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="R44" s="167"/>
       <c r="S44" s="168"/>
@@ -14847,7 +14841,7 @@
         <v>199</v>
       </c>
       <c r="X44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="Y44" s="167"/>
       <c r="Z44" s="168"/>
@@ -14858,7 +14852,7 @@
         <v>199</v>
       </c>
       <c r="AE44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="AF44" s="167"/>
       <c r="AG44" s="168"/>
@@ -14869,7 +14863,7 @@
         <v>199</v>
       </c>
       <c r="AL44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="AM44" s="167"/>
       <c r="AN44" s="168"/>
@@ -14880,7 +14874,7 @@
         <v>199</v>
       </c>
       <c r="AS44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="AT44" s="167"/>
       <c r="AU44" s="168"/>
@@ -14891,7 +14885,7 @@
         <v>199</v>
       </c>
       <c r="AZ44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="BA44" s="167"/>
       <c r="BB44" s="168"/>
@@ -14902,7 +14896,7 @@
         <v>199</v>
       </c>
       <c r="BG44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="BH44" s="167"/>
       <c r="BI44" s="168"/>
@@ -14913,7 +14907,7 @@
         <v>199</v>
       </c>
       <c r="BN44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="BO44" s="167"/>
       <c r="BP44" s="168"/>
@@ -14924,7 +14918,7 @@
         <v>199</v>
       </c>
       <c r="BU44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="BV44" s="167"/>
       <c r="BW44" s="168"/>
@@ -14935,7 +14929,7 @@
         <v>199</v>
       </c>
       <c r="CB44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="CC44" s="167"/>
       <c r="CD44" s="168"/>
@@ -14946,7 +14940,7 @@
         <v>199</v>
       </c>
       <c r="CI44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="CJ44" s="167"/>
       <c r="CK44" s="168"/>
@@ -14957,7 +14951,7 @@
         <v>199</v>
       </c>
       <c r="CP44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="CQ44" s="167"/>
       <c r="CR44" s="168"/>
@@ -14968,7 +14962,7 @@
         <v>199</v>
       </c>
       <c r="CW44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="CX44" s="167"/>
       <c r="CY44" s="168"/>
@@ -14979,7 +14973,7 @@
         <v>199</v>
       </c>
       <c r="DD44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="DE44" s="167"/>
       <c r="DF44" s="168"/>
@@ -14990,7 +14984,7 @@
         <v>199</v>
       </c>
       <c r="DK44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="DL44" s="167"/>
       <c r="DM44" s="168"/>
@@ -15001,7 +14995,7 @@
         <v>199</v>
       </c>
       <c r="DR44" s="166" t="s">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="DS44" s="167"/>
       <c r="DT44" s="168"/>
@@ -15611,7 +15605,7 @@
     </row>
     <row r="48">
       <c r="B48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C48" s="171" t="s">
         <v>292</v>
@@ -15626,7 +15620,7 @@
         <f>=ROUND(IFERROR(D48/E48,0),6)</f>
       </c>
       <c r="I48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J48" s="171" t="s">
         <v>292</v>
@@ -15641,7 +15635,7 @@
         <f>=ROUND(IFERROR(K48/L48,0),6)</f>
       </c>
       <c r="P48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q48" s="171" t="s">
         <v>292</v>
@@ -15656,7 +15650,7 @@
         <f>=ROUND(IFERROR(R48/S48,0),6)</f>
       </c>
       <c r="W48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X48" s="171" t="s">
         <v>292</v>
@@ -15671,7 +15665,7 @@
         <f>=ROUND(IFERROR(Y48/Z48,0),6)</f>
       </c>
       <c r="AD48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AE48" s="171" t="s">
         <v>292</v>
@@ -15686,7 +15680,7 @@
         <f>=ROUND(IFERROR(AF48/AG48,0),6)</f>
       </c>
       <c r="AK48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AL48" s="171" t="s">
         <v>292</v>
@@ -15701,7 +15695,7 @@
         <f>=ROUND(IFERROR(AM48/AN48,0),6)</f>
       </c>
       <c r="AR48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AS48" s="171" t="s">
         <v>292</v>
@@ -15716,7 +15710,7 @@
         <f>=ROUND(IFERROR(AT48/AU48,0),6)</f>
       </c>
       <c r="AY48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AZ48" s="171" t="s">
         <v>292</v>
@@ -15731,7 +15725,7 @@
         <f>=ROUND(IFERROR(BA48/BB48,0),6)</f>
       </c>
       <c r="BF48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="BG48" s="171" t="s">
         <v>292</v>
@@ -15746,7 +15740,7 @@
         <f>=ROUND(IFERROR(BH48/BI48,0),6)</f>
       </c>
       <c r="BM48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="BN48" s="171" t="s">
         <v>292</v>
@@ -15761,7 +15755,7 @@
         <f>=ROUND(IFERROR(BO48/BP48,0),6)</f>
       </c>
       <c r="BT48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="BU48" s="171" t="s">
         <v>292</v>
@@ -15776,7 +15770,7 @@
         <f>=ROUND(IFERROR(BV48/BW48,0),6)</f>
       </c>
       <c r="CA48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="CB48" s="171" t="s">
         <v>292</v>
@@ -15791,7 +15785,7 @@
         <f>=ROUND(IFERROR(CC48/CD48,0),6)</f>
       </c>
       <c r="CH48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="CI48" s="171" t="s">
         <v>292</v>
@@ -15806,7 +15800,7 @@
         <f>=ROUND(IFERROR(CJ48/CK48,0),6)</f>
       </c>
       <c r="CO48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="CP48" s="171" t="s">
         <v>292</v>
@@ -15821,7 +15815,7 @@
         <f>=ROUND(IFERROR(CQ48/CR48,0),6)</f>
       </c>
       <c r="CV48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="CW48" s="171" t="s">
         <v>292</v>
@@ -15836,7 +15830,7 @@
         <f>=ROUND(IFERROR(CX48/CY48,0),6)</f>
       </c>
       <c r="DC48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="DD48" s="171" t="s">
         <v>292</v>
@@ -15851,7 +15845,7 @@
         <f>=ROUND(IFERROR(DE48/DF48,0),6)</f>
       </c>
       <c r="DJ48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="DK48" s="171" t="s">
         <v>292</v>
@@ -15866,7 +15860,7 @@
         <f>=ROUND(IFERROR(DL48/DM48,0),6)</f>
       </c>
       <c r="DQ48" s="170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="DR48" s="171" t="s">
         <v>292</v>
@@ -15883,58 +15877,58 @@
     </row>
     <row r="50">
       <c r="B50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="W50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AD50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AK50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AR50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AY50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="BF50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="BM50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="BT50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="CA50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="CH50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="CO50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="CV50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="DC50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="DJ50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="DQ50" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51">
@@ -16214,7 +16208,7 @@
         <v>194</v>
       </c>
       <c r="C52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="D52" s="167">
         <v>250000</v>
@@ -16229,7 +16223,7 @@
         <v>194</v>
       </c>
       <c r="J52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="K52" s="167">
         <v>200000</v>
@@ -16244,7 +16238,7 @@
         <v>194</v>
       </c>
       <c r="Q52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="R52" s="167"/>
       <c r="S52" s="175" t="str">
@@ -16257,7 +16251,7 @@
         <v>194</v>
       </c>
       <c r="X52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="Y52" s="167"/>
       <c r="Z52" s="175" t="str">
@@ -16270,7 +16264,7 @@
         <v>194</v>
       </c>
       <c r="AE52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="AF52" s="167"/>
       <c r="AG52" s="175" t="str">
@@ -16283,7 +16277,7 @@
         <v>194</v>
       </c>
       <c r="AL52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="AM52" s="167"/>
       <c r="AN52" s="175" t="str">
@@ -16296,7 +16290,7 @@
         <v>194</v>
       </c>
       <c r="AS52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="AT52" s="167"/>
       <c r="AU52" s="175" t="str">
@@ -16309,7 +16303,7 @@
         <v>194</v>
       </c>
       <c r="AZ52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="BA52" s="167"/>
       <c r="BB52" s="175" t="str">
@@ -16322,7 +16316,7 @@
         <v>194</v>
       </c>
       <c r="BG52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="BH52" s="167"/>
       <c r="BI52" s="175" t="str">
@@ -16335,7 +16329,7 @@
         <v>194</v>
       </c>
       <c r="BN52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="BO52" s="167"/>
       <c r="BP52" s="175" t="str">
@@ -16348,7 +16342,7 @@
         <v>194</v>
       </c>
       <c r="BU52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="BV52" s="167"/>
       <c r="BW52" s="175" t="str">
@@ -16361,7 +16355,7 @@
         <v>194</v>
       </c>
       <c r="CB52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="CC52" s="167"/>
       <c r="CD52" s="175" t="str">
@@ -16374,7 +16368,7 @@
         <v>194</v>
       </c>
       <c r="CI52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="CJ52" s="167"/>
       <c r="CK52" s="175" t="str">
@@ -16387,7 +16381,7 @@
         <v>194</v>
       </c>
       <c r="CP52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="CQ52" s="167"/>
       <c r="CR52" s="175" t="str">
@@ -16400,7 +16394,7 @@
         <v>194</v>
       </c>
       <c r="CW52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="CX52" s="167"/>
       <c r="CY52" s="175" t="str">
@@ -16413,7 +16407,7 @@
         <v>194</v>
       </c>
       <c r="DD52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="DE52" s="167"/>
       <c r="DF52" s="175" t="str">
@@ -16426,7 +16420,7 @@
         <v>194</v>
       </c>
       <c r="DK52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="DL52" s="167"/>
       <c r="DM52" s="175" t="str">
@@ -16439,7 +16433,7 @@
         <v>194</v>
       </c>
       <c r="DR52" s="166" t="s">
-        <v>323</v>
+        <v>158</v>
       </c>
       <c r="DS52" s="167"/>
       <c r="DT52" s="175" t="str">
@@ -16694,7 +16688,7 @@
         <v>301</v>
       </c>
       <c r="C54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="D54" s="167"/>
       <c r="E54" s="175" t="str">
@@ -16707,7 +16701,7 @@
         <v>301</v>
       </c>
       <c r="J54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="K54" s="167"/>
       <c r="L54" s="175" t="str">
@@ -16720,7 +16714,7 @@
         <v>301</v>
       </c>
       <c r="Q54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="R54" s="167"/>
       <c r="S54" s="175" t="str">
@@ -16733,7 +16727,7 @@
         <v>301</v>
       </c>
       <c r="X54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="Y54" s="167"/>
       <c r="Z54" s="175" t="str">
@@ -16746,7 +16740,7 @@
         <v>301</v>
       </c>
       <c r="AE54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="AF54" s="167"/>
       <c r="AG54" s="175" t="str">
@@ -16759,7 +16753,7 @@
         <v>301</v>
       </c>
       <c r="AL54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="AM54" s="167"/>
       <c r="AN54" s="175" t="str">
@@ -16772,7 +16766,7 @@
         <v>301</v>
       </c>
       <c r="AS54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="AT54" s="167"/>
       <c r="AU54" s="175" t="str">
@@ -16785,7 +16779,7 @@
         <v>301</v>
       </c>
       <c r="AZ54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="BA54" s="167"/>
       <c r="BB54" s="175" t="str">
@@ -16798,7 +16792,7 @@
         <v>301</v>
       </c>
       <c r="BG54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="BH54" s="167"/>
       <c r="BI54" s="175" t="str">
@@ -16811,7 +16805,7 @@
         <v>301</v>
       </c>
       <c r="BN54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="BO54" s="167"/>
       <c r="BP54" s="175" t="str">
@@ -16824,7 +16818,7 @@
         <v>301</v>
       </c>
       <c r="BU54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="BV54" s="167"/>
       <c r="BW54" s="175" t="str">
@@ -16837,7 +16831,7 @@
         <v>301</v>
       </c>
       <c r="CB54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="CC54" s="167"/>
       <c r="CD54" s="175" t="str">
@@ -16850,7 +16844,7 @@
         <v>301</v>
       </c>
       <c r="CI54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="CJ54" s="167"/>
       <c r="CK54" s="175" t="str">
@@ -16863,7 +16857,7 @@
         <v>301</v>
       </c>
       <c r="CP54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="CQ54" s="167"/>
       <c r="CR54" s="175" t="str">
@@ -16876,7 +16870,7 @@
         <v>301</v>
       </c>
       <c r="CW54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="CX54" s="167"/>
       <c r="CY54" s="175" t="str">
@@ -16889,7 +16883,7 @@
         <v>301</v>
       </c>
       <c r="DD54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="DE54" s="167"/>
       <c r="DF54" s="175" t="str">
@@ -16902,7 +16896,7 @@
         <v>301</v>
       </c>
       <c r="DK54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="DL54" s="167"/>
       <c r="DM54" s="175" t="str">
@@ -16915,7 +16909,7 @@
         <v>301</v>
       </c>
       <c r="DR54" s="166" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="DS54" s="167"/>
       <c r="DT54" s="175" t="str">
@@ -17635,7 +17629,7 @@
     </row>
     <row r="58">
       <c r="B58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C58" s="171" t="s">
         <v>292</v>
@@ -17650,7 +17644,7 @@
         <f>=ROUND(IFERROR(D58/E58,0),6)</f>
       </c>
       <c r="I58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J58" s="171" t="s">
         <v>292</v>
@@ -17665,7 +17659,7 @@
         <f>=ROUND(IFERROR(K58/L58,0),6)</f>
       </c>
       <c r="P58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="Q58" s="171" t="s">
         <v>292</v>
@@ -17680,7 +17674,7 @@
         <f>=ROUND(IFERROR(R58/S58,0),6)</f>
       </c>
       <c r="W58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="X58" s="171" t="s">
         <v>292</v>
@@ -17695,7 +17689,7 @@
         <f>=ROUND(IFERROR(Y58/Z58,0),6)</f>
       </c>
       <c r="AD58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AE58" s="171" t="s">
         <v>292</v>
@@ -17710,7 +17704,7 @@
         <f>=ROUND(IFERROR(AF58/AG58,0),6)</f>
       </c>
       <c r="AK58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AL58" s="171" t="s">
         <v>292</v>
@@ -17725,7 +17719,7 @@
         <f>=ROUND(IFERROR(AM58/AN58,0),6)</f>
       </c>
       <c r="AR58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AS58" s="171" t="s">
         <v>292</v>
@@ -17740,7 +17734,7 @@
         <f>=ROUND(IFERROR(AT58/AU58,0),6)</f>
       </c>
       <c r="AY58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AZ58" s="171" t="s">
         <v>292</v>
@@ -17755,7 +17749,7 @@
         <f>=ROUND(IFERROR(BA58/BB58,0),6)</f>
       </c>
       <c r="BF58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="BG58" s="171" t="s">
         <v>292</v>
@@ -17770,7 +17764,7 @@
         <f>=ROUND(IFERROR(BH58/BI58,0),6)</f>
       </c>
       <c r="BM58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="BN58" s="171" t="s">
         <v>292</v>
@@ -17785,7 +17779,7 @@
         <f>=ROUND(IFERROR(BO58/BP58,0),6)</f>
       </c>
       <c r="BT58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="BU58" s="171" t="s">
         <v>292</v>
@@ -17800,7 +17794,7 @@
         <f>=ROUND(IFERROR(BV58/BW58,0),6)</f>
       </c>
       <c r="CA58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="CB58" s="171" t="s">
         <v>292</v>
@@ -17815,7 +17809,7 @@
         <f>=ROUND(IFERROR(CC58/CD58,0),6)</f>
       </c>
       <c r="CH58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="CI58" s="171" t="s">
         <v>292</v>
@@ -17830,7 +17824,7 @@
         <f>=ROUND(IFERROR(CJ58/CK58,0),6)</f>
       </c>
       <c r="CO58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="CP58" s="171" t="s">
         <v>292</v>
@@ -17845,7 +17839,7 @@
         <f>=ROUND(IFERROR(CQ58/CR58,0),6)</f>
       </c>
       <c r="CV58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="CW58" s="171" t="s">
         <v>292</v>
@@ -17860,7 +17854,7 @@
         <f>=ROUND(IFERROR(CX58/CY58,0),6)</f>
       </c>
       <c r="DC58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="DD58" s="171" t="s">
         <v>292</v>
@@ -17875,7 +17869,7 @@
         <f>=ROUND(IFERROR(DE58/DF58,0),6)</f>
       </c>
       <c r="DJ58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="DK58" s="171" t="s">
         <v>292</v>
@@ -17890,7 +17884,7 @@
         <f>=ROUND(IFERROR(DL58/DM58,0),6)</f>
       </c>
       <c r="DQ58" s="170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="DR58" s="171" t="s">
         <v>292</v>
@@ -18521,55 +18515,55 @@
   <sheetData>
     <row r="3">
       <c r="E3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="U3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Y3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AC3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AK3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AO3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AS3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AW3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BA3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BE3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BI3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BM3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BQ3" s="176" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4">
@@ -19022,96 +19016,96 @@
     </row>
     <row r="8">
       <c r="B8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C8" s="179">
         <v>125</v>
       </c>
       <c r="D8" s="179"/>
       <c r="F8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G8" s="179">
         <v>125</v>
       </c>
       <c r="H8" s="179"/>
       <c r="J8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="K8" s="179"/>
       <c r="L8" s="179"/>
       <c r="N8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="O8" s="179"/>
       <c r="P8" s="179"/>
       <c r="R8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S8" s="179"/>
       <c r="T8" s="179"/>
       <c r="V8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="W8" s="179"/>
       <c r="X8" s="179"/>
       <c r="Z8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AA8" s="179"/>
       <c r="AB8" s="179"/>
       <c r="AD8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AE8" s="179"/>
       <c r="AF8" s="179"/>
       <c r="AH8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AI8" s="179"/>
       <c r="AJ8" s="179"/>
       <c r="AL8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AM8" s="179"/>
       <c r="AN8" s="179"/>
       <c r="AP8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AQ8" s="179"/>
       <c r="AR8" s="179"/>
       <c r="AT8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AU8" s="179"/>
       <c r="AV8" s="179"/>
       <c r="AX8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AY8" s="179"/>
       <c r="AZ8" s="179"/>
       <c r="BB8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="BC8" s="179"/>
       <c r="BD8" s="179"/>
       <c r="BF8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="BG8" s="179"/>
       <c r="BH8" s="179"/>
       <c r="BJ8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="BK8" s="179"/>
       <c r="BL8" s="179"/>
       <c r="BN8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="BO8" s="179"/>
       <c r="BP8" s="179"/>
       <c r="BR8" s="105" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="BS8" s="179"/>
       <c r="BT8" s="179"/>
@@ -19121,163 +19115,163 @@
         <v>202</v>
       </c>
       <c r="C9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="G9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="K9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="O9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="R9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="S9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="T9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="V9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="W9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="X9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="Z9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="AA9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AB9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AD9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="AE9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AF9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AH9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="AI9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AJ9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AL9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="AM9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AN9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AP9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="AQ9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AR9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AT9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="AU9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AV9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AX9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="AY9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AZ9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="BB9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="BC9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="BD9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="BF9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="BG9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="BH9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="BJ9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="BK9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="BL9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="BN9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="BO9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="BP9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="BR9" s="180" t="s">
         <v>202</v>
       </c>
       <c r="BS9" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="BT9" s="180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -20328,7 +20322,7 @@
     </row>
     <row r="18">
       <c r="B18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_1[Angefordert (LC)]),2)</f>
@@ -20337,7 +20331,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_1[Angefordert (EUR)]),2)</f>
       </c>
       <c r="F18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_2[Angefordert (LC)]),2)</f>
@@ -20346,7 +20340,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_2[Angefordert (EUR)]),2)</f>
       </c>
       <c r="J18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="K18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_3[Angefordert (LC)]),2)</f>
@@ -20355,7 +20349,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_3[Angefordert (EUR)]),2)</f>
       </c>
       <c r="N18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_4[Angefordert (LC)]),2)</f>
@@ -20364,7 +20358,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_4[Angefordert (EUR)]),2)</f>
       </c>
       <c r="R18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="S18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_5[Angefordert (LC)]),2)</f>
@@ -20373,7 +20367,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_5[Angefordert (EUR)]),2)</f>
       </c>
       <c r="V18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="W18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_6[Angefordert (LC)]),2)</f>
@@ -20382,7 +20376,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_6[Angefordert (EUR)]),2)</f>
       </c>
       <c r="Z18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AA18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_7[Angefordert (LC)]),2)</f>
@@ -20391,7 +20385,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_7[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AD18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AE18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_8[Angefordert (LC)]),2)</f>
@@ -20400,7 +20394,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_8[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AH18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AI18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_9[Angefordert (LC)]),2)</f>
@@ -20409,7 +20403,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_9[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AL18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AM18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_10[Angefordert (LC)]),2)</f>
@@ -20418,7 +20412,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_10[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AP18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AQ18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_11[Angefordert (LC)]),2)</f>
@@ -20427,7 +20421,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_11[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AT18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AU18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_12[Angefordert (LC)]),2)</f>
@@ -20436,7 +20430,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_12[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AX18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AY18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_13[Angefordert (LC)]),2)</f>
@@ -20445,7 +20439,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_13[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BB18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BC18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_14[Angefordert (LC)]),2)</f>
@@ -20454,7 +20448,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_14[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BF18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BG18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_15[Angefordert (LC)]),2)</f>
@@ -20463,7 +20457,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_15[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BJ18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BK18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_16[Angefordert (LC)]),2)</f>
@@ -20472,7 +20466,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_16[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BN18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BO18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_17[Angefordert (LC)]),2)</f>
@@ -20481,7 +20475,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_17[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BR18" s="183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BS18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_18[Angefordert (LC)]),2)</f>
@@ -20492,7 +20486,7 @@
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C20" s="186" t="str">
         <f>=ROUND($C$18,2)</f>
@@ -20501,7 +20495,7 @@
         <f>=ROUND($D$18,2)</f>
       </c>
       <c r="F20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G20" s="186" t="str">
         <f>=ROUND($G$18,2)</f>
@@ -20510,7 +20504,7 @@
         <f>=ROUND($H$18,2)</f>
       </c>
       <c r="J20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K20" s="186" t="str">
         <f>=ROUND($K$18,2)</f>
@@ -20519,7 +20513,7 @@
         <f>=ROUND($L$18,2)</f>
       </c>
       <c r="N20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="O20" s="186" t="str">
         <f>=ROUND($O$18,2)</f>
@@ -20528,7 +20522,7 @@
         <f>=ROUND($P$18,2)</f>
       </c>
       <c r="R20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S20" s="186" t="str">
         <f>=ROUND($S$18,2)</f>
@@ -20537,7 +20531,7 @@
         <f>=ROUND($T$18,2)</f>
       </c>
       <c r="V20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="W20" s="186" t="str">
         <f>=ROUND($W$18,2)</f>
@@ -20546,7 +20540,7 @@
         <f>=ROUND($X$18,2)</f>
       </c>
       <c r="Z20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AA20" s="186" t="str">
         <f>=ROUND($AA$18,2)</f>
@@ -20555,7 +20549,7 @@
         <f>=ROUND($AB$18,2)</f>
       </c>
       <c r="AD20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AE20" s="186" t="str">
         <f>=ROUND($AE$18,2)</f>
@@ -20564,7 +20558,7 @@
         <f>=ROUND($AF$18,2)</f>
       </c>
       <c r="AH20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AI20" s="186" t="str">
         <f>=ROUND($AI$18,2)</f>
@@ -20573,7 +20567,7 @@
         <f>=ROUND($AJ$18,2)</f>
       </c>
       <c r="AL20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AM20" s="186" t="str">
         <f>=ROUND($AM$18,2)</f>
@@ -20582,7 +20576,7 @@
         <f>=ROUND($AN$18,2)</f>
       </c>
       <c r="AP20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AQ20" s="186" t="str">
         <f>=ROUND($AQ$18,2)</f>
@@ -20591,7 +20585,7 @@
         <f>=ROUND($AR$18,2)</f>
       </c>
       <c r="AT20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AU20" s="186" t="str">
         <f>=ROUND($AU$18,2)</f>
@@ -20600,7 +20594,7 @@
         <f>=ROUND($AV$18,2)</f>
       </c>
       <c r="AX20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AY20" s="186" t="str">
         <f>=ROUND($AY$18,2)</f>
@@ -20609,7 +20603,7 @@
         <f>=ROUND($AZ$18,2)</f>
       </c>
       <c r="BB20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="BC20" s="186" t="str">
         <f>=ROUND($BC$18,2)</f>
@@ -20618,7 +20612,7 @@
         <f>=ROUND($BD$18,2)</f>
       </c>
       <c r="BF20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="BG20" s="186" t="str">
         <f>=ROUND($BG$18,2)</f>
@@ -20627,7 +20621,7 @@
         <f>=ROUND($BH$18,2)</f>
       </c>
       <c r="BJ20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="BK20" s="186" t="str">
         <f>=ROUND($BK$18,2)</f>
@@ -20636,7 +20630,7 @@
         <f>=ROUND($BL$18,2)</f>
       </c>
       <c r="BN20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="BO20" s="186" t="str">
         <f>=ROUND($BO$18,2)</f>
@@ -20645,7 +20639,7 @@
         <f>=ROUND($BP$18,2)</f>
       </c>
       <c r="BR20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="BS20" s="186" t="str">
         <f>=ROUND($BS$18,2)</f>
@@ -20656,7 +20650,7 @@
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C21" s="24">
         <v>250000</v>
@@ -20665,7 +20659,7 @@
         <f>=IFERROR(ROUND($C$21/$C$8,2),0)</f>
       </c>
       <c r="F21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G21" s="24">
         <v>200000</v>
@@ -20674,112 +20668,112 @@
         <f>=IFERROR(ROUND($G$21/$G$8,2),0)</f>
       </c>
       <c r="J21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="K21" s="24"/>
       <c r="L21" s="182" t="str">
         <f>=IFERROR(ROUND($K$21/$K$8,2),0)</f>
       </c>
       <c r="N21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="O21" s="24"/>
       <c r="P21" s="182" t="str">
         <f>=IFERROR(ROUND($O$21/$O$8,2),0)</f>
       </c>
       <c r="R21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S21" s="24"/>
       <c r="T21" s="182" t="str">
         <f>=IFERROR(ROUND($S$21/$S$8,2),0)</f>
       </c>
       <c r="V21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="W21" s="24"/>
       <c r="X21" s="182" t="str">
         <f>=IFERROR(ROUND($W$21/$W$8,2),0)</f>
       </c>
       <c r="Z21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AA21" s="24"/>
       <c r="AB21" s="182" t="str">
         <f>=IFERROR(ROUND($AA$21/$AA$8,2),0)</f>
       </c>
       <c r="AD21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AE21" s="24"/>
       <c r="AF21" s="182" t="str">
         <f>=IFERROR(ROUND($AE$21/$AE$8,2),0)</f>
       </c>
       <c r="AH21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AI21" s="24"/>
       <c r="AJ21" s="182" t="str">
         <f>=IFERROR(ROUND($AI$21/$AI$8,2),0)</f>
       </c>
       <c r="AL21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AM21" s="24"/>
       <c r="AN21" s="182" t="str">
         <f>=IFERROR(ROUND($AM$21/$AM$8,2),0)</f>
       </c>
       <c r="AP21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AQ21" s="24"/>
       <c r="AR21" s="182" t="str">
         <f>=IFERROR(ROUND($AQ$21/$AQ$8,2),0)</f>
       </c>
       <c r="AT21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AU21" s="24"/>
       <c r="AV21" s="182" t="str">
         <f>=IFERROR(ROUND($AU$21/$AU$8,2),0)</f>
       </c>
       <c r="AX21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AY21" s="24"/>
       <c r="AZ21" s="182" t="str">
         <f>=IFERROR(ROUND($AY$21/$AY$8,2),0)</f>
       </c>
       <c r="BB21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="BC21" s="24"/>
       <c r="BD21" s="182" t="str">
         <f>=IFERROR(ROUND($BC$21/$BC$8,2),0)</f>
       </c>
       <c r="BF21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="BG21" s="24"/>
       <c r="BH21" s="182" t="str">
         <f>=IFERROR(ROUND($BG$21/$BG$8,2),0)</f>
       </c>
       <c r="BJ21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="BK21" s="24"/>
       <c r="BL21" s="182" t="str">
         <f>=IFERROR(ROUND($BK$21/$BK$8,2),0)</f>
       </c>
       <c r="BN21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="BO21" s="24"/>
       <c r="BP21" s="182" t="str">
         <f>=IFERROR(ROUND($BO$21/$BO$8,2),0)</f>
       </c>
       <c r="BR21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="BS21" s="24"/>
       <c r="BT21" s="182" t="str">
@@ -20788,7 +20782,7 @@
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C22" s="24">
         <v>125000</v>
@@ -20797,7 +20791,7 @@
         <f>=IFERROR(ROUND($C$22/$C$8,2),0)</f>
       </c>
       <c r="F22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G22" s="24">
         <v>100000</v>
@@ -20806,112 +20800,112 @@
         <f>=IFERROR(ROUND($G$22/$G$8,2),0)</f>
       </c>
       <c r="J22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K22" s="24"/>
       <c r="L22" s="182" t="str">
         <f>=IFERROR(ROUND($K$22/$K$8,2),0)</f>
       </c>
       <c r="N22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="O22" s="24"/>
       <c r="P22" s="182" t="str">
         <f>=IFERROR(ROUND($O$22/$O$8,2),0)</f>
       </c>
       <c r="R22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="S22" s="24"/>
       <c r="T22" s="182" t="str">
         <f>=IFERROR(ROUND($S$22/$S$8,2),0)</f>
       </c>
       <c r="V22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="W22" s="24"/>
       <c r="X22" s="182" t="str">
         <f>=IFERROR(ROUND($W$22/$W$8,2),0)</f>
       </c>
       <c r="Z22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AA22" s="24"/>
       <c r="AB22" s="182" t="str">
         <f>=IFERROR(ROUND($AA$22/$AA$8,2),0)</f>
       </c>
       <c r="AD22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AE22" s="24"/>
       <c r="AF22" s="182" t="str">
         <f>=IFERROR(ROUND($AE$22/$AE$8,2),0)</f>
       </c>
       <c r="AH22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AI22" s="24"/>
       <c r="AJ22" s="182" t="str">
         <f>=IFERROR(ROUND($AI$22/$AI$8,2),0)</f>
       </c>
       <c r="AL22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AM22" s="24"/>
       <c r="AN22" s="182" t="str">
         <f>=IFERROR(ROUND($AM$22/$AM$8,2),0)</f>
       </c>
       <c r="AP22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AQ22" s="24"/>
       <c r="AR22" s="182" t="str">
         <f>=IFERROR(ROUND($AQ$22/$AQ$8,2),0)</f>
       </c>
       <c r="AT22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AU22" s="24"/>
       <c r="AV22" s="182" t="str">
         <f>=IFERROR(ROUND($AU$22/$AU$8,2),0)</f>
       </c>
       <c r="AX22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AY22" s="24"/>
       <c r="AZ22" s="182" t="str">
         <f>=IFERROR(ROUND($AY$22/$AY$8,2),0)</f>
       </c>
       <c r="BB22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="BC22" s="24"/>
       <c r="BD22" s="182" t="str">
         <f>=IFERROR(ROUND($BC$22/$BC$8,2),0)</f>
       </c>
       <c r="BF22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="BG22" s="24"/>
       <c r="BH22" s="182" t="str">
         <f>=IFERROR(ROUND($BG$22/$BG$8,2),0)</f>
       </c>
       <c r="BJ22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="BK22" s="24"/>
       <c r="BL22" s="182" t="str">
         <f>=IFERROR(ROUND($BK$22/$BK$8,2),0)</f>
       </c>
       <c r="BN22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="BO22" s="24"/>
       <c r="BP22" s="182" t="str">
         <f>=IFERROR(ROUND($BO$22/$BO$8,2),0)</f>
       </c>
       <c r="BR22" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="BS22" s="24"/>
       <c r="BT22" s="182" t="str">
@@ -20920,7 +20914,7 @@
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C23" s="188" t="str">
         <f>=ROUND(IF(Saldovortrag_LW="",0,Saldovortrag_LW),2)</f>
@@ -20929,7 +20923,7 @@
         <f>=IFERROR(ROUND($C$23/$C$8,2),0)</f>
       </c>
       <c r="F23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_1,0),2)</f>
@@ -20938,7 +20932,7 @@
         <f>=IFERROR(ROUND($G$23/$G$8,2),0)</f>
       </c>
       <c r="J23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="K23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_2,0),2)</f>
@@ -20947,7 +20941,7 @@
         <f>=IFERROR(ROUND($K$23/$K$8,2),0)</f>
       </c>
       <c r="N23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_3,0),2)</f>
@@ -20956,7 +20950,7 @@
         <f>=IFERROR(ROUND($O$23/$O$8,2),0)</f>
       </c>
       <c r="R23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_4,0),2)</f>
@@ -20965,7 +20959,7 @@
         <f>=IFERROR(ROUND($S$23/$S$8,2),0)</f>
       </c>
       <c r="V23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="W23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_5,0),2)</f>
@@ -20974,7 +20968,7 @@
         <f>=IFERROR(ROUND($W$23/$W$8,2),0)</f>
       </c>
       <c r="Z23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_6,0),2)</f>
@@ -20983,7 +20977,7 @@
         <f>=IFERROR(ROUND($AA$23/$AA$8,2),0)</f>
       </c>
       <c r="AD23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AE23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_7,0),2)</f>
@@ -20992,7 +20986,7 @@
         <f>=IFERROR(ROUND($AE$23/$AE$8,2),0)</f>
       </c>
       <c r="AH23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AI23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_8,0),2)</f>
@@ -21001,7 +20995,7 @@
         <f>=IFERROR(ROUND($AI$23/$AI$8,2),0)</f>
       </c>
       <c r="AL23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AM23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_9,0),2)</f>
@@ -21010,7 +21004,7 @@
         <f>=IFERROR(ROUND($AM$23/$AM$8,2),0)</f>
       </c>
       <c r="AP23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AQ23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_10,0),2)</f>
@@ -21019,7 +21013,7 @@
         <f>=IFERROR(ROUND($AQ$23/$AQ$8,2),0)</f>
       </c>
       <c r="AT23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AU23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_11,0),2)</f>
@@ -21028,7 +21022,7 @@
         <f>=IFERROR(ROUND($AU$23/$AU$8,2),0)</f>
       </c>
       <c r="AX23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AY23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_12,0),2)</f>
@@ -21037,7 +21031,7 @@
         <f>=IFERROR(ROUND($AY$23/$AY$8,2),0)</f>
       </c>
       <c r="BB23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="BC23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_13,0),2)</f>
@@ -21046,7 +21040,7 @@
         <f>=IFERROR(ROUND($BC$23/$BC$8,2),0)</f>
       </c>
       <c r="BF23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="BG23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_14,0),2)</f>
@@ -21055,7 +21049,7 @@
         <f>=IFERROR(ROUND($BG$23/$BG$8,2),0)</f>
       </c>
       <c r="BJ23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="BK23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_15,0),2)</f>
@@ -21064,7 +21058,7 @@
         <f>=IFERROR(ROUND($BK$23/$BK$8,2),0)</f>
       </c>
       <c r="BN23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="BO23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_16,0),2)</f>
@@ -21073,7 +21067,7 @@
         <f>=IFERROR(ROUND($BO$23/$BO$8,2),0)</f>
       </c>
       <c r="BR23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="BS23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_17,0),2)</f>
@@ -21084,7 +21078,7 @@
     </row>
     <row r="25">
       <c r="B25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C25" s="190" t="str">
         <f>=IFERROR(ROUND($C$18-$C$21-$C$22-$C$23,2),0)</f>
@@ -21093,7 +21087,7 @@
         <f>=IFERROR(ROUND($D$18-$D$21-$D$22-$D$23,2),0)</f>
       </c>
       <c r="F25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G25" s="190" t="str">
         <f>=IFERROR(ROUND($G$18-$G$21-$G$22-$G$23,2),0)</f>
@@ -21102,7 +21096,7 @@
         <f>=IFERROR(ROUND($H$18-$H$21-$H$22-$H$23,2),0)</f>
       </c>
       <c r="J25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="K25" s="190" t="str">
         <f>=IFERROR(ROUND($K$18-$K$21-$K$22-$K$23,2),0)</f>
@@ -21111,7 +21105,7 @@
         <f>=IFERROR(ROUND($L$18-$L$21-$L$22-$L$23,2),0)</f>
       </c>
       <c r="N25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="O25" s="190" t="str">
         <f>=IFERROR(ROUND($O$18-$O$21-$O$22-$O$23,2),0)</f>
@@ -21120,7 +21114,7 @@
         <f>=IFERROR(ROUND($P$18-$P$21-$P$22-$P$23,2),0)</f>
       </c>
       <c r="R25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="S25" s="190" t="str">
         <f>=IFERROR(ROUND($S$18-$S$21-$S$22-$S$23,2),0)</f>
@@ -21129,7 +21123,7 @@
         <f>=IFERROR(ROUND($T$18-$T$21-$T$22-$T$23,2),0)</f>
       </c>
       <c r="V25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="W25" s="190" t="str">
         <f>=IFERROR(ROUND($W$18-$W$21-$W$22-$W$23,2),0)</f>
@@ -21138,7 +21132,7 @@
         <f>=IFERROR(ROUND($X$18-$X$21-$X$22-$X$23,2),0)</f>
       </c>
       <c r="Z25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AA25" s="190" t="str">
         <f>=IFERROR(ROUND($AA$18-$AA$21-$AA$22-$AA$23,2),0)</f>
@@ -21147,7 +21141,7 @@
         <f>=IFERROR(ROUND($AB$18-$AB$21-$AB$22-$AB$23,2),0)</f>
       </c>
       <c r="AD25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AE25" s="190" t="str">
         <f>=IFERROR(ROUND($AE$18-$AE$21-$AE$22-$AE$23,2),0)</f>
@@ -21156,7 +21150,7 @@
         <f>=IFERROR(ROUND($AF$18-$AF$21-$AF$22-$AF$23,2),0)</f>
       </c>
       <c r="AH25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AI25" s="190" t="str">
         <f>=IFERROR(ROUND($AI$18-$AI$21-$AI$22-$AI$23,2),0)</f>
@@ -21165,7 +21159,7 @@
         <f>=IFERROR(ROUND($AJ$18-$AJ$21-$AJ$22-$AJ$23,2),0)</f>
       </c>
       <c r="AL25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AM25" s="190" t="str">
         <f>=IFERROR(ROUND($AM$18-$AM$21-$AM$22-$AM$23,2),0)</f>
@@ -21174,7 +21168,7 @@
         <f>=IFERROR(ROUND($AN$18-$AN$21-$AN$22-$AN$23,2),0)</f>
       </c>
       <c r="AP25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AQ25" s="190" t="str">
         <f>=IFERROR(ROUND($AQ$18-$AQ$21-$AQ$22-$AQ$23,2),0)</f>
@@ -21183,7 +21177,7 @@
         <f>=IFERROR(ROUND($AR$18-$AR$21-$AR$22-$AR$23,2),0)</f>
       </c>
       <c r="AT25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AU25" s="190" t="str">
         <f>=IFERROR(ROUND($AU$18-$AU$21-$AU$22-$AU$23,2),0)</f>
@@ -21192,7 +21186,7 @@
         <f>=IFERROR(ROUND($AV$18-$AV$21-$AV$22-$AV$23,2),0)</f>
       </c>
       <c r="AX25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AY25" s="190" t="str">
         <f>=IFERROR(ROUND($AY$18-$AY$21-$AY$22-$AY$23,2),0)</f>
@@ -21201,7 +21195,7 @@
         <f>=IFERROR(ROUND($AZ$18-$AZ$21-$AZ$22-$AZ$23,2),0)</f>
       </c>
       <c r="BB25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="BC25" s="190" t="str">
         <f>=IFERROR(ROUND($BC$18-$BC$21-$BC$22-$BC$23,2),0)</f>
@@ -21210,7 +21204,7 @@
         <f>=IFERROR(ROUND($BD$18-$BD$21-$BD$22-$BD$23,2),0)</f>
       </c>
       <c r="BF25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="BG25" s="190" t="str">
         <f>=IFERROR(ROUND($BG$18-$BG$21-$BG$22-$BG$23,2),0)</f>
@@ -21219,7 +21213,7 @@
         <f>=IFERROR(ROUND($BH$18-$BH$21-$BH$22-$BH$23,2),0)</f>
       </c>
       <c r="BJ25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="BK25" s="190" t="str">
         <f>=IFERROR(ROUND($BK$18-$BK$21-$BK$22-$BK$23,2),0)</f>
@@ -21228,7 +21222,7 @@
         <f>=IFERROR(ROUND($BL$18-$BL$21-$BL$22-$BL$23,2),0)</f>
       </c>
       <c r="BN25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="BO25" s="190" t="str">
         <f>=IFERROR(ROUND($BO$18-$BO$21-$BO$22-$BO$23,2),0)</f>
@@ -21237,7 +21231,7 @@
         <f>=IFERROR(ROUND($BP$18-$BP$21-$BP$22-$BP$23,2),0)</f>
       </c>
       <c r="BR25" s="189" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="BS25" s="190" t="str">
         <f>=IFERROR(ROUND($BS$18-$BS$21-$BS$22-$BS$23,2),0)</f>
@@ -21437,7 +21431,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="true">
       <c r="B2" s="192" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C2" s="192"/>
       <c r="D2" s="192"/>
@@ -21450,7 +21444,7 @@
     </row>
     <row r="3" ht="18" customHeight="true">
       <c r="B3" s="193" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C3" s="193"/>
       <c r="D3" s="193"/>
@@ -21463,7 +21457,7 @@
     </row>
     <row r="5" ht="22" customHeight="true">
       <c r="B5" s="194" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C5" s="194"/>
       <c r="D5" s="194"/>
@@ -21484,7 +21478,7 @@
     </row>
     <row r="6">
       <c r="B6" s="195" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C6" s="195"/>
       <c r="D6" s="195"/>
@@ -21513,7 +21507,7 @@
     </row>
     <row r="8" ht="22" customHeight="true">
       <c r="C8" s="202" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D8" s="203"/>
       <c r="E8" s="203"/>
@@ -21529,11 +21523,11 @@
     </row>
     <row r="9">
       <c r="C9" s="205" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D9" s="197"/>
       <c r="E9" s="63" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F9" s="63"/>
       <c r="G9" s="206"/>
@@ -21547,7 +21541,7 @@
     </row>
     <row r="10">
       <c r="C10" s="205" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D10" s="197"/>
       <c r="E10" s="198" t="str">
@@ -21557,7 +21551,7 @@
       <c r="F10" s="198"/>
       <c r="G10" s="207"/>
       <c r="L10" s="315" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M10" s="310" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$8,'IV. MA'!$G$8,'IV. MA'!$K$8,'IV. MA'!$O$8,'IV. MA'!$S$8,'IV. MA'!$W$8,'IV. MA'!$AA$8,'IV. MA'!$AE$8,'IV. MA'!$AI$8,'IV. MA'!$AM$8,'IV. MA'!$AQ$8,'IV. MA'!$AU$8,'IV. MA'!$AY$8,'IV. MA'!$BC$8,'IV. MA'!$BG$8,'IV. MA'!$BK$8,'IV. MA'!$BO$8,'IV. MA'!$BS$8),"")</f>
@@ -21566,7 +21560,7 @@
     </row>
     <row r="11">
       <c r="C11" s="205" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D11" s="197"/>
       <c r="E11" s="198" t="str">
@@ -21579,7 +21573,7 @@
     </row>
     <row r="12">
       <c r="C12" s="209" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D12" s="199"/>
       <c r="E12" s="199"/>
@@ -21589,10 +21583,10 @@
         <v>202</v>
       </c>
       <c r="M12" s="180" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N12" s="321" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13">
@@ -21740,7 +21734,7 @@
     </row>
     <row r="20" ht="22" customHeight="true">
       <c r="B20" s="18" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -21762,7 +21756,7 @@
     </row>
     <row r="21">
       <c r="L21" s="322" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M21" s="243" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$18,'IV. MA'!$G$18,'IV. MA'!$K$18,'IV. MA'!$O$18,'IV. MA'!$S$18,'IV. MA'!$W$18,'IV. MA'!$AA$18,'IV. MA'!$AE$18,'IV. MA'!$AI$18,'IV. MA'!$AM$18,'IV. MA'!$AQ$18,'IV. MA'!$AU$18,'IV. MA'!$AY$18,'IV. MA'!$BC$18,'IV. MA'!$BG$18,'IV. MA'!$BK$18,'IV. MA'!$BO$18,'IV. MA'!$BS$18),"")</f>
@@ -21773,14 +21767,14 @@
     </row>
     <row r="22">
       <c r="B22" s="223" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C22" s="224"/>
       <c r="D22" s="225" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
       <c r="F22" s="230" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G22" s="231"/>
       <c r="H22" s="231"/>
@@ -21790,24 +21784,24 @@
     </row>
     <row r="23">
       <c r="B23" s="205" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C23" s="197"/>
       <c r="D23" s="226" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
       <c r="F23" s="233" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G23" s="197" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H23" s="197"/>
       <c r="I23" s="234" t="str">
         <f>=IFERROR(ROUND(Saldovortrag_EUR,2),0)</f>
       </c>
       <c r="L23" s="143" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M23" s="116" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$20,'IV. MA'!$G$20,'IV. MA'!$K$20,'IV. MA'!$O$20,'IV. MA'!$S$20,'IV. MA'!$W$20,'IV. MA'!$AA$20,'IV. MA'!$AE$20,'IV. MA'!$AI$20,'IV. MA'!$AM$20,'IV. MA'!$AQ$20,'IV. MA'!$AU$20,'IV. MA'!$AY$20,'IV. MA'!$BC$20,'IV. MA'!$BG$20,'IV. MA'!$BK$20,'IV. MA'!$BO$20,'IV. MA'!$BS$20),"")</f>
@@ -21825,10 +21819,10 @@
         <f>=IF(Reserve_Freigabe="Ja",ROUND($D$22,2),ROUND($D$22-$D$23,2))</f>
       </c>
       <c r="F24" s="233" t="s">
+        <v>352</v>
+      </c>
+      <c r="G24" s="197" t="s">
         <v>354</v>
-      </c>
-      <c r="G24" s="197" t="s">
-        <v>356</v>
       </c>
       <c r="H24" s="197"/>
       <c r="I24" s="234" t="str">
@@ -21836,7 +21830,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="143" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M24" s="116" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$21,'IV. MA'!$G$21,'IV. MA'!$K$21,'IV. MA'!$O$21,'IV. MA'!$S$21,'IV. MA'!$W$21,'IV. MA'!$AA$21,'IV. MA'!$AE$21,'IV. MA'!$AI$21,'IV. MA'!$AM$21,'IV. MA'!$AQ$21,'IV. MA'!$AU$21,'IV. MA'!$AY$21,'IV. MA'!$BC$21,'IV. MA'!$BG$21,'IV. MA'!$BK$21,'IV. MA'!$BO$21,'IV. MA'!$BS$21),"")</f>
@@ -21847,17 +21841,17 @@
     </row>
     <row r="25">
       <c r="B25" s="205" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C25" s="197"/>
       <c r="D25" s="226" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblKMWMittel[Betrag]),2),0)</f>
       </c>
       <c r="F25" s="233" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G25" s="197" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H25" s="197"/>
       <c r="I25" s="234" t="str">
@@ -21865,7 +21859,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="143" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M25" s="116" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$22,'IV. MA'!$G$22,'IV. MA'!$K$22,'IV. MA'!$O$22,'IV. MA'!$S$22,'IV. MA'!$W$22,'IV. MA'!$AA$22,'IV. MA'!$AE$22,'IV. MA'!$AI$22,'IV. MA'!$AM$22,'IV. MA'!$AQ$22,'IV. MA'!$AU$22,'IV. MA'!$AY$22,'IV. MA'!$BC$22,'IV. MA'!$BG$22,'IV. MA'!$BK$22,'IV. MA'!$BO$22,'IV. MA'!$BS$22),"")</f>
@@ -21876,7 +21870,7 @@
     </row>
     <row r="26">
       <c r="B26" s="227" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C26" s="228"/>
       <c r="D26" s="229" t="str">
@@ -21884,7 +21878,7 @@
       </c>
       <c r="F26" s="47"/>
       <c r="G26" s="218" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H26" s="218"/>
       <c r="I26" s="235" t="str">
@@ -21903,7 +21897,7 @@
     <row r="27">
       <c r="F27" s="236"/>
       <c r="G27" s="228" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H27" s="228"/>
       <c r="I27" s="229" t="str">
@@ -21914,7 +21908,7 @@
     </row>
     <row r="28">
       <c r="L28" s="323" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="M28" s="324" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$25,'IV. MA'!$G$25,'IV. MA'!$K$25,'IV. MA'!$O$25,'IV. MA'!$S$25,'IV. MA'!$W$25,'IV. MA'!$AA$25,'IV. MA'!$AE$25,'IV. MA'!$AI$25,'IV. MA'!$AM$25,'IV. MA'!$AQ$25,'IV. MA'!$AU$25,'IV. MA'!$AY$25,'IV. MA'!$BC$25,'IV. MA'!$BG$25,'IV. MA'!$BK$25,'IV. MA'!$BO$25,'IV. MA'!$BS$25),"")</f>
@@ -21925,14 +21919,14 @@
     </row>
     <row r="29">
       <c r="B29" s="223" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C29" s="224"/>
       <c r="D29" s="225" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,E11),2),0)</f>
       </c>
       <c r="F29" s="223" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G29" s="224"/>
       <c r="H29" s="224"/>
@@ -21942,14 +21936,14 @@
     </row>
     <row r="30">
       <c r="B30" s="227" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C30" s="228"/>
       <c r="D30" s="229" t="str">
         <f>=ROUND($D$26-MAX(0,$D$29),2)</f>
       </c>
       <c r="F30" s="227" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G30" s="228"/>
       <c r="H30" s="228"/>
@@ -21959,12 +21953,12 @@
     </row>
     <row r="32">
       <c r="B32" s="223" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C32" s="224"/>
       <c r="D32" s="237"/>
       <c r="F32" s="223" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G32" s="224"/>
       <c r="H32" s="224"/>
@@ -21972,14 +21966,14 @@
     </row>
     <row r="33">
       <c r="B33" s="227" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C33" s="228"/>
       <c r="D33" s="229" t="str">
         <f>=ROUND($D$26-MAX(0,$D$29)-MAX(0,$D$32),2)</f>
       </c>
       <c r="F33" s="227" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G33" s="228"/>
       <c r="H33" s="228"/>
@@ -21989,7 +21983,7 @@
     </row>
     <row r="36" ht="22" customHeight="true">
       <c r="B36" s="18" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
@@ -22005,18 +21999,18 @@
         <v>158</v>
       </c>
       <c r="C38" s="247" t="s">
+        <v>363</v>
+      </c>
+      <c r="D38" s="247" t="s">
+        <v>364</v>
+      </c>
+      <c r="E38" s="248" t="s">
         <v>365</v>
-      </c>
-      <c r="D38" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="E38" s="248" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="205" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C39" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,"&lt;="&amp;E11,'Daten'!$BD$1:$BD$18,"&gt;=1"),2),0)</f>
@@ -22028,7 +22022,7 @@
     </row>
     <row r="40">
       <c r="B40" s="205" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C40" s="239" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 1]),2),0)</f>
@@ -22042,7 +22036,7 @@
     </row>
     <row r="41">
       <c r="B41" s="205" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C41" s="239" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 2]),2),0)</f>
@@ -22056,7 +22050,7 @@
     </row>
     <row r="42">
       <c r="B42" s="205" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C42" s="239" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 3]),2),0)</f>
@@ -22070,7 +22064,7 @@
     </row>
     <row r="43">
       <c r="B43" s="205" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C43" s="242" t="str">
         <f>=$D$40+$D$41+$D$42</f>
@@ -22080,7 +22074,7 @@
     </row>
     <row r="44">
       <c r="B44" s="205" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C44" s="242" t="str">
         <f>=IFERROR(CHOOSE(IFERROR(SUMPRODUCT('Daten'!$BA$1:$BA$18,('Daten'!$BB$1:$BB$18=E10)*('Daten'!$BD$1:$BD$18=E11)),0),'IV. MA'!$C$7,'IV. MA'!$G$7,'IV. MA'!$K$7,'IV. MA'!$O$7,'IV. MA'!$S$7,'IV. MA'!$W$7,'IV. MA'!$AA$7,'IV. MA'!$AE$7,'IV. MA'!$AI$7,'IV. MA'!$AM$7,'IV. MA'!$AQ$7,'IV. MA'!$AU$7,'IV. MA'!$AY$7,'IV. MA'!$BC$7,'IV. MA'!$BG$7,'IV. MA'!$BK$7,'IV. MA'!$BO$7,'IV. MA'!$BS$7),0)</f>
@@ -22090,7 +22084,7 @@
     </row>
     <row r="45">
       <c r="B45" s="251" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C45" s="243" t="str">
         <f>=IFERROR(ROUND($C$40*$D$40/12+$C$41*$D$41/12+$C$42*$D$42/12,2),0)</f>
@@ -22102,7 +22096,7 @@
     </row>
     <row r="46">
       <c r="B46" s="251" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C46" s="244" t="str">
         <f>=IF($C$39&lt;=$C$45,"OK","ÜBERSCHRITTEN")</f>
@@ -22114,7 +22108,7 @@
     </row>
     <row r="47">
       <c r="B47" s="205" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C47" s="239" t="str">
         <f>=ROUND(MAX(0,$C$39-$C$45),2)</f>
@@ -22126,7 +22120,7 @@
     </row>
     <row r="48">
       <c r="B48" s="253" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C48" s="254" t="str">
         <f>=IFERROR($C$39/$C$45,0)</f>
@@ -22138,7 +22132,7 @@
     </row>
     <row r="50" ht="22" customHeight="true">
       <c r="B50" s="18" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
@@ -22151,31 +22145,31 @@
     </row>
     <row r="52" ht="28" customHeight="true">
       <c r="B52" s="263" t="s">
+        <v>377</v>
+      </c>
+      <c r="C52" s="264" t="s">
+        <v>378</v>
+      </c>
+      <c r="D52" s="264" t="s">
         <v>379</v>
       </c>
-      <c r="C52" s="264" t="s">
+      <c r="E52" s="264" t="s">
         <v>380</v>
       </c>
-      <c r="D52" s="264" t="s">
+      <c r="F52" s="264" t="s">
         <v>381</v>
       </c>
-      <c r="E52" s="264" t="s">
+      <c r="G52" s="264" t="s">
         <v>382</v>
       </c>
-      <c r="F52" s="264" t="s">
+      <c r="H52" s="264" t="s">
         <v>383</v>
       </c>
-      <c r="G52" s="264" t="s">
+      <c r="I52" s="264" t="s">
         <v>384</v>
       </c>
-      <c r="H52" s="264" t="s">
+      <c r="J52" s="265" t="s">
         <v>385</v>
-      </c>
-      <c r="I52" s="264" t="s">
-        <v>386</v>
-      </c>
-      <c r="J52" s="265" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="53">
@@ -22325,7 +22319,7 @@
     </row>
     <row r="59" ht="22" customHeight="true">
       <c r="B59" s="18" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
@@ -22338,31 +22332,31 @@
     </row>
     <row r="61" ht="28" customHeight="true">
       <c r="B61" s="263" t="s">
+        <v>377</v>
+      </c>
+      <c r="C61" s="264" t="s">
+        <v>378</v>
+      </c>
+      <c r="D61" s="264" t="s">
         <v>379</v>
       </c>
-      <c r="C61" s="264" t="s">
+      <c r="E61" s="264" t="s">
         <v>380</v>
       </c>
-      <c r="D61" s="264" t="s">
+      <c r="F61" s="264" t="s">
         <v>381</v>
       </c>
-      <c r="E61" s="264" t="s">
+      <c r="G61" s="264" t="s">
         <v>382</v>
       </c>
-      <c r="F61" s="264" t="s">
+      <c r="H61" s="264" t="s">
         <v>383</v>
       </c>
-      <c r="G61" s="264" t="s">
+      <c r="I61" s="264" t="s">
         <v>384</v>
       </c>
-      <c r="H61" s="264" t="s">
+      <c r="J61" s="265" t="s">
         <v>385</v>
-      </c>
-      <c r="I61" s="264" t="s">
-        <v>386</v>
-      </c>
-      <c r="J61" s="265" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="62">
@@ -22628,7 +22622,7 @@
     </row>
     <row r="76" ht="22" customHeight="true">
       <c r="B76" s="194" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C76" s="194"/>
       <c r="D76" s="194"/>
@@ -22648,7 +22642,7 @@
     </row>
     <row r="77">
       <c r="B77" s="195" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C77" s="195"/>
       <c r="D77" s="195"/>
@@ -22681,7 +22675,7 @@
     </row>
     <row r="79" ht="22" customHeight="true">
       <c r="C79" s="202" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D79" s="203"/>
       <c r="E79" s="203"/>
@@ -22699,11 +22693,11 @@
     </row>
     <row r="80">
       <c r="C80" s="205" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D80" s="197"/>
       <c r="E80" s="63" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F80" s="63"/>
       <c r="G80" s="206"/>
@@ -22719,7 +22713,7 @@
     </row>
     <row r="81">
       <c r="C81" s="253" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D81" s="286"/>
       <c r="E81" s="287" t="str">
@@ -22743,7 +22737,7 @@
     </row>
     <row r="83" ht="22" customHeight="true">
       <c r="B83" s="18" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C83" s="18"/>
       <c r="D83" s="18"/>
@@ -22780,14 +22774,14 @@
     </row>
     <row r="85">
       <c r="B85" s="223" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C85" s="224"/>
       <c r="D85" s="225" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
       <c r="F85" s="230" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G85" s="231"/>
       <c r="H85" s="231"/>
@@ -22810,17 +22804,17 @@
     </row>
     <row r="86">
       <c r="B86" s="205" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C86" s="197"/>
       <c r="D86" s="226" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
       <c r="F86" s="233" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G86" s="197" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H86" s="197"/>
       <c r="I86" s="234" t="str">
@@ -22851,10 +22845,10 @@
         <f>=IF(Reserve_Freigabe="Ja",ROUND($D$85,2),ROUND($D$85-$D$86,2))</f>
       </c>
       <c r="F87" s="233" t="s">
+        <v>352</v>
+      </c>
+      <c r="G87" s="197" t="s">
         <v>354</v>
-      </c>
-      <c r="G87" s="197" t="s">
-        <v>356</v>
       </c>
       <c r="H87" s="197"/>
       <c r="I87" s="234" t="str">
@@ -22879,7 +22873,7 @@
     </row>
     <row r="88">
       <c r="B88" s="205" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C88" s="197"/>
       <c r="D88" s="226" t="str">
@@ -22887,7 +22881,7 @@
       </c>
       <c r="F88" s="47"/>
       <c r="G88" s="218" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H88" s="218"/>
       <c r="I88" s="235" t="str">
@@ -22911,7 +22905,7 @@
     </row>
     <row r="89">
       <c r="B89" s="227" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C89" s="228"/>
       <c r="D89" s="229" t="str">
@@ -22919,7 +22913,7 @@
       </c>
       <c r="F89" s="236"/>
       <c r="G89" s="228" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H89" s="228"/>
       <c r="I89" s="229" t="str">
@@ -22986,7 +22980,7 @@
     </row>
     <row r="93" ht="22" customHeight="true">
       <c r="B93" s="18" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C93" s="18"/>
       <c r="D93" s="18"/>
@@ -23031,31 +23025,31 @@
     </row>
     <row r="95" ht="28" customHeight="true">
       <c r="B95" s="263" t="s">
+        <v>377</v>
+      </c>
+      <c r="C95" s="264" t="s">
+        <v>393</v>
+      </c>
+      <c r="D95" s="264" t="s">
         <v>379</v>
       </c>
-      <c r="C95" s="264" t="s">
-        <v>395</v>
-      </c>
-      <c r="D95" s="264" t="s">
+      <c r="E95" s="264" t="s">
+        <v>380</v>
+      </c>
+      <c r="F95" s="264" t="s">
         <v>381</v>
       </c>
-      <c r="E95" s="264" t="s">
-        <v>382</v>
-      </c>
-      <c r="F95" s="264" t="s">
+      <c r="G95" s="264" t="s">
+        <v>394</v>
+      </c>
+      <c r="H95" s="264" t="s">
         <v>383</v>
       </c>
-      <c r="G95" s="264" t="s">
-        <v>396</v>
-      </c>
-      <c r="H95" s="264" t="s">
+      <c r="I95" s="264" t="s">
+        <v>384</v>
+      </c>
+      <c r="J95" s="265" t="s">
         <v>385</v>
-      </c>
-      <c r="I95" s="264" t="s">
-        <v>386</v>
-      </c>
-      <c r="J95" s="265" t="s">
-        <v>387</v>
       </c>
       <c r="L95" s="143" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$B$21,'III. Finanzberichte'!$I$21,'III. Finanzberichte'!$P$21,'III. Finanzberichte'!$W$21,'III. Finanzberichte'!$AD$21,'III. Finanzberichte'!$AK$21,'III. Finanzberichte'!$AR$21,'III. Finanzberichte'!$AY$21,'III. Finanzberichte'!$BF$21,'III. Finanzberichte'!$BM$21,'III. Finanzberichte'!$BT$21,'III. Finanzberichte'!$CA$21,'III. Finanzberichte'!$CH$21,'III. Finanzberichte'!$CO$21,'III. Finanzberichte'!$CV$21,'III. Finanzberichte'!$DC$21,'III. Finanzberichte'!$DJ$21,'III. Finanzberichte'!$DQ$21),"")</f>
@@ -23312,7 +23306,7 @@
     </row>
     <row r="102" ht="22" customHeight="true">
       <c r="B102" s="18" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C102" s="18"/>
       <c r="D102" s="18"/>
@@ -23357,31 +23351,31 @@
     </row>
     <row r="104" ht="28" customHeight="true">
       <c r="B104" s="263" t="s">
+        <v>377</v>
+      </c>
+      <c r="C104" s="264" t="s">
+        <v>393</v>
+      </c>
+      <c r="D104" s="264" t="s">
         <v>379</v>
       </c>
-      <c r="C104" s="264" t="s">
-        <v>395</v>
-      </c>
-      <c r="D104" s="264" t="s">
+      <c r="E104" s="264" t="s">
+        <v>380</v>
+      </c>
+      <c r="F104" s="264" t="s">
         <v>381</v>
       </c>
-      <c r="E104" s="264" t="s">
-        <v>382</v>
-      </c>
-      <c r="F104" s="264" t="s">
+      <c r="G104" s="264" t="s">
+        <v>394</v>
+      </c>
+      <c r="H104" s="264" t="s">
         <v>383</v>
       </c>
-      <c r="G104" s="264" t="s">
-        <v>396</v>
-      </c>
-      <c r="H104" s="264" t="s">
+      <c r="I104" s="264" t="s">
+        <v>384</v>
+      </c>
+      <c r="J104" s="265" t="s">
         <v>385</v>
-      </c>
-      <c r="I104" s="264" t="s">
-        <v>386</v>
-      </c>
-      <c r="J104" s="265" t="s">
-        <v>387</v>
       </c>
       <c r="L104" s="47"/>
       <c r="P104" s="48"/>
@@ -24004,16 +23998,16 @@
         <v>247</v>
       </c>
       <c r="C1" s="351" t="s">
+        <v>398</v>
+      </c>
+      <c r="I1" s="351" t="s">
+        <v>399</v>
+      </c>
+      <c r="O1" s="351" t="s">
         <v>400</v>
       </c>
-      <c r="I1" s="351" t="s">
+      <c r="U1" s="351" t="s">
         <v>401</v>
-      </c>
-      <c r="O1" s="351" t="s">
-        <v>402</v>
-      </c>
-      <c r="U1" s="351" t="s">
-        <v>403</v>
       </c>
       <c r="BA1">
         <v>1</v>

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -2285,7 +2285,7 @@
     <xf numFmtId="166" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -6760,7 +6760,7 @@
       <formula>$K$5="Ja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8:M8">
+  <conditionalFormatting sqref="K8">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>$K$5="Ja"</formula>
     </cfRule>

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -3306,7 +3306,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="17">
     <dxf>
       <font>
         <name val="Segoe UI"/>
@@ -3354,35 +3354,6 @@
           <color rgb="FF808080"/>
         </top>
         <bottom style="medium">
-          <color rgb="FF808080"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <b val="1"/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF3C3C3C"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF808080"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF808080"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF808080"/>
-        </top>
-        <bottom style="thin">
           <color rgb="FF808080"/>
         </bottom>
       </border>
@@ -6760,63 +6731,58 @@
       <formula>$K$5="Ja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8">
+  <conditionalFormatting sqref="K9:M12">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>$K$5="Ja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K9:M12">
+  <conditionalFormatting sqref="E32">
     <cfRule type="expression" dxfId="4" priority="3">
-      <formula>$K$5="Ja"</formula>
+      <formula>$E$32="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32">
     <cfRule type="expression" dxfId="5" priority="4">
-      <formula>$E$32="OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E32">
-    <cfRule type="expression" dxfId="6" priority="5">
       <formula>$E$32&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$E$33="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$E$33&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34">
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>$E$34="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34">
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="5" priority="8">
       <formula>$E$34&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35">
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>$E$35="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35">
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="5" priority="10">
       <formula>$E$35&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36">
-    <cfRule type="expression" dxfId="7" priority="12">
+    <cfRule type="expression" dxfId="6" priority="11">
       <formula>$E$36="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36">
-    <cfRule type="expression" dxfId="8" priority="13">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>$E$36&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23749,202 +23715,202 @@
     <mergeCell ref="L91:P91"/>
   </mergeCells>
   <conditionalFormatting sqref="C13:D13">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$C$13&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:F13">
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>$C$13&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13:G13">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>$C$13&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:D14">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>$C$14&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:F14">
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>$C$14&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:G14">
-    <cfRule type="expression" dxfId="11" priority="6">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>$C$14&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>$C$15&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15:F15">
-    <cfRule type="expression" dxfId="10" priority="8">
+    <cfRule type="expression" dxfId="9" priority="8">
       <formula>$C$15&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:G15">
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>$C$15&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:D16">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="8" priority="10">
       <formula>$C$16&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16:F16">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>$C$16&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16:G16">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>$C$16&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:D17">
-    <cfRule type="expression" dxfId="9" priority="13">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>$C$17&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17:F17">
-    <cfRule type="expression" dxfId="10" priority="14">
+    <cfRule type="expression" dxfId="9" priority="14">
       <formula>$C$17&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:G17">
-    <cfRule type="expression" dxfId="11" priority="15">
+    <cfRule type="expression" dxfId="10" priority="15">
       <formula>$C$17&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:D18">
-    <cfRule type="expression" dxfId="9" priority="16">
+    <cfRule type="expression" dxfId="8" priority="16">
       <formula>$C$18&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:F18">
-    <cfRule type="expression" dxfId="10" priority="17">
+    <cfRule type="expression" dxfId="9" priority="17">
       <formula>$C$18&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18:G18">
-    <cfRule type="expression" dxfId="11" priority="18">
+    <cfRule type="expression" dxfId="10" priority="18">
       <formula>$C$18&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46">
-    <cfRule type="expression" dxfId="12" priority="19">
+    <cfRule type="expression" dxfId="11" priority="19">
       <formula>$C$46="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46">
-    <cfRule type="expression" dxfId="13" priority="20">
+    <cfRule type="expression" dxfId="12" priority="20">
       <formula>$C$46&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46">
-    <cfRule type="expression" dxfId="12" priority="21">
+    <cfRule type="expression" dxfId="11" priority="21">
       <formula>$E$46="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46">
-    <cfRule type="expression" dxfId="13" priority="22">
+    <cfRule type="expression" dxfId="12" priority="22">
       <formula>$E$46&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="expression" dxfId="14" priority="23">
+    <cfRule type="expression" dxfId="13" priority="23">
       <formula>$C$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="expression" dxfId="15" priority="24">
+    <cfRule type="expression" dxfId="14" priority="24">
       <formula>$E$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53:F56">
-    <cfRule type="expression" dxfId="16" priority="25">
+    <cfRule type="expression" dxfId="15" priority="25">
       <formula>F53&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53:F56">
-    <cfRule type="expression" dxfId="17" priority="26">
+    <cfRule type="expression" dxfId="16" priority="26">
       <formula>AND(F53&gt;=0.1,F53&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J53:J56">
-    <cfRule type="expression" dxfId="16" priority="27">
+    <cfRule type="expression" dxfId="15" priority="27">
       <formula>J53&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J53:J56">
-    <cfRule type="expression" dxfId="17" priority="28">
+    <cfRule type="expression" dxfId="16" priority="28">
       <formula>AND(J53&gt;=0.1,J53&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62:F69">
-    <cfRule type="expression" dxfId="16" priority="29">
+    <cfRule type="expression" dxfId="15" priority="29">
       <formula>F62&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62:F69">
-    <cfRule type="expression" dxfId="17" priority="30">
+    <cfRule type="expression" dxfId="16" priority="30">
       <formula>AND(F62&gt;=0.1,F62&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J62:J69">
-    <cfRule type="expression" dxfId="16" priority="31">
+    <cfRule type="expression" dxfId="15" priority="31">
       <formula>J62&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J62:J69">
-    <cfRule type="expression" dxfId="17" priority="32">
+    <cfRule type="expression" dxfId="16" priority="32">
       <formula>AND(J62&gt;=0.1,J62&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F99">
-    <cfRule type="expression" dxfId="16" priority="33">
+    <cfRule type="expression" dxfId="15" priority="33">
       <formula>F96&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F99">
-    <cfRule type="expression" dxfId="17" priority="34">
+    <cfRule type="expression" dxfId="16" priority="34">
       <formula>AND(F96&gt;=0.1,F96&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J96:J99">
-    <cfRule type="expression" dxfId="16" priority="35">
+    <cfRule type="expression" dxfId="15" priority="35">
       <formula>J96&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J96:J99">
-    <cfRule type="expression" dxfId="17" priority="36">
+    <cfRule type="expression" dxfId="16" priority="36">
       <formula>AND(J96&gt;=0.1,J96&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:F112">
-    <cfRule type="expression" dxfId="16" priority="37">
+    <cfRule type="expression" dxfId="15" priority="37">
       <formula>F105&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:F112">
-    <cfRule type="expression" dxfId="17" priority="38">
+    <cfRule type="expression" dxfId="16" priority="38">
       <formula>AND(F105&gt;=0.1,F105&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J105:J112">
-    <cfRule type="expression" dxfId="16" priority="39">
+    <cfRule type="expression" dxfId="15" priority="39">
       <formula>J105&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J105:J112">
-    <cfRule type="expression" dxfId="17" priority="40">
+    <cfRule type="expression" dxfId="16" priority="40">
       <formula>AND(J105&gt;=0.1,J105&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -1374,7 +1374,7 @@
     <numFmt numFmtId="172" formatCode="0"/>
     <numFmt numFmtId="173" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1478,13 +1478,6 @@
       <family val="2"/>
       <b val="1"/>
       <color rgb="FF595959"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF7F7F7F"/>
       <sz val="9"/>
     </font>
     <font>
@@ -2456,13 +2449,13 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="37" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="38" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2474,16 +2467,16 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="40" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="21" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2639,13 +2632,13 @@
     <xf numFmtId="167" fontId="3" fillId="9" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -2711,13 +2704,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="false">
@@ -2774,7 +2767,7 @@
     <xf numFmtId="167" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="44" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2813,43 +2806,127 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="10" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="166" fontId="19" fillId="10" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="10" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="167" fontId="19" fillId="10" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="52" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="12" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="167" fontId="3" fillId="8" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="8" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2861,90 +2938,6 @@
     <xf numFmtId="0" fontId="23" fillId="11" borderId="52" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="12" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="8" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="52" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3017,31 +3010,31 @@
     <xf numFmtId="173" fontId="3" fillId="8" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="173" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="166" fontId="25" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="26" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="173" fontId="25" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="167" fontId="25" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="52" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="52" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -3059,19 +3052,19 @@
     <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="32" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="32" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="166" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="26" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="173" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="167" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="26" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="173" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -3098,10 +3091,10 @@
     <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="26" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="173" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="26" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="173" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -3128,10 +3121,10 @@
     <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="26" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="173" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="26" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="173" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -3158,10 +3151,10 @@
     <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="26" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="173" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="26" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="173" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -103,23 +103,41 @@
     <definedName name="FB_SaldoLC_18">'III. Finanzberichte'!$DR$31</definedName>
     <definedName name="FB_SaldoEUR_18">'III. Finanzberichte'!$DS$31</definedName>
     <definedName name="MA_Kurs_1">'IV. MA'!$C$8</definedName>
+    <definedName name="MA_ManBetrag_1">'IV. MA'!$D$24</definedName>
     <definedName name="MA_Kurs_2">'IV. MA'!$G$8</definedName>
+    <definedName name="MA_ManBetrag_2">'IV. MA'!$H$24</definedName>
     <definedName name="MA_Kurs_3">'IV. MA'!$K$8</definedName>
+    <definedName name="MA_ManBetrag_3">'IV. MA'!$L$24</definedName>
     <definedName name="MA_Kurs_4">'IV. MA'!$O$8</definedName>
+    <definedName name="MA_ManBetrag_4">'IV. MA'!$P$24</definedName>
     <definedName name="MA_Kurs_5">'IV. MA'!$S$8</definedName>
+    <definedName name="MA_ManBetrag_5">'IV. MA'!$T$24</definedName>
     <definedName name="MA_Kurs_6">'IV. MA'!$W$8</definedName>
+    <definedName name="MA_ManBetrag_6">'IV. MA'!$X$24</definedName>
     <definedName name="MA_Kurs_7">'IV. MA'!$AA$8</definedName>
+    <definedName name="MA_ManBetrag_7">'IV. MA'!$AB$24</definedName>
     <definedName name="MA_Kurs_8">'IV. MA'!$AE$8</definedName>
+    <definedName name="MA_ManBetrag_8">'IV. MA'!$AF$24</definedName>
     <definedName name="MA_Kurs_9">'IV. MA'!$AI$8</definedName>
+    <definedName name="MA_ManBetrag_9">'IV. MA'!$AJ$24</definedName>
     <definedName name="MA_Kurs_10">'IV. MA'!$AM$8</definedName>
+    <definedName name="MA_ManBetrag_10">'IV. MA'!$AN$24</definedName>
     <definedName name="MA_Kurs_11">'IV. MA'!$AQ$8</definedName>
+    <definedName name="MA_ManBetrag_11">'IV. MA'!$AR$24</definedName>
     <definedName name="MA_Kurs_12">'IV. MA'!$AU$8</definedName>
+    <definedName name="MA_ManBetrag_12">'IV. MA'!$AV$24</definedName>
     <definedName name="MA_Kurs_13">'IV. MA'!$AY$8</definedName>
+    <definedName name="MA_ManBetrag_13">'IV. MA'!$AZ$24</definedName>
     <definedName name="MA_Kurs_14">'IV. MA'!$BC$8</definedName>
+    <definedName name="MA_ManBetrag_14">'IV. MA'!$BD$24</definedName>
     <definedName name="MA_Kurs_15">'IV. MA'!$BG$8</definedName>
+    <definedName name="MA_ManBetrag_15">'IV. MA'!$BH$24</definedName>
     <definedName name="MA_Kurs_16">'IV. MA'!$BK$8</definedName>
+    <definedName name="MA_ManBetrag_16">'IV. MA'!$BL$24</definedName>
     <definedName name="MA_Kurs_17">'IV. MA'!$BO$8</definedName>
+    <definedName name="MA_ManBetrag_17">'IV. MA'!$BP$24</definedName>
     <definedName name="MA_Kurs_18">'IV. MA'!$BS$8</definedName>
+    <definedName name="MA_ManBetrag_18">'IV. MA'!$BT$24</definedName>
     <definedName name="FB_Auswahl_Liste">OFFSET('Daten'!$BP$1,0,0,COUNTA('Daten'!$BP:$BP),1)</definedName>
     <definedName name="MA_Auswahl_Liste">OFFSET('Daten'!$BN$1,0,0,COUNTA('Daten'!$BN:$BN),1)</definedName>
   </definedNames>
@@ -150,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
   <si>
     <t xml:space="preserve">  DASHBOARD (v1.0)</t>
   </si>
@@ -1152,6 +1170,9 @@
   </si>
   <si>
     <t>abzueglich Saldo Vorprojekt:</t>
+  </si>
+  <si>
+    <t>Manueller Betrag:</t>
   </si>
   <si>
     <t>KMW-Mittel Anforderung:</t>
@@ -2806,6 +2827,9 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2950,7 +2974,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="167" fontId="3" fillId="12" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2958,9 +2982,6 @@
     </xf>
     <xf numFmtId="166" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment/>
     </xf>
     <xf numFmtId="172" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -20882,7 +20903,7 @@
         <f>=IFERROR(ROUND($C$23/$C$8,2),0)</f>
       </c>
       <c r="F23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_1,0),2)</f>
@@ -20891,7 +20912,7 @@
         <f>=IFERROR(ROUND($G$23/$G$8,2),0)</f>
       </c>
       <c r="J23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_2,0),2)</f>
@@ -20900,7 +20921,7 @@
         <f>=IFERROR(ROUND($K$23/$K$8,2),0)</f>
       </c>
       <c r="N23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_3,0),2)</f>
@@ -20909,7 +20930,7 @@
         <f>=IFERROR(ROUND($O$23/$O$8,2),0)</f>
       </c>
       <c r="R23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="S23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_4,0),2)</f>
@@ -20918,7 +20939,7 @@
         <f>=IFERROR(ROUND($S$23/$S$8,2),0)</f>
       </c>
       <c r="V23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="W23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_5,0),2)</f>
@@ -20927,7 +20948,7 @@
         <f>=IFERROR(ROUND($W$23/$W$8,2),0)</f>
       </c>
       <c r="Z23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_6,0),2)</f>
@@ -20936,7 +20957,7 @@
         <f>=IFERROR(ROUND($AA$23/$AA$8,2),0)</f>
       </c>
       <c r="AD23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AE23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_7,0),2)</f>
@@ -20945,7 +20966,7 @@
         <f>=IFERROR(ROUND($AE$23/$AE$8,2),0)</f>
       </c>
       <c r="AH23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AI23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_8,0),2)</f>
@@ -20954,7 +20975,7 @@
         <f>=IFERROR(ROUND($AI$23/$AI$8,2),0)</f>
       </c>
       <c r="AL23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AM23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_9,0),2)</f>
@@ -20963,7 +20984,7 @@
         <f>=IFERROR(ROUND($AM$23/$AM$8,2),0)</f>
       </c>
       <c r="AP23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AQ23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_10,0),2)</f>
@@ -20972,7 +20993,7 @@
         <f>=IFERROR(ROUND($AQ$23/$AQ$8,2),0)</f>
       </c>
       <c r="AT23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AU23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_11,0),2)</f>
@@ -20981,7 +21002,7 @@
         <f>=IFERROR(ROUND($AU$23/$AU$8,2),0)</f>
       </c>
       <c r="AX23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AY23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_12,0),2)</f>
@@ -20990,7 +21011,7 @@
         <f>=IFERROR(ROUND($AY$23/$AY$8,2),0)</f>
       </c>
       <c r="BB23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="BC23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_13,0),2)</f>
@@ -20999,7 +21020,7 @@
         <f>=IFERROR(ROUND($BC$23/$BC$8,2),0)</f>
       </c>
       <c r="BF23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="BG23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_14,0),2)</f>
@@ -21008,7 +21029,7 @@
         <f>=IFERROR(ROUND($BG$23/$BG$8,2),0)</f>
       </c>
       <c r="BJ23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="BK23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_15,0),2)</f>
@@ -21017,7 +21038,7 @@
         <f>=IFERROR(ROUND($BK$23/$BK$8,2),0)</f>
       </c>
       <c r="BN23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="BO23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_16,0),2)</f>
@@ -21026,7 +21047,7 @@
         <f>=IFERROR(ROUND($BO$23/$BO$8,2),0)</f>
       </c>
       <c r="BR23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="BS23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_17,0),2)</f>
@@ -21035,167 +21056,259 @@
         <f>=IFERROR(ROUND($BS$23/$BS$8,2),0)</f>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="s">
+        <v>334</v>
+      </c>
+      <c r="C24" s="189"/>
+      <c r="D24" s="25"/>
+      <c r="F24" t="s">
+        <v>334</v>
+      </c>
+      <c r="G24" s="189"/>
+      <c r="H24" s="25"/>
+      <c r="J24" t="s">
+        <v>334</v>
+      </c>
+      <c r="K24" s="189"/>
+      <c r="L24" s="25"/>
+      <c r="N24" t="s">
+        <v>334</v>
+      </c>
+      <c r="O24" s="189"/>
+      <c r="P24" s="25"/>
+      <c r="R24" t="s">
+        <v>334</v>
+      </c>
+      <c r="S24" s="189"/>
+      <c r="T24" s="25"/>
+      <c r="V24" t="s">
+        <v>334</v>
+      </c>
+      <c r="W24" s="189"/>
+      <c r="X24" s="25"/>
+      <c r="Z24" t="s">
+        <v>334</v>
+      </c>
+      <c r="AA24" s="189"/>
+      <c r="AB24" s="25"/>
+      <c r="AD24" t="s">
+        <v>334</v>
+      </c>
+      <c r="AE24" s="189"/>
+      <c r="AF24" s="25"/>
+      <c r="AH24" t="s">
+        <v>334</v>
+      </c>
+      <c r="AI24" s="189"/>
+      <c r="AJ24" s="25"/>
+      <c r="AL24" t="s">
+        <v>334</v>
+      </c>
+      <c r="AM24" s="189"/>
+      <c r="AN24" s="25"/>
+      <c r="AP24" t="s">
+        <v>334</v>
+      </c>
+      <c r="AQ24" s="189"/>
+      <c r="AR24" s="25"/>
+      <c r="AT24" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU24" s="189"/>
+      <c r="AV24" s="25"/>
+      <c r="AX24" t="s">
+        <v>334</v>
+      </c>
+      <c r="AY24" s="189"/>
+      <c r="AZ24" s="25"/>
+      <c r="BB24" t="s">
+        <v>334</v>
+      </c>
+      <c r="BC24" s="189"/>
+      <c r="BD24" s="25"/>
+      <c r="BF24" t="s">
+        <v>334</v>
+      </c>
+      <c r="BG24" s="189"/>
+      <c r="BH24" s="25"/>
+      <c r="BJ24" t="s">
+        <v>334</v>
+      </c>
+      <c r="BK24" s="189"/>
+      <c r="BL24" s="25"/>
+      <c r="BN24" t="s">
+        <v>334</v>
+      </c>
+      <c r="BO24" s="189"/>
+      <c r="BP24" s="25"/>
+      <c r="BR24" t="s">
+        <v>334</v>
+      </c>
+      <c r="BS24" s="189"/>
+      <c r="BT24" s="25"/>
+    </row>
     <row r="25">
-      <c r="B25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="C25" s="190" t="str">
+      <c r="B25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="C25" s="191" t="str">
         <f>=IFERROR(ROUND($C$18-$C$21-$C$22-$C$23,2),0)</f>
       </c>
-      <c r="D25" s="191" t="str">
+      <c r="D25" s="192" t="str">
         <f>=IFERROR(ROUND($D$18-$D$21-$D$22-$D$23,2),0)</f>
       </c>
-      <c r="F25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="G25" s="190" t="str">
+      <c r="F25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="G25" s="191" t="str">
         <f>=IFERROR(ROUND($G$18-$G$21-$G$22-$G$23,2),0)</f>
       </c>
-      <c r="H25" s="191" t="str">
+      <c r="H25" s="192" t="str">
         <f>=IFERROR(ROUND($H$18-$H$21-$H$22-$H$23,2),0)</f>
       </c>
-      <c r="J25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="K25" s="190" t="str">
+      <c r="J25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="K25" s="191" t="str">
         <f>=IFERROR(ROUND($K$18-$K$21-$K$22-$K$23,2),0)</f>
       </c>
-      <c r="L25" s="191" t="str">
+      <c r="L25" s="192" t="str">
         <f>=IFERROR(ROUND($L$18-$L$21-$L$22-$L$23,2),0)</f>
       </c>
-      <c r="N25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="O25" s="190" t="str">
+      <c r="N25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="O25" s="191" t="str">
         <f>=IFERROR(ROUND($O$18-$O$21-$O$22-$O$23,2),0)</f>
       </c>
-      <c r="P25" s="191" t="str">
+      <c r="P25" s="192" t="str">
         <f>=IFERROR(ROUND($P$18-$P$21-$P$22-$P$23,2),0)</f>
       </c>
-      <c r="R25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="S25" s="190" t="str">
+      <c r="R25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="S25" s="191" t="str">
         <f>=IFERROR(ROUND($S$18-$S$21-$S$22-$S$23,2),0)</f>
       </c>
-      <c r="T25" s="191" t="str">
+      <c r="T25" s="192" t="str">
         <f>=IFERROR(ROUND($T$18-$T$21-$T$22-$T$23,2),0)</f>
       </c>
-      <c r="V25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="W25" s="190" t="str">
+      <c r="V25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="W25" s="191" t="str">
         <f>=IFERROR(ROUND($W$18-$W$21-$W$22-$W$23,2),0)</f>
       </c>
-      <c r="X25" s="191" t="str">
+      <c r="X25" s="192" t="str">
         <f>=IFERROR(ROUND($X$18-$X$21-$X$22-$X$23,2),0)</f>
       </c>
-      <c r="Z25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="AA25" s="190" t="str">
+      <c r="Z25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="AA25" s="191" t="str">
         <f>=IFERROR(ROUND($AA$18-$AA$21-$AA$22-$AA$23,2),0)</f>
       </c>
-      <c r="AB25" s="191" t="str">
+      <c r="AB25" s="192" t="str">
         <f>=IFERROR(ROUND($AB$18-$AB$21-$AB$22-$AB$23,2),0)</f>
       </c>
-      <c r="AD25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="AE25" s="190" t="str">
+      <c r="AD25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="AE25" s="191" t="str">
         <f>=IFERROR(ROUND($AE$18-$AE$21-$AE$22-$AE$23,2),0)</f>
       </c>
-      <c r="AF25" s="191" t="str">
+      <c r="AF25" s="192" t="str">
         <f>=IFERROR(ROUND($AF$18-$AF$21-$AF$22-$AF$23,2),0)</f>
       </c>
-      <c r="AH25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="AI25" s="190" t="str">
+      <c r="AH25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="AI25" s="191" t="str">
         <f>=IFERROR(ROUND($AI$18-$AI$21-$AI$22-$AI$23,2),0)</f>
       </c>
-      <c r="AJ25" s="191" t="str">
+      <c r="AJ25" s="192" t="str">
         <f>=IFERROR(ROUND($AJ$18-$AJ$21-$AJ$22-$AJ$23,2),0)</f>
       </c>
-      <c r="AL25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="AM25" s="190" t="str">
+      <c r="AL25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="AM25" s="191" t="str">
         <f>=IFERROR(ROUND($AM$18-$AM$21-$AM$22-$AM$23,2),0)</f>
       </c>
-      <c r="AN25" s="191" t="str">
+      <c r="AN25" s="192" t="str">
         <f>=IFERROR(ROUND($AN$18-$AN$21-$AN$22-$AN$23,2),0)</f>
       </c>
-      <c r="AP25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="AQ25" s="190" t="str">
+      <c r="AP25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="AQ25" s="191" t="str">
         <f>=IFERROR(ROUND($AQ$18-$AQ$21-$AQ$22-$AQ$23,2),0)</f>
       </c>
-      <c r="AR25" s="191" t="str">
+      <c r="AR25" s="192" t="str">
         <f>=IFERROR(ROUND($AR$18-$AR$21-$AR$22-$AR$23,2),0)</f>
       </c>
-      <c r="AT25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="AU25" s="190" t="str">
+      <c r="AT25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="AU25" s="191" t="str">
         <f>=IFERROR(ROUND($AU$18-$AU$21-$AU$22-$AU$23,2),0)</f>
       </c>
-      <c r="AV25" s="191" t="str">
+      <c r="AV25" s="192" t="str">
         <f>=IFERROR(ROUND($AV$18-$AV$21-$AV$22-$AV$23,2),0)</f>
       </c>
-      <c r="AX25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="AY25" s="190" t="str">
+      <c r="AX25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="AY25" s="191" t="str">
         <f>=IFERROR(ROUND($AY$18-$AY$21-$AY$22-$AY$23,2),0)</f>
       </c>
-      <c r="AZ25" s="191" t="str">
+      <c r="AZ25" s="192" t="str">
         <f>=IFERROR(ROUND($AZ$18-$AZ$21-$AZ$22-$AZ$23,2),0)</f>
       </c>
-      <c r="BB25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="BC25" s="190" t="str">
+      <c r="BB25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="BC25" s="191" t="str">
         <f>=IFERROR(ROUND($BC$18-$BC$21-$BC$22-$BC$23,2),0)</f>
       </c>
-      <c r="BD25" s="191" t="str">
+      <c r="BD25" s="192" t="str">
         <f>=IFERROR(ROUND($BD$18-$BD$21-$BD$22-$BD$23,2),0)</f>
       </c>
-      <c r="BF25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="BG25" s="190" t="str">
+      <c r="BF25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="BG25" s="191" t="str">
         <f>=IFERROR(ROUND($BG$18-$BG$21-$BG$22-$BG$23,2),0)</f>
       </c>
-      <c r="BH25" s="191" t="str">
+      <c r="BH25" s="192" t="str">
         <f>=IFERROR(ROUND($BH$18-$BH$21-$BH$22-$BH$23,2),0)</f>
       </c>
-      <c r="BJ25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="BK25" s="190" t="str">
+      <c r="BJ25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="BK25" s="191" t="str">
         <f>=IFERROR(ROUND($BK$18-$BK$21-$BK$22-$BK$23,2),0)</f>
       </c>
-      <c r="BL25" s="191" t="str">
+      <c r="BL25" s="192" t="str">
         <f>=IFERROR(ROUND($BL$18-$BL$21-$BL$22-$BL$23,2),0)</f>
       </c>
-      <c r="BN25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="BO25" s="190" t="str">
+      <c r="BN25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="BO25" s="191" t="str">
         <f>=IFERROR(ROUND($BO$18-$BO$21-$BO$22-$BO$23,2),0)</f>
       </c>
-      <c r="BP25" s="191" t="str">
+      <c r="BP25" s="192" t="str">
         <f>=IFERROR(ROUND($BP$18-$BP$21-$BP$22-$BP$23,2),0)</f>
       </c>
-      <c r="BR25" s="189" t="s">
-        <v>334</v>
-      </c>
-      <c r="BS25" s="190" t="str">
+      <c r="BR25" s="190" t="s">
+        <v>335</v>
+      </c>
+      <c r="BS25" s="191" t="str">
         <f>=IFERROR(ROUND($BS$18-$BS$21-$BS$22-$BS$23,2),0)</f>
       </c>
-      <c r="BT25" s="191" t="str">
+      <c r="BT25" s="192" t="str">
         <f>=IFERROR(ROUND($BT$18-$BT$21-$BT$22-$BT$23,2),0)</f>
       </c>
     </row>
@@ -21389,64 +21502,64 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="true">
-      <c r="B2" s="192" t="s">
-        <v>336</v>
-      </c>
-      <c r="C2" s="192"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="192"/>
-      <c r="F2" s="192"/>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="192"/>
-      <c r="J2" s="192"/>
+      <c r="B2" s="193" t="s">
+        <v>337</v>
+      </c>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="193"/>
     </row>
     <row r="3" ht="18" customHeight="true">
-      <c r="B3" s="193" t="s">
-        <v>337</v>
-      </c>
-      <c r="C3" s="193"/>
-      <c r="D3" s="193"/>
-      <c r="E3" s="193"/>
-      <c r="F3" s="193"/>
-      <c r="G3" s="193"/>
-      <c r="H3" s="193"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
+      <c r="B3" s="194" t="s">
+        <v>338</v>
+      </c>
+      <c r="C3" s="194"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="194"/>
+      <c r="F3" s="194"/>
+      <c r="G3" s="194"/>
+      <c r="H3" s="194"/>
+      <c r="I3" s="194"/>
+      <c r="J3" s="194"/>
     </row>
     <row r="5" ht="22" customHeight="true">
-      <c r="B5" s="194" t="s">
-        <v>338</v>
-      </c>
-      <c r="C5" s="194"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="194"/>
-      <c r="J5" s="194"/>
-      <c r="L5" s="202" t="str">
+      <c r="B5" s="195" t="s">
+        <v>339</v>
+      </c>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="195"/>
+      <c r="G5" s="195"/>
+      <c r="H5" s="195"/>
+      <c r="I5" s="195"/>
+      <c r="J5" s="195"/>
+      <c r="L5" s="203" t="str">
         <f>=IF(E11=0,"Aktuelle Mittelanforderung (keine gewählt)","Aktuelle Mittelanforderung – Periode "&amp;E10&amp;" (#"&amp;E11&amp;")")</f>
       </c>
-      <c r="M5" s="203"/>
-      <c r="N5" s="204"/>
+      <c r="M5" s="204"/>
+      <c r="N5" s="205"/>
       <c r="AD5" t="str">
         <f>=IFERROR(SUMPRODUCT('Daten'!$BA$1:$BA$18,('Daten'!$BB$1:$BB$18=E10)*('Daten'!$BD$1:$BD$18=E11)),0)</f>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="195" t="s">
-        <v>339</v>
-      </c>
-      <c r="C6" s="195"/>
-      <c r="D6" s="195"/>
-      <c r="E6" s="195"/>
-      <c r="F6" s="195"/>
-      <c r="G6" s="195"/>
-      <c r="H6" s="195"/>
-      <c r="I6" s="195"/>
-      <c r="J6" s="195"/>
+      <c r="B6" s="196" t="s">
+        <v>340</v>
+      </c>
+      <c r="C6" s="196"/>
+      <c r="D6" s="196"/>
+      <c r="E6" s="196"/>
+      <c r="F6" s="196"/>
+      <c r="G6" s="196"/>
+      <c r="H6" s="196"/>
+      <c r="I6" s="196"/>
+      <c r="J6" s="196"/>
       <c r="L6" s="315" t="s">
         <v>288</v>
       </c>
@@ -21465,13 +21578,13 @@
       <c r="N7" s="317"/>
     </row>
     <row r="8" ht="22" customHeight="true">
-      <c r="C8" s="202" t="s">
-        <v>340</v>
-      </c>
-      <c r="D8" s="203"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-      <c r="G8" s="204"/>
+      <c r="C8" s="203" t="s">
+        <v>341</v>
+      </c>
+      <c r="D8" s="204"/>
+      <c r="E8" s="204"/>
+      <c r="F8" s="204"/>
+      <c r="G8" s="205"/>
       <c r="L8" s="315" t="s">
         <v>290</v>
       </c>
@@ -21481,15 +21594,15 @@
       <c r="N8" s="317"/>
     </row>
     <row r="9">
-      <c r="C9" s="205" t="s">
-        <v>341</v>
-      </c>
-      <c r="D9" s="197"/>
+      <c r="C9" s="206" t="s">
+        <v>342</v>
+      </c>
+      <c r="D9" s="198"/>
       <c r="E9" s="63" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F9" s="63"/>
-      <c r="G9" s="206"/>
+      <c r="G9" s="207"/>
       <c r="L9" s="315" t="s">
         <v>291</v>
       </c>
@@ -21499,16 +21612,16 @@
       <c r="N9" s="318"/>
     </row>
     <row r="10">
-      <c r="C10" s="205" t="s">
-        <v>343</v>
-      </c>
-      <c r="D10" s="197"/>
-      <c r="E10" s="198" t="str">
+      <c r="C10" s="206" t="s">
+        <v>344</v>
+      </c>
+      <c r="D10" s="198"/>
+      <c r="E10" s="199" t="str">
         <f>=E81+1</f>
         <v>0</v>
       </c>
-      <c r="F10" s="198"/>
-      <c r="G10" s="207"/>
+      <c r="F10" s="199"/>
+      <c r="G10" s="208"/>
       <c r="L10" s="315" t="s">
         <v>326</v>
       </c>
@@ -21518,26 +21631,26 @@
       <c r="N10" s="319"/>
     </row>
     <row r="11">
-      <c r="C11" s="205" t="s">
-        <v>344</v>
-      </c>
-      <c r="D11" s="197"/>
-      <c r="E11" s="198" t="str">
+      <c r="C11" s="206" t="s">
+        <v>345</v>
+      </c>
+      <c r="D11" s="198"/>
+      <c r="E11" s="199" t="str">
         <f>=IF(E9="Neuste MA",IFERROR(SUMPRODUCT(MAX(('Daten'!$BB$1:$BB$18=E10)*('Daten'!$BC$1:$BC$18=1)*'Daten'!$BD$1:$BD$18)),0),IFERROR(VALUE(MID(E9,FIND("(#",E9)+2,FIND(")",E9)-FIND("(#",E9)-2)),0))</f>
       </c>
-      <c r="F11" s="198"/>
-      <c r="G11" s="208"/>
+      <c r="F11" s="199"/>
+      <c r="G11" s="209"/>
       <c r="L11" s="47"/>
       <c r="N11" s="48"/>
     </row>
     <row r="12">
-      <c r="C12" s="209" t="s">
-        <v>345</v>
-      </c>
-      <c r="D12" s="199"/>
-      <c r="E12" s="199"/>
-      <c r="F12" s="199"/>
-      <c r="G12" s="210"/>
+      <c r="C12" s="210" t="s">
+        <v>346</v>
+      </c>
+      <c r="D12" s="200"/>
+      <c r="E12" s="200"/>
+      <c r="F12" s="200"/>
+      <c r="G12" s="211"/>
       <c r="L12" s="320" t="s">
         <v>202</v>
       </c>
@@ -21549,15 +21662,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="211" t="str">
+      <c r="C13" s="212" t="str">
         <f>=IF(1&lt;=E11,"Periode "&amp;E10&amp;" (#1)","")</f>
       </c>
-      <c r="D13" s="200"/>
-      <c r="E13" s="201" t="str">
+      <c r="D13" s="201"/>
+      <c r="E13" s="202" t="str">
         <f>=IF(1&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,1),0),"")</f>
       </c>
-      <c r="F13" s="201"/>
-      <c r="G13" s="212" t="str">
+      <c r="F13" s="202"/>
+      <c r="G13" s="213" t="str">
         <f>=IF(1&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,1),0),"")</f>
       </c>
       <c r="L13" s="143" t="s">
@@ -21571,15 +21684,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="211" t="str">
+      <c r="C14" s="212" t="str">
         <f>=IF(2&lt;=E11,"Periode "&amp;E10&amp;" (#2)","")</f>
       </c>
-      <c r="D14" s="200"/>
-      <c r="E14" s="201" t="str">
+      <c r="D14" s="201"/>
+      <c r="E14" s="202" t="str">
         <f>=IF(2&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,2),0),"")</f>
       </c>
-      <c r="F14" s="201"/>
-      <c r="G14" s="212" t="str">
+      <c r="F14" s="202"/>
+      <c r="G14" s="213" t="str">
         <f>=IF(2&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,2),0),"")</f>
       </c>
       <c r="L14" s="143" t="s">
@@ -21593,15 +21706,15 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="211" t="str">
+      <c r="C15" s="212" t="str">
         <f>=IF(3&lt;=E11,"Periode "&amp;E10&amp;" (#3)","")</f>
       </c>
-      <c r="D15" s="200"/>
-      <c r="E15" s="201" t="str">
+      <c r="D15" s="201"/>
+      <c r="E15" s="202" t="str">
         <f>=IF(3&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,3),0),"")</f>
       </c>
-      <c r="F15" s="201"/>
-      <c r="G15" s="212" t="str">
+      <c r="F15" s="202"/>
+      <c r="G15" s="213" t="str">
         <f>=IF(3&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,3),0),"")</f>
       </c>
       <c r="L15" s="143" t="s">
@@ -21615,15 +21728,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="211" t="str">
+      <c r="C16" s="212" t="str">
         <f>=IF(4&lt;=E11,"Periode "&amp;E10&amp;" (#4)","")</f>
       </c>
-      <c r="D16" s="200"/>
-      <c r="E16" s="201" t="str">
+      <c r="D16" s="201"/>
+      <c r="E16" s="202" t="str">
         <f>=IF(4&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,4),0),"")</f>
       </c>
-      <c r="F16" s="201"/>
-      <c r="G16" s="212" t="str">
+      <c r="F16" s="202"/>
+      <c r="G16" s="213" t="str">
         <f>=IF(4&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,4),0),"")</f>
       </c>
       <c r="L16" s="143" t="s">
@@ -21637,15 +21750,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="211" t="str">
+      <c r="C17" s="212" t="str">
         <f>=IF(5&lt;=E11,"Periode "&amp;E10&amp;" (#5)","")</f>
       </c>
-      <c r="D17" s="200"/>
-      <c r="E17" s="201" t="str">
+      <c r="D17" s="201"/>
+      <c r="E17" s="202" t="str">
         <f>=IF(5&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,5),0),"")</f>
       </c>
-      <c r="F17" s="201"/>
-      <c r="G17" s="212" t="str">
+      <c r="F17" s="202"/>
+      <c r="G17" s="213" t="str">
         <f>=IF(5&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,5),0),"")</f>
       </c>
       <c r="L17" s="143" t="s">
@@ -21659,15 +21772,15 @@
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="213" t="str">
+      <c r="C18" s="214" t="str">
         <f>=IF(6&lt;=E11,"Periode "&amp;E10&amp;" (#6)","")</f>
       </c>
-      <c r="D18" s="214"/>
-      <c r="E18" s="215" t="str">
+      <c r="D18" s="215"/>
+      <c r="E18" s="216" t="str">
         <f>=IF(6&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,6),0),"")</f>
       </c>
-      <c r="F18" s="215"/>
-      <c r="G18" s="216" t="str">
+      <c r="F18" s="216"/>
+      <c r="G18" s="217" t="str">
         <f>=IF(6&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,6),0),"")</f>
       </c>
       <c r="L18" s="143" t="s">
@@ -21693,7 +21806,7 @@
     </row>
     <row r="20" ht="22" customHeight="true">
       <c r="B20" s="18" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -21720,43 +21833,43 @@
       <c r="M21" s="243" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$18,'IV. MA'!$G$18,'IV. MA'!$K$18,'IV. MA'!$O$18,'IV. MA'!$S$18,'IV. MA'!$W$18,'IV. MA'!$AA$18,'IV. MA'!$AE$18,'IV. MA'!$AI$18,'IV. MA'!$AM$18,'IV. MA'!$AQ$18,'IV. MA'!$AU$18,'IV. MA'!$AY$18,'IV. MA'!$BC$18,'IV. MA'!$BG$18,'IV. MA'!$BK$18,'IV. MA'!$BO$18,'IV. MA'!$BS$18),"")</f>
       </c>
-      <c r="N21" s="235" t="str">
+      <c r="N21" s="236" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$D$18,'IV. MA'!$H$18,'IV. MA'!$L$18,'IV. MA'!$P$18,'IV. MA'!$T$18,'IV. MA'!$X$18,'IV. MA'!$AB$18,'IV. MA'!$AF$18,'IV. MA'!$AJ$18,'IV. MA'!$AN$18,'IV. MA'!$AR$18,'IV. MA'!$AV$18,'IV. MA'!$AZ$18,'IV. MA'!$BD$18,'IV. MA'!$BH$18,'IV. MA'!$BL$18,'IV. MA'!$BP$18,'IV. MA'!$BT$18),"")</f>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="223" t="s">
-        <v>347</v>
-      </c>
-      <c r="C22" s="224"/>
-      <c r="D22" s="225" t="str">
+      <c r="B22" s="224" t="s">
+        <v>348</v>
+      </c>
+      <c r="C22" s="225"/>
+      <c r="D22" s="226" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
-      <c r="F22" s="230" t="s">
-        <v>351</v>
-      </c>
-      <c r="G22" s="231"/>
-      <c r="H22" s="231"/>
-      <c r="I22" s="232"/>
+      <c r="F22" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="G22" s="232"/>
+      <c r="H22" s="232"/>
+      <c r="I22" s="233"/>
       <c r="L22" s="47"/>
       <c r="N22" s="48"/>
     </row>
     <row r="23">
-      <c r="B23" s="205" t="s">
-        <v>348</v>
-      </c>
-      <c r="C23" s="197"/>
-      <c r="D23" s="226" t="str">
+      <c r="B23" s="206" t="s">
+        <v>349</v>
+      </c>
+      <c r="C23" s="198"/>
+      <c r="D23" s="227" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
-      <c r="F23" s="233" t="s">
-        <v>352</v>
-      </c>
-      <c r="G23" s="197" t="s">
+      <c r="F23" s="234" t="s">
         <v>353</v>
       </c>
-      <c r="H23" s="197"/>
-      <c r="I23" s="234" t="str">
+      <c r="G23" s="198" t="s">
+        <v>354</v>
+      </c>
+      <c r="H23" s="198"/>
+      <c r="I23" s="235" t="str">
         <f>=IFERROR(ROUND(Saldovortrag_EUR,2),0)</f>
       </c>
       <c r="L23" s="143" t="s">
@@ -21770,26 +21883,26 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="205" t="str">
+      <c r="B24" s="206" t="str">
         <f>=IF(Reserve_Freigabe="Ja","Operatives Budget (Reserve freigegeben)","Operatives Budget (abzgl. Reserve)")</f>
       </c>
-      <c r="C24" s="197"/>
-      <c r="D24" s="226" t="str">
+      <c r="C24" s="198"/>
+      <c r="D24" s="227" t="str">
         <f>=IF(Reserve_Freigabe="Ja",ROUND($D$22,2),ROUND($D$22-$D$23,2))</f>
       </c>
-      <c r="F24" s="233" t="s">
-        <v>352</v>
-      </c>
-      <c r="G24" s="197" t="s">
-        <v>354</v>
-      </c>
-      <c r="H24" s="197"/>
-      <c r="I24" s="234" t="str">
+      <c r="F24" s="234" t="s">
+        <v>353</v>
+      </c>
+      <c r="G24" s="198" t="s">
+        <v>355</v>
+      </c>
+      <c r="H24" s="198"/>
+      <c r="I24" s="235" t="str">
         <f>=I87</f>
         <v>0</v>
       </c>
       <c r="L24" s="143" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M24" s="116" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$21,'IV. MA'!$G$21,'IV. MA'!$K$21,'IV. MA'!$O$21,'IV. MA'!$S$21,'IV. MA'!$W$21,'IV. MA'!$AA$21,'IV. MA'!$AE$21,'IV. MA'!$AI$21,'IV. MA'!$AM$21,'IV. MA'!$AQ$21,'IV. MA'!$AU$21,'IV. MA'!$AY$21,'IV. MA'!$BC$21,'IV. MA'!$BG$21,'IV. MA'!$BK$21,'IV. MA'!$BO$21,'IV. MA'!$BS$21),"")</f>
@@ -21799,26 +21912,26 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="205" t="s">
-        <v>349</v>
-      </c>
-      <c r="C25" s="197"/>
-      <c r="D25" s="226" t="str">
+      <c r="B25" s="206" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="198"/>
+      <c r="D25" s="227" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblKMWMittel[Betrag]),2),0)</f>
       </c>
-      <c r="F25" s="233" t="s">
-        <v>352</v>
-      </c>
-      <c r="G25" s="197" t="s">
-        <v>355</v>
-      </c>
-      <c r="H25" s="197"/>
-      <c r="I25" s="234" t="str">
+      <c r="F25" s="234" t="s">
+        <v>353</v>
+      </c>
+      <c r="G25" s="198" t="s">
+        <v>356</v>
+      </c>
+      <c r="H25" s="198"/>
+      <c r="I25" s="235" t="str">
         <f>=ROUND(MAX(0,MAX(0,(SUM($G$96:$G$99)-$G$98)+SUMIFS('Daten'!$BH$1:$BH$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,"&lt;="&amp;E11,'Daten'!$BD$1:$BD$18,"&gt;=1")-(SUM($H$96:$H$99)-$H$98))-I87),2)</f>
         <v>0</v>
       </c>
       <c r="L25" s="143" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M25" s="116" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$22,'IV. MA'!$G$22,'IV. MA'!$K$22,'IV. MA'!$O$22,'IV. MA'!$S$22,'IV. MA'!$W$22,'IV. MA'!$AA$22,'IV. MA'!$AE$22,'IV. MA'!$AI$22,'IV. MA'!$AM$22,'IV. MA'!$AQ$22,'IV. MA'!$AU$22,'IV. MA'!$AY$22,'IV. MA'!$BC$22,'IV. MA'!$BG$22,'IV. MA'!$BK$22,'IV. MA'!$BO$22,'IV. MA'!$BS$22),"")</f>
@@ -21828,19 +21941,19 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="227" t="s">
-        <v>350</v>
-      </c>
-      <c r="C26" s="228"/>
-      <c r="D26" s="229" t="str">
+      <c r="B26" s="228" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="229"/>
+      <c r="D26" s="230" t="str">
         <f>=ROUND($D$24-$D$25,2)</f>
       </c>
       <c r="F26" s="47"/>
-      <c r="G26" s="218" t="s">
-        <v>356</v>
-      </c>
-      <c r="H26" s="218"/>
-      <c r="I26" s="235" t="str">
+      <c r="G26" s="219" t="s">
+        <v>357</v>
+      </c>
+      <c r="H26" s="219"/>
+      <c r="I26" s="236" t="str">
         <f>=ROUND(IF($F$23="Abzug",MAX(0,$I$23),0)+IF($F$24="Abzug",MAX(0,$I$24),0)+IF($F$25="Abzug",MAX(0,$I$25),0),2)</f>
       </c>
       <c r="L26" s="143" t="str">
@@ -21854,12 +21967,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="F27" s="236"/>
-      <c r="G27" s="228" t="s">
-        <v>357</v>
-      </c>
-      <c r="H27" s="228"/>
-      <c r="I27" s="229" t="str">
+      <c r="F27" s="237"/>
+      <c r="G27" s="229" t="s">
+        <v>358</v>
+      </c>
+      <c r="H27" s="229"/>
+      <c r="I27" s="230" t="str">
         <f>=ROUND($D$26-$I$26,2)</f>
       </c>
       <c r="L27" s="47"/>
@@ -21867,7 +21980,7 @@
     </row>
     <row r="28">
       <c r="L28" s="323" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M28" s="324" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$25,'IV. MA'!$G$25,'IV. MA'!$K$25,'IV. MA'!$O$25,'IV. MA'!$S$25,'IV. MA'!$W$25,'IV. MA'!$AA$25,'IV. MA'!$AE$25,'IV. MA'!$AI$25,'IV. MA'!$AM$25,'IV. MA'!$AQ$25,'IV. MA'!$AU$25,'IV. MA'!$AY$25,'IV. MA'!$BC$25,'IV. MA'!$BG$25,'IV. MA'!$BK$25,'IV. MA'!$BO$25,'IV. MA'!$BS$25),"")</f>
@@ -21877,72 +21990,76 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="223" t="s">
-        <v>358</v>
-      </c>
-      <c r="C29" s="224"/>
-      <c r="D29" s="225" t="str">
+      <c r="B29" s="224" t="s">
+        <v>359</v>
+      </c>
+      <c r="C29" s="225"/>
+      <c r="D29" s="226" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,E11),2),0)</f>
       </c>
-      <c r="F29" s="223" t="s">
-        <v>358</v>
-      </c>
-      <c r="G29" s="224"/>
-      <c r="H29" s="224"/>
-      <c r="I29" s="225" t="str">
+      <c r="F29" s="224" t="s">
+        <v>359</v>
+      </c>
+      <c r="G29" s="225"/>
+      <c r="H29" s="225"/>
+      <c r="I29" s="226" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,E11),2),0)</f>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="227" t="s">
-        <v>359</v>
-      </c>
-      <c r="C30" s="228"/>
-      <c r="D30" s="229" t="str">
+      <c r="B30" s="228" t="s">
+        <v>360</v>
+      </c>
+      <c r="C30" s="229"/>
+      <c r="D30" s="230" t="str">
         <f>=ROUND($D$26-MAX(0,$D$29),2)</f>
       </c>
-      <c r="F30" s="227" t="s">
+      <c r="F30" s="228" t="s">
+        <v>361</v>
+      </c>
+      <c r="G30" s="229"/>
+      <c r="H30" s="229"/>
+      <c r="I30" s="230" t="str">
+        <f>=ROUND($I$27-MAX(0,$I$29),2)</f>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="224" t="s">
+        <v>362</v>
+      </c>
+      <c r="C32" s="225"/>
+      <c r="D32" s="238" t="str">
+        <f>=IFERROR(CHOOSE(E10,MA_ManBetrag_1,MA_ManBetrag_2,MA_ManBetrag_3,MA_ManBetrag_4,MA_ManBetrag_5,MA_ManBetrag_6,MA_ManBetrag_7,MA_ManBetrag_8,MA_ManBetrag_9,MA_ManBetrag_10,MA_ManBetrag_11,MA_ManBetrag_12,MA_ManBetrag_13,MA_ManBetrag_14,MA_ManBetrag_15,MA_ManBetrag_16,MA_ManBetrag_17,MA_ManBetrag_18),0)</f>
+      </c>
+      <c r="F32" s="224" t="s">
+        <v>362</v>
+      </c>
+      <c r="G32" s="225"/>
+      <c r="H32" s="225"/>
+      <c r="I32" s="238" t="str">
+        <f>=IFERROR(CHOOSE(E10,MA_ManBetrag_1,MA_ManBetrag_2,MA_ManBetrag_3,MA_ManBetrag_4,MA_ManBetrag_5,MA_ManBetrag_6,MA_ManBetrag_7,MA_ManBetrag_8,MA_ManBetrag_9,MA_ManBetrag_10,MA_ManBetrag_11,MA_ManBetrag_12,MA_ManBetrag_13,MA_ManBetrag_14,MA_ManBetrag_15,MA_ManBetrag_16,MA_ManBetrag_17,MA_ManBetrag_18),0)</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="228" t="s">
         <v>360</v>
       </c>
-      <c r="G30" s="228"/>
-      <c r="H30" s="228"/>
-      <c r="I30" s="229" t="str">
-        <f>=ROUND($I$27-MAX(0,$I$29),2)</f>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="223" t="s">
+      <c r="C33" s="229"/>
+      <c r="D33" s="230" t="str">
+        <f>=ROUND($D$26-MAX(0,$D$29)-MAX(0,$D$32),2)</f>
+      </c>
+      <c r="F33" s="228" t="s">
         <v>361</v>
       </c>
-      <c r="C32" s="224"/>
-      <c r="D32" s="237"/>
-      <c r="F32" s="223" t="s">
-        <v>361</v>
-      </c>
-      <c r="G32" s="224"/>
-      <c r="H32" s="224"/>
-      <c r="I32" s="237"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="227" t="s">
-        <v>359</v>
-      </c>
-      <c r="C33" s="228"/>
-      <c r="D33" s="229" t="str">
-        <f>=ROUND($D$26-MAX(0,$D$29)-MAX(0,$D$32),2)</f>
-      </c>
-      <c r="F33" s="227" t="s">
-        <v>360</v>
-      </c>
-      <c r="G33" s="228"/>
-      <c r="H33" s="228"/>
-      <c r="I33" s="229" t="str">
+      <c r="G33" s="229"/>
+      <c r="H33" s="229"/>
+      <c r="I33" s="230" t="str">
         <f>=ROUND($I$27-MAX(0,$I$29)-MAX(0,$I$32),2)</f>
       </c>
     </row>
     <row r="36" ht="22" customHeight="true">
       <c r="B36" s="18" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
@@ -21958,72 +22075,72 @@
         <v>158</v>
       </c>
       <c r="C38" s="247" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D38" s="247" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E38" s="248" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="205" t="s">
-        <v>366</v>
-      </c>
-      <c r="C39" s="239" t="str">
+      <c r="B39" s="206" t="s">
+        <v>367</v>
+      </c>
+      <c r="C39" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,"&lt;="&amp;E11,'Daten'!$BD$1:$BD$18,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D39" s="240"/>
-      <c r="E39" s="226" t="str">
+      <c r="D39" s="189"/>
+      <c r="E39" s="227" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,"&lt;="&amp;E11,'Daten'!$BD$1:$BD$18,"&gt;=1"),2),0)</f>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="205" t="s">
-        <v>367</v>
-      </c>
-      <c r="C40" s="239" t="str">
+      <c r="B40" s="206" t="s">
+        <v>368</v>
+      </c>
+      <c r="C40" s="240" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 1]),2),0)</f>
       </c>
       <c r="D40" s="241">
         <v>8</v>
       </c>
-      <c r="E40" s="226" t="str">
+      <c r="E40" s="227" t="str">
         <f>=IFERROR(ROUND($C$40/Budget_Kurs,2),0)</f>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="205" t="s">
-        <v>368</v>
-      </c>
-      <c r="C41" s="239" t="str">
+      <c r="B41" s="206" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" s="240" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 2]),2),0)</f>
       </c>
       <c r="D41" s="241">
         <v>0</v>
       </c>
-      <c r="E41" s="226" t="str">
+      <c r="E41" s="227" t="str">
         <f>=IFERROR(ROUND($C$41/Budget_Kurs,2),0)</f>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="205" t="s">
-        <v>369</v>
-      </c>
-      <c r="C42" s="239" t="str">
+      <c r="B42" s="206" t="s">
+        <v>370</v>
+      </c>
+      <c r="C42" s="240" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 3]),2),0)</f>
       </c>
       <c r="D42" s="241">
         <v>0</v>
       </c>
-      <c r="E42" s="226" t="str">
+      <c r="E42" s="227" t="str">
         <f>=IFERROR(ROUND($C$42/Budget_Kurs,2),0)</f>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="205" t="s">
-        <v>370</v>
+      <c r="B43" s="206" t="s">
+        <v>371</v>
       </c>
       <c r="C43" s="242" t="str">
         <f>=$D$40+$D$41+$D$42</f>
@@ -22032,8 +22149,8 @@
       <c r="E43" s="249"/>
     </row>
     <row r="44">
-      <c r="B44" s="205" t="s">
-        <v>371</v>
+      <c r="B44" s="206" t="s">
+        <v>372</v>
       </c>
       <c r="C44" s="242" t="str">
         <f>=IFERROR(CHOOSE(IFERROR(SUMPRODUCT('Daten'!$BA$1:$BA$18,('Daten'!$BB$1:$BB$18=E10)*('Daten'!$BD$1:$BD$18=E11)),0),'IV. MA'!$C$7,'IV. MA'!$G$7,'IV. MA'!$K$7,'IV. MA'!$O$7,'IV. MA'!$S$7,'IV. MA'!$W$7,'IV. MA'!$AA$7,'IV. MA'!$AE$7,'IV. MA'!$AI$7,'IV. MA'!$AM$7,'IV. MA'!$AQ$7,'IV. MA'!$AU$7,'IV. MA'!$AY$7,'IV. MA'!$BC$7,'IV. MA'!$BG$7,'IV. MA'!$BK$7,'IV. MA'!$BO$7,'IV. MA'!$BS$7),0)</f>
@@ -22043,43 +22160,43 @@
     </row>
     <row r="45">
       <c r="B45" s="251" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C45" s="243" t="str">
         <f>=IFERROR(ROUND($C$40*$D$40/12+$C$41*$D$41/12+$C$42*$D$42/12,2),0)</f>
       </c>
-      <c r="D45" s="240"/>
-      <c r="E45" s="235" t="str">
+      <c r="D45" s="189"/>
+      <c r="E45" s="236" t="str">
         <f>=IFERROR(ROUND($E$40*$D$40/12+$E$41*$D$41/12+$E$42*$D$42/12,2),0)</f>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="251" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C46" s="244" t="str">
         <f>=IF($C$39&lt;=$C$45,"OK","ÜBERSCHRITTEN")</f>
       </c>
-      <c r="D46" s="240"/>
+      <c r="D46" s="189"/>
       <c r="E46" s="252" t="str">
         <f>=IF($E$39&lt;=$E$45,"OK","ÜBERSCHRITTEN")</f>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="205" t="s">
-        <v>374</v>
-      </c>
-      <c r="C47" s="239" t="str">
+      <c r="B47" s="206" t="s">
+        <v>375</v>
+      </c>
+      <c r="C47" s="240" t="str">
         <f>=ROUND(MAX(0,$C$39-$C$45),2)</f>
       </c>
-      <c r="D47" s="240"/>
-      <c r="E47" s="226" t="str">
+      <c r="D47" s="189"/>
+      <c r="E47" s="227" t="str">
         <f>=ROUND(MAX(0,$E$39-$E$45),2)</f>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="253" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C48" s="254" t="str">
         <f>=IFERROR($C$39/$C$45,0)</f>
@@ -22091,7 +22208,7 @@
     </row>
     <row r="50" ht="22" customHeight="true">
       <c r="B50" s="18" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
@@ -22104,53 +22221,53 @@
     </row>
     <row r="52" ht="28" customHeight="true">
       <c r="B52" s="263" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C52" s="264" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D52" s="264" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E52" s="264" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F52" s="264" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G52" s="264" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H52" s="264" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I52" s="264" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J52" s="265" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="266" t="s">
         <v>194</v>
       </c>
-      <c r="C53" s="239" t="str">
+      <c r="C53" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Eigenmittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D53" s="239" t="str">
+      <c r="D53" s="240" t="str">
         <f>=IFERROR(ROUND(Eigenmittel_LW,2),0)</f>
       </c>
-      <c r="E53" s="201" t="str">
+      <c r="E53" s="202" t="str">
         <f>=ROUND(IFERROR($C$53-$D$53,0),2)</f>
       </c>
       <c r="F53" s="258" t="str">
         <f>=ROUND(IFERROR(($C$53/$D$53)-1,0),4)</f>
       </c>
-      <c r="G53" s="217" t="str">
+      <c r="G53" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Eigenmittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H53" s="217" t="str">
+      <c r="H53" s="218" t="str">
         <f>=IFERROR(ROUND(Eigenmittel_EUR,2),0)</f>
       </c>
       <c r="I53" s="182" t="str">
@@ -22164,22 +22281,22 @@
       <c r="B54" s="266" t="s">
         <v>300</v>
       </c>
-      <c r="C54" s="239" t="str">
+      <c r="C54" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Drittmittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D54" s="239" t="str">
+      <c r="D54" s="240" t="str">
         <f>=IFERROR(ROUND(Drittmittel_LW,2),0)</f>
       </c>
-      <c r="E54" s="201" t="str">
+      <c r="E54" s="202" t="str">
         <f>=ROUND(IFERROR($C$54-$D$54,0),2)</f>
       </c>
       <c r="F54" s="258" t="str">
         <f>=ROUND(IFERROR(($C$54/$D$54)-1,0),4)</f>
       </c>
-      <c r="G54" s="217" t="str">
+      <c r="G54" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Drittmittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H54" s="217" t="str">
+      <c r="H54" s="218" t="str">
         <f>=IFERROR(ROUND(Drittmittel_EUR,2),0)</f>
       </c>
       <c r="I54" s="182" t="str">
@@ -22193,22 +22310,22 @@
       <c r="B55" s="266" t="s">
         <v>199</v>
       </c>
-      <c r="C55" s="239" t="str">
+      <c r="C55" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D55" s="239" t="str">
+      <c r="D55" s="240" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_LW,2),0)</f>
       </c>
-      <c r="E55" s="201" t="str">
+      <c r="E55" s="202" t="str">
         <f>=ROUND(IFERROR($C$55-$D$55,0),2)</f>
       </c>
       <c r="F55" s="258" t="str">
         <f>=ROUND(IFERROR(($C$55/$D$55)-1,0),4)</f>
       </c>
-      <c r="G55" s="217" t="str">
+      <c r="G55" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H55" s="217" t="str">
+      <c r="H55" s="218" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
       <c r="I55" s="182" t="str">
@@ -22222,22 +22339,22 @@
       <c r="B56" s="266" t="s">
         <v>301</v>
       </c>
-      <c r="C56" s="239" t="str">
+      <c r="C56" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Zinsertraege",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D56" s="239" t="str">
+      <c r="D56" s="240" t="str">
         <f>=IFERROR(ROUND(0,2),0)</f>
       </c>
-      <c r="E56" s="201" t="str">
+      <c r="E56" s="202" t="str">
         <f>=ROUND(IFERROR($C$56-$D$56,0),2)</f>
       </c>
       <c r="F56" s="258" t="str">
         <f>=ROUND(IFERROR(($C$56/$D$56)-1,0),4)</f>
       </c>
-      <c r="G56" s="217" t="str">
+      <c r="G56" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Zinsertraege",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H56" s="217" t="str">
+      <c r="H56" s="218" t="str">
         <f>=IFERROR(ROUND(0,2),0)</f>
       </c>
       <c r="I56" s="182" t="str">
@@ -22278,7 +22395,7 @@
     </row>
     <row r="59" ht="22" customHeight="true">
       <c r="B59" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
@@ -22291,53 +22408,53 @@
     </row>
     <row r="61" ht="28" customHeight="true">
       <c r="B61" s="263" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C61" s="264" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D61" s="264" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E61" s="264" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F61" s="264" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G61" s="264" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H61" s="264" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I61" s="264" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J61" s="265" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="266" t="s">
         <v>205</v>
       </c>
-      <c r="C62" s="239" t="str">
+      <c r="C62" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Bauausgaben",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D62" s="239" t="str">
+      <c r="D62" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Bauausgaben_LW,2),0)</f>
       </c>
-      <c r="E62" s="201" t="str">
+      <c r="E62" s="202" t="str">
         <f>=ROUND(IFERROR($C$62-$D$62,0),2)</f>
       </c>
       <c r="F62" s="258" t="str">
         <f>=ROUND(IFERROR(($C$62/$D$62)-1,0),4)</f>
       </c>
-      <c r="G62" s="217" t="str">
+      <c r="G62" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Bauausgaben",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H62" s="217" t="str">
+      <c r="H62" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Bauausgaben_EUR,2),0)</f>
       </c>
       <c r="I62" s="182" t="str">
@@ -22351,22 +22468,22 @@
       <c r="B63" s="266" t="s">
         <v>210</v>
       </c>
-      <c r="C63" s="239" t="str">
+      <c r="C63" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Investitionen",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D63" s="239" t="str">
+      <c r="D63" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Investitionen_LW,2),0)</f>
       </c>
-      <c r="E63" s="201" t="str">
+      <c r="E63" s="202" t="str">
         <f>=ROUND(IFERROR($C$63-$D$63,0),2)</f>
       </c>
       <c r="F63" s="258" t="str">
         <f>=ROUND(IFERROR(($C$63/$D$63)-1,0),4)</f>
       </c>
-      <c r="G63" s="217" t="str">
+      <c r="G63" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Investitionen",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H63" s="217" t="str">
+      <c r="H63" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Investitionen_EUR,2),0)</f>
       </c>
       <c r="I63" s="182" t="str">
@@ -22380,22 +22497,22 @@
       <c r="B64" s="266" t="s">
         <v>213</v>
       </c>
-      <c r="C64" s="239" t="str">
+      <c r="C64" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Personalkosten",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D64" s="239" t="str">
+      <c r="D64" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Personalkosten_LW,2),0)</f>
       </c>
-      <c r="E64" s="201" t="str">
+      <c r="E64" s="202" t="str">
         <f>=ROUND(IFERROR($C$64-$D$64,0),2)</f>
       </c>
       <c r="F64" s="258" t="str">
         <f>=ROUND(IFERROR(($C$64/$D$64)-1,0),4)</f>
       </c>
-      <c r="G64" s="217" t="str">
+      <c r="G64" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Personalkosten",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H64" s="217" t="str">
+      <c r="H64" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Personalkosten_EUR,2),0)</f>
       </c>
       <c r="I64" s="182" t="str">
@@ -22409,22 +22526,22 @@
       <c r="B65" s="266" t="s">
         <v>218</v>
       </c>
-      <c r="C65" s="239" t="str">
+      <c r="C65" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Projektaktivitaeten",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D65" s="239" t="str">
+      <c r="D65" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektaktivitaeten_LW,2),0)</f>
       </c>
-      <c r="E65" s="201" t="str">
+      <c r="E65" s="202" t="str">
         <f>=ROUND(IFERROR($C$65-$D$65,0),2)</f>
       </c>
       <c r="F65" s="258" t="str">
         <f>=ROUND(IFERROR(($C$65/$D$65)-1,0),4)</f>
       </c>
-      <c r="G65" s="217" t="str">
+      <c r="G65" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Projektaktivitaeten",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H65" s="217" t="str">
+      <c r="H65" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektaktivitaeten_EUR,2),0)</f>
       </c>
       <c r="I65" s="182" t="str">
@@ -22438,22 +22555,22 @@
       <c r="B66" s="266" t="s">
         <v>221</v>
       </c>
-      <c r="C66" s="239" t="str">
+      <c r="C66" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Projektverwaltung",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D66" s="239" t="str">
+      <c r="D66" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektverwaltung_LW,2),0)</f>
       </c>
-      <c r="E66" s="201" t="str">
+      <c r="E66" s="202" t="str">
         <f>=ROUND(IFERROR($C$66-$D$66,0),2)</f>
       </c>
       <c r="F66" s="258" t="str">
         <f>=ROUND(IFERROR(($C$66/$D$66)-1,0),4)</f>
       </c>
-      <c r="G66" s="217" t="str">
+      <c r="G66" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Projektverwaltung",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H66" s="217" t="str">
+      <c r="H66" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektverwaltung_EUR,2),0)</f>
       </c>
       <c r="I66" s="182" t="str">
@@ -22467,22 +22584,22 @@
       <c r="B67" s="266" t="s">
         <v>224</v>
       </c>
-      <c r="C67" s="239" t="str">
+      <c r="C67" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Evaluierung",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D67" s="239" t="str">
+      <c r="D67" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Evaluierung_LW,2),0)</f>
       </c>
-      <c r="E67" s="201" t="str">
+      <c r="E67" s="202" t="str">
         <f>=ROUND(IFERROR($C$67-$D$67,0),2)</f>
       </c>
       <c r="F67" s="258" t="str">
         <f>=ROUND(IFERROR(($C$67/$D$67)-1,0),4)</f>
       </c>
-      <c r="G67" s="217" t="str">
+      <c r="G67" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Evaluierung",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H67" s="217" t="str">
+      <c r="H67" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Evaluierung_EUR,2),0)</f>
       </c>
       <c r="I67" s="182" t="str">
@@ -22496,22 +22613,22 @@
       <c r="B68" s="266" t="s">
         <v>227</v>
       </c>
-      <c r="C68" s="239" t="str">
+      <c r="C68" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Audit",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D68" s="239" t="str">
+      <c r="D68" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Audit_LW,2),0)</f>
       </c>
-      <c r="E68" s="201" t="str">
+      <c r="E68" s="202" t="str">
         <f>=ROUND(IFERROR($C$68-$D$68,0),2)</f>
       </c>
       <c r="F68" s="258" t="str">
         <f>=ROUND(IFERROR(($C$68/$D$68)-1,0),4)</f>
       </c>
-      <c r="G68" s="217" t="str">
+      <c r="G68" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Audit",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H68" s="217" t="str">
+      <c r="H68" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Audit_EUR,2),0)</f>
       </c>
       <c r="I68" s="182" t="str">
@@ -22525,22 +22642,22 @@
       <c r="B69" s="266" t="s">
         <v>230</v>
       </c>
-      <c r="C69" s="239" t="str">
+      <c r="C69" s="240" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Reserve",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D69" s="239" t="str">
+      <c r="D69" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_LW,2),0)</f>
       </c>
-      <c r="E69" s="201" t="str">
+      <c r="E69" s="202" t="str">
         <f>=ROUND(IFERROR($C$69-$D$69,0),2)</f>
       </c>
       <c r="F69" s="258" t="str">
         <f>=ROUND(IFERROR(($C$69/$D$69)-1,0),4)</f>
       </c>
-      <c r="G69" s="217" t="str">
+      <c r="G69" s="218" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Reserve",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H69" s="217" t="str">
+      <c r="H69" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
       <c r="I69" s="182" t="str">
@@ -22580,37 +22697,37 @@
       </c>
     </row>
     <row r="76" ht="22" customHeight="true">
-      <c r="B76" s="194" t="s">
-        <v>387</v>
-      </c>
-      <c r="C76" s="194"/>
-      <c r="D76" s="194"/>
-      <c r="E76" s="194"/>
-      <c r="F76" s="194"/>
-      <c r="G76" s="194"/>
-      <c r="H76" s="194"/>
-      <c r="I76" s="194"/>
-      <c r="J76" s="194"/>
-      <c r="L76" s="202" t="str">
+      <c r="B76" s="195" t="s">
+        <v>388</v>
+      </c>
+      <c r="C76" s="195"/>
+      <c r="D76" s="195"/>
+      <c r="E76" s="195"/>
+      <c r="F76" s="195"/>
+      <c r="G76" s="195"/>
+      <c r="H76" s="195"/>
+      <c r="I76" s="195"/>
+      <c r="J76" s="195"/>
+      <c r="L76" s="203" t="str">
         <f>=IF(E81=0,"Aktueller Finanzbericht (keiner gewählt)","Aktueller Finanzbericht – Periode "&amp;E81)</f>
       </c>
-      <c r="M76" s="203"/>
-      <c r="N76" s="203"/>
-      <c r="O76" s="203"/>
-      <c r="P76" s="204"/>
+      <c r="M76" s="204"/>
+      <c r="N76" s="204"/>
+      <c r="O76" s="204"/>
+      <c r="P76" s="205"/>
     </row>
     <row r="77">
-      <c r="B77" s="195" t="s">
-        <v>388</v>
-      </c>
-      <c r="C77" s="195"/>
-      <c r="D77" s="195"/>
-      <c r="E77" s="195"/>
-      <c r="F77" s="195"/>
-      <c r="G77" s="195"/>
-      <c r="H77" s="195"/>
-      <c r="I77" s="195"/>
-      <c r="J77" s="195"/>
+      <c r="B77" s="196" t="s">
+        <v>389</v>
+      </c>
+      <c r="C77" s="196"/>
+      <c r="D77" s="196"/>
+      <c r="E77" s="196"/>
+      <c r="F77" s="196"/>
+      <c r="G77" s="196"/>
+      <c r="H77" s="196"/>
+      <c r="I77" s="196"/>
+      <c r="J77" s="196"/>
       <c r="L77" s="315" t="s">
         <v>288</v>
       </c>
@@ -22633,13 +22750,13 @@
       <c r="P78" s="338"/>
     </row>
     <row r="79" ht="22" customHeight="true">
-      <c r="C79" s="202" t="s">
-        <v>389</v>
-      </c>
-      <c r="D79" s="203"/>
-      <c r="E79" s="203"/>
-      <c r="F79" s="203"/>
-      <c r="G79" s="204"/>
+      <c r="C79" s="203" t="s">
+        <v>390</v>
+      </c>
+      <c r="D79" s="204"/>
+      <c r="E79" s="204"/>
+      <c r="F79" s="204"/>
+      <c r="G79" s="205"/>
       <c r="L79" s="315" t="s">
         <v>290</v>
       </c>
@@ -22651,15 +22768,15 @@
       <c r="P79" s="338"/>
     </row>
     <row r="80">
-      <c r="C80" s="205" t="s">
-        <v>341</v>
-      </c>
-      <c r="D80" s="197"/>
+      <c r="C80" s="206" t="s">
+        <v>342</v>
+      </c>
+      <c r="D80" s="198"/>
       <c r="E80" s="63" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F80" s="63"/>
-      <c r="G80" s="206"/>
+      <c r="G80" s="207"/>
       <c r="L80" s="315" t="s">
         <v>291</v>
       </c>
@@ -22672,7 +22789,7 @@
     </row>
     <row r="81">
       <c r="C81" s="253" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D81" s="286"/>
       <c r="E81" s="287" t="str">
@@ -22696,7 +22813,7 @@
     </row>
     <row r="83" ht="22" customHeight="true">
       <c r="B83" s="18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C83" s="18"/>
       <c r="D83" s="18"/>
@@ -22732,19 +22849,19 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="223" t="s">
-        <v>347</v>
-      </c>
-      <c r="C85" s="224"/>
-      <c r="D85" s="225" t="str">
+      <c r="B85" s="224" t="s">
+        <v>348</v>
+      </c>
+      <c r="C85" s="225"/>
+      <c r="D85" s="226" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
-      <c r="F85" s="230" t="s">
-        <v>351</v>
-      </c>
-      <c r="G85" s="231"/>
-      <c r="H85" s="231"/>
-      <c r="I85" s="232"/>
+      <c r="F85" s="231" t="s">
+        <v>352</v>
+      </c>
+      <c r="G85" s="232"/>
+      <c r="H85" s="232"/>
+      <c r="I85" s="233"/>
       <c r="L85" s="143" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$B$11,'III. Finanzberichte'!$I$11,'III. Finanzberichte'!$P$11,'III. Finanzberichte'!$W$11,'III. Finanzberichte'!$AD$11,'III. Finanzberichte'!$AK$11,'III. Finanzberichte'!$AR$11,'III. Finanzberichte'!$AY$11,'III. Finanzberichte'!$BF$11,'III. Finanzberichte'!$BM$11,'III. Finanzberichte'!$BT$11,'III. Finanzberichte'!$CA$11,'III. Finanzberichte'!$CH$11,'III. Finanzberichte'!$CO$11,'III. Finanzberichte'!$CV$11,'III. Finanzberichte'!$DC$11,'III. Finanzberichte'!$DJ$11,'III. Finanzberichte'!$DQ$11),"")</f>
       </c>
@@ -22762,21 +22879,21 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="205" t="s">
-        <v>348</v>
-      </c>
-      <c r="C86" s="197"/>
-      <c r="D86" s="226" t="str">
+      <c r="B86" s="206" t="s">
+        <v>349</v>
+      </c>
+      <c r="C86" s="198"/>
+      <c r="D86" s="227" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
-      <c r="F86" s="233" t="s">
-        <v>352</v>
-      </c>
-      <c r="G86" s="197" t="s">
+      <c r="F86" s="234" t="s">
         <v>353</v>
       </c>
-      <c r="H86" s="197"/>
-      <c r="I86" s="234" t="str">
+      <c r="G86" s="198" t="s">
+        <v>354</v>
+      </c>
+      <c r="H86" s="198"/>
+      <c r="I86" s="235" t="str">
         <f>=IFERROR(ROUND(Saldovortrag_EUR,2),0)</f>
       </c>
       <c r="L86" s="143" t="s">
@@ -22796,21 +22913,21 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="205" t="str">
+      <c r="B87" s="206" t="str">
         <f>=IF(Reserve_Freigabe="Ja","Operatives Budget (Reserve freigegeben)","Operatives Budget (abzgl. Reserve)")</f>
       </c>
-      <c r="C87" s="197"/>
-      <c r="D87" s="226" t="str">
+      <c r="C87" s="198"/>
+      <c r="D87" s="227" t="str">
         <f>=IF(Reserve_Freigabe="Ja",ROUND($D$85,2),ROUND($D$85-$D$86,2))</f>
       </c>
-      <c r="F87" s="233" t="s">
-        <v>352</v>
-      </c>
-      <c r="G87" s="197" t="s">
-        <v>354</v>
-      </c>
-      <c r="H87" s="197"/>
-      <c r="I87" s="234" t="str">
+      <c r="F87" s="234" t="s">
+        <v>353</v>
+      </c>
+      <c r="G87" s="198" t="s">
+        <v>355</v>
+      </c>
+      <c r="H87" s="198"/>
+      <c r="I87" s="235" t="str">
         <f>=IFERROR(ROUND(MAX(0,(SUM($G$96:$G$99)-$G$98)-(SUM($H$96:$H$99)-$H$98)),2),0)</f>
         <v>0</v>
       </c>
@@ -22831,19 +22948,19 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="205" t="s">
-        <v>349</v>
-      </c>
-      <c r="C88" s="197"/>
-      <c r="D88" s="226" t="str">
+      <c r="B88" s="206" t="s">
+        <v>350</v>
+      </c>
+      <c r="C88" s="198"/>
+      <c r="D88" s="227" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblKMWMittel[Betrag]),2),0)</f>
       </c>
       <c r="F88" s="47"/>
-      <c r="G88" s="218" t="s">
-        <v>356</v>
-      </c>
-      <c r="H88" s="218"/>
-      <c r="I88" s="235" t="str">
+      <c r="G88" s="219" t="s">
+        <v>357</v>
+      </c>
+      <c r="H88" s="219"/>
+      <c r="I88" s="236" t="str">
         <f>=ROUND(IF($F$86="Abzug",MAX(0,$I$86),0)+IF($F$87="Abzug",MAX(0,$I$87),0),2)</f>
       </c>
       <c r="L88" s="143" t="s">
@@ -22863,19 +22980,19 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="227" t="s">
-        <v>350</v>
-      </c>
-      <c r="C89" s="228"/>
-      <c r="D89" s="229" t="str">
+      <c r="B89" s="228" t="s">
+        <v>351</v>
+      </c>
+      <c r="C89" s="229"/>
+      <c r="D89" s="230" t="str">
         <f>=ROUND($D$87-$D$88,2)</f>
       </c>
-      <c r="F89" s="236"/>
-      <c r="G89" s="228" t="s">
-        <v>357</v>
-      </c>
-      <c r="H89" s="228"/>
-      <c r="I89" s="229" t="str">
+      <c r="F89" s="237"/>
+      <c r="G89" s="229" t="s">
+        <v>358</v>
+      </c>
+      <c r="H89" s="229"/>
+      <c r="I89" s="230" t="str">
         <f>=ROUND($D$89-$I$88,2)</f>
       </c>
       <c r="L89" s="143" t="s">
@@ -22939,7 +23056,7 @@
     </row>
     <row r="93" ht="22" customHeight="true">
       <c r="B93" s="18" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C93" s="18"/>
       <c r="D93" s="18"/>
@@ -22984,31 +23101,31 @@
     </row>
     <row r="95" ht="28" customHeight="true">
       <c r="B95" s="263" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C95" s="264" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D95" s="264" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E95" s="264" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F95" s="264" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G95" s="264" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H95" s="264" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I95" s="264" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J95" s="265" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L95" s="143" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$B$21,'III. Finanzberichte'!$I$21,'III. Finanzberichte'!$P$21,'III. Finanzberichte'!$W$21,'III. Finanzberichte'!$AD$21,'III. Finanzberichte'!$AK$21,'III. Finanzberichte'!$AR$21,'III. Finanzberichte'!$AY$21,'III. Finanzberichte'!$BF$21,'III. Finanzberichte'!$BM$21,'III. Finanzberichte'!$BT$21,'III. Finanzberichte'!$CA$21,'III. Finanzberichte'!$CH$21,'III. Finanzberichte'!$CO$21,'III. Finanzberichte'!$CV$21,'III. Finanzberichte'!$DC$21,'III. Finanzberichte'!$DJ$21,'III. Finanzberichte'!$DQ$21),"")</f>
@@ -23030,22 +23147,22 @@
       <c r="B96" s="266" t="s">
         <v>194</v>
       </c>
-      <c r="C96" s="239" t="str">
+      <c r="C96" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$12,'III. Finanzberichte'!$L$12,'III. Finanzberichte'!$S$12,'III. Finanzberichte'!$Z$12,'III. Finanzberichte'!$AG$12,'III. Finanzberichte'!$AN$12,'III. Finanzberichte'!$AU$12,'III. Finanzberichte'!$BB$12,'III. Finanzberichte'!$BI$12,'III. Finanzberichte'!$BP$12,'III. Finanzberichte'!$BW$12,'III. Finanzberichte'!$CD$12,'III. Finanzberichte'!$CK$12,'III. Finanzberichte'!$CR$12,'III. Finanzberichte'!$CY$12,'III. Finanzberichte'!$DF$12,'III. Finanzberichte'!$DM$12,'III. Finanzberichte'!$DT$12),2),0)</f>
       </c>
-      <c r="D96" s="239" t="str">
+      <c r="D96" s="240" t="str">
         <f>=IFERROR(ROUND(Eigenmittel_LW,2),0)</f>
       </c>
-      <c r="E96" s="201" t="str">
+      <c r="E96" s="202" t="str">
         <f>=ROUND(IFERROR($C$96-$D$96,0),2)</f>
       </c>
       <c r="F96" s="258" t="str">
         <f>=ROUND(IFERROR(($C$96/$D$96)-1,0),4)</f>
       </c>
-      <c r="G96" s="217" t="str">
+      <c r="G96" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$12,'III. Finanzberichte'!$M$12,'III. Finanzberichte'!$T$12,'III. Finanzberichte'!$AA$12,'III. Finanzberichte'!$AH$12,'III. Finanzberichte'!$AO$12,'III. Finanzberichte'!$AV$12,'III. Finanzberichte'!$BC$12,'III. Finanzberichte'!$BJ$12,'III. Finanzberichte'!$BQ$12,'III. Finanzberichte'!$BX$12,'III. Finanzberichte'!$CE$12,'III. Finanzberichte'!$CL$12,'III. Finanzberichte'!$CS$12,'III. Finanzberichte'!$CZ$12,'III. Finanzberichte'!$DG$12,'III. Finanzberichte'!$DN$12,'III. Finanzberichte'!$DU$12),2),0)</f>
       </c>
-      <c r="H96" s="217" t="str">
+      <c r="H96" s="218" t="str">
         <f>=IFERROR(ROUND(Eigenmittel_EUR,2),0)</f>
       </c>
       <c r="I96" s="182" t="str">
@@ -23074,22 +23191,22 @@
       <c r="B97" s="266" t="s">
         <v>300</v>
       </c>
-      <c r="C97" s="239" t="str">
+      <c r="C97" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$13,'III. Finanzberichte'!$L$13,'III. Finanzberichte'!$S$13,'III. Finanzberichte'!$Z$13,'III. Finanzberichte'!$AG$13,'III. Finanzberichte'!$AN$13,'III. Finanzberichte'!$AU$13,'III. Finanzberichte'!$BB$13,'III. Finanzberichte'!$BI$13,'III. Finanzberichte'!$BP$13,'III. Finanzberichte'!$BW$13,'III. Finanzberichte'!$CD$13,'III. Finanzberichte'!$CK$13,'III. Finanzberichte'!$CR$13,'III. Finanzberichte'!$CY$13,'III. Finanzberichte'!$DF$13,'III. Finanzberichte'!$DM$13,'III. Finanzberichte'!$DT$13),2),0)</f>
       </c>
-      <c r="D97" s="239" t="str">
+      <c r="D97" s="240" t="str">
         <f>=IFERROR(ROUND(Drittmittel_LW,2),0)</f>
       </c>
-      <c r="E97" s="201" t="str">
+      <c r="E97" s="202" t="str">
         <f>=ROUND(IFERROR($C$97-$D$97,0),2)</f>
       </c>
       <c r="F97" s="258" t="str">
         <f>=ROUND(IFERROR(($C$97/$D$97)-1,0),4)</f>
       </c>
-      <c r="G97" s="217" t="str">
+      <c r="G97" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$13,'III. Finanzberichte'!$M$13,'III. Finanzberichte'!$T$13,'III. Finanzberichte'!$AA$13,'III. Finanzberichte'!$AH$13,'III. Finanzberichte'!$AO$13,'III. Finanzberichte'!$AV$13,'III. Finanzberichte'!$BC$13,'III. Finanzberichte'!$BJ$13,'III. Finanzberichte'!$BQ$13,'III. Finanzberichte'!$BX$13,'III. Finanzberichte'!$CE$13,'III. Finanzberichte'!$CL$13,'III. Finanzberichte'!$CS$13,'III. Finanzberichte'!$CZ$13,'III. Finanzberichte'!$DG$13,'III. Finanzberichte'!$DN$13,'III. Finanzberichte'!$DU$13),2),0)</f>
       </c>
-      <c r="H97" s="217" t="str">
+      <c r="H97" s="218" t="str">
         <f>=IFERROR(ROUND(Drittmittel_EUR,2),0)</f>
       </c>
       <c r="I97" s="182" t="str">
@@ -23118,22 +23235,22 @@
       <c r="B98" s="266" t="s">
         <v>199</v>
       </c>
-      <c r="C98" s="239" t="str">
+      <c r="C98" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$14,'III. Finanzberichte'!$L$14,'III. Finanzberichte'!$S$14,'III. Finanzberichte'!$Z$14,'III. Finanzberichte'!$AG$14,'III. Finanzberichte'!$AN$14,'III. Finanzberichte'!$AU$14,'III. Finanzberichte'!$BB$14,'III. Finanzberichte'!$BI$14,'III. Finanzberichte'!$BP$14,'III. Finanzberichte'!$BW$14,'III. Finanzberichte'!$CD$14,'III. Finanzberichte'!$CK$14,'III. Finanzberichte'!$CR$14,'III. Finanzberichte'!$CY$14,'III. Finanzberichte'!$DF$14,'III. Finanzberichte'!$DM$14,'III. Finanzberichte'!$DT$14),2),0)</f>
       </c>
-      <c r="D98" s="239" t="str">
+      <c r="D98" s="240" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_LW,2),0)</f>
       </c>
-      <c r="E98" s="201" t="str">
+      <c r="E98" s="202" t="str">
         <f>=ROUND(IFERROR($C$98-$D$98,0),2)</f>
       </c>
       <c r="F98" s="258" t="str">
         <f>=ROUND(IFERROR(($C$98/$D$98)-1,0),4)</f>
       </c>
-      <c r="G98" s="217" t="str">
+      <c r="G98" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$14,'III. Finanzberichte'!$M$14,'III. Finanzberichte'!$T$14,'III. Finanzberichte'!$AA$14,'III. Finanzberichte'!$AH$14,'III. Finanzberichte'!$AO$14,'III. Finanzberichte'!$AV$14,'III. Finanzberichte'!$BC$14,'III. Finanzberichte'!$BJ$14,'III. Finanzberichte'!$BQ$14,'III. Finanzberichte'!$BX$14,'III. Finanzberichte'!$CE$14,'III. Finanzberichte'!$CL$14,'III. Finanzberichte'!$CS$14,'III. Finanzberichte'!$CZ$14,'III. Finanzberichte'!$DG$14,'III. Finanzberichte'!$DN$14,'III. Finanzberichte'!$DU$14),2),0)</f>
       </c>
-      <c r="H98" s="217" t="str">
+      <c r="H98" s="218" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
       <c r="I98" s="182" t="str">
@@ -23162,22 +23279,22 @@
       <c r="B99" s="266" t="s">
         <v>301</v>
       </c>
-      <c r="C99" s="239" t="str">
+      <c r="C99" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$15,'III. Finanzberichte'!$L$15,'III. Finanzberichte'!$S$15,'III. Finanzberichte'!$Z$15,'III. Finanzberichte'!$AG$15,'III. Finanzberichte'!$AN$15,'III. Finanzberichte'!$AU$15,'III. Finanzberichte'!$BB$15,'III. Finanzberichte'!$BI$15,'III. Finanzberichte'!$BP$15,'III. Finanzberichte'!$BW$15,'III. Finanzberichte'!$CD$15,'III. Finanzberichte'!$CK$15,'III. Finanzberichte'!$CR$15,'III. Finanzberichte'!$CY$15,'III. Finanzberichte'!$DF$15,'III. Finanzberichte'!$DM$15,'III. Finanzberichte'!$DT$15),2),0)</f>
       </c>
-      <c r="D99" s="239" t="str">
+      <c r="D99" s="240" t="str">
         <f>=IFERROR(ROUND(0,2),0)</f>
       </c>
-      <c r="E99" s="201" t="str">
+      <c r="E99" s="202" t="str">
         <f>=ROUND(IFERROR($C$99-$D$99,0),2)</f>
       </c>
       <c r="F99" s="258" t="str">
         <f>=ROUND(IFERROR(($C$99/$D$99)-1,0),4)</f>
       </c>
-      <c r="G99" s="217" t="str">
+      <c r="G99" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$15,'III. Finanzberichte'!$M$15,'III. Finanzberichte'!$T$15,'III. Finanzberichte'!$AA$15,'III. Finanzberichte'!$AH$15,'III. Finanzberichte'!$AO$15,'III. Finanzberichte'!$AV$15,'III. Finanzberichte'!$BC$15,'III. Finanzberichte'!$BJ$15,'III. Finanzberichte'!$BQ$15,'III. Finanzberichte'!$BX$15,'III. Finanzberichte'!$CE$15,'III. Finanzberichte'!$CL$15,'III. Finanzberichte'!$CS$15,'III. Finanzberichte'!$CZ$15,'III. Finanzberichte'!$DG$15,'III. Finanzberichte'!$DN$15,'III. Finanzberichte'!$DU$15),2),0)</f>
       </c>
-      <c r="H99" s="217" t="str">
+      <c r="H99" s="218" t="str">
         <f>=IFERROR(ROUND(0,2),0)</f>
       </c>
       <c r="I99" s="182" t="str">
@@ -23265,7 +23382,7 @@
     </row>
     <row r="102" ht="22" customHeight="true">
       <c r="B102" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C102" s="18"/>
       <c r="D102" s="18"/>
@@ -23310,31 +23427,31 @@
     </row>
     <row r="104" ht="28" customHeight="true">
       <c r="B104" s="263" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C104" s="264" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D104" s="264" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E104" s="264" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F104" s="264" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G104" s="264" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H104" s="264" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I104" s="264" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J104" s="265" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L104" s="47"/>
       <c r="P104" s="48"/>
@@ -23343,22 +23460,22 @@
       <c r="B105" s="266" t="s">
         <v>205</v>
       </c>
-      <c r="C105" s="239" t="str">
+      <c r="C105" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$19+'III. Finanzberichte'!$E$20,'III. Finanzberichte'!$L$19+'III. Finanzberichte'!$L$20,'III. Finanzberichte'!$S$19+'III. Finanzberichte'!$S$20,'III. Finanzberichte'!$Z$19+'III. Finanzberichte'!$Z$20,'III. Finanzberichte'!$AG$19+'III. Finanzberichte'!$AG$20,'III. Finanzberichte'!$AN$19+'III. Finanzberichte'!$AN$20,'III. Finanzberichte'!$AU$19+'III. Finanzberichte'!$AU$20,'III. Finanzberichte'!$BB$19+'III. Finanzberichte'!$BB$20,'III. Finanzberichte'!$BI$19+'III. Finanzberichte'!$BI$20,'III. Finanzberichte'!$BP$19+'III. Finanzberichte'!$BP$20,'III. Finanzberichte'!$BW$19+'III. Finanzberichte'!$BW$20,'III. Finanzberichte'!$CD$19+'III. Finanzberichte'!$CD$20,'III. Finanzberichte'!$CK$19+'III. Finanzberichte'!$CK$20,'III. Finanzberichte'!$CR$19+'III. Finanzberichte'!$CR$20,'III. Finanzberichte'!$CY$19+'III. Finanzberichte'!$CY$20,'III. Finanzberichte'!$DF$19+'III. Finanzberichte'!$DF$20,'III. Finanzberichte'!$DM$19+'III. Finanzberichte'!$DM$20,'III. Finanzberichte'!$DT$19+'III. Finanzberichte'!$DT$20),2),0)</f>
       </c>
-      <c r="D105" s="239" t="str">
+      <c r="D105" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Bauausgaben_LW,2),0)</f>
       </c>
-      <c r="E105" s="201" t="str">
+      <c r="E105" s="202" t="str">
         <f>=ROUND(IFERROR($C$105-$D$105,0),2)</f>
       </c>
       <c r="F105" s="258" t="str">
         <f>=ROUND(IFERROR(($C$105/$D$105)-1,0),4)</f>
       </c>
-      <c r="G105" s="217" t="str">
+      <c r="G105" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$19+'III. Finanzberichte'!$F$20,'III. Finanzberichte'!$M$19+'III. Finanzberichte'!$M$20,'III. Finanzberichte'!$T$19+'III. Finanzberichte'!$T$20,'III. Finanzberichte'!$AA$19+'III. Finanzberichte'!$AA$20,'III. Finanzberichte'!$AH$19+'III. Finanzberichte'!$AH$20,'III. Finanzberichte'!$AO$19+'III. Finanzberichte'!$AO$20,'III. Finanzberichte'!$AV$19+'III. Finanzberichte'!$AV$20,'III. Finanzberichte'!$BC$19+'III. Finanzberichte'!$BC$20,'III. Finanzberichte'!$BJ$19+'III. Finanzberichte'!$BJ$20,'III. Finanzberichte'!$BQ$19+'III. Finanzberichte'!$BQ$20,'III. Finanzberichte'!$BX$19+'III. Finanzberichte'!$BX$20,'III. Finanzberichte'!$CE$19+'III. Finanzberichte'!$CE$20,'III. Finanzberichte'!$CL$19+'III. Finanzberichte'!$CL$20,'III. Finanzberichte'!$CS$19+'III. Finanzberichte'!$CS$20,'III. Finanzberichte'!$CZ$19+'III. Finanzberichte'!$CZ$20,'III. Finanzberichte'!$DG$19+'III. Finanzberichte'!$DG$20,'III. Finanzberichte'!$DN$19+'III. Finanzberichte'!$DN$20,'III. Finanzberichte'!$DU$19+'III. Finanzberichte'!$DU$20),2),0)</f>
       </c>
-      <c r="H105" s="217" t="str">
+      <c r="H105" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Bauausgaben_EUR,2),0)</f>
       </c>
       <c r="I105" s="182" t="str">
@@ -23387,22 +23504,22 @@
       <c r="B106" s="266" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="239" t="str">
+      <c r="C106" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$21,'III. Finanzberichte'!$L$21,'III. Finanzberichte'!$S$21,'III. Finanzberichte'!$Z$21,'III. Finanzberichte'!$AG$21,'III. Finanzberichte'!$AN$21,'III. Finanzberichte'!$AU$21,'III. Finanzberichte'!$BB$21,'III. Finanzberichte'!$BI$21,'III. Finanzberichte'!$BP$21,'III. Finanzberichte'!$BW$21,'III. Finanzberichte'!$CD$21,'III. Finanzberichte'!$CK$21,'III. Finanzberichte'!$CR$21,'III. Finanzberichte'!$CY$21,'III. Finanzberichte'!$DF$21,'III. Finanzberichte'!$DM$21,'III. Finanzberichte'!$DT$21),2),0)</f>
       </c>
-      <c r="D106" s="239" t="str">
+      <c r="D106" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Investitionen_LW,2),0)</f>
       </c>
-      <c r="E106" s="201" t="str">
+      <c r="E106" s="202" t="str">
         <f>=ROUND(IFERROR($C$106-$D$106,0),2)</f>
       </c>
       <c r="F106" s="258" t="str">
         <f>=ROUND(IFERROR(($C$106/$D$106)-1,0),4)</f>
       </c>
-      <c r="G106" s="217" t="str">
+      <c r="G106" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$21,'III. Finanzberichte'!$M$21,'III. Finanzberichte'!$T$21,'III. Finanzberichte'!$AA$21,'III. Finanzberichte'!$AH$21,'III. Finanzberichte'!$AO$21,'III. Finanzberichte'!$AV$21,'III. Finanzberichte'!$BC$21,'III. Finanzberichte'!$BJ$21,'III. Finanzberichte'!$BQ$21,'III. Finanzberichte'!$BX$21,'III. Finanzberichte'!$CE$21,'III. Finanzberichte'!$CL$21,'III. Finanzberichte'!$CS$21,'III. Finanzberichte'!$CZ$21,'III. Finanzberichte'!$DG$21,'III. Finanzberichte'!$DN$21,'III. Finanzberichte'!$DU$21),2),0)</f>
       </c>
-      <c r="H106" s="217" t="str">
+      <c r="H106" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Investitionen_EUR,2),0)</f>
       </c>
       <c r="I106" s="182" t="str">
@@ -23416,22 +23533,22 @@
       <c r="B107" s="266" t="s">
         <v>213</v>
       </c>
-      <c r="C107" s="239" t="str">
+      <c r="C107" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$22+'III. Finanzberichte'!$E$23,'III. Finanzberichte'!$L$22+'III. Finanzberichte'!$L$23,'III. Finanzberichte'!$S$22+'III. Finanzberichte'!$S$23,'III. Finanzberichte'!$Z$22+'III. Finanzberichte'!$Z$23,'III. Finanzberichte'!$AG$22+'III. Finanzberichte'!$AG$23,'III. Finanzberichte'!$AN$22+'III. Finanzberichte'!$AN$23,'III. Finanzberichte'!$AU$22+'III. Finanzberichte'!$AU$23,'III. Finanzberichte'!$BB$22+'III. Finanzberichte'!$BB$23,'III. Finanzberichte'!$BI$22+'III. Finanzberichte'!$BI$23,'III. Finanzberichte'!$BP$22+'III. Finanzberichte'!$BP$23,'III. Finanzberichte'!$BW$22+'III. Finanzberichte'!$BW$23,'III. Finanzberichte'!$CD$22+'III. Finanzberichte'!$CD$23,'III. Finanzberichte'!$CK$22+'III. Finanzberichte'!$CK$23,'III. Finanzberichte'!$CR$22+'III. Finanzberichte'!$CR$23,'III. Finanzberichte'!$CY$22+'III. Finanzberichte'!$CY$23,'III. Finanzberichte'!$DF$22+'III. Finanzberichte'!$DF$23,'III. Finanzberichte'!$DM$22+'III. Finanzberichte'!$DM$23,'III. Finanzberichte'!$DT$22+'III. Finanzberichte'!$DT$23),2),0)</f>
       </c>
-      <c r="D107" s="239" t="str">
+      <c r="D107" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Personalkosten_LW,2),0)</f>
       </c>
-      <c r="E107" s="201" t="str">
+      <c r="E107" s="202" t="str">
         <f>=ROUND(IFERROR($C$107-$D$107,0),2)</f>
       </c>
       <c r="F107" s="258" t="str">
         <f>=ROUND(IFERROR(($C$107/$D$107)-1,0),4)</f>
       </c>
-      <c r="G107" s="217" t="str">
+      <c r="G107" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$22+'III. Finanzberichte'!$F$23,'III. Finanzberichte'!$M$22+'III. Finanzberichte'!$M$23,'III. Finanzberichte'!$T$22+'III. Finanzberichte'!$T$23,'III. Finanzberichte'!$AA$22+'III. Finanzberichte'!$AA$23,'III. Finanzberichte'!$AH$22+'III. Finanzberichte'!$AH$23,'III. Finanzberichte'!$AO$22+'III. Finanzberichte'!$AO$23,'III. Finanzberichte'!$AV$22+'III. Finanzberichte'!$AV$23,'III. Finanzberichte'!$BC$22+'III. Finanzberichte'!$BC$23,'III. Finanzberichte'!$BJ$22+'III. Finanzberichte'!$BJ$23,'III. Finanzberichte'!$BQ$22+'III. Finanzberichte'!$BQ$23,'III. Finanzberichte'!$BX$22+'III. Finanzberichte'!$BX$23,'III. Finanzberichte'!$CE$22+'III. Finanzberichte'!$CE$23,'III. Finanzberichte'!$CL$22+'III. Finanzberichte'!$CL$23,'III. Finanzberichte'!$CS$22+'III. Finanzberichte'!$CS$23,'III. Finanzberichte'!$CZ$22+'III. Finanzberichte'!$CZ$23,'III. Finanzberichte'!$DG$22+'III. Finanzberichte'!$DG$23,'III. Finanzberichte'!$DN$22+'III. Finanzberichte'!$DN$23,'III. Finanzberichte'!$DU$22+'III. Finanzberichte'!$DU$23),2),0)</f>
       </c>
-      <c r="H107" s="217" t="str">
+      <c r="H107" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Personalkosten_EUR,2),0)</f>
       </c>
       <c r="I107" s="182" t="str">
@@ -23445,22 +23562,22 @@
       <c r="B108" s="266" t="s">
         <v>218</v>
       </c>
-      <c r="C108" s="239" t="str">
+      <c r="C108" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$24,'III. Finanzberichte'!$L$24,'III. Finanzberichte'!$S$24,'III. Finanzberichte'!$Z$24,'III. Finanzberichte'!$AG$24,'III. Finanzberichte'!$AN$24,'III. Finanzberichte'!$AU$24,'III. Finanzberichte'!$BB$24,'III. Finanzberichte'!$BI$24,'III. Finanzberichte'!$BP$24,'III. Finanzberichte'!$BW$24,'III. Finanzberichte'!$CD$24,'III. Finanzberichte'!$CK$24,'III. Finanzberichte'!$CR$24,'III. Finanzberichte'!$CY$24,'III. Finanzberichte'!$DF$24,'III. Finanzberichte'!$DM$24,'III. Finanzberichte'!$DT$24),2),0)</f>
       </c>
-      <c r="D108" s="239" t="str">
+      <c r="D108" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektaktivitaeten_LW,2),0)</f>
       </c>
-      <c r="E108" s="201" t="str">
+      <c r="E108" s="202" t="str">
         <f>=ROUND(IFERROR($C$108-$D$108,0),2)</f>
       </c>
       <c r="F108" s="258" t="str">
         <f>=ROUND(IFERROR(($C$108/$D$108)-1,0),4)</f>
       </c>
-      <c r="G108" s="217" t="str">
+      <c r="G108" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$24,'III. Finanzberichte'!$M$24,'III. Finanzberichte'!$T$24,'III. Finanzberichte'!$AA$24,'III. Finanzberichte'!$AH$24,'III. Finanzberichte'!$AO$24,'III. Finanzberichte'!$AV$24,'III. Finanzberichte'!$BC$24,'III. Finanzberichte'!$BJ$24,'III. Finanzberichte'!$BQ$24,'III. Finanzberichte'!$BX$24,'III. Finanzberichte'!$CE$24,'III. Finanzberichte'!$CL$24,'III. Finanzberichte'!$CS$24,'III. Finanzberichte'!$CZ$24,'III. Finanzberichte'!$DG$24,'III. Finanzberichte'!$DN$24,'III. Finanzberichte'!$DU$24),2),0)</f>
       </c>
-      <c r="H108" s="217" t="str">
+      <c r="H108" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektaktivitaeten_EUR,2),0)</f>
       </c>
       <c r="I108" s="182" t="str">
@@ -23474,22 +23591,22 @@
       <c r="B109" s="266" t="s">
         <v>221</v>
       </c>
-      <c r="C109" s="239" t="str">
+      <c r="C109" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$25,'III. Finanzberichte'!$L$25,'III. Finanzberichte'!$S$25,'III. Finanzberichte'!$Z$25,'III. Finanzberichte'!$AG$25,'III. Finanzberichte'!$AN$25,'III. Finanzberichte'!$AU$25,'III. Finanzberichte'!$BB$25,'III. Finanzberichte'!$BI$25,'III. Finanzberichte'!$BP$25,'III. Finanzberichte'!$BW$25,'III. Finanzberichte'!$CD$25,'III. Finanzberichte'!$CK$25,'III. Finanzberichte'!$CR$25,'III. Finanzberichte'!$CY$25,'III. Finanzberichte'!$DF$25,'III. Finanzberichte'!$DM$25,'III. Finanzberichte'!$DT$25),2),0)</f>
       </c>
-      <c r="D109" s="239" t="str">
+      <c r="D109" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektverwaltung_LW,2),0)</f>
       </c>
-      <c r="E109" s="201" t="str">
+      <c r="E109" s="202" t="str">
         <f>=ROUND(IFERROR($C$109-$D$109,0),2)</f>
       </c>
       <c r="F109" s="258" t="str">
         <f>=ROUND(IFERROR(($C$109/$D$109)-1,0),4)</f>
       </c>
-      <c r="G109" s="217" t="str">
+      <c r="G109" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$25,'III. Finanzberichte'!$M$25,'III. Finanzberichte'!$T$25,'III. Finanzberichte'!$AA$25,'III. Finanzberichte'!$AH$25,'III. Finanzberichte'!$AO$25,'III. Finanzberichte'!$AV$25,'III. Finanzberichte'!$BC$25,'III. Finanzberichte'!$BJ$25,'III. Finanzberichte'!$BQ$25,'III. Finanzberichte'!$BX$25,'III. Finanzberichte'!$CE$25,'III. Finanzberichte'!$CL$25,'III. Finanzberichte'!$CS$25,'III. Finanzberichte'!$CZ$25,'III. Finanzberichte'!$DG$25,'III. Finanzberichte'!$DN$25,'III. Finanzberichte'!$DU$25),2),0)</f>
       </c>
-      <c r="H109" s="217" t="str">
+      <c r="H109" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektverwaltung_EUR,2),0)</f>
       </c>
       <c r="I109" s="182" t="str">
@@ -23503,22 +23620,22 @@
       <c r="B110" s="266" t="s">
         <v>224</v>
       </c>
-      <c r="C110" s="239" t="str">
+      <c r="C110" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$26,'III. Finanzberichte'!$L$26,'III. Finanzberichte'!$S$26,'III. Finanzberichte'!$Z$26,'III. Finanzberichte'!$AG$26,'III. Finanzberichte'!$AN$26,'III. Finanzberichte'!$AU$26,'III. Finanzberichte'!$BB$26,'III. Finanzberichte'!$BI$26,'III. Finanzberichte'!$BP$26,'III. Finanzberichte'!$BW$26,'III. Finanzberichte'!$CD$26,'III. Finanzberichte'!$CK$26,'III. Finanzberichte'!$CR$26,'III. Finanzberichte'!$CY$26,'III. Finanzberichte'!$DF$26,'III. Finanzberichte'!$DM$26,'III. Finanzberichte'!$DT$26),2),0)</f>
       </c>
-      <c r="D110" s="239" t="str">
+      <c r="D110" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Evaluierung_LW,2),0)</f>
       </c>
-      <c r="E110" s="201" t="str">
+      <c r="E110" s="202" t="str">
         <f>=ROUND(IFERROR($C$110-$D$110,0),2)</f>
       </c>
       <c r="F110" s="258" t="str">
         <f>=ROUND(IFERROR(($C$110/$D$110)-1,0),4)</f>
       </c>
-      <c r="G110" s="217" t="str">
+      <c r="G110" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$26,'III. Finanzberichte'!$M$26,'III. Finanzberichte'!$T$26,'III. Finanzberichte'!$AA$26,'III. Finanzberichte'!$AH$26,'III. Finanzberichte'!$AO$26,'III. Finanzberichte'!$AV$26,'III. Finanzberichte'!$BC$26,'III. Finanzberichte'!$BJ$26,'III. Finanzberichte'!$BQ$26,'III. Finanzberichte'!$BX$26,'III. Finanzberichte'!$CE$26,'III. Finanzberichte'!$CL$26,'III. Finanzberichte'!$CS$26,'III. Finanzberichte'!$CZ$26,'III. Finanzberichte'!$DG$26,'III. Finanzberichte'!$DN$26,'III. Finanzberichte'!$DU$26),2),0)</f>
       </c>
-      <c r="H110" s="217" t="str">
+      <c r="H110" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Evaluierung_EUR,2),0)</f>
       </c>
       <c r="I110" s="182" t="str">
@@ -23532,22 +23649,22 @@
       <c r="B111" s="266" t="s">
         <v>227</v>
       </c>
-      <c r="C111" s="239" t="str">
+      <c r="C111" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$27,'III. Finanzberichte'!$L$27,'III. Finanzberichte'!$S$27,'III. Finanzberichte'!$Z$27,'III. Finanzberichte'!$AG$27,'III. Finanzberichte'!$AN$27,'III. Finanzberichte'!$AU$27,'III. Finanzberichte'!$BB$27,'III. Finanzberichte'!$BI$27,'III. Finanzberichte'!$BP$27,'III. Finanzberichte'!$BW$27,'III. Finanzberichte'!$CD$27,'III. Finanzberichte'!$CK$27,'III. Finanzberichte'!$CR$27,'III. Finanzberichte'!$CY$27,'III. Finanzberichte'!$DF$27,'III. Finanzberichte'!$DM$27,'III. Finanzberichte'!$DT$27),2),0)</f>
       </c>
-      <c r="D111" s="239" t="str">
+      <c r="D111" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Audit_LW,2),0)</f>
       </c>
-      <c r="E111" s="201" t="str">
+      <c r="E111" s="202" t="str">
         <f>=ROUND(IFERROR($C$111-$D$111,0),2)</f>
       </c>
       <c r="F111" s="258" t="str">
         <f>=ROUND(IFERROR(($C$111/$D$111)-1,0),4)</f>
       </c>
-      <c r="G111" s="217" t="str">
+      <c r="G111" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$27,'III. Finanzberichte'!$M$27,'III. Finanzberichte'!$T$27,'III. Finanzberichte'!$AA$27,'III. Finanzberichte'!$AH$27,'III. Finanzberichte'!$AO$27,'III. Finanzberichte'!$AV$27,'III. Finanzberichte'!$BC$27,'III. Finanzberichte'!$BJ$27,'III. Finanzberichte'!$BQ$27,'III. Finanzberichte'!$BX$27,'III. Finanzberichte'!$CE$27,'III. Finanzberichte'!$CL$27,'III. Finanzberichte'!$CS$27,'III. Finanzberichte'!$CZ$27,'III. Finanzberichte'!$DG$27,'III. Finanzberichte'!$DN$27,'III. Finanzberichte'!$DU$27),2),0)</f>
       </c>
-      <c r="H111" s="217" t="str">
+      <c r="H111" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Audit_EUR,2),0)</f>
       </c>
       <c r="I111" s="182" t="str">
@@ -23561,22 +23678,22 @@
       <c r="B112" s="266" t="s">
         <v>230</v>
       </c>
-      <c r="C112" s="239" t="str">
+      <c r="C112" s="240" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$28,'III. Finanzberichte'!$L$28,'III. Finanzberichte'!$S$28,'III. Finanzberichte'!$Z$28,'III. Finanzberichte'!$AG$28,'III. Finanzberichte'!$AN$28,'III. Finanzberichte'!$AU$28,'III. Finanzberichte'!$BB$28,'III. Finanzberichte'!$BI$28,'III. Finanzberichte'!$BP$28,'III. Finanzberichte'!$BW$28,'III. Finanzberichte'!$CD$28,'III. Finanzberichte'!$CK$28,'III. Finanzberichte'!$CR$28,'III. Finanzberichte'!$CY$28,'III. Finanzberichte'!$DF$28,'III. Finanzberichte'!$DM$28,'III. Finanzberichte'!$DT$28),2),0)</f>
       </c>
-      <c r="D112" s="239" t="str">
+      <c r="D112" s="240" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_LW,2),0)</f>
       </c>
-      <c r="E112" s="201" t="str">
+      <c r="E112" s="202" t="str">
         <f>=ROUND(IFERROR($C$112-$D$112,0),2)</f>
       </c>
       <c r="F112" s="258" t="str">
         <f>=ROUND(IFERROR(($C$112/$D$112)-1,0),4)</f>
       </c>
-      <c r="G112" s="217" t="str">
+      <c r="G112" s="218" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$28,'III. Finanzberichte'!$M$28,'III. Finanzberichte'!$T$28,'III. Finanzberichte'!$AA$28,'III. Finanzberichte'!$AH$28,'III. Finanzberichte'!$AO$28,'III. Finanzberichte'!$AV$28,'III. Finanzberichte'!$BC$28,'III. Finanzberichte'!$BJ$28,'III. Finanzberichte'!$BQ$28,'III. Finanzberichte'!$BX$28,'III. Finanzberichte'!$CE$28,'III. Finanzberichte'!$CL$28,'III. Finanzberichte'!$CS$28,'III. Finanzberichte'!$CZ$28,'III. Finanzberichte'!$DG$28,'III. Finanzberichte'!$DN$28,'III. Finanzberichte'!$DU$28),2),0)</f>
       </c>
-      <c r="H112" s="217" t="str">
+      <c r="H112" s="218" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
       <c r="I112" s="182" t="str">
@@ -23957,16 +24074,16 @@
         <v>247</v>
       </c>
       <c r="C1" s="351" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I1" s="351" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O1" s="351" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="U1" s="351" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="BA1">
         <v>1</v>

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -103,41 +103,41 @@
     <definedName name="FB_SaldoLC_18">'III. Finanzberichte'!$DR$31</definedName>
     <definedName name="FB_SaldoEUR_18">'III. Finanzberichte'!$DS$31</definedName>
     <definedName name="MA_Kurs_1">'IV. MA'!$C$8</definedName>
-    <definedName name="MA_ManBetrag_1">'IV. MA'!$D$24</definedName>
+    <definedName name="MA_ManBetrag_1">'IV. MA'!$D$27</definedName>
     <definedName name="MA_Kurs_2">'IV. MA'!$G$8</definedName>
-    <definedName name="MA_ManBetrag_2">'IV. MA'!$H$24</definedName>
+    <definedName name="MA_ManBetrag_2">'IV. MA'!$H$27</definedName>
     <definedName name="MA_Kurs_3">'IV. MA'!$K$8</definedName>
-    <definedName name="MA_ManBetrag_3">'IV. MA'!$L$24</definedName>
+    <definedName name="MA_ManBetrag_3">'IV. MA'!$L$27</definedName>
     <definedName name="MA_Kurs_4">'IV. MA'!$O$8</definedName>
-    <definedName name="MA_ManBetrag_4">'IV. MA'!$P$24</definedName>
+    <definedName name="MA_ManBetrag_4">'IV. MA'!$P$27</definedName>
     <definedName name="MA_Kurs_5">'IV. MA'!$S$8</definedName>
-    <definedName name="MA_ManBetrag_5">'IV. MA'!$T$24</definedName>
+    <definedName name="MA_ManBetrag_5">'IV. MA'!$T$27</definedName>
     <definedName name="MA_Kurs_6">'IV. MA'!$W$8</definedName>
-    <definedName name="MA_ManBetrag_6">'IV. MA'!$X$24</definedName>
+    <definedName name="MA_ManBetrag_6">'IV. MA'!$X$27</definedName>
     <definedName name="MA_Kurs_7">'IV. MA'!$AA$8</definedName>
-    <definedName name="MA_ManBetrag_7">'IV. MA'!$AB$24</definedName>
+    <definedName name="MA_ManBetrag_7">'IV. MA'!$AB$27</definedName>
     <definedName name="MA_Kurs_8">'IV. MA'!$AE$8</definedName>
-    <definedName name="MA_ManBetrag_8">'IV. MA'!$AF$24</definedName>
+    <definedName name="MA_ManBetrag_8">'IV. MA'!$AF$27</definedName>
     <definedName name="MA_Kurs_9">'IV. MA'!$AI$8</definedName>
-    <definedName name="MA_ManBetrag_9">'IV. MA'!$AJ$24</definedName>
+    <definedName name="MA_ManBetrag_9">'IV. MA'!$AJ$27</definedName>
     <definedName name="MA_Kurs_10">'IV. MA'!$AM$8</definedName>
-    <definedName name="MA_ManBetrag_10">'IV. MA'!$AN$24</definedName>
+    <definedName name="MA_ManBetrag_10">'IV. MA'!$AN$27</definedName>
     <definedName name="MA_Kurs_11">'IV. MA'!$AQ$8</definedName>
-    <definedName name="MA_ManBetrag_11">'IV. MA'!$AR$24</definedName>
+    <definedName name="MA_ManBetrag_11">'IV. MA'!$AR$27</definedName>
     <definedName name="MA_Kurs_12">'IV. MA'!$AU$8</definedName>
-    <definedName name="MA_ManBetrag_12">'IV. MA'!$AV$24</definedName>
+    <definedName name="MA_ManBetrag_12">'IV. MA'!$AV$27</definedName>
     <definedName name="MA_Kurs_13">'IV. MA'!$AY$8</definedName>
-    <definedName name="MA_ManBetrag_13">'IV. MA'!$AZ$24</definedName>
+    <definedName name="MA_ManBetrag_13">'IV. MA'!$AZ$27</definedName>
     <definedName name="MA_Kurs_14">'IV. MA'!$BC$8</definedName>
-    <definedName name="MA_ManBetrag_14">'IV. MA'!$BD$24</definedName>
+    <definedName name="MA_ManBetrag_14">'IV. MA'!$BD$27</definedName>
     <definedName name="MA_Kurs_15">'IV. MA'!$BG$8</definedName>
-    <definedName name="MA_ManBetrag_15">'IV. MA'!$BH$24</definedName>
+    <definedName name="MA_ManBetrag_15">'IV. MA'!$BH$27</definedName>
     <definedName name="MA_Kurs_16">'IV. MA'!$BK$8</definedName>
-    <definedName name="MA_ManBetrag_16">'IV. MA'!$BL$24</definedName>
+    <definedName name="MA_ManBetrag_16">'IV. MA'!$BL$27</definedName>
     <definedName name="MA_Kurs_17">'IV. MA'!$BO$8</definedName>
-    <definedName name="MA_ManBetrag_17">'IV. MA'!$BP$24</definedName>
+    <definedName name="MA_ManBetrag_17">'IV. MA'!$BP$27</definedName>
     <definedName name="MA_Kurs_18">'IV. MA'!$BS$8</definedName>
-    <definedName name="MA_ManBetrag_18">'IV. MA'!$BT$24</definedName>
+    <definedName name="MA_ManBetrag_18">'IV. MA'!$BT$27</definedName>
     <definedName name="FB_Auswahl_Liste">OFFSET('Daten'!$BP$1,0,0,COUNTA('Daten'!$BP:$BP),1)</definedName>
     <definedName name="MA_Auswahl_Liste">OFFSET('Daten'!$BN$1,0,0,COUNTA('Daten'!$BN:$BN),1)</definedName>
   </definedNames>
@@ -1172,10 +1172,10 @@
     <t>abzueglich Saldo Vorprojekt:</t>
   </si>
   <si>
-    <t>Manueller Betrag:</t>
-  </si>
-  <si>
     <t>KMW-Mittel Anforderung:</t>
+  </si>
+  <si>
+    <t>Manueller Betrag (EUR):</t>
   </si>
   <si>
     <t>abzueglich Saldo Vorperiode (FB):</t>
@@ -2827,161 +2827,161 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="10" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="10" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="52" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="12" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="8" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="8" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="52" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="12" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="12" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="10" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="10" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="52" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="12" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="8" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="52" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="12" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="12" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -21056,354 +21056,372 @@
         <f>=IFERROR(ROUND($BS$23/$BS$8,2),0)</f>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="s">
+    <row r="25">
+      <c r="B25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="C24" s="189"/>
-      <c r="D24" s="25"/>
-      <c r="F24" t="s">
+      <c r="C25" s="190" t="str">
+        <f>=IFERROR(ROUND($C$18-$C$21-$C$22-$C$23,2),0)</f>
+      </c>
+      <c r="D25" s="191" t="str">
+        <f>=IFERROR(ROUND($D$18-$D$21-$D$22-$D$23,2),0)</f>
+      </c>
+      <c r="F25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="G24" s="189"/>
-      <c r="H24" s="25"/>
-      <c r="J24" t="s">
+      <c r="G25" s="190" t="str">
+        <f>=IFERROR(ROUND($G$18-$G$21-$G$22-$G$23,2),0)</f>
+      </c>
+      <c r="H25" s="191" t="str">
+        <f>=IFERROR(ROUND($H$18-$H$21-$H$22-$H$23,2),0)</f>
+      </c>
+      <c r="J25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="K24" s="189"/>
-      <c r="L24" s="25"/>
-      <c r="N24" t="s">
+      <c r="K25" s="190" t="str">
+        <f>=IFERROR(ROUND($K$18-$K$21-$K$22-$K$23,2),0)</f>
+      </c>
+      <c r="L25" s="191" t="str">
+        <f>=IFERROR(ROUND($L$18-$L$21-$L$22-$L$23,2),0)</f>
+      </c>
+      <c r="N25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="O24" s="189"/>
-      <c r="P24" s="25"/>
-      <c r="R24" t="s">
+      <c r="O25" s="190" t="str">
+        <f>=IFERROR(ROUND($O$18-$O$21-$O$22-$O$23,2),0)</f>
+      </c>
+      <c r="P25" s="191" t="str">
+        <f>=IFERROR(ROUND($P$18-$P$21-$P$22-$P$23,2),0)</f>
+      </c>
+      <c r="R25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="S24" s="189"/>
-      <c r="T24" s="25"/>
-      <c r="V24" t="s">
+      <c r="S25" s="190" t="str">
+        <f>=IFERROR(ROUND($S$18-$S$21-$S$22-$S$23,2),0)</f>
+      </c>
+      <c r="T25" s="191" t="str">
+        <f>=IFERROR(ROUND($T$18-$T$21-$T$22-$T$23,2),0)</f>
+      </c>
+      <c r="V25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="W24" s="189"/>
-      <c r="X24" s="25"/>
-      <c r="Z24" t="s">
+      <c r="W25" s="190" t="str">
+        <f>=IFERROR(ROUND($W$18-$W$21-$W$22-$W$23,2),0)</f>
+      </c>
+      <c r="X25" s="191" t="str">
+        <f>=IFERROR(ROUND($X$18-$X$21-$X$22-$X$23,2),0)</f>
+      </c>
+      <c r="Z25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="AA24" s="189"/>
-      <c r="AB24" s="25"/>
-      <c r="AD24" t="s">
+      <c r="AA25" s="190" t="str">
+        <f>=IFERROR(ROUND($AA$18-$AA$21-$AA$22-$AA$23,2),0)</f>
+      </c>
+      <c r="AB25" s="191" t="str">
+        <f>=IFERROR(ROUND($AB$18-$AB$21-$AB$22-$AB$23,2),0)</f>
+      </c>
+      <c r="AD25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="AE24" s="189"/>
-      <c r="AF24" s="25"/>
-      <c r="AH24" t="s">
+      <c r="AE25" s="190" t="str">
+        <f>=IFERROR(ROUND($AE$18-$AE$21-$AE$22-$AE$23,2),0)</f>
+      </c>
+      <c r="AF25" s="191" t="str">
+        <f>=IFERROR(ROUND($AF$18-$AF$21-$AF$22-$AF$23,2),0)</f>
+      </c>
+      <c r="AH25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="AI24" s="189"/>
-      <c r="AJ24" s="25"/>
-      <c r="AL24" t="s">
+      <c r="AI25" s="190" t="str">
+        <f>=IFERROR(ROUND($AI$18-$AI$21-$AI$22-$AI$23,2),0)</f>
+      </c>
+      <c r="AJ25" s="191" t="str">
+        <f>=IFERROR(ROUND($AJ$18-$AJ$21-$AJ$22-$AJ$23,2),0)</f>
+      </c>
+      <c r="AL25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="AM24" s="189"/>
-      <c r="AN24" s="25"/>
-      <c r="AP24" t="s">
+      <c r="AM25" s="190" t="str">
+        <f>=IFERROR(ROUND($AM$18-$AM$21-$AM$22-$AM$23,2),0)</f>
+      </c>
+      <c r="AN25" s="191" t="str">
+        <f>=IFERROR(ROUND($AN$18-$AN$21-$AN$22-$AN$23,2),0)</f>
+      </c>
+      <c r="AP25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="AQ24" s="189"/>
-      <c r="AR24" s="25"/>
-      <c r="AT24" t="s">
+      <c r="AQ25" s="190" t="str">
+        <f>=IFERROR(ROUND($AQ$18-$AQ$21-$AQ$22-$AQ$23,2),0)</f>
+      </c>
+      <c r="AR25" s="191" t="str">
+        <f>=IFERROR(ROUND($AR$18-$AR$21-$AR$22-$AR$23,2),0)</f>
+      </c>
+      <c r="AT25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="AU24" s="189"/>
-      <c r="AV24" s="25"/>
-      <c r="AX24" t="s">
+      <c r="AU25" s="190" t="str">
+        <f>=IFERROR(ROUND($AU$18-$AU$21-$AU$22-$AU$23,2),0)</f>
+      </c>
+      <c r="AV25" s="191" t="str">
+        <f>=IFERROR(ROUND($AV$18-$AV$21-$AV$22-$AV$23,2),0)</f>
+      </c>
+      <c r="AX25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="AY24" s="189"/>
-      <c r="AZ24" s="25"/>
-      <c r="BB24" t="s">
+      <c r="AY25" s="190" t="str">
+        <f>=IFERROR(ROUND($AY$18-$AY$21-$AY$22-$AY$23,2),0)</f>
+      </c>
+      <c r="AZ25" s="191" t="str">
+        <f>=IFERROR(ROUND($AZ$18-$AZ$21-$AZ$22-$AZ$23,2),0)</f>
+      </c>
+      <c r="BB25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="BC24" s="189"/>
-      <c r="BD24" s="25"/>
-      <c r="BF24" t="s">
+      <c r="BC25" s="190" t="str">
+        <f>=IFERROR(ROUND($BC$18-$BC$21-$BC$22-$BC$23,2),0)</f>
+      </c>
+      <c r="BD25" s="191" t="str">
+        <f>=IFERROR(ROUND($BD$18-$BD$21-$BD$22-$BD$23,2),0)</f>
+      </c>
+      <c r="BF25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="BG24" s="189"/>
-      <c r="BH24" s="25"/>
-      <c r="BJ24" t="s">
+      <c r="BG25" s="190" t="str">
+        <f>=IFERROR(ROUND($BG$18-$BG$21-$BG$22-$BG$23,2),0)</f>
+      </c>
+      <c r="BH25" s="191" t="str">
+        <f>=IFERROR(ROUND($BH$18-$BH$21-$BH$22-$BH$23,2),0)</f>
+      </c>
+      <c r="BJ25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="BK24" s="189"/>
-      <c r="BL24" s="25"/>
-      <c r="BN24" t="s">
+      <c r="BK25" s="190" t="str">
+        <f>=IFERROR(ROUND($BK$18-$BK$21-$BK$22-$BK$23,2),0)</f>
+      </c>
+      <c r="BL25" s="191" t="str">
+        <f>=IFERROR(ROUND($BL$18-$BL$21-$BL$22-$BL$23,2),0)</f>
+      </c>
+      <c r="BN25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="BO24" s="189"/>
-      <c r="BP24" s="25"/>
-      <c r="BR24" t="s">
+      <c r="BO25" s="190" t="str">
+        <f>=IFERROR(ROUND($BO$18-$BO$21-$BO$22-$BO$23,2),0)</f>
+      </c>
+      <c r="BP25" s="191" t="str">
+        <f>=IFERROR(ROUND($BP$18-$BP$21-$BP$22-$BP$23,2),0)</f>
+      </c>
+      <c r="BR25" s="189" t="s">
         <v>334</v>
       </c>
-      <c r="BS24" s="189"/>
-      <c r="BT24" s="25"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="190" t="s">
+      <c r="BS25" s="190" t="str">
+        <f>=IFERROR(ROUND($BS$18-$BS$21-$BS$22-$BS$23,2),0)</f>
+      </c>
+      <c r="BT25" s="191" t="str">
+        <f>=IFERROR(ROUND($BT$18-$BT$21-$BT$22-$BT$23,2),0)</f>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="C25" s="191" t="str">
-        <f>=IFERROR(ROUND($C$18-$C$21-$C$22-$C$23,2),0)</f>
-      </c>
-      <c r="D25" s="192" t="str">
-        <f>=IFERROR(ROUND($D$18-$D$21-$D$22-$D$23,2),0)</f>
-      </c>
-      <c r="F25" s="190" t="s">
+      <c r="C27" s="181"/>
+      <c r="D27" s="25"/>
+      <c r="F27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="G25" s="191" t="str">
-        <f>=IFERROR(ROUND($G$18-$G$21-$G$22-$G$23,2),0)</f>
-      </c>
-      <c r="H25" s="192" t="str">
-        <f>=IFERROR(ROUND($H$18-$H$21-$H$22-$H$23,2),0)</f>
-      </c>
-      <c r="J25" s="190" t="s">
+      <c r="G27" s="181"/>
+      <c r="H27" s="25"/>
+      <c r="J27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="K25" s="191" t="str">
-        <f>=IFERROR(ROUND($K$18-$K$21-$K$22-$K$23,2),0)</f>
-      </c>
-      <c r="L25" s="192" t="str">
-        <f>=IFERROR(ROUND($L$18-$L$21-$L$22-$L$23,2),0)</f>
-      </c>
-      <c r="N25" s="190" t="s">
+      <c r="K27" s="181"/>
+      <c r="L27" s="25"/>
+      <c r="N27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="O25" s="191" t="str">
-        <f>=IFERROR(ROUND($O$18-$O$21-$O$22-$O$23,2),0)</f>
-      </c>
-      <c r="P25" s="192" t="str">
-        <f>=IFERROR(ROUND($P$18-$P$21-$P$22-$P$23,2),0)</f>
-      </c>
-      <c r="R25" s="190" t="s">
+      <c r="O27" s="181"/>
+      <c r="P27" s="25"/>
+      <c r="R27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="S25" s="191" t="str">
-        <f>=IFERROR(ROUND($S$18-$S$21-$S$22-$S$23,2),0)</f>
-      </c>
-      <c r="T25" s="192" t="str">
-        <f>=IFERROR(ROUND($T$18-$T$21-$T$22-$T$23,2),0)</f>
-      </c>
-      <c r="V25" s="190" t="s">
+      <c r="S27" s="181"/>
+      <c r="T27" s="25"/>
+      <c r="V27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="W25" s="191" t="str">
-        <f>=IFERROR(ROUND($W$18-$W$21-$W$22-$W$23,2),0)</f>
-      </c>
-      <c r="X25" s="192" t="str">
-        <f>=IFERROR(ROUND($X$18-$X$21-$X$22-$X$23,2),0)</f>
-      </c>
-      <c r="Z25" s="190" t="s">
+      <c r="W27" s="181"/>
+      <c r="X27" s="25"/>
+      <c r="Z27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="AA25" s="191" t="str">
-        <f>=IFERROR(ROUND($AA$18-$AA$21-$AA$22-$AA$23,2),0)</f>
-      </c>
-      <c r="AB25" s="192" t="str">
-        <f>=IFERROR(ROUND($AB$18-$AB$21-$AB$22-$AB$23,2),0)</f>
-      </c>
-      <c r="AD25" s="190" t="s">
+      <c r="AA27" s="181"/>
+      <c r="AB27" s="25"/>
+      <c r="AD27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="AE25" s="191" t="str">
-        <f>=IFERROR(ROUND($AE$18-$AE$21-$AE$22-$AE$23,2),0)</f>
-      </c>
-      <c r="AF25" s="192" t="str">
-        <f>=IFERROR(ROUND($AF$18-$AF$21-$AF$22-$AF$23,2),0)</f>
-      </c>
-      <c r="AH25" s="190" t="s">
+      <c r="AE27" s="181"/>
+      <c r="AF27" s="25"/>
+      <c r="AH27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="AI25" s="191" t="str">
-        <f>=IFERROR(ROUND($AI$18-$AI$21-$AI$22-$AI$23,2),0)</f>
-      </c>
-      <c r="AJ25" s="192" t="str">
-        <f>=IFERROR(ROUND($AJ$18-$AJ$21-$AJ$22-$AJ$23,2),0)</f>
-      </c>
-      <c r="AL25" s="190" t="s">
+      <c r="AI27" s="181"/>
+      <c r="AJ27" s="25"/>
+      <c r="AL27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="AM25" s="191" t="str">
-        <f>=IFERROR(ROUND($AM$18-$AM$21-$AM$22-$AM$23,2),0)</f>
-      </c>
-      <c r="AN25" s="192" t="str">
-        <f>=IFERROR(ROUND($AN$18-$AN$21-$AN$22-$AN$23,2),0)</f>
-      </c>
-      <c r="AP25" s="190" t="s">
+      <c r="AM27" s="181"/>
+      <c r="AN27" s="25"/>
+      <c r="AP27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="AQ25" s="191" t="str">
-        <f>=IFERROR(ROUND($AQ$18-$AQ$21-$AQ$22-$AQ$23,2),0)</f>
-      </c>
-      <c r="AR25" s="192" t="str">
-        <f>=IFERROR(ROUND($AR$18-$AR$21-$AR$22-$AR$23,2),0)</f>
-      </c>
-      <c r="AT25" s="190" t="s">
+      <c r="AQ27" s="181"/>
+      <c r="AR27" s="25"/>
+      <c r="AT27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="AU25" s="191" t="str">
-        <f>=IFERROR(ROUND($AU$18-$AU$21-$AU$22-$AU$23,2),0)</f>
-      </c>
-      <c r="AV25" s="192" t="str">
-        <f>=IFERROR(ROUND($AV$18-$AV$21-$AV$22-$AV$23,2),0)</f>
-      </c>
-      <c r="AX25" s="190" t="s">
+      <c r="AU27" s="181"/>
+      <c r="AV27" s="25"/>
+      <c r="AX27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="AY25" s="191" t="str">
-        <f>=IFERROR(ROUND($AY$18-$AY$21-$AY$22-$AY$23,2),0)</f>
-      </c>
-      <c r="AZ25" s="192" t="str">
-        <f>=IFERROR(ROUND($AZ$18-$AZ$21-$AZ$22-$AZ$23,2),0)</f>
-      </c>
-      <c r="BB25" s="190" t="s">
+      <c r="AY27" s="181"/>
+      <c r="AZ27" s="25"/>
+      <c r="BB27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="BC25" s="191" t="str">
-        <f>=IFERROR(ROUND($BC$18-$BC$21-$BC$22-$BC$23,2),0)</f>
-      </c>
-      <c r="BD25" s="192" t="str">
-        <f>=IFERROR(ROUND($BD$18-$BD$21-$BD$22-$BD$23,2),0)</f>
-      </c>
-      <c r="BF25" s="190" t="s">
+      <c r="BC27" s="181"/>
+      <c r="BD27" s="25"/>
+      <c r="BF27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="BG25" s="191" t="str">
-        <f>=IFERROR(ROUND($BG$18-$BG$21-$BG$22-$BG$23,2),0)</f>
-      </c>
-      <c r="BH25" s="192" t="str">
-        <f>=IFERROR(ROUND($BH$18-$BH$21-$BH$22-$BH$23,2),0)</f>
-      </c>
-      <c r="BJ25" s="190" t="s">
+      <c r="BG27" s="181"/>
+      <c r="BH27" s="25"/>
+      <c r="BJ27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="BK25" s="191" t="str">
-        <f>=IFERROR(ROUND($BK$18-$BK$21-$BK$22-$BK$23,2),0)</f>
-      </c>
-      <c r="BL25" s="192" t="str">
-        <f>=IFERROR(ROUND($BL$18-$BL$21-$BL$22-$BL$23,2),0)</f>
-      </c>
-      <c r="BN25" s="190" t="s">
+      <c r="BK27" s="181"/>
+      <c r="BL27" s="25"/>
+      <c r="BN27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="BO25" s="191" t="str">
-        <f>=IFERROR(ROUND($BO$18-$BO$21-$BO$22-$BO$23,2),0)</f>
-      </c>
-      <c r="BP25" s="192" t="str">
-        <f>=IFERROR(ROUND($BP$18-$BP$21-$BP$22-$BP$23,2),0)</f>
-      </c>
-      <c r="BR25" s="190" t="s">
+      <c r="BO27" s="181"/>
+      <c r="BP27" s="25"/>
+      <c r="BR27" s="181" t="s">
         <v>335</v>
       </c>
-      <c r="BS25" s="191" t="str">
-        <f>=IFERROR(ROUND($BS$18-$BS$21-$BS$22-$BS$23,2),0)</f>
-      </c>
-      <c r="BT25" s="192" t="str">
-        <f>=IFERROR(ROUND($BT$18-$BT$21-$BT$22-$BT$23,2),0)</f>
-      </c>
+      <c r="BS27" s="181"/>
+      <c r="BT27" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="90">
+  <mergeCells count="108">
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
+    <mergeCell ref="F27:G27"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="K8:L8"/>
+    <mergeCell ref="J27:K27"/>
     <mergeCell ref="O4:P4"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="O6:P6"/>
     <mergeCell ref="O7:P7"/>
     <mergeCell ref="O8:P8"/>
+    <mergeCell ref="N27:O27"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="S5:T5"/>
     <mergeCell ref="S6:T6"/>
     <mergeCell ref="S7:T7"/>
     <mergeCell ref="S8:T8"/>
+    <mergeCell ref="R27:S27"/>
     <mergeCell ref="W4:X4"/>
     <mergeCell ref="W5:X5"/>
     <mergeCell ref="W6:X6"/>
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="W8:X8"/>
+    <mergeCell ref="V27:W27"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="AA5:AB5"/>
     <mergeCell ref="AA6:AB6"/>
     <mergeCell ref="AA7:AB7"/>
     <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="Z27:AA27"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AE5:AF5"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="AE7:AF7"/>
     <mergeCell ref="AE8:AF8"/>
+    <mergeCell ref="AD27:AE27"/>
     <mergeCell ref="AI4:AJ4"/>
     <mergeCell ref="AI5:AJ5"/>
     <mergeCell ref="AI6:AJ6"/>
     <mergeCell ref="AI7:AJ7"/>
     <mergeCell ref="AI8:AJ8"/>
+    <mergeCell ref="AH27:AI27"/>
     <mergeCell ref="AM4:AN4"/>
     <mergeCell ref="AM5:AN5"/>
     <mergeCell ref="AM6:AN6"/>
     <mergeCell ref="AM7:AN7"/>
     <mergeCell ref="AM8:AN8"/>
+    <mergeCell ref="AL27:AM27"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="AQ5:AR5"/>
     <mergeCell ref="AQ6:AR6"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AQ8:AR8"/>
+    <mergeCell ref="AP27:AQ27"/>
     <mergeCell ref="AU4:AV4"/>
     <mergeCell ref="AU5:AV5"/>
     <mergeCell ref="AU6:AV6"/>
     <mergeCell ref="AU7:AV7"/>
     <mergeCell ref="AU8:AV8"/>
+    <mergeCell ref="AT27:AU27"/>
     <mergeCell ref="AY4:AZ4"/>
     <mergeCell ref="AY5:AZ5"/>
     <mergeCell ref="AY6:AZ6"/>
     <mergeCell ref="AY7:AZ7"/>
     <mergeCell ref="AY8:AZ8"/>
+    <mergeCell ref="AX27:AY27"/>
     <mergeCell ref="BC4:BD4"/>
     <mergeCell ref="BC5:BD5"/>
     <mergeCell ref="BC6:BD6"/>
     <mergeCell ref="BC7:BD7"/>
     <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BB27:BC27"/>
     <mergeCell ref="BG4:BH4"/>
     <mergeCell ref="BG5:BH5"/>
     <mergeCell ref="BG6:BH6"/>
     <mergeCell ref="BG7:BH7"/>
     <mergeCell ref="BG8:BH8"/>
+    <mergeCell ref="BF27:BG27"/>
     <mergeCell ref="BK4:BL4"/>
     <mergeCell ref="BK5:BL5"/>
     <mergeCell ref="BK6:BL6"/>
     <mergeCell ref="BK7:BL7"/>
     <mergeCell ref="BK8:BL8"/>
+    <mergeCell ref="BJ27:BK27"/>
     <mergeCell ref="BO4:BP4"/>
     <mergeCell ref="BO5:BP5"/>
     <mergeCell ref="BO6:BP6"/>
     <mergeCell ref="BO7:BP7"/>
     <mergeCell ref="BO8:BP8"/>
+    <mergeCell ref="BN27:BO27"/>
     <mergeCell ref="BS4:BT4"/>
     <mergeCell ref="BS5:BT5"/>
     <mergeCell ref="BS6:BT6"/>
     <mergeCell ref="BS7:BT7"/>
     <mergeCell ref="BS8:BT8"/>
+    <mergeCell ref="BR27:BS27"/>
   </mergeCells>
   <dataValidations count="18">
     <dataValidation allowBlank="true" sqref="C4" type="list">
@@ -21502,64 +21520,64 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="true">
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="192" t="s">
         <v>337</v>
       </c>
-      <c r="C2" s="193"/>
-      <c r="D2" s="193"/>
-      <c r="E2" s="193"/>
-      <c r="F2" s="193"/>
-      <c r="G2" s="193"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="193"/>
-      <c r="J2" s="193"/>
+      <c r="C2" s="192"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="192"/>
+      <c r="F2" s="192"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
+      <c r="I2" s="192"/>
+      <c r="J2" s="192"/>
     </row>
     <row r="3" ht="18" customHeight="true">
-      <c r="B3" s="194" t="s">
+      <c r="B3" s="193" t="s">
         <v>338</v>
       </c>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
+      <c r="C3" s="193"/>
+      <c r="D3" s="193"/>
+      <c r="E3" s="193"/>
+      <c r="F3" s="193"/>
+      <c r="G3" s="193"/>
+      <c r="H3" s="193"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
     </row>
     <row r="5" ht="22" customHeight="true">
-      <c r="B5" s="195" t="s">
+      <c r="B5" s="194" t="s">
         <v>339</v>
       </c>
-      <c r="C5" s="195"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="195"/>
-      <c r="G5" s="195"/>
-      <c r="H5" s="195"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="195"/>
-      <c r="L5" s="203" t="str">
+      <c r="C5" s="194"/>
+      <c r="D5" s="194"/>
+      <c r="E5" s="194"/>
+      <c r="F5" s="194"/>
+      <c r="G5" s="194"/>
+      <c r="H5" s="194"/>
+      <c r="I5" s="194"/>
+      <c r="J5" s="194"/>
+      <c r="L5" s="202" t="str">
         <f>=IF(E11=0,"Aktuelle Mittelanforderung (keine gewählt)","Aktuelle Mittelanforderung – Periode "&amp;E10&amp;" (#"&amp;E11&amp;")")</f>
       </c>
-      <c r="M5" s="204"/>
-      <c r="N5" s="205"/>
+      <c r="M5" s="203"/>
+      <c r="N5" s="204"/>
       <c r="AD5" t="str">
         <f>=IFERROR(SUMPRODUCT('Daten'!$BA$1:$BA$18,('Daten'!$BB$1:$BB$18=E10)*('Daten'!$BD$1:$BD$18=E11)),0)</f>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="196" t="s">
+      <c r="B6" s="195" t="s">
         <v>340</v>
       </c>
-      <c r="C6" s="196"/>
-      <c r="D6" s="196"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="196"/>
-      <c r="H6" s="196"/>
-      <c r="I6" s="196"/>
-      <c r="J6" s="196"/>
+      <c r="C6" s="195"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="195"/>
+      <c r="I6" s="195"/>
+      <c r="J6" s="195"/>
       <c r="L6" s="315" t="s">
         <v>288</v>
       </c>
@@ -21578,13 +21596,13 @@
       <c r="N7" s="317"/>
     </row>
     <row r="8" ht="22" customHeight="true">
-      <c r="C8" s="203" t="s">
+      <c r="C8" s="202" t="s">
         <v>341</v>
       </c>
-      <c r="D8" s="204"/>
-      <c r="E8" s="204"/>
-      <c r="F8" s="204"/>
-      <c r="G8" s="205"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
+      <c r="G8" s="204"/>
       <c r="L8" s="315" t="s">
         <v>290</v>
       </c>
@@ -21594,15 +21612,15 @@
       <c r="N8" s="317"/>
     </row>
     <row r="9">
-      <c r="C9" s="206" t="s">
+      <c r="C9" s="205" t="s">
         <v>342</v>
       </c>
-      <c r="D9" s="198"/>
+      <c r="D9" s="197"/>
       <c r="E9" s="63" t="s">
         <v>343</v>
       </c>
       <c r="F9" s="63"/>
-      <c r="G9" s="207"/>
+      <c r="G9" s="206"/>
       <c r="L9" s="315" t="s">
         <v>291</v>
       </c>
@@ -21612,16 +21630,16 @@
       <c r="N9" s="318"/>
     </row>
     <row r="10">
-      <c r="C10" s="206" t="s">
+      <c r="C10" s="205" t="s">
         <v>344</v>
       </c>
-      <c r="D10" s="198"/>
-      <c r="E10" s="199" t="str">
+      <c r="D10" s="197"/>
+      <c r="E10" s="198" t="str">
         <f>=E81+1</f>
         <v>0</v>
       </c>
-      <c r="F10" s="199"/>
-      <c r="G10" s="208"/>
+      <c r="F10" s="198"/>
+      <c r="G10" s="207"/>
       <c r="L10" s="315" t="s">
         <v>326</v>
       </c>
@@ -21631,26 +21649,26 @@
       <c r="N10" s="319"/>
     </row>
     <row r="11">
-      <c r="C11" s="206" t="s">
+      <c r="C11" s="205" t="s">
         <v>345</v>
       </c>
-      <c r="D11" s="198"/>
-      <c r="E11" s="199" t="str">
+      <c r="D11" s="197"/>
+      <c r="E11" s="198" t="str">
         <f>=IF(E9="Neuste MA",IFERROR(SUMPRODUCT(MAX(('Daten'!$BB$1:$BB$18=E10)*('Daten'!$BC$1:$BC$18=1)*'Daten'!$BD$1:$BD$18)),0),IFERROR(VALUE(MID(E9,FIND("(#",E9)+2,FIND(")",E9)-FIND("(#",E9)-2)),0))</f>
       </c>
-      <c r="F11" s="199"/>
-      <c r="G11" s="209"/>
+      <c r="F11" s="198"/>
+      <c r="G11" s="208"/>
       <c r="L11" s="47"/>
       <c r="N11" s="48"/>
     </row>
     <row r="12">
-      <c r="C12" s="210" t="s">
+      <c r="C12" s="209" t="s">
         <v>346</v>
       </c>
-      <c r="D12" s="200"/>
-      <c r="E12" s="200"/>
-      <c r="F12" s="200"/>
-      <c r="G12" s="211"/>
+      <c r="D12" s="199"/>
+      <c r="E12" s="199"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="210"/>
       <c r="L12" s="320" t="s">
         <v>202</v>
       </c>
@@ -21662,15 +21680,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="212" t="str">
+      <c r="C13" s="211" t="str">
         <f>=IF(1&lt;=E11,"Periode "&amp;E10&amp;" (#1)","")</f>
       </c>
-      <c r="D13" s="201"/>
-      <c r="E13" s="202" t="str">
+      <c r="D13" s="200"/>
+      <c r="E13" s="201" t="str">
         <f>=IF(1&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,1),0),"")</f>
       </c>
-      <c r="F13" s="202"/>
-      <c r="G13" s="213" t="str">
+      <c r="F13" s="201"/>
+      <c r="G13" s="212" t="str">
         <f>=IF(1&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,1),0),"")</f>
       </c>
       <c r="L13" s="143" t="s">
@@ -21684,15 +21702,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="212" t="str">
+      <c r="C14" s="211" t="str">
         <f>=IF(2&lt;=E11,"Periode "&amp;E10&amp;" (#2)","")</f>
       </c>
-      <c r="D14" s="201"/>
-      <c r="E14" s="202" t="str">
+      <c r="D14" s="200"/>
+      <c r="E14" s="201" t="str">
         <f>=IF(2&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,2),0),"")</f>
       </c>
-      <c r="F14" s="202"/>
-      <c r="G14" s="213" t="str">
+      <c r="F14" s="201"/>
+      <c r="G14" s="212" t="str">
         <f>=IF(2&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,2),0),"")</f>
       </c>
       <c r="L14" s="143" t="s">
@@ -21706,15 +21724,15 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="212" t="str">
+      <c r="C15" s="211" t="str">
         <f>=IF(3&lt;=E11,"Periode "&amp;E10&amp;" (#3)","")</f>
       </c>
-      <c r="D15" s="201"/>
-      <c r="E15" s="202" t="str">
+      <c r="D15" s="200"/>
+      <c r="E15" s="201" t="str">
         <f>=IF(3&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,3),0),"")</f>
       </c>
-      <c r="F15" s="202"/>
-      <c r="G15" s="213" t="str">
+      <c r="F15" s="201"/>
+      <c r="G15" s="212" t="str">
         <f>=IF(3&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,3),0),"")</f>
       </c>
       <c r="L15" s="143" t="s">
@@ -21728,15 +21746,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="212" t="str">
+      <c r="C16" s="211" t="str">
         <f>=IF(4&lt;=E11,"Periode "&amp;E10&amp;" (#4)","")</f>
       </c>
-      <c r="D16" s="201"/>
-      <c r="E16" s="202" t="str">
+      <c r="D16" s="200"/>
+      <c r="E16" s="201" t="str">
         <f>=IF(4&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,4),0),"")</f>
       </c>
-      <c r="F16" s="202"/>
-      <c r="G16" s="213" t="str">
+      <c r="F16" s="201"/>
+      <c r="G16" s="212" t="str">
         <f>=IF(4&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,4),0),"")</f>
       </c>
       <c r="L16" s="143" t="s">
@@ -21750,15 +21768,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="212" t="str">
+      <c r="C17" s="211" t="str">
         <f>=IF(5&lt;=E11,"Periode "&amp;E10&amp;" (#5)","")</f>
       </c>
-      <c r="D17" s="201"/>
-      <c r="E17" s="202" t="str">
+      <c r="D17" s="200"/>
+      <c r="E17" s="201" t="str">
         <f>=IF(5&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,5),0),"")</f>
       </c>
-      <c r="F17" s="202"/>
-      <c r="G17" s="213" t="str">
+      <c r="F17" s="201"/>
+      <c r="G17" s="212" t="str">
         <f>=IF(5&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,5),0),"")</f>
       </c>
       <c r="L17" s="143" t="s">
@@ -21772,15 +21790,15 @@
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="214" t="str">
+      <c r="C18" s="213" t="str">
         <f>=IF(6&lt;=E11,"Periode "&amp;E10&amp;" (#6)","")</f>
       </c>
-      <c r="D18" s="215"/>
-      <c r="E18" s="216" t="str">
+      <c r="D18" s="214"/>
+      <c r="E18" s="215" t="str">
         <f>=IF(6&lt;=E11,IFERROR(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,6),0),"")</f>
       </c>
-      <c r="F18" s="216"/>
-      <c r="G18" s="217" t="str">
+      <c r="F18" s="215"/>
+      <c r="G18" s="216" t="str">
         <f>=IF(6&lt;=E11,IFERROR(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,6),0),"")</f>
       </c>
       <c r="L18" s="143" t="s">
@@ -21833,43 +21851,43 @@
       <c r="M21" s="243" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$18,'IV. MA'!$G$18,'IV. MA'!$K$18,'IV. MA'!$O$18,'IV. MA'!$S$18,'IV. MA'!$W$18,'IV. MA'!$AA$18,'IV. MA'!$AE$18,'IV. MA'!$AI$18,'IV. MA'!$AM$18,'IV. MA'!$AQ$18,'IV. MA'!$AU$18,'IV. MA'!$AY$18,'IV. MA'!$BC$18,'IV. MA'!$BG$18,'IV. MA'!$BK$18,'IV. MA'!$BO$18,'IV. MA'!$BS$18),"")</f>
       </c>
-      <c r="N21" s="236" t="str">
+      <c r="N21" s="235" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$D$18,'IV. MA'!$H$18,'IV. MA'!$L$18,'IV. MA'!$P$18,'IV. MA'!$T$18,'IV. MA'!$X$18,'IV. MA'!$AB$18,'IV. MA'!$AF$18,'IV. MA'!$AJ$18,'IV. MA'!$AN$18,'IV. MA'!$AR$18,'IV. MA'!$AV$18,'IV. MA'!$AZ$18,'IV. MA'!$BD$18,'IV. MA'!$BH$18,'IV. MA'!$BL$18,'IV. MA'!$BP$18,'IV. MA'!$BT$18),"")</f>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="224" t="s">
+      <c r="B22" s="223" t="s">
         <v>348</v>
       </c>
-      <c r="C22" s="225"/>
-      <c r="D22" s="226" t="str">
+      <c r="C22" s="224"/>
+      <c r="D22" s="225" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
-      <c r="F22" s="231" t="s">
+      <c r="F22" s="230" t="s">
         <v>352</v>
       </c>
-      <c r="G22" s="232"/>
-      <c r="H22" s="232"/>
-      <c r="I22" s="233"/>
+      <c r="G22" s="231"/>
+      <c r="H22" s="231"/>
+      <c r="I22" s="232"/>
       <c r="L22" s="47"/>
       <c r="N22" s="48"/>
     </row>
     <row r="23">
-      <c r="B23" s="206" t="s">
+      <c r="B23" s="205" t="s">
         <v>349</v>
       </c>
-      <c r="C23" s="198"/>
-      <c r="D23" s="227" t="str">
+      <c r="C23" s="197"/>
+      <c r="D23" s="226" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
-      <c r="F23" s="234" t="s">
+      <c r="F23" s="233" t="s">
         <v>353</v>
       </c>
-      <c r="G23" s="198" t="s">
+      <c r="G23" s="197" t="s">
         <v>354</v>
       </c>
-      <c r="H23" s="198"/>
-      <c r="I23" s="235" t="str">
+      <c r="H23" s="197"/>
+      <c r="I23" s="234" t="str">
         <f>=IFERROR(ROUND(Saldovortrag_EUR,2),0)</f>
       </c>
       <c r="L23" s="143" t="s">
@@ -21883,21 +21901,21 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="206" t="str">
+      <c r="B24" s="205" t="str">
         <f>=IF(Reserve_Freigabe="Ja","Operatives Budget (Reserve freigegeben)","Operatives Budget (abzgl. Reserve)")</f>
       </c>
-      <c r="C24" s="198"/>
-      <c r="D24" s="227" t="str">
+      <c r="C24" s="197"/>
+      <c r="D24" s="226" t="str">
         <f>=IF(Reserve_Freigabe="Ja",ROUND($D$22,2),ROUND($D$22-$D$23,2))</f>
       </c>
-      <c r="F24" s="234" t="s">
+      <c r="F24" s="233" t="s">
         <v>353</v>
       </c>
-      <c r="G24" s="198" t="s">
+      <c r="G24" s="197" t="s">
         <v>355</v>
       </c>
-      <c r="H24" s="198"/>
-      <c r="I24" s="235" t="str">
+      <c r="H24" s="197"/>
+      <c r="I24" s="234" t="str">
         <f>=I87</f>
         <v>0</v>
       </c>
@@ -21912,21 +21930,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="206" t="s">
+      <c r="B25" s="205" t="s">
         <v>350</v>
       </c>
-      <c r="C25" s="198"/>
-      <c r="D25" s="227" t="str">
+      <c r="C25" s="197"/>
+      <c r="D25" s="226" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblKMWMittel[Betrag]),2),0)</f>
       </c>
-      <c r="F25" s="234" t="s">
+      <c r="F25" s="233" t="s">
         <v>353</v>
       </c>
-      <c r="G25" s="198" t="s">
+      <c r="G25" s="197" t="s">
         <v>356</v>
       </c>
-      <c r="H25" s="198"/>
-      <c r="I25" s="235" t="str">
+      <c r="H25" s="197"/>
+      <c r="I25" s="234" t="str">
         <f>=ROUND(MAX(0,MAX(0,(SUM($G$96:$G$99)-$G$98)+SUMIFS('Daten'!$BH$1:$BH$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,"&lt;="&amp;E11,'Daten'!$BD$1:$BD$18,"&gt;=1")-(SUM($H$96:$H$99)-$H$98))-I87),2)</f>
         <v>0</v>
       </c>
@@ -21941,19 +21959,19 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="228" t="s">
+      <c r="B26" s="227" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="229"/>
-      <c r="D26" s="230" t="str">
+      <c r="C26" s="228"/>
+      <c r="D26" s="229" t="str">
         <f>=ROUND($D$24-$D$25,2)</f>
       </c>
       <c r="F26" s="47"/>
-      <c r="G26" s="219" t="s">
+      <c r="G26" s="218" t="s">
         <v>357</v>
       </c>
-      <c r="H26" s="219"/>
-      <c r="I26" s="236" t="str">
+      <c r="H26" s="218"/>
+      <c r="I26" s="235" t="str">
         <f>=ROUND(IF($F$23="Abzug",MAX(0,$I$23),0)+IF($F$24="Abzug",MAX(0,$I$24),0)+IF($F$25="Abzug",MAX(0,$I$25),0),2)</f>
       </c>
       <c r="L26" s="143" t="str">
@@ -21967,12 +21985,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="F27" s="237"/>
-      <c r="G27" s="229" t="s">
+      <c r="F27" s="236"/>
+      <c r="G27" s="228" t="s">
         <v>358</v>
       </c>
-      <c r="H27" s="229"/>
-      <c r="I27" s="230" t="str">
+      <c r="H27" s="228"/>
+      <c r="I27" s="229" t="str">
         <f>=ROUND($D$26-$I$26,2)</f>
       </c>
       <c r="L27" s="47"/>
@@ -21980,7 +21998,7 @@
     </row>
     <row r="28">
       <c r="L28" s="323" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M28" s="324" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$25,'IV. MA'!$G$25,'IV. MA'!$K$25,'IV. MA'!$O$25,'IV. MA'!$S$25,'IV. MA'!$W$25,'IV. MA'!$AA$25,'IV. MA'!$AE$25,'IV. MA'!$AI$25,'IV. MA'!$AM$25,'IV. MA'!$AQ$25,'IV. MA'!$AU$25,'IV. MA'!$AY$25,'IV. MA'!$BC$25,'IV. MA'!$BG$25,'IV. MA'!$BK$25,'IV. MA'!$BO$25,'IV. MA'!$BS$25),"")</f>
@@ -21990,70 +22008,70 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="224" t="s">
+      <c r="B29" s="223" t="s">
         <v>359</v>
       </c>
-      <c r="C29" s="225"/>
-      <c r="D29" s="226" t="str">
+      <c r="C29" s="224"/>
+      <c r="D29" s="225" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,E11),2),0)</f>
       </c>
-      <c r="F29" s="224" t="s">
+      <c r="F29" s="223" t="s">
         <v>359</v>
       </c>
-      <c r="G29" s="225"/>
-      <c r="H29" s="225"/>
-      <c r="I29" s="226" t="str">
+      <c r="G29" s="224"/>
+      <c r="H29" s="224"/>
+      <c r="I29" s="225" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,E11),2),0)</f>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="228" t="s">
+      <c r="B30" s="227" t="s">
         <v>360</v>
       </c>
-      <c r="C30" s="229"/>
-      <c r="D30" s="230" t="str">
+      <c r="C30" s="228"/>
+      <c r="D30" s="229" t="str">
         <f>=ROUND($D$26-MAX(0,$D$29),2)</f>
       </c>
-      <c r="F30" s="228" t="s">
+      <c r="F30" s="227" t="s">
         <v>361</v>
       </c>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="230" t="str">
+      <c r="G30" s="228"/>
+      <c r="H30" s="228"/>
+      <c r="I30" s="229" t="str">
         <f>=ROUND($I$27-MAX(0,$I$29),2)</f>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="224" t="s">
+      <c r="B32" s="223" t="s">
         <v>362</v>
       </c>
-      <c r="C32" s="225"/>
-      <c r="D32" s="238" t="str">
+      <c r="C32" s="224"/>
+      <c r="D32" s="237" t="str">
         <f>=IFERROR(CHOOSE(E10,MA_ManBetrag_1,MA_ManBetrag_2,MA_ManBetrag_3,MA_ManBetrag_4,MA_ManBetrag_5,MA_ManBetrag_6,MA_ManBetrag_7,MA_ManBetrag_8,MA_ManBetrag_9,MA_ManBetrag_10,MA_ManBetrag_11,MA_ManBetrag_12,MA_ManBetrag_13,MA_ManBetrag_14,MA_ManBetrag_15,MA_ManBetrag_16,MA_ManBetrag_17,MA_ManBetrag_18),0)</f>
       </c>
-      <c r="F32" s="224" t="s">
+      <c r="F32" s="223" t="s">
         <v>362</v>
       </c>
-      <c r="G32" s="225"/>
-      <c r="H32" s="225"/>
-      <c r="I32" s="238" t="str">
+      <c r="G32" s="224"/>
+      <c r="H32" s="224"/>
+      <c r="I32" s="237" t="str">
         <f>=IFERROR(CHOOSE(E10,MA_ManBetrag_1,MA_ManBetrag_2,MA_ManBetrag_3,MA_ManBetrag_4,MA_ManBetrag_5,MA_ManBetrag_6,MA_ManBetrag_7,MA_ManBetrag_8,MA_ManBetrag_9,MA_ManBetrag_10,MA_ManBetrag_11,MA_ManBetrag_12,MA_ManBetrag_13,MA_ManBetrag_14,MA_ManBetrag_15,MA_ManBetrag_16,MA_ManBetrag_17,MA_ManBetrag_18),0)</f>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="228" t="s">
+      <c r="B33" s="227" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="229"/>
-      <c r="D33" s="230" t="str">
+      <c r="C33" s="228"/>
+      <c r="D33" s="229" t="str">
         <f>=ROUND($D$26-MAX(0,$D$29)-MAX(0,$D$32),2)</f>
       </c>
-      <c r="F33" s="228" t="s">
+      <c r="F33" s="227" t="s">
         <v>361</v>
       </c>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="230" t="str">
+      <c r="G33" s="228"/>
+      <c r="H33" s="228"/>
+      <c r="I33" s="229" t="str">
         <f>=ROUND($I$27-MAX(0,$I$29)-MAX(0,$I$32),2)</f>
       </c>
     </row>
@@ -22085,61 +22103,61 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="206" t="s">
+      <c r="B39" s="205" t="s">
         <v>367</v>
       </c>
-      <c r="C39" s="240" t="str">
+      <c r="C39" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,"&lt;="&amp;E11,'Daten'!$BD$1:$BD$18,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D39" s="189"/>
-      <c r="E39" s="227" t="str">
+      <c r="D39" s="240"/>
+      <c r="E39" s="226" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BG$1:$BG$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,"&lt;="&amp;E11,'Daten'!$BD$1:$BD$18,"&gt;=1"),2),0)</f>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="206" t="s">
+      <c r="B40" s="205" t="s">
         <v>368</v>
       </c>
-      <c r="C40" s="240" t="str">
+      <c r="C40" s="239" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 1]),2),0)</f>
       </c>
       <c r="D40" s="241">
         <v>8</v>
       </c>
-      <c r="E40" s="227" t="str">
+      <c r="E40" s="226" t="str">
         <f>=IFERROR(ROUND($C$40/Budget_Kurs,2),0)</f>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="206" t="s">
+      <c r="B41" s="205" t="s">
         <v>369</v>
       </c>
-      <c r="C41" s="240" t="str">
+      <c r="C41" s="239" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 2]),2),0)</f>
       </c>
       <c r="D41" s="241">
         <v>0</v>
       </c>
-      <c r="E41" s="227" t="str">
+      <c r="E41" s="226" t="str">
         <f>=IFERROR(ROUND($C$41/Budget_Kurs,2),0)</f>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="206" t="s">
+      <c r="B42" s="205" t="s">
         <v>370</v>
       </c>
-      <c r="C42" s="240" t="str">
+      <c r="C42" s="239" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 3]),2),0)</f>
       </c>
       <c r="D42" s="241">
         <v>0</v>
       </c>
-      <c r="E42" s="227" t="str">
+      <c r="E42" s="226" t="str">
         <f>=IFERROR(ROUND($C$42/Budget_Kurs,2),0)</f>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="206" t="s">
+      <c r="B43" s="205" t="s">
         <v>371</v>
       </c>
       <c r="C43" s="242" t="str">
@@ -22149,7 +22167,7 @@
       <c r="E43" s="249"/>
     </row>
     <row r="44">
-      <c r="B44" s="206" t="s">
+      <c r="B44" s="205" t="s">
         <v>372</v>
       </c>
       <c r="C44" s="242" t="str">
@@ -22165,8 +22183,8 @@
       <c r="C45" s="243" t="str">
         <f>=IFERROR(ROUND($C$40*$D$40/12+$C$41*$D$41/12+$C$42*$D$42/12,2),0)</f>
       </c>
-      <c r="D45" s="189"/>
-      <c r="E45" s="236" t="str">
+      <c r="D45" s="240"/>
+      <c r="E45" s="235" t="str">
         <f>=IFERROR(ROUND($E$40*$D$40/12+$E$41*$D$41/12+$E$42*$D$42/12,2),0)</f>
       </c>
     </row>
@@ -22177,20 +22195,20 @@
       <c r="C46" s="244" t="str">
         <f>=IF($C$39&lt;=$C$45,"OK","ÜBERSCHRITTEN")</f>
       </c>
-      <c r="D46" s="189"/>
+      <c r="D46" s="240"/>
       <c r="E46" s="252" t="str">
         <f>=IF($E$39&lt;=$E$45,"OK","ÜBERSCHRITTEN")</f>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="206" t="s">
+      <c r="B47" s="205" t="s">
         <v>375</v>
       </c>
-      <c r="C47" s="240" t="str">
+      <c r="C47" s="239" t="str">
         <f>=ROUND(MAX(0,$C$39-$C$45),2)</f>
       </c>
-      <c r="D47" s="189"/>
-      <c r="E47" s="227" t="str">
+      <c r="D47" s="240"/>
+      <c r="E47" s="226" t="str">
         <f>=ROUND(MAX(0,$E$39-$E$45),2)</f>
       </c>
     </row>
@@ -22252,22 +22270,22 @@
       <c r="B53" s="266" t="s">
         <v>194</v>
       </c>
-      <c r="C53" s="240" t="str">
+      <c r="C53" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Eigenmittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D53" s="240" t="str">
+      <c r="D53" s="239" t="str">
         <f>=IFERROR(ROUND(Eigenmittel_LW,2),0)</f>
       </c>
-      <c r="E53" s="202" t="str">
+      <c r="E53" s="201" t="str">
         <f>=ROUND(IFERROR($C$53-$D$53,0),2)</f>
       </c>
       <c r="F53" s="258" t="str">
         <f>=ROUND(IFERROR(($C$53/$D$53)-1,0),4)</f>
       </c>
-      <c r="G53" s="218" t="str">
+      <c r="G53" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Eigenmittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H53" s="218" t="str">
+      <c r="H53" s="217" t="str">
         <f>=IFERROR(ROUND(Eigenmittel_EUR,2),0)</f>
       </c>
       <c r="I53" s="182" t="str">
@@ -22281,22 +22299,22 @@
       <c r="B54" s="266" t="s">
         <v>300</v>
       </c>
-      <c r="C54" s="240" t="str">
+      <c r="C54" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Drittmittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D54" s="240" t="str">
+      <c r="D54" s="239" t="str">
         <f>=IFERROR(ROUND(Drittmittel_LW,2),0)</f>
       </c>
-      <c r="E54" s="202" t="str">
+      <c r="E54" s="201" t="str">
         <f>=ROUND(IFERROR($C$54-$D$54,0),2)</f>
       </c>
       <c r="F54" s="258" t="str">
         <f>=ROUND(IFERROR(($C$54/$D$54)-1,0),4)</f>
       </c>
-      <c r="G54" s="218" t="str">
+      <c r="G54" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Drittmittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H54" s="218" t="str">
+      <c r="H54" s="217" t="str">
         <f>=IFERROR(ROUND(Drittmittel_EUR,2),0)</f>
       </c>
       <c r="I54" s="182" t="str">
@@ -22310,22 +22328,22 @@
       <c r="B55" s="266" t="s">
         <v>199</v>
       </c>
-      <c r="C55" s="240" t="str">
+      <c r="C55" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D55" s="240" t="str">
+      <c r="D55" s="239" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_LW,2),0)</f>
       </c>
-      <c r="E55" s="202" t="str">
+      <c r="E55" s="201" t="str">
         <f>=ROUND(IFERROR($C$55-$D$55,0),2)</f>
       </c>
       <c r="F55" s="258" t="str">
         <f>=ROUND(IFERROR(($C$55/$D$55)-1,0),4)</f>
       </c>
-      <c r="G55" s="218" t="str">
+      <c r="G55" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H55" s="218" t="str">
+      <c r="H55" s="217" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
       <c r="I55" s="182" t="str">
@@ -22339,22 +22357,22 @@
       <c r="B56" s="266" t="s">
         <v>301</v>
       </c>
-      <c r="C56" s="240" t="str">
+      <c r="C56" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Zinsertraege",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D56" s="240" t="str">
+      <c r="D56" s="239" t="str">
         <f>=IFERROR(ROUND(0,2),0)</f>
       </c>
-      <c r="E56" s="202" t="str">
+      <c r="E56" s="201" t="str">
         <f>=ROUND(IFERROR($C$56-$D$56,0),2)</f>
       </c>
       <c r="F56" s="258" t="str">
         <f>=ROUND(IFERROR(($C$56/$D$56)-1,0),4)</f>
       </c>
-      <c r="G56" s="218" t="str">
+      <c r="G56" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Zinsertraege",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H56" s="218" t="str">
+      <c r="H56" s="217" t="str">
         <f>=IFERROR(ROUND(0,2),0)</f>
       </c>
       <c r="I56" s="182" t="str">
@@ -22439,22 +22457,22 @@
       <c r="B62" s="266" t="s">
         <v>205</v>
       </c>
-      <c r="C62" s="240" t="str">
+      <c r="C62" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Bauausgaben",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D62" s="240" t="str">
+      <c r="D62" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Bauausgaben_LW,2),0)</f>
       </c>
-      <c r="E62" s="202" t="str">
+      <c r="E62" s="201" t="str">
         <f>=ROUND(IFERROR($C$62-$D$62,0),2)</f>
       </c>
       <c r="F62" s="258" t="str">
         <f>=ROUND(IFERROR(($C$62/$D$62)-1,0),4)</f>
       </c>
-      <c r="G62" s="218" t="str">
+      <c r="G62" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Bauausgaben",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H62" s="218" t="str">
+      <c r="H62" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Bauausgaben_EUR,2),0)</f>
       </c>
       <c r="I62" s="182" t="str">
@@ -22468,22 +22486,22 @@
       <c r="B63" s="266" t="s">
         <v>210</v>
       </c>
-      <c r="C63" s="240" t="str">
+      <c r="C63" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Investitionen",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D63" s="240" t="str">
+      <c r="D63" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Investitionen_LW,2),0)</f>
       </c>
-      <c r="E63" s="202" t="str">
+      <c r="E63" s="201" t="str">
         <f>=ROUND(IFERROR($C$63-$D$63,0),2)</f>
       </c>
       <c r="F63" s="258" t="str">
         <f>=ROUND(IFERROR(($C$63/$D$63)-1,0),4)</f>
       </c>
-      <c r="G63" s="218" t="str">
+      <c r="G63" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Investitionen",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H63" s="218" t="str">
+      <c r="H63" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Investitionen_EUR,2),0)</f>
       </c>
       <c r="I63" s="182" t="str">
@@ -22497,22 +22515,22 @@
       <c r="B64" s="266" t="s">
         <v>213</v>
       </c>
-      <c r="C64" s="240" t="str">
+      <c r="C64" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Personalkosten",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D64" s="240" t="str">
+      <c r="D64" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Personalkosten_LW,2),0)</f>
       </c>
-      <c r="E64" s="202" t="str">
+      <c r="E64" s="201" t="str">
         <f>=ROUND(IFERROR($C$64-$D$64,0),2)</f>
       </c>
       <c r="F64" s="258" t="str">
         <f>=ROUND(IFERROR(($C$64/$D$64)-1,0),4)</f>
       </c>
-      <c r="G64" s="218" t="str">
+      <c r="G64" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Personalkosten",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H64" s="218" t="str">
+      <c r="H64" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Personalkosten_EUR,2),0)</f>
       </c>
       <c r="I64" s="182" t="str">
@@ -22526,22 +22544,22 @@
       <c r="B65" s="266" t="s">
         <v>218</v>
       </c>
-      <c r="C65" s="240" t="str">
+      <c r="C65" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Projektaktivitaeten",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D65" s="240" t="str">
+      <c r="D65" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektaktivitaeten_LW,2),0)</f>
       </c>
-      <c r="E65" s="202" t="str">
+      <c r="E65" s="201" t="str">
         <f>=ROUND(IFERROR($C$65-$D$65,0),2)</f>
       </c>
       <c r="F65" s="258" t="str">
         <f>=ROUND(IFERROR(($C$65/$D$65)-1,0),4)</f>
       </c>
-      <c r="G65" s="218" t="str">
+      <c r="G65" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Projektaktivitaeten",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H65" s="218" t="str">
+      <c r="H65" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektaktivitaeten_EUR,2),0)</f>
       </c>
       <c r="I65" s="182" t="str">
@@ -22555,22 +22573,22 @@
       <c r="B66" s="266" t="s">
         <v>221</v>
       </c>
-      <c r="C66" s="240" t="str">
+      <c r="C66" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Projektverwaltung",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D66" s="240" t="str">
+      <c r="D66" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektverwaltung_LW,2),0)</f>
       </c>
-      <c r="E66" s="202" t="str">
+      <c r="E66" s="201" t="str">
         <f>=ROUND(IFERROR($C$66-$D$66,0),2)</f>
       </c>
       <c r="F66" s="258" t="str">
         <f>=ROUND(IFERROR(($C$66/$D$66)-1,0),4)</f>
       </c>
-      <c r="G66" s="218" t="str">
+      <c r="G66" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Projektverwaltung",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H66" s="218" t="str">
+      <c r="H66" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektverwaltung_EUR,2),0)</f>
       </c>
       <c r="I66" s="182" t="str">
@@ -22584,22 +22602,22 @@
       <c r="B67" s="266" t="s">
         <v>224</v>
       </c>
-      <c r="C67" s="240" t="str">
+      <c r="C67" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Evaluierung",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D67" s="240" t="str">
+      <c r="D67" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Evaluierung_LW,2),0)</f>
       </c>
-      <c r="E67" s="202" t="str">
+      <c r="E67" s="201" t="str">
         <f>=ROUND(IFERROR($C$67-$D$67,0),2)</f>
       </c>
       <c r="F67" s="258" t="str">
         <f>=ROUND(IFERROR(($C$67/$D$67)-1,0),4)</f>
       </c>
-      <c r="G67" s="218" t="str">
+      <c r="G67" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Evaluierung",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H67" s="218" t="str">
+      <c r="H67" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Evaluierung_EUR,2),0)</f>
       </c>
       <c r="I67" s="182" t="str">
@@ -22613,22 +22631,22 @@
       <c r="B68" s="266" t="s">
         <v>227</v>
       </c>
-      <c r="C68" s="240" t="str">
+      <c r="C68" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Audit",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D68" s="240" t="str">
+      <c r="D68" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Audit_LW,2),0)</f>
       </c>
-      <c r="E68" s="202" t="str">
+      <c r="E68" s="201" t="str">
         <f>=ROUND(IFERROR($C$68-$D$68,0),2)</f>
       </c>
       <c r="F68" s="258" t="str">
         <f>=ROUND(IFERROR(($C$68/$D$68)-1,0),4)</f>
       </c>
-      <c r="G68" s="218" t="str">
+      <c r="G68" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Audit",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H68" s="218" t="str">
+      <c r="H68" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Audit_EUR,2),0)</f>
       </c>
       <c r="I68" s="182" t="str">
@@ -22642,22 +22660,22 @@
       <c r="B69" s="266" t="s">
         <v>230</v>
       </c>
-      <c r="C69" s="240" t="str">
+      <c r="C69" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Reserve",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="D69" s="240" t="str">
+      <c r="D69" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_LW,2),0)</f>
       </c>
-      <c r="E69" s="202" t="str">
+      <c r="E69" s="201" t="str">
         <f>=ROUND(IFERROR($C$69-$D$69,0),2)</f>
       </c>
       <c r="F69" s="258" t="str">
         <f>=ROUND(IFERROR(($C$69/$D$69)-1,0),4)</f>
       </c>
-      <c r="G69" s="218" t="str">
+      <c r="G69" s="217" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"Reserve",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
       </c>
-      <c r="H69" s="218" t="str">
+      <c r="H69" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
       <c r="I69" s="182" t="str">
@@ -22697,37 +22715,37 @@
       </c>
     </row>
     <row r="76" ht="22" customHeight="true">
-      <c r="B76" s="195" t="s">
+      <c r="B76" s="194" t="s">
         <v>388</v>
       </c>
-      <c r="C76" s="195"/>
-      <c r="D76" s="195"/>
-      <c r="E76" s="195"/>
-      <c r="F76" s="195"/>
-      <c r="G76" s="195"/>
-      <c r="H76" s="195"/>
-      <c r="I76" s="195"/>
-      <c r="J76" s="195"/>
-      <c r="L76" s="203" t="str">
+      <c r="C76" s="194"/>
+      <c r="D76" s="194"/>
+      <c r="E76" s="194"/>
+      <c r="F76" s="194"/>
+      <c r="G76" s="194"/>
+      <c r="H76" s="194"/>
+      <c r="I76" s="194"/>
+      <c r="J76" s="194"/>
+      <c r="L76" s="202" t="str">
         <f>=IF(E81=0,"Aktueller Finanzbericht (keiner gewählt)","Aktueller Finanzbericht – Periode "&amp;E81)</f>
       </c>
-      <c r="M76" s="204"/>
-      <c r="N76" s="204"/>
-      <c r="O76" s="204"/>
-      <c r="P76" s="205"/>
+      <c r="M76" s="203"/>
+      <c r="N76" s="203"/>
+      <c r="O76" s="203"/>
+      <c r="P76" s="204"/>
     </row>
     <row r="77">
-      <c r="B77" s="196" t="s">
+      <c r="B77" s="195" t="s">
         <v>389</v>
       </c>
-      <c r="C77" s="196"/>
-      <c r="D77" s="196"/>
-      <c r="E77" s="196"/>
-      <c r="F77" s="196"/>
-      <c r="G77" s="196"/>
-      <c r="H77" s="196"/>
-      <c r="I77" s="196"/>
-      <c r="J77" s="196"/>
+      <c r="C77" s="195"/>
+      <c r="D77" s="195"/>
+      <c r="E77" s="195"/>
+      <c r="F77" s="195"/>
+      <c r="G77" s="195"/>
+      <c r="H77" s="195"/>
+      <c r="I77" s="195"/>
+      <c r="J77" s="195"/>
       <c r="L77" s="315" t="s">
         <v>288</v>
       </c>
@@ -22750,13 +22768,13 @@
       <c r="P78" s="338"/>
     </row>
     <row r="79" ht="22" customHeight="true">
-      <c r="C79" s="203" t="s">
+      <c r="C79" s="202" t="s">
         <v>390</v>
       </c>
-      <c r="D79" s="204"/>
-      <c r="E79" s="204"/>
-      <c r="F79" s="204"/>
-      <c r="G79" s="205"/>
+      <c r="D79" s="203"/>
+      <c r="E79" s="203"/>
+      <c r="F79" s="203"/>
+      <c r="G79" s="204"/>
       <c r="L79" s="315" t="s">
         <v>290</v>
       </c>
@@ -22768,15 +22786,15 @@
       <c r="P79" s="338"/>
     </row>
     <row r="80">
-      <c r="C80" s="206" t="s">
+      <c r="C80" s="205" t="s">
         <v>342</v>
       </c>
-      <c r="D80" s="198"/>
+      <c r="D80" s="197"/>
       <c r="E80" s="63" t="s">
         <v>391</v>
       </c>
       <c r="F80" s="63"/>
-      <c r="G80" s="207"/>
+      <c r="G80" s="206"/>
       <c r="L80" s="315" t="s">
         <v>291</v>
       </c>
@@ -22849,19 +22867,19 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="224" t="s">
+      <c r="B85" s="223" t="s">
         <v>348</v>
       </c>
-      <c r="C85" s="225"/>
-      <c r="D85" s="226" t="str">
+      <c r="C85" s="224"/>
+      <c r="D85" s="225" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
-      <c r="F85" s="231" t="s">
+      <c r="F85" s="230" t="s">
         <v>352</v>
       </c>
-      <c r="G85" s="232"/>
-      <c r="H85" s="232"/>
-      <c r="I85" s="233"/>
+      <c r="G85" s="231"/>
+      <c r="H85" s="231"/>
+      <c r="I85" s="232"/>
       <c r="L85" s="143" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$B$11,'III. Finanzberichte'!$I$11,'III. Finanzberichte'!$P$11,'III. Finanzberichte'!$W$11,'III. Finanzberichte'!$AD$11,'III. Finanzberichte'!$AK$11,'III. Finanzberichte'!$AR$11,'III. Finanzberichte'!$AY$11,'III. Finanzberichte'!$BF$11,'III. Finanzberichte'!$BM$11,'III. Finanzberichte'!$BT$11,'III. Finanzberichte'!$CA$11,'III. Finanzberichte'!$CH$11,'III. Finanzberichte'!$CO$11,'III. Finanzberichte'!$CV$11,'III. Finanzberichte'!$DC$11,'III. Finanzberichte'!$DJ$11,'III. Finanzberichte'!$DQ$11),"")</f>
       </c>
@@ -22879,21 +22897,21 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="206" t="s">
+      <c r="B86" s="205" t="s">
         <v>349</v>
       </c>
-      <c r="C86" s="198"/>
-      <c r="D86" s="227" t="str">
+      <c r="C86" s="197"/>
+      <c r="D86" s="226" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
-      <c r="F86" s="234" t="s">
+      <c r="F86" s="233" t="s">
         <v>353</v>
       </c>
-      <c r="G86" s="198" t="s">
+      <c r="G86" s="197" t="s">
         <v>354</v>
       </c>
-      <c r="H86" s="198"/>
-      <c r="I86" s="235" t="str">
+      <c r="H86" s="197"/>
+      <c r="I86" s="234" t="str">
         <f>=IFERROR(ROUND(Saldovortrag_EUR,2),0)</f>
       </c>
       <c r="L86" s="143" t="s">
@@ -22913,21 +22931,21 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="206" t="str">
+      <c r="B87" s="205" t="str">
         <f>=IF(Reserve_Freigabe="Ja","Operatives Budget (Reserve freigegeben)","Operatives Budget (abzgl. Reserve)")</f>
       </c>
-      <c r="C87" s="198"/>
-      <c r="D87" s="227" t="str">
+      <c r="C87" s="197"/>
+      <c r="D87" s="226" t="str">
         <f>=IF(Reserve_Freigabe="Ja",ROUND($D$85,2),ROUND($D$85-$D$86,2))</f>
       </c>
-      <c r="F87" s="234" t="s">
+      <c r="F87" s="233" t="s">
         <v>353</v>
       </c>
-      <c r="G87" s="198" t="s">
+      <c r="G87" s="197" t="s">
         <v>355</v>
       </c>
-      <c r="H87" s="198"/>
-      <c r="I87" s="235" t="str">
+      <c r="H87" s="197"/>
+      <c r="I87" s="234" t="str">
         <f>=IFERROR(ROUND(MAX(0,(SUM($G$96:$G$99)-$G$98)-(SUM($H$96:$H$99)-$H$98)),2),0)</f>
         <v>0</v>
       </c>
@@ -22948,19 +22966,19 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="206" t="s">
+      <c r="B88" s="205" t="s">
         <v>350</v>
       </c>
-      <c r="C88" s="198"/>
-      <c r="D88" s="227" t="str">
+      <c r="C88" s="197"/>
+      <c r="D88" s="226" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblKMWMittel[Betrag]),2),0)</f>
       </c>
       <c r="F88" s="47"/>
-      <c r="G88" s="219" t="s">
+      <c r="G88" s="218" t="s">
         <v>357</v>
       </c>
-      <c r="H88" s="219"/>
-      <c r="I88" s="236" t="str">
+      <c r="H88" s="218"/>
+      <c r="I88" s="235" t="str">
         <f>=ROUND(IF($F$86="Abzug",MAX(0,$I$86),0)+IF($F$87="Abzug",MAX(0,$I$87),0),2)</f>
       </c>
       <c r="L88" s="143" t="s">
@@ -22980,19 +22998,19 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="228" t="s">
+      <c r="B89" s="227" t="s">
         <v>351</v>
       </c>
-      <c r="C89" s="229"/>
-      <c r="D89" s="230" t="str">
+      <c r="C89" s="228"/>
+      <c r="D89" s="229" t="str">
         <f>=ROUND($D$87-$D$88,2)</f>
       </c>
-      <c r="F89" s="237"/>
-      <c r="G89" s="229" t="s">
+      <c r="F89" s="236"/>
+      <c r="G89" s="228" t="s">
         <v>358</v>
       </c>
-      <c r="H89" s="229"/>
-      <c r="I89" s="230" t="str">
+      <c r="H89" s="228"/>
+      <c r="I89" s="229" t="str">
         <f>=ROUND($D$89-$I$88,2)</f>
       </c>
       <c r="L89" s="143" t="s">
@@ -23147,22 +23165,22 @@
       <c r="B96" s="266" t="s">
         <v>194</v>
       </c>
-      <c r="C96" s="240" t="str">
+      <c r="C96" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$12,'III. Finanzberichte'!$L$12,'III. Finanzberichte'!$S$12,'III. Finanzberichte'!$Z$12,'III. Finanzberichte'!$AG$12,'III. Finanzberichte'!$AN$12,'III. Finanzberichte'!$AU$12,'III. Finanzberichte'!$BB$12,'III. Finanzberichte'!$BI$12,'III. Finanzberichte'!$BP$12,'III. Finanzberichte'!$BW$12,'III. Finanzberichte'!$CD$12,'III. Finanzberichte'!$CK$12,'III. Finanzberichte'!$CR$12,'III. Finanzberichte'!$CY$12,'III. Finanzberichte'!$DF$12,'III. Finanzberichte'!$DM$12,'III. Finanzberichte'!$DT$12),2),0)</f>
       </c>
-      <c r="D96" s="240" t="str">
+      <c r="D96" s="239" t="str">
         <f>=IFERROR(ROUND(Eigenmittel_LW,2),0)</f>
       </c>
-      <c r="E96" s="202" t="str">
+      <c r="E96" s="201" t="str">
         <f>=ROUND(IFERROR($C$96-$D$96,0),2)</f>
       </c>
       <c r="F96" s="258" t="str">
         <f>=ROUND(IFERROR(($C$96/$D$96)-1,0),4)</f>
       </c>
-      <c r="G96" s="218" t="str">
+      <c r="G96" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$12,'III. Finanzberichte'!$M$12,'III. Finanzberichte'!$T$12,'III. Finanzberichte'!$AA$12,'III. Finanzberichte'!$AH$12,'III. Finanzberichte'!$AO$12,'III. Finanzberichte'!$AV$12,'III. Finanzberichte'!$BC$12,'III. Finanzberichte'!$BJ$12,'III. Finanzberichte'!$BQ$12,'III. Finanzberichte'!$BX$12,'III. Finanzberichte'!$CE$12,'III. Finanzberichte'!$CL$12,'III. Finanzberichte'!$CS$12,'III. Finanzberichte'!$CZ$12,'III. Finanzberichte'!$DG$12,'III. Finanzberichte'!$DN$12,'III. Finanzberichte'!$DU$12),2),0)</f>
       </c>
-      <c r="H96" s="218" t="str">
+      <c r="H96" s="217" t="str">
         <f>=IFERROR(ROUND(Eigenmittel_EUR,2),0)</f>
       </c>
       <c r="I96" s="182" t="str">
@@ -23191,22 +23209,22 @@
       <c r="B97" s="266" t="s">
         <v>300</v>
       </c>
-      <c r="C97" s="240" t="str">
+      <c r="C97" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$13,'III. Finanzberichte'!$L$13,'III. Finanzberichte'!$S$13,'III. Finanzberichte'!$Z$13,'III. Finanzberichte'!$AG$13,'III. Finanzberichte'!$AN$13,'III. Finanzberichte'!$AU$13,'III. Finanzberichte'!$BB$13,'III. Finanzberichte'!$BI$13,'III. Finanzberichte'!$BP$13,'III. Finanzberichte'!$BW$13,'III. Finanzberichte'!$CD$13,'III. Finanzberichte'!$CK$13,'III. Finanzberichte'!$CR$13,'III. Finanzberichte'!$CY$13,'III. Finanzberichte'!$DF$13,'III. Finanzberichte'!$DM$13,'III. Finanzberichte'!$DT$13),2),0)</f>
       </c>
-      <c r="D97" s="240" t="str">
+      <c r="D97" s="239" t="str">
         <f>=IFERROR(ROUND(Drittmittel_LW,2),0)</f>
       </c>
-      <c r="E97" s="202" t="str">
+      <c r="E97" s="201" t="str">
         <f>=ROUND(IFERROR($C$97-$D$97,0),2)</f>
       </c>
       <c r="F97" s="258" t="str">
         <f>=ROUND(IFERROR(($C$97/$D$97)-1,0),4)</f>
       </c>
-      <c r="G97" s="218" t="str">
+      <c r="G97" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$13,'III. Finanzberichte'!$M$13,'III. Finanzberichte'!$T$13,'III. Finanzberichte'!$AA$13,'III. Finanzberichte'!$AH$13,'III. Finanzberichte'!$AO$13,'III. Finanzberichte'!$AV$13,'III. Finanzberichte'!$BC$13,'III. Finanzberichte'!$BJ$13,'III. Finanzberichte'!$BQ$13,'III. Finanzberichte'!$BX$13,'III. Finanzberichte'!$CE$13,'III. Finanzberichte'!$CL$13,'III. Finanzberichte'!$CS$13,'III. Finanzberichte'!$CZ$13,'III. Finanzberichte'!$DG$13,'III. Finanzberichte'!$DN$13,'III. Finanzberichte'!$DU$13),2),0)</f>
       </c>
-      <c r="H97" s="218" t="str">
+      <c r="H97" s="217" t="str">
         <f>=IFERROR(ROUND(Drittmittel_EUR,2),0)</f>
       </c>
       <c r="I97" s="182" t="str">
@@ -23235,22 +23253,22 @@
       <c r="B98" s="266" t="s">
         <v>199</v>
       </c>
-      <c r="C98" s="240" t="str">
+      <c r="C98" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$14,'III. Finanzberichte'!$L$14,'III. Finanzberichte'!$S$14,'III. Finanzberichte'!$Z$14,'III. Finanzberichte'!$AG$14,'III. Finanzberichte'!$AN$14,'III. Finanzberichte'!$AU$14,'III. Finanzberichte'!$BB$14,'III. Finanzberichte'!$BI$14,'III. Finanzberichte'!$BP$14,'III. Finanzberichte'!$BW$14,'III. Finanzberichte'!$CD$14,'III. Finanzberichte'!$CK$14,'III. Finanzberichte'!$CR$14,'III. Finanzberichte'!$CY$14,'III. Finanzberichte'!$DF$14,'III. Finanzberichte'!$DM$14,'III. Finanzberichte'!$DT$14),2),0)</f>
       </c>
-      <c r="D98" s="240" t="str">
+      <c r="D98" s="239" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_LW,2),0)</f>
       </c>
-      <c r="E98" s="202" t="str">
+      <c r="E98" s="201" t="str">
         <f>=ROUND(IFERROR($C$98-$D$98,0),2)</f>
       </c>
       <c r="F98" s="258" t="str">
         <f>=ROUND(IFERROR(($C$98/$D$98)-1,0),4)</f>
       </c>
-      <c r="G98" s="218" t="str">
+      <c r="G98" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$14,'III. Finanzberichte'!$M$14,'III. Finanzberichte'!$T$14,'III. Finanzberichte'!$AA$14,'III. Finanzberichte'!$AH$14,'III. Finanzberichte'!$AO$14,'III. Finanzberichte'!$AV$14,'III. Finanzberichte'!$BC$14,'III. Finanzberichte'!$BJ$14,'III. Finanzberichte'!$BQ$14,'III. Finanzberichte'!$BX$14,'III. Finanzberichte'!$CE$14,'III. Finanzberichte'!$CL$14,'III. Finanzberichte'!$CS$14,'III. Finanzberichte'!$CZ$14,'III. Finanzberichte'!$DG$14,'III. Finanzberichte'!$DN$14,'III. Finanzberichte'!$DU$14),2),0)</f>
       </c>
-      <c r="H98" s="218" t="str">
+      <c r="H98" s="217" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
       <c r="I98" s="182" t="str">
@@ -23279,22 +23297,22 @@
       <c r="B99" s="266" t="s">
         <v>301</v>
       </c>
-      <c r="C99" s="240" t="str">
+      <c r="C99" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$15,'III. Finanzberichte'!$L$15,'III. Finanzberichte'!$S$15,'III. Finanzberichte'!$Z$15,'III. Finanzberichte'!$AG$15,'III. Finanzberichte'!$AN$15,'III. Finanzberichte'!$AU$15,'III. Finanzberichte'!$BB$15,'III. Finanzberichte'!$BI$15,'III. Finanzberichte'!$BP$15,'III. Finanzberichte'!$BW$15,'III. Finanzberichte'!$CD$15,'III. Finanzberichte'!$CK$15,'III. Finanzberichte'!$CR$15,'III. Finanzberichte'!$CY$15,'III. Finanzberichte'!$DF$15,'III. Finanzberichte'!$DM$15,'III. Finanzberichte'!$DT$15),2),0)</f>
       </c>
-      <c r="D99" s="240" t="str">
+      <c r="D99" s="239" t="str">
         <f>=IFERROR(ROUND(0,2),0)</f>
       </c>
-      <c r="E99" s="202" t="str">
+      <c r="E99" s="201" t="str">
         <f>=ROUND(IFERROR($C$99-$D$99,0),2)</f>
       </c>
       <c r="F99" s="258" t="str">
         <f>=ROUND(IFERROR(($C$99/$D$99)-1,0),4)</f>
       </c>
-      <c r="G99" s="218" t="str">
+      <c r="G99" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$15,'III. Finanzberichte'!$M$15,'III. Finanzberichte'!$T$15,'III. Finanzberichte'!$AA$15,'III. Finanzberichte'!$AH$15,'III. Finanzberichte'!$AO$15,'III. Finanzberichte'!$AV$15,'III. Finanzberichte'!$BC$15,'III. Finanzberichte'!$BJ$15,'III. Finanzberichte'!$BQ$15,'III. Finanzberichte'!$BX$15,'III. Finanzberichte'!$CE$15,'III. Finanzberichte'!$CL$15,'III. Finanzberichte'!$CS$15,'III. Finanzberichte'!$CZ$15,'III. Finanzberichte'!$DG$15,'III. Finanzberichte'!$DN$15,'III. Finanzberichte'!$DU$15),2),0)</f>
       </c>
-      <c r="H99" s="218" t="str">
+      <c r="H99" s="217" t="str">
         <f>=IFERROR(ROUND(0,2),0)</f>
       </c>
       <c r="I99" s="182" t="str">
@@ -23460,22 +23478,22 @@
       <c r="B105" s="266" t="s">
         <v>205</v>
       </c>
-      <c r="C105" s="240" t="str">
+      <c r="C105" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$19+'III. Finanzberichte'!$E$20,'III. Finanzberichte'!$L$19+'III. Finanzberichte'!$L$20,'III. Finanzberichte'!$S$19+'III. Finanzberichte'!$S$20,'III. Finanzberichte'!$Z$19+'III. Finanzberichte'!$Z$20,'III. Finanzberichte'!$AG$19+'III. Finanzberichte'!$AG$20,'III. Finanzberichte'!$AN$19+'III. Finanzberichte'!$AN$20,'III. Finanzberichte'!$AU$19+'III. Finanzberichte'!$AU$20,'III. Finanzberichte'!$BB$19+'III. Finanzberichte'!$BB$20,'III. Finanzberichte'!$BI$19+'III. Finanzberichte'!$BI$20,'III. Finanzberichte'!$BP$19+'III. Finanzberichte'!$BP$20,'III. Finanzberichte'!$BW$19+'III. Finanzberichte'!$BW$20,'III. Finanzberichte'!$CD$19+'III. Finanzberichte'!$CD$20,'III. Finanzberichte'!$CK$19+'III. Finanzberichte'!$CK$20,'III. Finanzberichte'!$CR$19+'III. Finanzberichte'!$CR$20,'III. Finanzberichte'!$CY$19+'III. Finanzberichte'!$CY$20,'III. Finanzberichte'!$DF$19+'III. Finanzberichte'!$DF$20,'III. Finanzberichte'!$DM$19+'III. Finanzberichte'!$DM$20,'III. Finanzberichte'!$DT$19+'III. Finanzberichte'!$DT$20),2),0)</f>
       </c>
-      <c r="D105" s="240" t="str">
+      <c r="D105" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Bauausgaben_LW,2),0)</f>
       </c>
-      <c r="E105" s="202" t="str">
+      <c r="E105" s="201" t="str">
         <f>=ROUND(IFERROR($C$105-$D$105,0),2)</f>
       </c>
       <c r="F105" s="258" t="str">
         <f>=ROUND(IFERROR(($C$105/$D$105)-1,0),4)</f>
       </c>
-      <c r="G105" s="218" t="str">
+      <c r="G105" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$19+'III. Finanzberichte'!$F$20,'III. Finanzberichte'!$M$19+'III. Finanzberichte'!$M$20,'III. Finanzberichte'!$T$19+'III. Finanzberichte'!$T$20,'III. Finanzberichte'!$AA$19+'III. Finanzberichte'!$AA$20,'III. Finanzberichte'!$AH$19+'III. Finanzberichte'!$AH$20,'III. Finanzberichte'!$AO$19+'III. Finanzberichte'!$AO$20,'III. Finanzberichte'!$AV$19+'III. Finanzberichte'!$AV$20,'III. Finanzberichte'!$BC$19+'III. Finanzberichte'!$BC$20,'III. Finanzberichte'!$BJ$19+'III. Finanzberichte'!$BJ$20,'III. Finanzberichte'!$BQ$19+'III. Finanzberichte'!$BQ$20,'III. Finanzberichte'!$BX$19+'III. Finanzberichte'!$BX$20,'III. Finanzberichte'!$CE$19+'III. Finanzberichte'!$CE$20,'III. Finanzberichte'!$CL$19+'III. Finanzberichte'!$CL$20,'III. Finanzberichte'!$CS$19+'III. Finanzberichte'!$CS$20,'III. Finanzberichte'!$CZ$19+'III. Finanzberichte'!$CZ$20,'III. Finanzberichte'!$DG$19+'III. Finanzberichte'!$DG$20,'III. Finanzberichte'!$DN$19+'III. Finanzberichte'!$DN$20,'III. Finanzberichte'!$DU$19+'III. Finanzberichte'!$DU$20),2),0)</f>
       </c>
-      <c r="H105" s="218" t="str">
+      <c r="H105" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Bauausgaben_EUR,2),0)</f>
       </c>
       <c r="I105" s="182" t="str">
@@ -23504,22 +23522,22 @@
       <c r="B106" s="266" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="240" t="str">
+      <c r="C106" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$21,'III. Finanzberichte'!$L$21,'III. Finanzberichte'!$S$21,'III. Finanzberichte'!$Z$21,'III. Finanzberichte'!$AG$21,'III. Finanzberichte'!$AN$21,'III. Finanzberichte'!$AU$21,'III. Finanzberichte'!$BB$21,'III. Finanzberichte'!$BI$21,'III. Finanzberichte'!$BP$21,'III. Finanzberichte'!$BW$21,'III. Finanzberichte'!$CD$21,'III. Finanzberichte'!$CK$21,'III. Finanzberichte'!$CR$21,'III. Finanzberichte'!$CY$21,'III. Finanzberichte'!$DF$21,'III. Finanzberichte'!$DM$21,'III. Finanzberichte'!$DT$21),2),0)</f>
       </c>
-      <c r="D106" s="240" t="str">
+      <c r="D106" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Investitionen_LW,2),0)</f>
       </c>
-      <c r="E106" s="202" t="str">
+      <c r="E106" s="201" t="str">
         <f>=ROUND(IFERROR($C$106-$D$106,0),2)</f>
       </c>
       <c r="F106" s="258" t="str">
         <f>=ROUND(IFERROR(($C$106/$D$106)-1,0),4)</f>
       </c>
-      <c r="G106" s="218" t="str">
+      <c r="G106" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$21,'III. Finanzberichte'!$M$21,'III. Finanzberichte'!$T$21,'III. Finanzberichte'!$AA$21,'III. Finanzberichte'!$AH$21,'III. Finanzberichte'!$AO$21,'III. Finanzberichte'!$AV$21,'III. Finanzberichte'!$BC$21,'III. Finanzberichte'!$BJ$21,'III. Finanzberichte'!$BQ$21,'III. Finanzberichte'!$BX$21,'III. Finanzberichte'!$CE$21,'III. Finanzberichte'!$CL$21,'III. Finanzberichte'!$CS$21,'III. Finanzberichte'!$CZ$21,'III. Finanzberichte'!$DG$21,'III. Finanzberichte'!$DN$21,'III. Finanzberichte'!$DU$21),2),0)</f>
       </c>
-      <c r="H106" s="218" t="str">
+      <c r="H106" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Investitionen_EUR,2),0)</f>
       </c>
       <c r="I106" s="182" t="str">
@@ -23533,22 +23551,22 @@
       <c r="B107" s="266" t="s">
         <v>213</v>
       </c>
-      <c r="C107" s="240" t="str">
+      <c r="C107" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$22+'III. Finanzberichte'!$E$23,'III. Finanzberichte'!$L$22+'III. Finanzberichte'!$L$23,'III. Finanzberichte'!$S$22+'III. Finanzberichte'!$S$23,'III. Finanzberichte'!$Z$22+'III. Finanzberichte'!$Z$23,'III. Finanzberichte'!$AG$22+'III. Finanzberichte'!$AG$23,'III. Finanzberichte'!$AN$22+'III. Finanzberichte'!$AN$23,'III. Finanzberichte'!$AU$22+'III. Finanzberichte'!$AU$23,'III. Finanzberichte'!$BB$22+'III. Finanzberichte'!$BB$23,'III. Finanzberichte'!$BI$22+'III. Finanzberichte'!$BI$23,'III. Finanzberichte'!$BP$22+'III. Finanzberichte'!$BP$23,'III. Finanzberichte'!$BW$22+'III. Finanzberichte'!$BW$23,'III. Finanzberichte'!$CD$22+'III. Finanzberichte'!$CD$23,'III. Finanzberichte'!$CK$22+'III. Finanzberichte'!$CK$23,'III. Finanzberichte'!$CR$22+'III. Finanzberichte'!$CR$23,'III. Finanzberichte'!$CY$22+'III. Finanzberichte'!$CY$23,'III. Finanzberichte'!$DF$22+'III. Finanzberichte'!$DF$23,'III. Finanzberichte'!$DM$22+'III. Finanzberichte'!$DM$23,'III. Finanzberichte'!$DT$22+'III. Finanzberichte'!$DT$23),2),0)</f>
       </c>
-      <c r="D107" s="240" t="str">
+      <c r="D107" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Personalkosten_LW,2),0)</f>
       </c>
-      <c r="E107" s="202" t="str">
+      <c r="E107" s="201" t="str">
         <f>=ROUND(IFERROR($C$107-$D$107,0),2)</f>
       </c>
       <c r="F107" s="258" t="str">
         <f>=ROUND(IFERROR(($C$107/$D$107)-1,0),4)</f>
       </c>
-      <c r="G107" s="218" t="str">
+      <c r="G107" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$22+'III. Finanzberichte'!$F$23,'III. Finanzberichte'!$M$22+'III. Finanzberichte'!$M$23,'III. Finanzberichte'!$T$22+'III. Finanzberichte'!$T$23,'III. Finanzberichte'!$AA$22+'III. Finanzberichte'!$AA$23,'III. Finanzberichte'!$AH$22+'III. Finanzberichte'!$AH$23,'III. Finanzberichte'!$AO$22+'III. Finanzberichte'!$AO$23,'III. Finanzberichte'!$AV$22+'III. Finanzberichte'!$AV$23,'III. Finanzberichte'!$BC$22+'III. Finanzberichte'!$BC$23,'III. Finanzberichte'!$BJ$22+'III. Finanzberichte'!$BJ$23,'III. Finanzberichte'!$BQ$22+'III. Finanzberichte'!$BQ$23,'III. Finanzberichte'!$BX$22+'III. Finanzberichte'!$BX$23,'III. Finanzberichte'!$CE$22+'III. Finanzberichte'!$CE$23,'III. Finanzberichte'!$CL$22+'III. Finanzberichte'!$CL$23,'III. Finanzberichte'!$CS$22+'III. Finanzberichte'!$CS$23,'III. Finanzberichte'!$CZ$22+'III. Finanzberichte'!$CZ$23,'III. Finanzberichte'!$DG$22+'III. Finanzberichte'!$DG$23,'III. Finanzberichte'!$DN$22+'III. Finanzberichte'!$DN$23,'III. Finanzberichte'!$DU$22+'III. Finanzberichte'!$DU$23),2),0)</f>
       </c>
-      <c r="H107" s="218" t="str">
+      <c r="H107" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Personalkosten_EUR,2),0)</f>
       </c>
       <c r="I107" s="182" t="str">
@@ -23562,22 +23580,22 @@
       <c r="B108" s="266" t="s">
         <v>218</v>
       </c>
-      <c r="C108" s="240" t="str">
+      <c r="C108" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$24,'III. Finanzberichte'!$L$24,'III. Finanzberichte'!$S$24,'III. Finanzberichte'!$Z$24,'III. Finanzberichte'!$AG$24,'III. Finanzberichte'!$AN$24,'III. Finanzberichte'!$AU$24,'III. Finanzberichte'!$BB$24,'III. Finanzberichte'!$BI$24,'III. Finanzberichte'!$BP$24,'III. Finanzberichte'!$BW$24,'III. Finanzberichte'!$CD$24,'III. Finanzberichte'!$CK$24,'III. Finanzberichte'!$CR$24,'III. Finanzberichte'!$CY$24,'III. Finanzberichte'!$DF$24,'III. Finanzberichte'!$DM$24,'III. Finanzberichte'!$DT$24),2),0)</f>
       </c>
-      <c r="D108" s="240" t="str">
+      <c r="D108" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektaktivitaeten_LW,2),0)</f>
       </c>
-      <c r="E108" s="202" t="str">
+      <c r="E108" s="201" t="str">
         <f>=ROUND(IFERROR($C$108-$D$108,0),2)</f>
       </c>
       <c r="F108" s="258" t="str">
         <f>=ROUND(IFERROR(($C$108/$D$108)-1,0),4)</f>
       </c>
-      <c r="G108" s="218" t="str">
+      <c r="G108" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$24,'III. Finanzberichte'!$M$24,'III. Finanzberichte'!$T$24,'III. Finanzberichte'!$AA$24,'III. Finanzberichte'!$AH$24,'III. Finanzberichte'!$AO$24,'III. Finanzberichte'!$AV$24,'III. Finanzberichte'!$BC$24,'III. Finanzberichte'!$BJ$24,'III. Finanzberichte'!$BQ$24,'III. Finanzberichte'!$BX$24,'III. Finanzberichte'!$CE$24,'III. Finanzberichte'!$CL$24,'III. Finanzberichte'!$CS$24,'III. Finanzberichte'!$CZ$24,'III. Finanzberichte'!$DG$24,'III. Finanzberichte'!$DN$24,'III. Finanzberichte'!$DU$24),2),0)</f>
       </c>
-      <c r="H108" s="218" t="str">
+      <c r="H108" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektaktivitaeten_EUR,2),0)</f>
       </c>
       <c r="I108" s="182" t="str">
@@ -23591,22 +23609,22 @@
       <c r="B109" s="266" t="s">
         <v>221</v>
       </c>
-      <c r="C109" s="240" t="str">
+      <c r="C109" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$25,'III. Finanzberichte'!$L$25,'III. Finanzberichte'!$S$25,'III. Finanzberichte'!$Z$25,'III. Finanzberichte'!$AG$25,'III. Finanzberichte'!$AN$25,'III. Finanzberichte'!$AU$25,'III. Finanzberichte'!$BB$25,'III. Finanzberichte'!$BI$25,'III. Finanzberichte'!$BP$25,'III. Finanzberichte'!$BW$25,'III. Finanzberichte'!$CD$25,'III. Finanzberichte'!$CK$25,'III. Finanzberichte'!$CR$25,'III. Finanzberichte'!$CY$25,'III. Finanzberichte'!$DF$25,'III. Finanzberichte'!$DM$25,'III. Finanzberichte'!$DT$25),2),0)</f>
       </c>
-      <c r="D109" s="240" t="str">
+      <c r="D109" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektverwaltung_LW,2),0)</f>
       </c>
-      <c r="E109" s="202" t="str">
+      <c r="E109" s="201" t="str">
         <f>=ROUND(IFERROR($C$109-$D$109,0),2)</f>
       </c>
       <c r="F109" s="258" t="str">
         <f>=ROUND(IFERROR(($C$109/$D$109)-1,0),4)</f>
       </c>
-      <c r="G109" s="218" t="str">
+      <c r="G109" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$25,'III. Finanzberichte'!$M$25,'III. Finanzberichte'!$T$25,'III. Finanzberichte'!$AA$25,'III. Finanzberichte'!$AH$25,'III. Finanzberichte'!$AO$25,'III. Finanzberichte'!$AV$25,'III. Finanzberichte'!$BC$25,'III. Finanzberichte'!$BJ$25,'III. Finanzberichte'!$BQ$25,'III. Finanzberichte'!$BX$25,'III. Finanzberichte'!$CE$25,'III. Finanzberichte'!$CL$25,'III. Finanzberichte'!$CS$25,'III. Finanzberichte'!$CZ$25,'III. Finanzberichte'!$DG$25,'III. Finanzberichte'!$DN$25,'III. Finanzberichte'!$DU$25),2),0)</f>
       </c>
-      <c r="H109" s="218" t="str">
+      <c r="H109" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Projektverwaltung_EUR,2),0)</f>
       </c>
       <c r="I109" s="182" t="str">
@@ -23620,22 +23638,22 @@
       <c r="B110" s="266" t="s">
         <v>224</v>
       </c>
-      <c r="C110" s="240" t="str">
+      <c r="C110" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$26,'III. Finanzberichte'!$L$26,'III. Finanzberichte'!$S$26,'III. Finanzberichte'!$Z$26,'III. Finanzberichte'!$AG$26,'III. Finanzberichte'!$AN$26,'III. Finanzberichte'!$AU$26,'III. Finanzberichte'!$BB$26,'III. Finanzberichte'!$BI$26,'III. Finanzberichte'!$BP$26,'III. Finanzberichte'!$BW$26,'III. Finanzberichte'!$CD$26,'III. Finanzberichte'!$CK$26,'III. Finanzberichte'!$CR$26,'III. Finanzberichte'!$CY$26,'III. Finanzberichte'!$DF$26,'III. Finanzberichte'!$DM$26,'III. Finanzberichte'!$DT$26),2),0)</f>
       </c>
-      <c r="D110" s="240" t="str">
+      <c r="D110" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Evaluierung_LW,2),0)</f>
       </c>
-      <c r="E110" s="202" t="str">
+      <c r="E110" s="201" t="str">
         <f>=ROUND(IFERROR($C$110-$D$110,0),2)</f>
       </c>
       <c r="F110" s="258" t="str">
         <f>=ROUND(IFERROR(($C$110/$D$110)-1,0),4)</f>
       </c>
-      <c r="G110" s="218" t="str">
+      <c r="G110" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$26,'III. Finanzberichte'!$M$26,'III. Finanzberichte'!$T$26,'III. Finanzberichte'!$AA$26,'III. Finanzberichte'!$AH$26,'III. Finanzberichte'!$AO$26,'III. Finanzberichte'!$AV$26,'III. Finanzberichte'!$BC$26,'III. Finanzberichte'!$BJ$26,'III. Finanzberichte'!$BQ$26,'III. Finanzberichte'!$BX$26,'III. Finanzberichte'!$CE$26,'III. Finanzberichte'!$CL$26,'III. Finanzberichte'!$CS$26,'III. Finanzberichte'!$CZ$26,'III. Finanzberichte'!$DG$26,'III. Finanzberichte'!$DN$26,'III. Finanzberichte'!$DU$26),2),0)</f>
       </c>
-      <c r="H110" s="218" t="str">
+      <c r="H110" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Evaluierung_EUR,2),0)</f>
       </c>
       <c r="I110" s="182" t="str">
@@ -23649,22 +23667,22 @@
       <c r="B111" s="266" t="s">
         <v>227</v>
       </c>
-      <c r="C111" s="240" t="str">
+      <c r="C111" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$27,'III. Finanzberichte'!$L$27,'III. Finanzberichte'!$S$27,'III. Finanzberichte'!$Z$27,'III. Finanzberichte'!$AG$27,'III. Finanzberichte'!$AN$27,'III. Finanzberichte'!$AU$27,'III. Finanzberichte'!$BB$27,'III. Finanzberichte'!$BI$27,'III. Finanzberichte'!$BP$27,'III. Finanzberichte'!$BW$27,'III. Finanzberichte'!$CD$27,'III. Finanzberichte'!$CK$27,'III. Finanzberichte'!$CR$27,'III. Finanzberichte'!$CY$27,'III. Finanzberichte'!$DF$27,'III. Finanzberichte'!$DM$27,'III. Finanzberichte'!$DT$27),2),0)</f>
       </c>
-      <c r="D111" s="240" t="str">
+      <c r="D111" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Audit_LW,2),0)</f>
       </c>
-      <c r="E111" s="202" t="str">
+      <c r="E111" s="201" t="str">
         <f>=ROUND(IFERROR($C$111-$D$111,0),2)</f>
       </c>
       <c r="F111" s="258" t="str">
         <f>=ROUND(IFERROR(($C$111/$D$111)-1,0),4)</f>
       </c>
-      <c r="G111" s="218" t="str">
+      <c r="G111" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$27,'III. Finanzberichte'!$M$27,'III. Finanzberichte'!$T$27,'III. Finanzberichte'!$AA$27,'III. Finanzberichte'!$AH$27,'III. Finanzberichte'!$AO$27,'III. Finanzberichte'!$AV$27,'III. Finanzberichte'!$BC$27,'III. Finanzberichte'!$BJ$27,'III. Finanzberichte'!$BQ$27,'III. Finanzberichte'!$BX$27,'III. Finanzberichte'!$CE$27,'III. Finanzberichte'!$CL$27,'III. Finanzberichte'!$CS$27,'III. Finanzberichte'!$CZ$27,'III. Finanzberichte'!$DG$27,'III. Finanzberichte'!$DN$27,'III. Finanzberichte'!$DU$27),2),0)</f>
       </c>
-      <c r="H111" s="218" t="str">
+      <c r="H111" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Audit_EUR,2),0)</f>
       </c>
       <c r="I111" s="182" t="str">
@@ -23678,22 +23696,22 @@
       <c r="B112" s="266" t="s">
         <v>230</v>
       </c>
-      <c r="C112" s="240" t="str">
+      <c r="C112" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$28,'III. Finanzberichte'!$L$28,'III. Finanzberichte'!$S$28,'III. Finanzberichte'!$Z$28,'III. Finanzberichte'!$AG$28,'III. Finanzberichte'!$AN$28,'III. Finanzberichte'!$AU$28,'III. Finanzberichte'!$BB$28,'III. Finanzberichte'!$BI$28,'III. Finanzberichte'!$BP$28,'III. Finanzberichte'!$BW$28,'III. Finanzberichte'!$CD$28,'III. Finanzberichte'!$CK$28,'III. Finanzberichte'!$CR$28,'III. Finanzberichte'!$CY$28,'III. Finanzberichte'!$DF$28,'III. Finanzberichte'!$DM$28,'III. Finanzberichte'!$DT$28),2),0)</f>
       </c>
-      <c r="D112" s="240" t="str">
+      <c r="D112" s="239" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_LW,2),0)</f>
       </c>
-      <c r="E112" s="202" t="str">
+      <c r="E112" s="201" t="str">
         <f>=ROUND(IFERROR($C$112-$D$112,0),2)</f>
       </c>
       <c r="F112" s="258" t="str">
         <f>=ROUND(IFERROR(($C$112/$D$112)-1,0),4)</f>
       </c>
-      <c r="G112" s="218" t="str">
+      <c r="G112" s="217" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$F$28,'III. Finanzberichte'!$M$28,'III. Finanzberichte'!$T$28,'III. Finanzberichte'!$AA$28,'III. Finanzberichte'!$AH$28,'III. Finanzberichte'!$AO$28,'III. Finanzberichte'!$AV$28,'III. Finanzberichte'!$BC$28,'III. Finanzberichte'!$BJ$28,'III. Finanzberichte'!$BQ$28,'III. Finanzberichte'!$BX$28,'III. Finanzberichte'!$CE$28,'III. Finanzberichte'!$CL$28,'III. Finanzberichte'!$CS$28,'III. Finanzberichte'!$CZ$28,'III. Finanzberichte'!$DG$28,'III. Finanzberichte'!$DN$28,'III. Finanzberichte'!$DU$28),2),0)</f>
       </c>
-      <c r="H112" s="218" t="str">
+      <c r="H112" s="217" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
       <c r="I112" s="182" t="str">

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -4969,7 +4969,7 @@
   <cols>
     <col customWidth="true" max="1" min="1" width="3"/>
     <col customWidth="true" max="2" min="2" width="32"/>
-    <col customWidth="true" max="3" min="3" width="25"/>
+    <col customWidth="true" max="3" min="3" width="43"/>
     <col customWidth="true" max="4" min="4" width="24"/>
     <col customWidth="true" max="5" min="5" width="35"/>
     <col customWidth="true" hidden="true" max="27" min="27" width="9.140625"/>
@@ -7170,42 +7170,42 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="2" min="2" width="16"/>
-    <col customWidth="true" max="6" min="3" width="18"/>
-    <col customWidth="true" max="9" min="9" width="16"/>
-    <col customWidth="true" max="13" min="10" width="18"/>
-    <col customWidth="true" max="16" min="16" width="16"/>
-    <col customWidth="true" max="20" min="17" width="18"/>
-    <col customWidth="true" max="23" min="23" width="16"/>
-    <col customWidth="true" max="27" min="24" width="18"/>
-    <col customWidth="true" max="30" min="30" width="16"/>
-    <col customWidth="true" max="34" min="31" width="18"/>
-    <col customWidth="true" max="37" min="37" width="16"/>
-    <col customWidth="true" max="41" min="38" width="18"/>
-    <col customWidth="true" max="44" min="44" width="16"/>
-    <col customWidth="true" max="48" min="45" width="18"/>
-    <col customWidth="true" max="51" min="51" width="16"/>
-    <col customWidth="true" max="55" min="52" width="18"/>
-    <col customWidth="true" max="58" min="58" width="16"/>
-    <col customWidth="true" max="62" min="59" width="18"/>
-    <col customWidth="true" max="65" min="65" width="16"/>
-    <col customWidth="true" max="69" min="66" width="18"/>
-    <col customWidth="true" max="72" min="72" width="16"/>
-    <col customWidth="true" max="76" min="73" width="18"/>
-    <col customWidth="true" max="79" min="79" width="16"/>
-    <col customWidth="true" max="83" min="80" width="18"/>
-    <col customWidth="true" max="86" min="86" width="16"/>
-    <col customWidth="true" max="90" min="87" width="18"/>
-    <col customWidth="true" max="93" min="93" width="16"/>
-    <col customWidth="true" max="97" min="94" width="18"/>
-    <col customWidth="true" max="100" min="100" width="16"/>
-    <col customWidth="true" max="104" min="101" width="18"/>
-    <col customWidth="true" max="107" min="107" width="16"/>
-    <col customWidth="true" max="111" min="108" width="18"/>
-    <col customWidth="true" max="114" min="114" width="16"/>
-    <col customWidth="true" max="118" min="115" width="18"/>
-    <col customWidth="true" max="121" min="121" width="16"/>
-    <col customWidth="true" max="125" min="122" width="18"/>
+    <col customWidth="true" max="2" min="2" width="30.43"/>
+    <col customWidth="true" max="6" min="3" width="20.71"/>
+    <col customWidth="true" hidden="true" max="9" min="9" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="13" min="10" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="16" min="16" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="20" min="17" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="23" min="23" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="27" min="24" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="30" min="30" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="34" min="31" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="37" min="37" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="41" min="38" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="44" min="44" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="48" min="45" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="51" min="51" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="55" min="52" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="58" min="58" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="62" min="59" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="65" min="65" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="69" min="66" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="72" min="72" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="76" min="73" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="79" min="79" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="83" min="80" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="86" min="86" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="90" min="87" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="93" min="93" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="97" min="94" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="100" min="100" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="104" min="101" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="107" min="107" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="111" min="108" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="114" min="114" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="118" min="115" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="121" min="121" outlineLevel="1" width="30.43"/>
+    <col customWidth="true" hidden="true" max="125" min="122" outlineLevel="1" width="20.71"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -18455,42 +18455,42 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="2" min="2" width="25"/>
-    <col customWidth="true" max="4" min="3" width="18"/>
-    <col customWidth="true" max="6" min="6" width="25"/>
-    <col customWidth="true" max="8" min="7" width="18"/>
-    <col customWidth="true" max="10" min="10" width="25"/>
-    <col customWidth="true" max="12" min="11" width="18"/>
-    <col customWidth="true" max="14" min="14" width="25"/>
-    <col customWidth="true" max="16" min="15" width="18"/>
-    <col customWidth="true" max="18" min="18" width="25"/>
-    <col customWidth="true" max="20" min="19" width="18"/>
-    <col customWidth="true" max="22" min="22" width="25"/>
-    <col customWidth="true" max="24" min="23" width="18"/>
-    <col customWidth="true" max="26" min="26" width="25"/>
-    <col customWidth="true" max="28" min="27" width="18"/>
-    <col customWidth="true" max="30" min="30" width="25"/>
-    <col customWidth="true" max="32" min="31" width="18"/>
-    <col customWidth="true" max="34" min="34" width="25"/>
-    <col customWidth="true" max="36" min="35" width="18"/>
-    <col customWidth="true" max="38" min="38" width="25"/>
-    <col customWidth="true" max="40" min="39" width="18"/>
-    <col customWidth="true" max="42" min="42" width="25"/>
-    <col customWidth="true" max="44" min="43" width="18"/>
-    <col customWidth="true" max="46" min="46" width="25"/>
-    <col customWidth="true" max="48" min="47" width="18"/>
-    <col customWidth="true" max="50" min="50" width="25"/>
-    <col customWidth="true" max="52" min="51" width="18"/>
-    <col customWidth="true" max="54" min="54" width="25"/>
-    <col customWidth="true" max="56" min="55" width="18"/>
-    <col customWidth="true" max="58" min="58" width="25"/>
-    <col customWidth="true" max="60" min="59" width="18"/>
-    <col customWidth="true" max="62" min="62" width="25"/>
-    <col customWidth="true" max="64" min="63" width="18"/>
-    <col customWidth="true" max="66" min="66" width="25"/>
-    <col customWidth="true" max="68" min="67" width="18"/>
-    <col customWidth="true" max="70" min="70" width="25"/>
-    <col customWidth="true" max="72" min="71" width="18"/>
+    <col customWidth="true" max="2" min="2" width="25.14"/>
+    <col customWidth="true" max="4" min="3" width="20.71"/>
+    <col customWidth="true" hidden="true" max="6" min="6" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="8" min="7" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="10" min="10" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="12" min="11" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="14" min="14" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="16" min="15" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="18" min="18" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="20" min="19" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="22" min="22" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="24" min="23" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="26" min="26" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="28" min="27" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="30" min="30" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="32" min="31" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="34" min="34" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="36" min="35" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="38" min="38" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="40" min="39" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="42" min="42" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="44" min="43" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="46" min="46" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="48" min="47" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="50" min="50" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="52" min="51" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="54" min="54" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="56" min="55" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="58" min="58" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="60" min="59" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="62" min="62" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="64" min="63" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="66" min="66" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="68" min="67" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="70" min="70" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="72" min="71" outlineLevel="1" width="20.71"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="C33" s="228"/>
       <c r="D33" s="229" t="str">
-        <f>=ROUND($D$26-MAX(0,$D$29)-MAX(0,$D$32),2)</f>
+        <f>=ROUND(MAX(0,$D$26-MAX(0,$D$32)),2)</f>
       </c>
       <c r="F33" s="227" t="s">
         <v>361</v>
@@ -22072,7 +22072,7 @@
       <c r="G33" s="228"/>
       <c r="H33" s="228"/>
       <c r="I33" s="229" t="str">
-        <f>=ROUND($I$27-MAX(0,$I$29)-MAX(0,$I$32),2)</f>
+        <f>=ROUND(MAX(0,$I$27-MAX(0,$I$32)),2)</f>
       </c>
     </row>
     <row r="36" ht="22" customHeight="true">

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -3320,7 +3320,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
     <dxf>
       <font>
         <name val="Segoe UI"/>
@@ -3600,6 +3600,44 @@
       <font>
         <name val="Segoe UI"/>
         <family val="2"/>
+        <color rgb="FFA0A0A0"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color rgb="FFD3D3D3"/>
+        </left>
+        <top style="thin">
+          <color rgb="FFD3D3D3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD3D3D3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment/>
+      <border>
+        <right style="medium">
+          <color rgb="FF808080"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Segoe UI"/>
+        <family val="2"/>
         <b val="1"/>
         <color rgb="FF006100"/>
       </font>
@@ -3631,7 +3669,7 @@
         <b val="1"/>
         <color rgb="FF9C0006"/>
       </font>
-      <numFmt numFmtId="165" formatCode="#,##0.00"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00"/>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
@@ -3646,7 +3684,7 @@
         <b val="1"/>
         <color rgb="FF9C0006"/>
       </font>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;"/>
+      <numFmt numFmtId="167" formatCode="#,##0.00&quot; €&quot;"/>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
@@ -3661,7 +3699,7 @@
         <b val="1"/>
         <color rgb="FF9C0006"/>
       </font>
-      <numFmt numFmtId="167" formatCode="0.0%"/>
+      <numFmt numFmtId="168" formatCode="0.0%"/>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
@@ -3676,7 +3714,7 @@
         <b val="1"/>
         <color rgb="FF9C640C"/>
       </font>
-      <numFmt numFmtId="168" formatCode="0.0%"/>
+      <numFmt numFmtId="169" formatCode="0.0%"/>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFCF3CF"/>
@@ -23932,113 +23970,163 @@
       <formula>$C$18&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I23">
+    <cfRule type="expression" dxfId="11" priority="19">
+      <formula>$F$23="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23">
+    <cfRule type="expression" dxfId="12" priority="20">
+      <formula>$F$23="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24">
+    <cfRule type="expression" dxfId="11" priority="21">
+      <formula>$F$24="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24">
+    <cfRule type="expression" dxfId="12" priority="22">
+      <formula>$F$24="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25">
+    <cfRule type="expression" dxfId="11" priority="23">
+      <formula>$F$25="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25">
+    <cfRule type="expression" dxfId="12" priority="24">
+      <formula>$F$25="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C46">
-    <cfRule type="expression" dxfId="11" priority="19">
+    <cfRule type="expression" dxfId="13" priority="25">
       <formula>$C$46="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46">
-    <cfRule type="expression" dxfId="12" priority="20">
+    <cfRule type="expression" dxfId="14" priority="26">
       <formula>$C$46&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46">
-    <cfRule type="expression" dxfId="11" priority="21">
+    <cfRule type="expression" dxfId="13" priority="27">
       <formula>$E$46="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46">
-    <cfRule type="expression" dxfId="12" priority="22">
+    <cfRule type="expression" dxfId="14" priority="28">
       <formula>$E$46&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C47">
-    <cfRule type="expression" dxfId="13" priority="23">
+    <cfRule type="expression" dxfId="15" priority="29">
       <formula>$C$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="expression" dxfId="14" priority="24">
+    <cfRule type="expression" dxfId="16" priority="30">
       <formula>$E$47&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53:F56">
-    <cfRule type="expression" dxfId="15" priority="25">
+    <cfRule type="expression" dxfId="17" priority="31">
       <formula>F53&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53:F56">
-    <cfRule type="expression" dxfId="16" priority="26">
+    <cfRule type="expression" dxfId="18" priority="32">
       <formula>AND(F53&gt;=0.1,F53&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J53:J56">
-    <cfRule type="expression" dxfId="15" priority="27">
+    <cfRule type="expression" dxfId="17" priority="33">
       <formula>J53&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J53:J56">
-    <cfRule type="expression" dxfId="16" priority="28">
+    <cfRule type="expression" dxfId="18" priority="34">
       <formula>AND(J53&gt;=0.1,J53&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62:F69">
-    <cfRule type="expression" dxfId="15" priority="29">
+    <cfRule type="expression" dxfId="17" priority="35">
       <formula>F62&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62:F69">
-    <cfRule type="expression" dxfId="16" priority="30">
+    <cfRule type="expression" dxfId="18" priority="36">
       <formula>AND(F62&gt;=0.1,F62&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J62:J69">
-    <cfRule type="expression" dxfId="15" priority="31">
+    <cfRule type="expression" dxfId="17" priority="37">
       <formula>J62&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J62:J69">
-    <cfRule type="expression" dxfId="16" priority="32">
+    <cfRule type="expression" dxfId="18" priority="38">
       <formula>AND(J62&gt;=0.1,J62&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I86">
+    <cfRule type="expression" dxfId="11" priority="39">
+      <formula>$F$86="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I86">
+    <cfRule type="expression" dxfId="12" priority="40">
+      <formula>$F$86="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I87">
+    <cfRule type="expression" dxfId="11" priority="41">
+      <formula>$F$87="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I87">
+    <cfRule type="expression" dxfId="12" priority="42">
+      <formula>$F$87="Kein Abzug"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F96:F99">
-    <cfRule type="expression" dxfId="15" priority="33">
+    <cfRule type="expression" dxfId="17" priority="43">
       <formula>F96&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F99">
-    <cfRule type="expression" dxfId="16" priority="34">
+    <cfRule type="expression" dxfId="18" priority="44">
       <formula>AND(F96&gt;=0.1,F96&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J96:J99">
-    <cfRule type="expression" dxfId="15" priority="35">
+    <cfRule type="expression" dxfId="17" priority="45">
       <formula>J96&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J96:J99">
-    <cfRule type="expression" dxfId="16" priority="36">
+    <cfRule type="expression" dxfId="18" priority="46">
       <formula>AND(J96&gt;=0.1,J96&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:F112">
-    <cfRule type="expression" dxfId="15" priority="37">
+    <cfRule type="expression" dxfId="17" priority="47">
       <formula>F105&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:F112">
-    <cfRule type="expression" dxfId="16" priority="38">
+    <cfRule type="expression" dxfId="18" priority="48">
       <formula>AND(F105&gt;=0.1,F105&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J105:J112">
-    <cfRule type="expression" dxfId="15" priority="39">
+    <cfRule type="expression" dxfId="17" priority="49">
       <formula>J105&gt;=0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J105:J112">
-    <cfRule type="expression" dxfId="16" priority="40">
+    <cfRule type="expression" dxfId="18" priority="50">
       <formula>AND(J105&gt;=0.1,J105&lt;0.2)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -18493,41 +18493,41 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="2" min="2" width="25.14"/>
+    <col customWidth="true" max="2" min="2" width="32"/>
     <col customWidth="true" max="4" min="3" width="20.71"/>
-    <col customWidth="true" hidden="true" max="6" min="6" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="6" min="6" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="8" min="7" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="10" min="10" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="10" min="10" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="12" min="11" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="14" min="14" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="14" min="14" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="16" min="15" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="18" min="18" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="18" min="18" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="20" min="19" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="22" min="22" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="22" min="22" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="24" min="23" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="26" min="26" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="26" min="26" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="28" min="27" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="30" min="30" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="30" min="30" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="32" min="31" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="34" min="34" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="34" min="34" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="36" min="35" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="38" min="38" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="38" min="38" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="40" min="39" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="42" min="42" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="42" min="42" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="44" min="43" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="46" min="46" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="46" min="46" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="48" min="47" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="50" min="50" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="50" min="50" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="52" min="51" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="54" min="54" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="54" min="54" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="56" min="55" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="58" min="58" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="58" min="58" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="60" min="59" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="62" min="62" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="62" min="62" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="64" min="63" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="66" min="66" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="66" min="66" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="68" min="67" outlineLevel="1" width="20.71"/>
-    <col customWidth="true" hidden="true" max="70" min="70" outlineLevel="1" width="25.14"/>
+    <col customWidth="true" hidden="true" max="70" min="70" outlineLevel="1" width="32"/>
     <col customWidth="true" hidden="true" max="72" min="71" outlineLevel="1" width="20.71"/>
   </cols>
   <sheetData>

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -7209,41 +7209,41 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="2" min="2" width="30.43"/>
-    <col customWidth="true" max="6" min="3" width="20.71"/>
+    <col customWidth="true" max="6" min="3" width="24.71"/>
     <col customWidth="true" hidden="true" max="9" min="9" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="13" min="10" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="13" min="10" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="16" min="16" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="20" min="17" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="20" min="17" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="23" min="23" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="27" min="24" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="27" min="24" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="30" min="30" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="34" min="31" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="34" min="31" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="37" min="37" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="41" min="38" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="41" min="38" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="44" min="44" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="48" min="45" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="48" min="45" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="51" min="51" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="55" min="52" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="55" min="52" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="58" min="58" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="62" min="59" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="62" min="59" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="65" min="65" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="69" min="66" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="69" min="66" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="72" min="72" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="76" min="73" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="76" min="73" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="79" min="79" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="83" min="80" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="83" min="80" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="86" min="86" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="90" min="87" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="90" min="87" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="93" min="93" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="97" min="94" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="97" min="94" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="100" min="100" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="104" min="101" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="104" min="101" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="107" min="107" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="111" min="108" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="111" min="108" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="114" min="114" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="118" min="115" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="118" min="115" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="121" min="121" outlineLevel="1" width="30.43"/>
-    <col customWidth="true" hidden="true" max="125" min="122" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="125" min="122" outlineLevel="1" width="24.71"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -18494,41 +18494,41 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="2" min="2" width="32"/>
-    <col customWidth="true" max="4" min="3" width="20.71"/>
+    <col customWidth="true" max="4" min="3" width="24.71"/>
     <col customWidth="true" hidden="true" max="6" min="6" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="8" min="7" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="8" min="7" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="10" min="10" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="12" min="11" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="12" min="11" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="14" min="14" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="16" min="15" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="16" min="15" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="18" min="18" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="20" min="19" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="20" min="19" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="22" min="22" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="24" min="23" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="24" min="23" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="26" min="26" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="28" min="27" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="28" min="27" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="30" min="30" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="32" min="31" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="32" min="31" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="34" min="34" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="36" min="35" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="36" min="35" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="38" min="38" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="40" min="39" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="40" min="39" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="42" min="42" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="44" min="43" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="44" min="43" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="46" min="46" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="48" min="47" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="48" min="47" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="50" min="50" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="52" min="51" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="52" min="51" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="54" min="54" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="56" min="55" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="56" min="55" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="58" min="58" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="60" min="59" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="60" min="59" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="62" min="62" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="64" min="63" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="64" min="63" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="66" min="66" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="68" min="67" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="68" min="67" outlineLevel="1" width="24.71"/>
     <col customWidth="true" hidden="true" max="70" min="70" outlineLevel="1" width="32"/>
-    <col customWidth="true" hidden="true" max="72" min="71" outlineLevel="1" width="20.71"/>
+    <col customWidth="true" hidden="true" max="72" min="71" outlineLevel="1" width="24.71"/>
   </cols>
   <sheetData>
     <row r="3">

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -1389,11 +1389,11 @@
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="168" formatCode="@"/>
-    <numFmt numFmtId="169" formatCode="DD.MM.YYYY"/>
-    <numFmt numFmtId="170" formatCode="0&quot; Monate&quot;"/>
-    <numFmt numFmtId="171" formatCode="0.000000"/>
-    <numFmt numFmtId="172" formatCode="0"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0&quot; Monate&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.000000"/>
+    <numFmt numFmtId="171" formatCode="0"/>
+    <numFmt numFmtId="172" formatCode="0.0%"/>
+    <numFmt numFmtId="173" formatCode="DD.MM.YYYY"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -2584,16 +2584,16 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="44" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="5" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="6" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="169" fontId="3" fillId="6" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2752,7 +2752,7 @@
     <xf numFmtId="167" fontId="8" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="170" fontId="8" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2767,7 +2767,7 @@
     <xf numFmtId="167" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="170" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2782,7 +2782,7 @@
     <xf numFmtId="167" fontId="12" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="12" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="170" fontId="12" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2794,7 +2794,7 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="44" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="8" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="169" fontId="3" fillId="8" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2854,7 +2854,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2881,10 +2881,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2983,10 +2983,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -2995,7 +2995,7 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="38" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -3007,10 +3007,10 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="40" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -3022,19 +3022,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="8" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="8" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="20" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="8" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="8" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="11" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -3043,7 +3043,7 @@
     <xf numFmtId="166" fontId="25" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="25" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="25" fillId="11" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -3061,16 +3061,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="11" borderId="32" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -3079,103 +3079,103 @@
     <xf numFmtId="166" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="12" fillId="8" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="12" fillId="8" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="8" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="171" fontId="12" fillId="8" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="25" fillId="11" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="172" fontId="25" fillId="11" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -3184,12 +3184,12 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="173" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="3" fillId="8" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3211,12 +3211,12 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="173" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="3" fillId="8" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3241,15 +3241,15 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="173" fontId="3" fillId="6" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="3" fillId="6" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="3" fillId="6" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="6" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3274,13 +3274,13 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="173" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="3" fillId="6" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="51" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -5129,13 +5129,13 @@
         <v>166</v>
       </c>
       <c r="C9" s="8" t="str">
-        <f>=IF(OR($C$8="",$E$8=""),"",TEXT($C$8,"dd.mm.yyyy")&amp;" - "&amp;TEXT($E$8,"dd.mm.yyyy"))</f>
+        <f>=IF(AND(ISNUMBER($C$8),ISNUMBER($E$8)),TEXT($C$8,"DD.MM.YYYY")&amp;" - "&amp;TEXT($E$8,"DD.MM.YYYY"),"")</f>
       </c>
       <c r="D9" s="4" t="s">
         <v>167</v>
       </c>
       <c r="E9" s="8" t="str">
-        <f>=IF(OR($C$8="",$E$8=""),"",DATEDIF($C$8,$E$8+1,"M"))</f>
+        <f>=IF(AND(ISNUMBER($C$8),ISNUMBER($E$8)),DATEDIF($C$8,$E$8+1,"M"),"")</f>
       </c>
       <c r="AA9" s="3" t="s">
         <v>10</v>

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -5129,7 +5129,7 @@
         <v>166</v>
       </c>
       <c r="C9" s="8" t="str">
-        <f>=IF(AND(ISNUMBER($C$8),ISNUMBER($E$8)),TEXT($C$8,"DD.MM.YYYY")&amp;" - "&amp;TEXT($E$8,"DD.MM.YYYY"),"")</f>
+        <f>=IF(AND(ISNUMBER($C$8),ISNUMBER($E$8)),TEXT(DAY($C$8),"00")&amp;"."&amp;TEXT(MONTH($C$8),"00")&amp;"."&amp;TEXT(YEAR($C$8),"0000")&amp;" - "&amp;TEXT(DAY($E$8),"00")&amp;"."&amp;TEXT(MONTH($E$8),"00")&amp;"."&amp;TEXT(YEAR($E$8),"0000"),"")</f>
       </c>
       <c r="D9" s="4" t="s">
         <v>167</v>

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -24240,11 +24240,11 @@
         <f>=IF(BK1=1,"Periode "&amp;BJ1,"")</f>
       </c>
       <c r="BN1" cm="1" s="3">
-        <f t="array" ref="BN1">_xlfn.VSTACK("Neuste MA",_xlfn._xlws.FILTER($BE$1:$BE$18,($BB$1:$BB$18='V. AUSWERTUNG'!E81+1)*($BC$1:$BC$18=1),""))</f>
+        <f t="array" ref="BN1">_xlfn.VSTACK(_xlfn._xlws.FILTER($BE$1:$BE$18,($BB$1:$BB$18='V. AUSWERTUNG'!E81+1)*($BC$1:$BC$18=1),""),"Neuste MA")</f>
         <v>0</v>
       </c>
       <c r="BP1" cm="1" s="3">
-        <f t="array" ref="BP1">_xlfn.VSTACK("Neuester FB","Kein Finanzbericht (Projektbeginn)",_xlfn._xlws.FILTER($BL$1:$BL$18,$BK$1:$BK$18=1,""))</f>
+        <f t="array" ref="BP1">_xlfn.VSTACK("Kein Finanzbericht (Projektbeginn)",_xlfn._xlws.FILTER($BL$1:$BL$18,$BK$1:$BK$18=1,""),"Neuester FB")</f>
         <v>0</v>
       </c>
       <c r="BR1" t="str">

--- a/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
+++ b/sidecars/Vorpruefung/vorpruefung_befuellt.xlsx
@@ -46,7 +46,7 @@
     <definedName name="Gesamtausgaben_LW">'I. Budget'!$O$12</definedName>
     <definedName name="Gesamtausgaben_EUR">'I. Budget'!$P$12</definedName>
     <definedName name="Budget_ID_Liste">OFFSET('I. Budget'!$S$1, 0, 0, COUNTA('I. Budget'!S:S), 1)</definedName>
-    <definedName name="Geber_Liste">OFFSET('I. Budget'!$K$19,0,0,MAX(1,COUNTA('I. Budget'!$K$19:$K$20)),1)</definedName>
+    <definedName name="Geber_Liste">OFFSET('I. Budget'!$K$19,0,0,MAX(1,COUNTA('I. Budget'!$K$19:$K$21)),1)</definedName>
     <definedName name="Reserve_Freigabe">'I. Budget'!$K$5</definedName>
     <definedName name="FB_Kurs_1">'III. Finanzberichte'!$C$8</definedName>
     <definedName name="FB_SaldoLC_1">'III. Finanzberichte'!$C$31</definedName>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
   <si>
     <t xml:space="preserve">  DASHBOARD (v1.0)</t>
   </si>
@@ -885,6 +885,9 @@
   </si>
   <si>
     <t>Bank XY</t>
+  </si>
+  <si>
+    <t>Sonstige</t>
   </si>
   <si>
     <t>Reserve Freigabe</t>
@@ -3890,8 +3893,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TblDrittmittel" displayName="TblDrittmittel" ref="K18:M20">
-  <autoFilter ref="K18:M20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TblDrittmittel" displayName="TblDrittmittel" ref="K18:M21">
+  <autoFilter ref="K18:M21"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Name des Gebers"/>
     <tableColumn id="2" name="Betrag (LC)"/>
@@ -6104,7 +6107,7 @@
       <c r="H2" s="17"/>
       <c r="I2" s="46"/>
       <c r="K2" s="65" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3">
@@ -6130,7 +6133,7 @@
       </c>
       <c r="I4" s="50"/>
       <c r="K4" s="67" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O4" s="3" t="str">
         <f>=SUMIFS(TblBudgetAusgaben[Betrag (LC)],TblBudgetAusgaben[Kostenkategorie],"Bauausgaben")</f>
@@ -6221,7 +6224,7 @@
       <c r="B8" s="47"/>
       <c r="I8" s="48"/>
       <c r="K8" s="70" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L8" s="70"/>
       <c r="M8" s="70"/>
@@ -6483,13 +6486,13 @@
       <c r="I20" s="41">
         <v>10000</v>
       </c>
-      <c r="K20" s="42" t="s">
+      <c r="K20" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="L20" s="43">
+      <c r="L20" s="24">
         <v>1250000</v>
       </c>
-      <c r="M20" s="44">
+      <c r="M20" s="41">
         <v>10000</v>
       </c>
     </row>
@@ -6518,6 +6521,11 @@
       <c r="I21" s="41">
         <v>8000</v>
       </c>
+      <c r="K21" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="L21" s="43"/>
+      <c r="M21" s="44"/>
     </row>
     <row r="22">
       <c r="B22" s="40" t="s">
@@ -6725,7 +6733,7 @@
     </row>
     <row r="31">
       <c r="B31" s="73" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
@@ -6733,7 +6741,7 @@
     </row>
     <row r="32">
       <c r="B32" s="76" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C32" s="72"/>
       <c r="D32" s="72"/>
@@ -6743,7 +6751,7 @@
     </row>
     <row r="33">
       <c r="B33" s="76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C33" s="72"/>
       <c r="D33" s="72"/>
@@ -6753,7 +6761,7 @@
     </row>
     <row r="34">
       <c r="B34" s="76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C34" s="72"/>
       <c r="D34" s="72"/>
@@ -6763,7 +6771,7 @@
     </row>
     <row r="35">
       <c r="B35" s="76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C35" s="72"/>
       <c r="D35" s="72"/>
@@ -6773,7 +6781,7 @@
     </row>
     <row r="36">
       <c r="B36" s="78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C36" s="79"/>
       <c r="D36" s="79"/>
@@ -6885,40 +6893,40 @@
   <sheetData>
     <row r="1">
       <c r="Z1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="true">
       <c r="B2" s="81" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C2" s="81"/>
       <c r="D2" s="81"/>
       <c r="E2" s="81"/>
       <c r="Z2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
       <c r="Z3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="true">
       <c r="B4" s="88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C4" s="89" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D4" s="89" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E4" s="90" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5">
@@ -6939,7 +6947,7 @@
         <v>45672</v>
       </c>
       <c r="Z5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6">
@@ -6960,7 +6968,7 @@
         <v>45762</v>
       </c>
       <c r="Z6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7">
@@ -6981,7 +6989,7 @@
         <v>45853</v>
       </c>
       <c r="Z7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8">
@@ -6990,7 +6998,7 @@
       <c r="D8" s="83"/>
       <c r="E8" s="96"/>
       <c r="Z8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9">
@@ -6999,7 +7007,7 @@
       <c r="D9" s="83"/>
       <c r="E9" s="96"/>
       <c r="Z9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -7008,7 +7016,7 @@
       <c r="D10" s="83"/>
       <c r="E10" s="96"/>
       <c r="Z10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -7017,7 +7025,7 @@
       <c r="D11" s="83"/>
       <c r="E11" s="96"/>
       <c r="Z11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -7026,7 +7034,7 @@
       <c r="D12" s="83"/>
       <c r="E12" s="96"/>
       <c r="Z12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13">
@@ -7035,7 +7043,7 @@
       <c r="D13" s="83"/>
       <c r="E13" s="96"/>
       <c r="Z13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14">
@@ -7044,7 +7052,7 @@
       <c r="D14" s="83"/>
       <c r="E14" s="96"/>
       <c r="Z14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15">
@@ -7053,7 +7061,7 @@
       <c r="D15" s="83"/>
       <c r="E15" s="96"/>
       <c r="Z15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16">
@@ -7062,7 +7070,7 @@
       <c r="D16" s="83"/>
       <c r="E16" s="96"/>
       <c r="Z16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17">
@@ -7071,7 +7079,7 @@
       <c r="D17" s="83"/>
       <c r="E17" s="96"/>
       <c r="Z17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18">
@@ -7080,7 +7088,7 @@
       <c r="D18" s="83"/>
       <c r="E18" s="96"/>
       <c r="Z18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19">
@@ -7089,7 +7097,7 @@
       <c r="D19" s="83"/>
       <c r="E19" s="96"/>
       <c r="Z19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20">
@@ -7098,7 +7106,7 @@
       <c r="D20" s="83"/>
       <c r="E20" s="96"/>
       <c r="Z20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21">
@@ -7107,7 +7115,7 @@
       <c r="D21" s="83"/>
       <c r="E21" s="96"/>
       <c r="Z21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22">
@@ -7116,12 +7124,12 @@
       <c r="D22" s="99"/>
       <c r="E22" s="100"/>
       <c r="Z22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="101" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C23" s="102"/>
       <c r="D23" s="103" t="str">
@@ -7129,72 +7137,72 @@
       </c>
       <c r="E23" s="104"/>
       <c r="Z23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24">
       <c r="Z24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25">
       <c r="Z25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26">
       <c r="Z26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27">
       <c r="Z27" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28">
       <c r="Z28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29">
       <c r="Z29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30">
       <c r="Z30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31">
       <c r="Z31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32">
       <c r="Z32" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33">
       <c r="Z33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34">
       <c r="Z34" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35">
       <c r="Z35" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36">
       <c r="Z36" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -7263,216 +7271,216 @@
   <sheetData>
     <row r="3">
       <c r="H3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="V3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AC3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AJ3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AX3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BE3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BL3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BS3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BZ3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="CG3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="CN3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="CU3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="DB3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="DI3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="DP3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C4" s="135" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D4" s="135"/>
       <c r="E4" s="136"/>
       <c r="F4" s="137"/>
       <c r="I4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J4" s="135" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K4" s="135"/>
       <c r="L4" s="136"/>
       <c r="M4" s="137"/>
       <c r="P4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q4" s="135" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R4" s="135"/>
       <c r="S4" s="136"/>
       <c r="T4" s="137"/>
       <c r="W4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="X4" s="135" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Y4" s="135"/>
       <c r="Z4" s="136"/>
       <c r="AA4" s="137"/>
       <c r="AD4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AE4" s="135" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AF4" s="135"/>
       <c r="AG4" s="136"/>
       <c r="AH4" s="137"/>
       <c r="AK4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM4" s="135"/>
       <c r="AN4" s="136"/>
       <c r="AO4" s="137"/>
       <c r="AR4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AS4" s="135" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AT4" s="135"/>
       <c r="AU4" s="136"/>
       <c r="AV4" s="137"/>
       <c r="AY4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AZ4" s="135" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="BA4" s="135"/>
       <c r="BB4" s="136"/>
       <c r="BC4" s="137"/>
       <c r="BF4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BG4" s="135" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="BH4" s="135"/>
       <c r="BI4" s="136"/>
       <c r="BJ4" s="137"/>
       <c r="BM4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BN4" s="135" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BO4" s="135"/>
       <c r="BP4" s="136"/>
       <c r="BQ4" s="137"/>
       <c r="BT4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BU4" s="135" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BV4" s="135"/>
       <c r="BW4" s="136"/>
       <c r="BX4" s="137"/>
       <c r="CA4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CB4" s="135" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CC4" s="135"/>
       <c r="CD4" s="136"/>
       <c r="CE4" s="137"/>
       <c r="CH4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CI4" s="135" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="CJ4" s="135"/>
       <c r="CK4" s="136"/>
       <c r="CL4" s="137"/>
       <c r="CO4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CP4" s="135" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="CQ4" s="135"/>
       <c r="CR4" s="136"/>
       <c r="CS4" s="137"/>
       <c r="CV4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CW4" s="135" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="CX4" s="135"/>
       <c r="CY4" s="136"/>
       <c r="CZ4" s="137"/>
       <c r="DC4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="DD4" s="135" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="DE4" s="135"/>
       <c r="DF4" s="136"/>
       <c r="DG4" s="137"/>
       <c r="DJ4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="DK4" s="135" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="DL4" s="135"/>
       <c r="DM4" s="136"/>
       <c r="DN4" s="137"/>
       <c r="DQ4" s="134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="DR4" s="135" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="DS4" s="135"/>
       <c r="DT4" s="136"/>
@@ -7480,7 +7488,7 @@
     </row>
     <row r="5">
       <c r="B5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C5" s="108">
         <v>45658</v>
@@ -7488,7 +7496,7 @@
       <c r="D5" s="108"/>
       <c r="F5" s="48"/>
       <c r="I5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J5" s="108">
         <v>45839</v>
@@ -7496,97 +7504,97 @@
       <c r="K5" s="108"/>
       <c r="M5" s="48"/>
       <c r="P5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q5" s="108"/>
       <c r="R5" s="108"/>
       <c r="T5" s="48"/>
       <c r="W5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="X5" s="108"/>
       <c r="Y5" s="108"/>
       <c r="AA5" s="48"/>
       <c r="AD5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AE5" s="108"/>
       <c r="AF5" s="108"/>
       <c r="AH5" s="48"/>
       <c r="AK5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL5" s="108"/>
       <c r="AM5" s="108"/>
       <c r="AO5" s="48"/>
       <c r="AR5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AS5" s="108"/>
       <c r="AT5" s="108"/>
       <c r="AV5" s="48"/>
       <c r="AY5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AZ5" s="108"/>
       <c r="BA5" s="108"/>
       <c r="BC5" s="48"/>
       <c r="BF5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BG5" s="108"/>
       <c r="BH5" s="108"/>
       <c r="BJ5" s="48"/>
       <c r="BM5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BN5" s="108"/>
       <c r="BO5" s="108"/>
       <c r="BQ5" s="48"/>
       <c r="BT5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BU5" s="108"/>
       <c r="BV5" s="108"/>
       <c r="BX5" s="48"/>
       <c r="CA5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="CB5" s="108"/>
       <c r="CC5" s="108"/>
       <c r="CE5" s="48"/>
       <c r="CH5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="CI5" s="108"/>
       <c r="CJ5" s="108"/>
       <c r="CL5" s="48"/>
       <c r="CO5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="CP5" s="108"/>
       <c r="CQ5" s="108"/>
       <c r="CS5" s="48"/>
       <c r="CV5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="CW5" s="108"/>
       <c r="CX5" s="108"/>
       <c r="CZ5" s="48"/>
       <c r="DC5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="DD5" s="108"/>
       <c r="DE5" s="108"/>
       <c r="DG5" s="48"/>
       <c r="DJ5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="DK5" s="108"/>
       <c r="DL5" s="108"/>
       <c r="DN5" s="48"/>
       <c r="DQ5" s="138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="DR5" s="108"/>
       <c r="DS5" s="108"/>
@@ -7594,7 +7602,7 @@
     </row>
     <row r="6">
       <c r="B6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C6" s="108">
         <v>45838</v>
@@ -7602,7 +7610,7 @@
       <c r="D6" s="108"/>
       <c r="F6" s="48"/>
       <c r="I6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J6" s="108">
         <v>46022</v>
@@ -7610,97 +7618,97 @@
       <c r="K6" s="108"/>
       <c r="M6" s="48"/>
       <c r="P6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q6" s="108"/>
       <c r="R6" s="108"/>
       <c r="T6" s="48"/>
       <c r="W6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="X6" s="108"/>
       <c r="Y6" s="108"/>
       <c r="AA6" s="48"/>
       <c r="AD6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AE6" s="108"/>
       <c r="AF6" s="108"/>
       <c r="AH6" s="48"/>
       <c r="AK6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL6" s="108"/>
       <c r="AM6" s="108"/>
       <c r="AO6" s="48"/>
       <c r="AR6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AS6" s="108"/>
       <c r="AT6" s="108"/>
       <c r="AV6" s="48"/>
       <c r="AY6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AZ6" s="108"/>
       <c r="BA6" s="108"/>
       <c r="BC6" s="48"/>
       <c r="BF6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG6" s="108"/>
       <c r="BH6" s="108"/>
       <c r="BJ6" s="48"/>
       <c r="BM6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BN6" s="108"/>
       <c r="BO6" s="108"/>
       <c r="BQ6" s="48"/>
       <c r="BT6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BU6" s="108"/>
       <c r="BV6" s="108"/>
       <c r="BX6" s="48"/>
       <c r="CA6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CB6" s="108"/>
       <c r="CC6" s="108"/>
       <c r="CE6" s="48"/>
       <c r="CH6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CI6" s="108"/>
       <c r="CJ6" s="108"/>
       <c r="CL6" s="48"/>
       <c r="CO6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CP6" s="108"/>
       <c r="CQ6" s="108"/>
       <c r="CS6" s="48"/>
       <c r="CV6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="CW6" s="108"/>
       <c r="CX6" s="108"/>
       <c r="CZ6" s="48"/>
       <c r="DC6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DD6" s="108"/>
       <c r="DE6" s="108"/>
       <c r="DG6" s="48"/>
       <c r="DJ6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DK6" s="108"/>
       <c r="DL6" s="108"/>
       <c r="DN6" s="48"/>
       <c r="DQ6" s="138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="DR6" s="108"/>
       <c r="DS6" s="108"/>
@@ -7708,7 +7716,7 @@
     </row>
     <row r="7">
       <c r="B7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C7" s="109" t="str">
         <f>=IF(OR(C5="",C6=""),"",DATEDIF(C5,C6,"m")+1)</f>
@@ -7717,7 +7725,7 @@
       <c r="D7" s="109"/>
       <c r="F7" s="48"/>
       <c r="I7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J7" s="109" t="str">
         <f>=IF(OR(J5="",J6=""),"",DATEDIF(J5,J6,"m")+1)</f>
@@ -7726,7 +7734,7 @@
       <c r="K7" s="109"/>
       <c r="M7" s="48"/>
       <c r="P7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q7" s="109" t="str">
         <f>=IF(OR(Q5="",Q6=""),"",DATEDIF(Q5,Q6,"m")+1)</f>
@@ -7735,7 +7743,7 @@
       <c r="R7" s="109"/>
       <c r="T7" s="48"/>
       <c r="W7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="X7" s="109" t="str">
         <f>=IF(OR(X5="",X6=""),"",DATEDIF(X5,X6,"m")+1)</f>
@@ -7744,7 +7752,7 @@
       <c r="Y7" s="109"/>
       <c r="AA7" s="48"/>
       <c r="AD7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AE7" s="109" t="str">
         <f>=IF(OR(AE5="",AE6=""),"",DATEDIF(AE5,AE6,"m")+1)</f>
@@ -7753,7 +7761,7 @@
       <c r="AF7" s="109"/>
       <c r="AH7" s="48"/>
       <c r="AK7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL7" s="109" t="str">
         <f>=IF(OR(AL5="",AL6=""),"",DATEDIF(AL5,AL6,"m")+1)</f>
@@ -7762,7 +7770,7 @@
       <c r="AM7" s="109"/>
       <c r="AO7" s="48"/>
       <c r="AR7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AS7" s="109" t="str">
         <f>=IF(OR(AS5="",AS6=""),"",DATEDIF(AS5,AS6,"m")+1)</f>
@@ -7771,7 +7779,7 @@
       <c r="AT7" s="109"/>
       <c r="AV7" s="48"/>
       <c r="AY7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AZ7" s="109" t="str">
         <f>=IF(OR(AZ5="",AZ6=""),"",DATEDIF(AZ5,AZ6,"m")+1)</f>
@@ -7780,7 +7788,7 @@
       <c r="BA7" s="109"/>
       <c r="BC7" s="48"/>
       <c r="BF7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BG7" s="109" t="str">
         <f>=IF(OR(BG5="",BG6=""),"",DATEDIF(BG5,BG6,"m")+1)</f>
@@ -7789,7 +7797,7 @@
       <c r="BH7" s="109"/>
       <c r="BJ7" s="48"/>
       <c r="BM7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BN7" s="109" t="str">
         <f>=IF(OR(BN5="",BN6=""),"",DATEDIF(BN5,BN6,"m")+1)</f>
@@ -7798,7 +7806,7 @@
       <c r="BO7" s="109"/>
       <c r="BQ7" s="48"/>
       <c r="BT7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BU7" s="109" t="str">
         <f>=IF(OR(BU5="",BU6=""),"",DATEDIF(BU5,BU6,"m")+1)</f>
@@ -7807,7 +7815,7 @@
       <c r="BV7" s="109"/>
       <c r="BX7" s="48"/>
       <c r="CA7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="CB7" s="109" t="str">
         <f>=IF(OR(CB5="",CB6=""),"",DATEDIF(CB5,CB6,"m")+1)</f>
@@ -7816,7 +7824,7 @@
       <c r="CC7" s="109"/>
       <c r="CE7" s="48"/>
       <c r="CH7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="CI7" s="109" t="str">
         <f>=IF(OR(CI5="",CI6=""),"",DATEDIF(CI5,CI6,"m")+1)</f>
@@ -7825,7 +7833,7 @@
       <c r="CJ7" s="109"/>
       <c r="CL7" s="48"/>
       <c r="CO7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="CP7" s="109" t="str">
         <f>=IF(OR(CP5="",CP6=""),"",DATEDIF(CP5,CP6,"m")+1)</f>
@@ -7834,7 +7842,7 @@
       <c r="CQ7" s="109"/>
       <c r="CS7" s="48"/>
       <c r="CV7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="CW7" s="109" t="str">
         <f>=IF(OR(CW5="",CW6=""),"",DATEDIF(CW5,CW6,"m")+1)</f>
@@ -7843,7 +7851,7 @@
       <c r="CX7" s="109"/>
       <c r="CZ7" s="48"/>
       <c r="DC7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="DD7" s="109" t="str">
         <f>=IF(OR(DD5="",DD6=""),"",DATEDIF(DD5,DD6,"m")+1)</f>
@@ -7852,7 +7860,7 @@
       <c r="DE7" s="109"/>
       <c r="DG7" s="48"/>
       <c r="DJ7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="DK7" s="109" t="str">
         <f>=IF(OR(DK5="",DK6=""),"",DATEDIF(DK5,DK6,"m")+1)</f>
@@ -7861,7 +7869,7 @@
       <c r="DL7" s="109"/>
       <c r="DN7" s="48"/>
       <c r="DQ7" s="138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="DR7" s="109" t="str">
         <f>=IF(OR(DR5="",DR6=""),"",DATEDIF(DR5,DR6,"m")+1)</f>
@@ -7872,7 +7880,7 @@
     </row>
     <row r="8">
       <c r="B8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C8" s="111" t="str">
         <f>=ROUND(IFERROR(F48,0),6)</f>
@@ -7881,7 +7889,7 @@
       <c r="D8" s="111"/>
       <c r="F8" s="48"/>
       <c r="I8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J8" s="111" t="str">
         <f>=ROUND(IFERROR(M48,0),6)</f>
@@ -7890,7 +7898,7 @@
       <c r="K8" s="111"/>
       <c r="M8" s="48"/>
       <c r="P8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q8" s="111" t="str">
         <f>=ROUND(IFERROR(T48,0),6)</f>
@@ -7899,7 +7907,7 @@
       <c r="R8" s="111"/>
       <c r="T8" s="48"/>
       <c r="W8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="X8" s="111" t="str">
         <f>=ROUND(IFERROR(AA48,0),6)</f>
@@ -7908,7 +7916,7 @@
       <c r="Y8" s="111"/>
       <c r="AA8" s="48"/>
       <c r="AD8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AE8" s="111" t="str">
         <f>=ROUND(IFERROR(AH48,0),6)</f>
@@ -7917,7 +7925,7 @@
       <c r="AF8" s="111"/>
       <c r="AH8" s="48"/>
       <c r="AK8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL8" s="111" t="str">
         <f>=ROUND(IFERROR(AO48,0),6)</f>
@@ -7926,7 +7934,7 @@
       <c r="AM8" s="111"/>
       <c r="AO8" s="48"/>
       <c r="AR8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AS8" s="111" t="str">
         <f>=ROUND(IFERROR(AV48,0),6)</f>
@@ -7935,7 +7943,7 @@
       <c r="AT8" s="111"/>
       <c r="AV8" s="48"/>
       <c r="AY8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AZ8" s="111" t="str">
         <f>=ROUND(IFERROR(BC48,0),6)</f>
@@ -7944,7 +7952,7 @@
       <c r="BA8" s="111"/>
       <c r="BC8" s="48"/>
       <c r="BF8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BG8" s="111" t="str">
         <f>=ROUND(IFERROR(BJ48,0),6)</f>
@@ -7953,7 +7961,7 @@
       <c r="BH8" s="111"/>
       <c r="BJ8" s="48"/>
       <c r="BM8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BN8" s="111" t="str">
         <f>=ROUND(IFERROR(BQ48,0),6)</f>
@@ -7962,7 +7970,7 @@
       <c r="BO8" s="111"/>
       <c r="BQ8" s="48"/>
       <c r="BT8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BU8" s="111" t="str">
         <f>=ROUND(IFERROR(BX48,0),6)</f>
@@ -7971,7 +7979,7 @@
       <c r="BV8" s="111"/>
       <c r="BX8" s="48"/>
       <c r="CA8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CB8" s="111" t="str">
         <f>=ROUND(IFERROR(CE48,0),6)</f>
@@ -7980,7 +7988,7 @@
       <c r="CC8" s="111"/>
       <c r="CE8" s="48"/>
       <c r="CH8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CI8" s="111" t="str">
         <f>=ROUND(IFERROR(CL48,0),6)</f>
@@ -7989,7 +7997,7 @@
       <c r="CJ8" s="111"/>
       <c r="CL8" s="48"/>
       <c r="CO8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CP8" s="111" t="str">
         <f>=ROUND(IFERROR(CS48,0),6)</f>
@@ -7998,7 +8006,7 @@
       <c r="CQ8" s="111"/>
       <c r="CS8" s="48"/>
       <c r="CV8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CW8" s="111" t="str">
         <f>=ROUND(IFERROR(CZ48,0),6)</f>
@@ -8007,7 +8015,7 @@
       <c r="CX8" s="111"/>
       <c r="CZ8" s="48"/>
       <c r="DC8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DD8" s="111" t="str">
         <f>=ROUND(IFERROR(DG48,0),6)</f>
@@ -8016,7 +8024,7 @@
       <c r="DE8" s="111"/>
       <c r="DG8" s="48"/>
       <c r="DJ8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DK8" s="111" t="str">
         <f>=ROUND(IFERROR(DN48,0),6)</f>
@@ -8025,7 +8033,7 @@
       <c r="DL8" s="111"/>
       <c r="DN8" s="48"/>
       <c r="DQ8" s="138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DR8" s="111" t="str">
         <f>=ROUND(IFERROR(DU48,0),6)</f>
@@ -8036,126 +8044,126 @@
     </row>
     <row r="9">
       <c r="B9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C9" s="112"/>
       <c r="D9" s="112"/>
       <c r="E9" s="112"/>
       <c r="F9" s="140"/>
       <c r="I9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J9" s="112"/>
       <c r="K9" s="112"/>
       <c r="L9" s="112"/>
       <c r="M9" s="140"/>
       <c r="P9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q9" s="112"/>
       <c r="R9" s="112"/>
       <c r="S9" s="112"/>
       <c r="T9" s="140"/>
       <c r="W9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="X9" s="112"/>
       <c r="Y9" s="112"/>
       <c r="Z9" s="112"/>
       <c r="AA9" s="140"/>
       <c r="AD9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AE9" s="112"/>
       <c r="AF9" s="112"/>
       <c r="AG9" s="112"/>
       <c r="AH9" s="140"/>
       <c r="AK9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL9" s="112"/>
       <c r="AM9" s="112"/>
       <c r="AN9" s="112"/>
       <c r="AO9" s="140"/>
       <c r="AR9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AS9" s="112"/>
       <c r="AT9" s="112"/>
       <c r="AU9" s="112"/>
       <c r="AV9" s="140"/>
       <c r="AY9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AZ9" s="112"/>
       <c r="BA9" s="112"/>
       <c r="BB9" s="112"/>
       <c r="BC9" s="140"/>
       <c r="BF9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="BG9" s="112"/>
       <c r="BH9" s="112"/>
       <c r="BI9" s="112"/>
       <c r="BJ9" s="140"/>
       <c r="BM9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="BN9" s="112"/>
       <c r="BO9" s="112"/>
       <c r="BP9" s="112"/>
       <c r="BQ9" s="140"/>
       <c r="BT9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="BU9" s="112"/>
       <c r="BV9" s="112"/>
       <c r="BW9" s="112"/>
       <c r="BX9" s="140"/>
       <c r="CA9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="CB9" s="112"/>
       <c r="CC9" s="112"/>
       <c r="CD9" s="112"/>
       <c r="CE9" s="140"/>
       <c r="CH9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="CI9" s="112"/>
       <c r="CJ9" s="112"/>
       <c r="CK9" s="112"/>
       <c r="CL9" s="140"/>
       <c r="CO9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="CP9" s="112"/>
       <c r="CQ9" s="112"/>
       <c r="CR9" s="112"/>
       <c r="CS9" s="140"/>
       <c r="CV9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="CW9" s="112"/>
       <c r="CX9" s="112"/>
       <c r="CY9" s="112"/>
       <c r="CZ9" s="140"/>
       <c r="DC9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="DD9" s="112"/>
       <c r="DE9" s="112"/>
       <c r="DF9" s="112"/>
       <c r="DG9" s="140"/>
       <c r="DJ9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="DK9" s="112"/>
       <c r="DL9" s="112"/>
       <c r="DM9" s="112"/>
       <c r="DN9" s="140"/>
       <c r="DQ9" s="139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="DR9" s="112"/>
       <c r="DS9" s="112"/>
@@ -8164,279 +8172,279 @@
     </row>
     <row r="10">
       <c r="B10" s="141" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C10" s="114" t="s">
+        <v>298</v>
+      </c>
+      <c r="D10" s="114" t="s">
+        <v>299</v>
+      </c>
+      <c r="E10" s="114" t="s">
+        <v>300</v>
+      </c>
+      <c r="F10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="I10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="D10" s="114" t="s">
+      <c r="J10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="E10" s="114" t="s">
+      <c r="K10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="F10" s="142" t="s">
+      <c r="L10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="I10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="J10" s="114" t="s">
+      <c r="M10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="P10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="K10" s="114" t="s">
+      <c r="Q10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="L10" s="114" t="s">
+      <c r="R10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="M10" s="142" t="s">
+      <c r="S10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="P10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q10" s="114" t="s">
+      <c r="T10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="W10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="R10" s="114" t="s">
+      <c r="X10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="S10" s="114" t="s">
+      <c r="Y10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="T10" s="142" t="s">
+      <c r="Z10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="W10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="X10" s="114" t="s">
+      <c r="AA10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="AD10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="Y10" s="114" t="s">
+      <c r="AE10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="Z10" s="114" t="s">
+      <c r="AF10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="AA10" s="142" t="s">
+      <c r="AG10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="AD10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="AE10" s="114" t="s">
+      <c r="AH10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="AK10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="AF10" s="114" t="s">
+      <c r="AL10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="AG10" s="114" t="s">
+      <c r="AM10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="AH10" s="142" t="s">
+      <c r="AN10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="AK10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="AL10" s="114" t="s">
+      <c r="AO10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="AR10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="AM10" s="114" t="s">
+      <c r="AS10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="AN10" s="114" t="s">
+      <c r="AT10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="AO10" s="142" t="s">
+      <c r="AU10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="AR10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="AS10" s="114" t="s">
+      <c r="AV10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="AY10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="AT10" s="114" t="s">
+      <c r="AZ10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="AU10" s="114" t="s">
+      <c r="BA10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="AV10" s="142" t="s">
+      <c r="BB10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="AY10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="AZ10" s="114" t="s">
+      <c r="BC10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="BF10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="BA10" s="114" t="s">
+      <c r="BG10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="BB10" s="114" t="s">
+      <c r="BH10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="BC10" s="142" t="s">
+      <c r="BI10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="BF10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="BG10" s="114" t="s">
+      <c r="BJ10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="BM10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="BH10" s="114" t="s">
+      <c r="BN10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="BI10" s="114" t="s">
+      <c r="BO10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="BJ10" s="142" t="s">
+      <c r="BP10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="BM10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="BN10" s="114" t="s">
+      <c r="BQ10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="BT10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="BO10" s="114" t="s">
+      <c r="BU10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="BP10" s="114" t="s">
+      <c r="BV10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="BQ10" s="142" t="s">
+      <c r="BW10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="BT10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="BU10" s="114" t="s">
+      <c r="BX10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="CA10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="BV10" s="114" t="s">
+      <c r="CB10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="BW10" s="114" t="s">
+      <c r="CC10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="BX10" s="142" t="s">
+      <c r="CD10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="CA10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="CB10" s="114" t="s">
+      <c r="CE10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="CH10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="CC10" s="114" t="s">
+      <c r="CI10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="CD10" s="114" t="s">
+      <c r="CJ10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="CE10" s="142" t="s">
+      <c r="CK10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="CH10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="CI10" s="114" t="s">
+      <c r="CL10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="CO10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="CJ10" s="114" t="s">
+      <c r="CP10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="CK10" s="114" t="s">
+      <c r="CQ10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="CL10" s="142" t="s">
+      <c r="CR10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="CO10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="CP10" s="114" t="s">
+      <c r="CS10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="CV10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="CQ10" s="114" t="s">
+      <c r="CW10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="CR10" s="114" t="s">
+      <c r="CX10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="CS10" s="142" t="s">
+      <c r="CY10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="CV10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="CW10" s="114" t="s">
+      <c r="CZ10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="DC10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="CX10" s="114" t="s">
+      <c r="DD10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="CY10" s="114" t="s">
+      <c r="DE10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="CZ10" s="142" t="s">
+      <c r="DF10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="DC10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="DD10" s="114" t="s">
+      <c r="DG10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="DJ10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="DE10" s="114" t="s">
+      <c r="DK10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="DF10" s="114" t="s">
+      <c r="DL10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="DG10" s="142" t="s">
+      <c r="DM10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="DJ10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="DK10" s="114" t="s">
+      <c r="DN10" s="142" t="s">
+        <v>301</v>
+      </c>
+      <c r="DQ10" s="141" t="s">
         <v>297</v>
       </c>
-      <c r="DL10" s="114" t="s">
+      <c r="DR10" s="114" t="s">
         <v>298</v>
       </c>
-      <c r="DM10" s="114" t="s">
+      <c r="DS10" s="114" t="s">
         <v>299</v>
       </c>
-      <c r="DN10" s="142" t="s">
+      <c r="DT10" s="114" t="s">
         <v>300</v>
       </c>
-      <c r="DQ10" s="141" t="s">
-        <v>296</v>
-      </c>
-      <c r="DR10" s="114" t="s">
-        <v>297</v>
-      </c>
-      <c r="DS10" s="114" t="s">
-        <v>298</v>
-      </c>
-      <c r="DT10" s="114" t="s">
-        <v>299</v>
-      </c>
       <c r="DU10" s="142" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="143" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C11" s="116" t="str">
         <f>=ROUND(IF(Saldovortrag_LW="",0,Saldovortrag_LW),2)</f>
@@ -8451,7 +8459,7 @@
         <f>=ROUND(IF(Saldovortrag_EUR="",0,Saldovortrag_EUR),2)</f>
       </c>
       <c r="I11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_1,2)</f>
@@ -8466,7 +8474,7 @@
         <f>=ROUND(FB_SaldoEUR_1,2)</f>
       </c>
       <c r="P11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_2,2)</f>
@@ -8481,7 +8489,7 @@
         <f>=ROUND(FB_SaldoEUR_2,2)</f>
       </c>
       <c r="W11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_3,2)</f>
@@ -8496,7 +8504,7 @@
         <f>=ROUND(FB_SaldoEUR_3,2)</f>
       </c>
       <c r="AD11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AE11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_4,2)</f>
@@ -8511,7 +8519,7 @@
         <f>=ROUND(FB_SaldoEUR_4,2)</f>
       </c>
       <c r="AK11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_5,2)</f>
@@ -8526,7 +8534,7 @@
         <f>=ROUND(FB_SaldoEUR_5,2)</f>
       </c>
       <c r="AR11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AS11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_6,2)</f>
@@ -8541,7 +8549,7 @@
         <f>=ROUND(FB_SaldoEUR_6,2)</f>
       </c>
       <c r="AY11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AZ11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_7,2)</f>
@@ -8556,7 +8564,7 @@
         <f>=ROUND(FB_SaldoEUR_7,2)</f>
       </c>
       <c r="BF11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="BG11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_8,2)</f>
@@ -8571,7 +8579,7 @@
         <f>=ROUND(FB_SaldoEUR_8,2)</f>
       </c>
       <c r="BM11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="BN11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_9,2)</f>
@@ -8586,7 +8594,7 @@
         <f>=ROUND(FB_SaldoEUR_9,2)</f>
       </c>
       <c r="BT11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="BU11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_10,2)</f>
@@ -8601,7 +8609,7 @@
         <f>=ROUND(FB_SaldoEUR_10,2)</f>
       </c>
       <c r="CA11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="CB11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_11,2)</f>
@@ -8616,7 +8624,7 @@
         <f>=ROUND(FB_SaldoEUR_11,2)</f>
       </c>
       <c r="CH11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="CI11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_12,2)</f>
@@ -8631,7 +8639,7 @@
         <f>=ROUND(FB_SaldoEUR_12,2)</f>
       </c>
       <c r="CO11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="CP11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_13,2)</f>
@@ -8646,7 +8654,7 @@
         <f>=ROUND(FB_SaldoEUR_13,2)</f>
       </c>
       <c r="CV11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="CW11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_14,2)</f>
@@ -8661,7 +8669,7 @@
         <f>=ROUND(FB_SaldoEUR_14,2)</f>
       </c>
       <c r="DC11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="DD11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_15,2)</f>
@@ -8676,7 +8684,7 @@
         <f>=ROUND(FB_SaldoEUR_15,2)</f>
       </c>
       <c r="DJ11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="DK11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_16,2)</f>
@@ -8691,7 +8699,7 @@
         <f>=ROUND(FB_SaldoEUR_16,2)</f>
       </c>
       <c r="DQ11" s="143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="DR11" s="116" t="str">
         <f>=ROUND(FB_SaldoLC_17,2)</f>
@@ -8980,7 +8988,7 @@
     </row>
     <row r="13">
       <c r="B13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C13" s="116" t="str">
         <f>=ROUND(SUMIF($B$43:$B$47,"Drittmittel",$D$43:$D$47)+SUMIF($B$52:$B$57,"Drittmittel",$D$52:$D$57),2)</f>
@@ -8995,7 +9003,7 @@
         <f>=ROUND(SUMIF($B$43:$B$47,"Drittmittel",$E$43:$E$47)+SUMIF($B$52:$B$57,"Drittmittel",$E$52:$E$57),2)</f>
       </c>
       <c r="I13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J13" s="116" t="str">
         <f>=ROUND(SUMIF($I$43:$I$47,"Drittmittel",$K$43:$K$47)+SUMIF($I$52:$I$57,"Drittmittel",$K$52:$K$57),2)</f>
@@ -9010,7 +9018,7 @@
         <f>=IFERROR(ROUND(F13 + K13, 2), K13)</f>
       </c>
       <c r="P13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q13" s="116" t="str">
         <f>=ROUND(SUMIF($P$43:$P$47,"Drittmittel",$R$43:$R$47)+SUMIF($P$52:$P$57,"Drittmittel",$R$52:$R$57),2)</f>
@@ -9025,7 +9033,7 @@
         <f>=IFERROR(ROUND(M13 + R13, 2), R13)</f>
       </c>
       <c r="W13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="X13" s="116" t="str">
         <f>=ROUND(SUMIF($W$43:$W$47,"Drittmittel",$Y$43:$Y$47)+SUMIF($W$52:$W$57,"Drittmittel",$Y$52:$Y$57),2)</f>
@@ -9040,7 +9048,7 @@
         <f>=IFERROR(ROUND(T13 + Y13, 2), Y13)</f>
       </c>
       <c r="AD13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AE13" s="116" t="str">
         <f>=ROUND(SUMIF($AD$43:$AD$47,"Drittmittel",$AF$43:$AF$47)+SUMIF($AD$52:$AD$57,"Drittmittel",$AF$52:$AF$57),2)</f>
@@ -9055,7 +9063,7 @@
         <f>=IFERROR(ROUND(AA13 + AF13, 2), AF13)</f>
       </c>
       <c r="AK13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL13" s="116" t="str">
         <f>=ROUND(SUMIF($AK$43:$AK$47,"Drittmittel",$AM$43:$AM$47)+SUMIF($AK$52:$AK$57,"Drittmittel",$AM$52:$AM$57),2)</f>
@@ -9070,7 +9078,7 @@
         <f>=IFERROR(ROUND(AH13 + AM13, 2), AM13)</f>
       </c>
       <c r="AR13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AS13" s="116" t="str">
         <f>=ROUND(SUMIF($AR$43:$AR$47,"Drittmittel",$AT$43:$AT$47)+SUMIF($AR$52:$AR$57,"Drittmittel",$AT$52:$AT$57),2)</f>
@@ -9085,7 +9093,7 @@
         <f>=IFERROR(ROUND(AO13 + AT13, 2), AT13)</f>
       </c>
       <c r="AY13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AZ13" s="116" t="str">
         <f>=ROUND(SUMIF($AY$43:$AY$47,"Drittmittel",$BA$43:$BA$47)+SUMIF($AY$52:$AY$57,"Drittmittel",$BA$52:$BA$57),2)</f>
@@ -9100,7 +9108,7 @@
         <f>=IFERROR(ROUND(AV13 + BA13, 2), BA13)</f>
       </c>
       <c r="BF13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BG13" s="116" t="str">
         <f>=ROUND(SUMIF($BF$43:$BF$47,"Drittmittel",$BH$43:$BH$47)+SUMIF($BF$52:$BF$57,"Drittmittel",$BH$52:$BH$57),2)</f>
@@ -9115,7 +9123,7 @@
         <f>=IFERROR(ROUND(BC13 + BH13, 2), BH13)</f>
       </c>
       <c r="BM13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BN13" s="116" t="str">
         <f>=ROUND(SUMIF($BM$43:$BM$47,"Drittmittel",$BO$43:$BO$47)+SUMIF($BM$52:$BM$57,"Drittmittel",$BO$52:$BO$57),2)</f>
@@ -9130,7 +9138,7 @@
         <f>=IFERROR(ROUND(BJ13 + BO13, 2), BO13)</f>
       </c>
       <c r="BT13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU13" s="116" t="str">
         <f>=ROUND(SUMIF($BT$43:$BT$47,"Drittmittel",$BV$43:$BV$47)+SUMIF($BT$52:$BT$57,"Drittmittel",$BV$52:$BV$57),2)</f>
@@ -9145,7 +9153,7 @@
         <f>=IFERROR(ROUND(BQ13 + BV13, 2), BV13)</f>
       </c>
       <c r="CA13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="CB13" s="116" t="str">
         <f>=ROUND(SUMIF($CA$43:$CA$47,"Drittmittel",$CC$43:$CC$47)+SUMIF($CA$52:$CA$57,"Drittmittel",$CC$52:$CC$57),2)</f>
@@ -9160,7 +9168,7 @@
         <f>=IFERROR(ROUND(BX13 + CC13, 2), CC13)</f>
       </c>
       <c r="CH13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="CI13" s="116" t="str">
         <f>=ROUND(SUMIF($CH$43:$CH$47,"Drittmittel",$CJ$43:$CJ$47)+SUMIF($CH$52:$CH$57,"Drittmittel",$CJ$52:$CJ$57),2)</f>
@@ -9175,7 +9183,7 @@
         <f>=IFERROR(ROUND(CE13 + CJ13, 2), CJ13)</f>
       </c>
       <c r="CO13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="CP13" s="116" t="str">
         <f>=ROUND(SUMIF($CO$43:$CO$47,"Drittmittel",$CQ$43:$CQ$47)+SUMIF($CO$52:$CO$57,"Drittmittel",$CQ$52:$CQ$57),2)</f>
@@ -9190,7 +9198,7 @@
         <f>=IFERROR(ROUND(CL13 + CQ13, 2), CQ13)</f>
       </c>
       <c r="CV13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="CW13" s="116" t="str">
         <f>=ROUND(SUMIF($CV$43:$CV$47,"Drittmittel",$CX$43:$CX$47)+SUMIF($CV$52:$CV$57,"Drittmittel",$CX$52:$CX$57),2)</f>
@@ -9205,7 +9213,7 @@
         <f>=IFERROR(ROUND(CS13 + CX13, 2), CX13)</f>
       </c>
       <c r="DC13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="DD13" s="116" t="str">
         <f>=ROUND(SUMIF($DC$43:$DC$47,"Drittmittel",$DE$43:$DE$47)+SUMIF($DC$52:$DC$57,"Drittmittel",$DE$52:$DE$57),2)</f>
@@ -9220,7 +9228,7 @@
         <f>=IFERROR(ROUND(CZ13 + DE13, 2), DE13)</f>
       </c>
       <c r="DJ13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="DK13" s="116" t="str">
         <f>=ROUND(SUMIF($DJ$43:$DJ$47,"Drittmittel",$DL$43:$DL$47)+SUMIF($DJ$52:$DJ$57,"Drittmittel",$DL$52:$DL$57),2)</f>
@@ -9235,7 +9243,7 @@
         <f>=IFERROR(ROUND(DG13 + DL13, 2), DL13)</f>
       </c>
       <c r="DQ13" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="DR13" s="116" t="str">
         <f>=ROUND(SUMIF($DQ$43:$DQ$47,"Drittmittel",$DS$43:$DS$47)+SUMIF($DQ$52:$DQ$57,"Drittmittel",$DS$52:$DS$57),2)</f>
@@ -9524,7 +9532,7 @@
     </row>
     <row r="15">
       <c r="B15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C15" s="116" t="str">
         <f>=ROUND(SUMIF($B$43:$B$47,"Zinsertraege",$D$43:$D$47)+SUMIF($B$52:$B$57,"Zinsertraege",$D$52:$D$57),2)</f>
@@ -9539,7 +9547,7 @@
         <f>=ROUND(SUMIF($B$43:$B$47,"Zinsertraege",$E$43:$E$47)+SUMIF($B$52:$B$57,"Zinsertraege",$E$52:$E$57),2)</f>
       </c>
       <c r="I15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J15" s="116" t="str">
         <f>=ROUND(SUMIF($I$43:$I$47,"Zinsertraege",$K$43:$K$47)+SUMIF($I$52:$I$57,"Zinsertraege",$K$52:$K$57),2)</f>
@@ -9554,7 +9562,7 @@
         <f>=IFERROR(ROUND(F15 + K15, 2), K15)</f>
       </c>
       <c r="P15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q15" s="116" t="str">
         <f>=ROUND(SUMIF($P$43:$P$47,"Zinsertraege",$R$43:$R$47)+SUMIF($P$52:$P$57,"Zinsertraege",$R$52:$R$57),2)</f>
@@ -9569,7 +9577,7 @@
         <f>=IFERROR(ROUND(M15 + R15, 2), R15)</f>
       </c>
       <c r="W15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="X15" s="116" t="str">
         <f>=ROUND(SUMIF($W$43:$W$47,"Zinsertraege",$Y$43:$Y$47)+SUMIF($W$52:$W$57,"Zinsertraege",$Y$52:$Y$57),2)</f>
@@ -9584,7 +9592,7 @@
         <f>=IFERROR(ROUND(T15 + Y15, 2), Y15)</f>
       </c>
       <c r="AD15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AE15" s="116" t="str">
         <f>=ROUND(SUMIF($AD$43:$AD$47,"Zinsertraege",$AF$43:$AF$47)+SUMIF($AD$52:$AD$57,"Zinsertraege",$AF$52:$AF$57),2)</f>
@@ -9599,7 +9607,7 @@
         <f>=IFERROR(ROUND(AA15 + AF15, 2), AF15)</f>
       </c>
       <c r="AK15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL15" s="116" t="str">
         <f>=ROUND(SUMIF($AK$43:$AK$47,"Zinsertraege",$AM$43:$AM$47)+SUMIF($AK$52:$AK$57,"Zinsertraege",$AM$52:$AM$57),2)</f>
@@ -9614,7 +9622,7 @@
         <f>=IFERROR(ROUND(AH15 + AM15, 2), AM15)</f>
       </c>
       <c r="AR15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AS15" s="116" t="str">
         <f>=ROUND(SUMIF($AR$43:$AR$47,"Zinsertraege",$AT$43:$AT$47)+SUMIF($AR$52:$AR$57,"Zinsertraege",$AT$52:$AT$57),2)</f>
@@ -9629,7 +9637,7 @@
         <f>=IFERROR(ROUND(AO15 + AT15, 2), AT15)</f>
       </c>
       <c r="AY15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AZ15" s="116" t="str">
         <f>=ROUND(SUMIF($AY$43:$AY$47,"Zinsertraege",$BA$43:$BA$47)+SUMIF($AY$52:$AY$57,"Zinsertraege",$BA$52:$BA$57),2)</f>
@@ -9644,7 +9652,7 @@
         <f>=IFERROR(ROUND(AV15 + BA15, 2), BA15)</f>
       </c>
       <c r="BF15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BG15" s="116" t="str">
         <f>=ROUND(SUMIF($BF$43:$BF$47,"Zinsertraege",$BH$43:$BH$47)+SUMIF($BF$52:$BF$57,"Zinsertraege",$BH$52:$BH$57),2)</f>
@@ -9659,7 +9667,7 @@
         <f>=IFERROR(ROUND(BC15 + BH15, 2), BH15)</f>
       </c>
       <c r="BM15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BN15" s="116" t="str">
         <f>=ROUND(SUMIF($BM$43:$BM$47,"Zinsertraege",$BO$43:$BO$47)+SUMIF($BM$52:$BM$57,"Zinsertraege",$BO$52:$BO$57),2)</f>
@@ -9674,7 +9682,7 @@
         <f>=IFERROR(ROUND(BJ15 + BO15, 2), BO15)</f>
       </c>
       <c r="BT15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BU15" s="116" t="str">
         <f>=ROUND(SUMIF($BT$43:$BT$47,"Zinsertraege",$BV$43:$BV$47)+SUMIF($BT$52:$BT$57,"Zinsertraege",$BV$52:$BV$57),2)</f>
@@ -9689,7 +9697,7 @@
         <f>=IFERROR(ROUND(BQ15 + BV15, 2), BV15)</f>
       </c>
       <c r="CA15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="CB15" s="116" t="str">
         <f>=ROUND(SUMIF($CA$43:$CA$47,"Zinsertraege",$CC$43:$CC$47)+SUMIF($CA$52:$CA$57,"Zinsertraege",$CC$52:$CC$57),2)</f>
@@ -9704,7 +9712,7 @@
         <f>=IFERROR(ROUND(BX15 + CC15, 2), CC15)</f>
       </c>
       <c r="CH15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="CI15" s="116" t="str">
         <f>=ROUND(SUMIF($CH$43:$CH$47,"Zinsertraege",$CJ$43:$CJ$47)+SUMIF($CH$52:$CH$57,"Zinsertraege",$CJ$52:$CJ$57),2)</f>
@@ -9719,7 +9727,7 @@
         <f>=IFERROR(ROUND(CE15 + CJ15, 2), CJ15)</f>
       </c>
       <c r="CO15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="CP15" s="116" t="str">
         <f>=ROUND(SUMIF($CO$43:$CO$47,"Zinsertraege",$CQ$43:$CQ$47)+SUMIF($CO$52:$CO$57,"Zinsertraege",$CQ$52:$CQ$57),2)</f>
@@ -9734,7 +9742,7 @@
         <f>=IFERROR(ROUND(CL15 + CQ15, 2), CQ15)</f>
       </c>
       <c r="CV15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="CW15" s="116" t="str">
         <f>=ROUND(SUMIF($CV$43:$CV$47,"Zinsertraege",$CX$43:$CX$47)+SUMIF($CV$52:$CV$57,"Zinsertraege",$CX$52:$CX$57),2)</f>
@@ -9749,7 +9757,7 @@
         <f>=IFERROR(ROUND(CS15 + CX15, 2), CX15)</f>
       </c>
       <c r="DC15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="DD15" s="116" t="str">
         <f>=ROUND(SUMIF($DC$43:$DC$47,"Zinsertraege",$DE$43:$DE$47)+SUMIF($DC$52:$DC$57,"Zinsertraege",$DE$52:$DE$57),2)</f>
@@ -9764,7 +9772,7 @@
         <f>=IFERROR(ROUND(CZ15 + DE15, 2), DE15)</f>
       </c>
       <c r="DJ15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="DK15" s="116" t="str">
         <f>=ROUND(SUMIF($DJ$43:$DJ$47,"Zinsertraege",$DL$43:$DL$47)+SUMIF($DJ$52:$DJ$57,"Zinsertraege",$DL$52:$DL$57),2)</f>
@@ -9779,7 +9787,7 @@
         <f>=IFERROR(ROUND(DG15 + DL15, 2), DL15)</f>
       </c>
       <c r="DQ15" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="DR15" s="116" t="str">
         <f>=ROUND(SUMIF($DQ$43:$DQ$47,"Zinsertraege",$DS$43:$DS$47)+SUMIF($DQ$52:$DQ$57,"Zinsertraege",$DS$52:$DS$57),2)</f>
@@ -9796,7 +9804,7 @@
     </row>
     <row r="16">
       <c r="B16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C16" s="119" t="str">
         <f>=ROUND(SUM(C11:C15),2)</f>
@@ -9811,7 +9819,7 @@
         <f>=ROUND(SUM(F11:F15),2)</f>
       </c>
       <c r="I16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J16" s="119" t="str">
         <f>=ROUND(SUM(J11:J15),2)</f>
@@ -9826,7 +9834,7 @@
         <f>=ROUND(SUM(M11:M15),2)</f>
       </c>
       <c r="P16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q16" s="119" t="str">
         <f>=ROUND(SUM(Q11:Q15),2)</f>
@@ -9841,7 +9849,7 @@
         <f>=ROUND(SUM(T11:T15),2)</f>
       </c>
       <c r="W16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="X16" s="119" t="str">
         <f>=ROUND(SUM(X11:X15),2)</f>
@@ -9856,7 +9864,7 @@
         <f>=ROUND(SUM(AA11:AA15),2)</f>
       </c>
       <c r="AD16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AE16" s="119" t="str">
         <f>=ROUND(SUM(AE11:AE15),2)</f>
@@ -9871,7 +9879,7 @@
         <f>=ROUND(SUM(AH11:AH15),2)</f>
       </c>
       <c r="AK16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL16" s="119" t="str">
         <f>=ROUND(SUM(AL11:AL15),2)</f>
@@ -9886,7 +9894,7 @@
         <f>=ROUND(SUM(AO11:AO15),2)</f>
       </c>
       <c r="AR16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AS16" s="119" t="str">
         <f>=ROUND(SUM(AS11:AS15),2)</f>
@@ -9901,7 +9909,7 @@
         <f>=ROUND(SUM(AV11:AV15),2)</f>
       </c>
       <c r="AY16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AZ16" s="119" t="str">
         <f>=ROUND(SUM(AZ11:AZ15),2)</f>
@@ -9916,7 +9924,7 @@
         <f>=ROUND(SUM(BC11:BC15),2)</f>
       </c>
       <c r="BF16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BG16" s="119" t="str">
         <f>=ROUND(SUM(BG11:BG15),2)</f>
@@ -9931,7 +9939,7 @@
         <f>=ROUND(SUM(BJ11:BJ15),2)</f>
       </c>
       <c r="BM16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BN16" s="119" t="str">
         <f>=ROUND(SUM(BN11:BN15),2)</f>
@@ -9946,7 +9954,7 @@
         <f>=ROUND(SUM(BQ11:BQ15),2)</f>
       </c>
       <c r="BT16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BU16" s="119" t="str">
         <f>=ROUND(SUM(BU11:BU15),2)</f>
@@ -9961,7 +9969,7 @@
         <f>=ROUND(SUM(BX11:BX15),2)</f>
       </c>
       <c r="CA16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="CB16" s="119" t="str">
         <f>=ROUND(SUM(CB11:CB15),2)</f>
@@ -9976,7 +9984,7 @@
         <f>=ROUND(SUM(CE11:CE15),2)</f>
       </c>
       <c r="CH16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="CI16" s="119" t="str">
         <f>=ROUND(SUM(CI11:CI15),2)</f>
@@ -9991,7 +9999,7 @@
         <f>=ROUND(SUM(CL11:CL15),2)</f>
       </c>
       <c r="CO16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="CP16" s="119" t="str">
         <f>=ROUND(SUM(CP11:CP15),2)</f>
@@ -10006,7 +10014,7 @@
         <f>=ROUND(SUM(CS11:CS15),2)</f>
       </c>
       <c r="CV16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="CW16" s="119" t="str">
         <f>=ROUND(SUM(CW11:CW15),2)</f>
@@ -10021,7 +10029,7 @@
         <f>=ROUND(SUM(CZ11:CZ15),2)</f>
       </c>
       <c r="DC16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="DD16" s="119" t="str">
         <f>=ROUND(SUM(DD11:DD15),2)</f>
@@ -10036,7 +10044,7 @@
         <f>=ROUND(SUM(DG11:DG15),2)</f>
       </c>
       <c r="DJ16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="DK16" s="119" t="str">
         <f>=ROUND(SUM(DK11:DK15),2)</f>
@@ -10051,7 +10059,7 @@
         <f>=ROUND(SUM(DN11:DN15),2)</f>
       </c>
       <c r="DQ16" s="145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="DR16" s="119" t="str">
         <f>=ROUND(SUM(DR11:DR15),2)</f>
@@ -10068,126 +10076,126 @@
     </row>
     <row r="17">
       <c r="B17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C17" s="112"/>
       <c r="D17" s="112"/>
       <c r="E17" s="112"/>
       <c r="F17" s="140"/>
       <c r="I17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J17" s="112"/>
       <c r="K17" s="112"/>
       <c r="L17" s="112"/>
       <c r="M17" s="140"/>
       <c r="P17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q17" s="112"/>
       <c r="R17" s="112"/>
       <c r="S17" s="112"/>
       <c r="T17" s="140"/>
       <c r="W17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="X17" s="112"/>
       <c r="Y17" s="112"/>
       <c r="Z17" s="112"/>
       <c r="AA17" s="140"/>
       <c r="AD17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AE17" s="112"/>
       <c r="AF17" s="112"/>
       <c r="AG17" s="112"/>
       <c r="AH17" s="140"/>
       <c r="AK17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL17" s="112"/>
       <c r="AM17" s="112"/>
       <c r="AN17" s="112"/>
       <c r="AO17" s="140"/>
       <c r="AR17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AS17" s="112"/>
       <c r="AT17" s="112"/>
       <c r="AU17" s="112"/>
       <c r="AV17" s="140"/>
       <c r="AY17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AZ17" s="112"/>
       <c r="BA17" s="112"/>
       <c r="BB17" s="112"/>
       <c r="BC17" s="140"/>
       <c r="BF17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="BG17" s="112"/>
       <c r="BH17" s="112"/>
       <c r="BI17" s="112"/>
       <c r="BJ17" s="140"/>
       <c r="BM17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="BN17" s="112"/>
       <c r="BO17" s="112"/>
       <c r="BP17" s="112"/>
       <c r="BQ17" s="140"/>
       <c r="BT17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="BU17" s="112"/>
       <c r="BV17" s="112"/>
       <c r="BW17" s="112"/>
       <c r="BX17" s="140"/>
       <c r="CA17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="CB17" s="112"/>
       <c r="CC17" s="112"/>
       <c r="CD17" s="112"/>
       <c r="CE17" s="140"/>
       <c r="CH17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="CI17" s="112"/>
       <c r="CJ17" s="112"/>
       <c r="CK17" s="112"/>
       <c r="CL17" s="140"/>
       <c r="CO17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="CP17" s="112"/>
       <c r="CQ17" s="112"/>
       <c r="CR17" s="112"/>
       <c r="CS17" s="140"/>
       <c r="CV17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="CW17" s="112"/>
       <c r="CX17" s="112"/>
       <c r="CY17" s="112"/>
       <c r="CZ17" s="140"/>
       <c r="DC17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="DD17" s="112"/>
       <c r="DE17" s="112"/>
       <c r="DF17" s="112"/>
       <c r="DG17" s="140"/>
       <c r="DJ17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="DK17" s="112"/>
       <c r="DL17" s="112"/>
       <c r="DM17" s="112"/>
       <c r="DN17" s="140"/>
       <c r="DQ17" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="DR17" s="112"/>
       <c r="DS17" s="112"/>
@@ -10199,271 +10207,271 @@
         <v>205</v>
       </c>
       <c r="C18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="J18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="Q18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="S18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="T18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="W18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="X18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Y18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AD18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="AE18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AF18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AH18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AK18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="AL18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AR18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="AS18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AT18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AU18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AV18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AY18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="AZ18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="BA18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BB18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="BC18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="BF18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="BG18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="BH18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BI18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="BJ18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="BM18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="BN18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="BO18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BP18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="BQ18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="BT18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="BU18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="BV18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BW18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="BX18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="CA18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="CB18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="CC18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="CD18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="CE18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="CH18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="CI18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="CJ18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="CK18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="CL18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="CO18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="CP18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="CQ18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="CR18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="CS18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="CV18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="CW18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="CX18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="CY18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="CZ18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="DC18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="DD18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="DE18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="DF18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="DG18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="DJ18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="DK18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="DL18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="DM18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="DN18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="DQ18" s="147" t="s">
         <v>205</v>
       </c>
       <c r="DR18" s="121" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="DS18" s="121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="DT18" s="121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="DU18" s="148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19">
@@ -12856,7 +12864,7 @@
     </row>
     <row r="29">
       <c r="B29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$C$19:$C$28),2)</f>
@@ -12871,7 +12879,7 @@
         <f>=ROUND(SUBTOTAL(109,$F$19:$F$28),2)</f>
       </c>
       <c r="I29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$J$19:$J$28),2)</f>
@@ -12886,7 +12894,7 @@
         <f>=ROUND(SUBTOTAL(109,$M$19:$M$28),2)</f>
       </c>
       <c r="P29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$Q$19:$Q$28),2)</f>
@@ -12901,7 +12909,7 @@
         <f>=ROUND(SUBTOTAL(109,$T$19:$T$28),2)</f>
       </c>
       <c r="W29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$X$19:$X$28),2)</f>
@@ -12916,7 +12924,7 @@
         <f>=ROUND(SUBTOTAL(109,$AA$19:$AA$28),2)</f>
       </c>
       <c r="AD29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AE29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$AE$19:$AE$28),2)</f>
@@ -12931,7 +12939,7 @@
         <f>=ROUND(SUBTOTAL(109,$AH$19:$AH$28),2)</f>
       </c>
       <c r="AK29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$AL$19:$AL$28),2)</f>
@@ -12946,7 +12954,7 @@
         <f>=ROUND(SUBTOTAL(109,$AO$19:$AO$28),2)</f>
       </c>
       <c r="AR29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AS29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$AS$19:$AS$28),2)</f>
@@ -12961,7 +12969,7 @@
         <f>=ROUND(SUBTOTAL(109,$AV$19:$AV$28),2)</f>
       </c>
       <c r="AY29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AZ29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$AZ$19:$AZ$28),2)</f>
@@ -12976,7 +12984,7 @@
         <f>=ROUND(SUBTOTAL(109,$BC$19:$BC$28),2)</f>
       </c>
       <c r="BF29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="BG29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$BG$19:$BG$28),2)</f>
@@ -12991,7 +12999,7 @@
         <f>=ROUND(SUBTOTAL(109,$BJ$19:$BJ$28),2)</f>
       </c>
       <c r="BM29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="BN29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$BN$19:$BN$28),2)</f>
@@ -13006,7 +13014,7 @@
         <f>=ROUND(SUBTOTAL(109,$BQ$19:$BQ$28),2)</f>
       </c>
       <c r="BT29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="BU29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$BU$19:$BU$28),2)</f>
@@ -13021,7 +13029,7 @@
         <f>=ROUND(SUBTOTAL(109,$BX$19:$BX$28),2)</f>
       </c>
       <c r="CA29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="CB29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$CB$19:$CB$28),2)</f>
@@ -13036,7 +13044,7 @@
         <f>=ROUND(SUBTOTAL(109,$CE$19:$CE$28),2)</f>
       </c>
       <c r="CH29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="CI29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$CI$19:$CI$28),2)</f>
@@ -13051,7 +13059,7 @@
         <f>=ROUND(SUBTOTAL(109,$CL$19:$CL$28),2)</f>
       </c>
       <c r="CO29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="CP29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$CP$19:$CP$28),2)</f>
@@ -13066,7 +13074,7 @@
         <f>=ROUND(SUBTOTAL(109,$CS$19:$CS$28),2)</f>
       </c>
       <c r="CV29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="CW29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$CW$19:$CW$28),2)</f>
@@ -13081,7 +13089,7 @@
         <f>=ROUND(SUBTOTAL(109,$CZ$19:$CZ$28),2)</f>
       </c>
       <c r="DC29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="DD29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$DD$19:$DD$28),2)</f>
@@ -13096,7 +13104,7 @@
         <f>=ROUND(SUBTOTAL(109,$DG$19:$DG$28),2)</f>
       </c>
       <c r="DJ29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="DK29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$DK$19:$DK$28),2)</f>
@@ -13111,7 +13119,7 @@
         <f>=ROUND(SUBTOTAL(109,$DN$19:$DN$28),2)</f>
       </c>
       <c r="DQ29" s="150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="DR29" s="124" t="str">
         <f>=ROUND(SUBTOTAL(109,$DR$19:$DR$28),2)</f>
@@ -13166,7 +13174,7 @@
     </row>
     <row r="31">
       <c r="B31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C31" s="126" t="str">
         <f>=ROUND(IFERROR(C16-$C$29,""),2)</f>
@@ -13181,7 +13189,7 @@
         <f>=ROUND(IFERROR(F16-F29,""),2)</f>
       </c>
       <c r="I31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J31" s="126" t="str">
         <f>=ROUND(IFERROR(J16-$J$29,""),2)</f>
@@ -13196,7 +13204,7 @@
         <f>=ROUND(IFERROR(M16-M29,""),2)</f>
       </c>
       <c r="P31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q31" s="126" t="str">
         <f>=ROUND(IFERROR(Q16-$Q$29,""),2)</f>
@@ -13211,7 +13219,7 @@
         <f>=ROUND(IFERROR(T16-T29,""),2)</f>
       </c>
       <c r="W31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="X31" s="126" t="str">
         <f>=ROUND(IFERROR(X16-$X$29,""),2)</f>
@@ -13226,7 +13234,7 @@
         <f>=ROUND(IFERROR(AA16-AA29,""),2)</f>
       </c>
       <c r="AD31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AE31" s="126" t="str">
         <f>=ROUND(IFERROR(AE16-$AE$29,""),2)</f>
@@ -13241,7 +13249,7 @@
         <f>=ROUND(IFERROR(AH16-AH29,""),2)</f>
       </c>
       <c r="AK31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL31" s="126" t="str">
         <f>=ROUND(IFERROR(AL16-$AL$29,""),2)</f>
@@ -13256,7 +13264,7 @@
         <f>=ROUND(IFERROR(AO16-AO29,""),2)</f>
       </c>
       <c r="AR31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AS31" s="126" t="str">
         <f>=ROUND(IFERROR(AS16-$AS$29,""),2)</f>
@@ -13271,7 +13279,7 @@
         <f>=ROUND(IFERROR(AV16-AV29,""),2)</f>
       </c>
       <c r="AY31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AZ31" s="126" t="str">
         <f>=ROUND(IFERROR(AZ16-$AZ$29,""),2)</f>
@@ -13286,7 +13294,7 @@
         <f>=ROUND(IFERROR(BC16-BC29,""),2)</f>
       </c>
       <c r="BF31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="BG31" s="126" t="str">
         <f>=ROUND(IFERROR(BG16-$BG$29,""),2)</f>
@@ -13301,7 +13309,7 @@
         <f>=ROUND(IFERROR(BJ16-BJ29,""),2)</f>
       </c>
       <c r="BM31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="BN31" s="126" t="str">
         <f>=ROUND(IFERROR(BN16-$BN$29,""),2)</f>
@@ -13316,7 +13324,7 @@
         <f>=ROUND(IFERROR(BQ16-BQ29,""),2)</f>
       </c>
       <c r="BT31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="BU31" s="126" t="str">
         <f>=ROUND(IFERROR(BU16-$BU$29,""),2)</f>
@@ -13331,7 +13339,7 @@
         <f>=ROUND(IFERROR(BX16-BX29,""),2)</f>
       </c>
       <c r="CA31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="CB31" s="126" t="str">
         <f>=ROUND(IFERROR(CB16-$CB$29,""),2)</f>
@@ -13346,7 +13354,7 @@
         <f>=ROUND(IFERROR(CE16-CE29,""),2)</f>
       </c>
       <c r="CH31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="CI31" s="126" t="str">
         <f>=ROUND(IFERROR(CI16-$CI$29,""),2)</f>
@@ -13361,7 +13369,7 @@
         <f>=ROUND(IFERROR(CL16-CL29,""),2)</f>
       </c>
       <c r="CO31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="CP31" s="126" t="str">
         <f>=ROUND(IFERROR(CP16-$CP$29,""),2)</f>
@@ -13376,7 +13384,7 @@
         <f>=ROUND(IFERROR(CS16-CS29,""),2)</f>
       </c>
       <c r="CV31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="CW31" s="126" t="str">
         <f>=ROUND(IFERROR(CW16-$CW$29,""),2)</f>
@@ -13391,7 +13399,7 @@
         <f>=ROUND(IFERROR(CZ16-CZ29,""),2)</f>
       </c>
       <c r="DC31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="DD31" s="126" t="str">
         <f>=ROUND(IFERROR(DD16-$DD$29,""),2)</f>
@@ -13406,7 +13414,7 @@
         <f>=ROUND(IFERROR(DG16-DG29,""),2)</f>
       </c>
       <c r="DJ31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="DK31" s="126" t="str">
         <f>=ROUND(IFERROR(DK16-$DK$29,""),2)</f>
@@ -13421,7 +13429,7 @@
         <f>=ROUND(IFERROR(DN16-DN29,""),2)</f>
       </c>
       <c r="DQ31" s="138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="DR31" s="126" t="str">
         <f>=ROUND(IFERROR(DR16-$DR$29,""),2)</f>
@@ -13476,81 +13484,81 @@
     </row>
     <row r="33">
       <c r="B33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F33" s="48"/>
       <c r="I33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M33" s="48"/>
       <c r="P33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="T33" s="48"/>
       <c r="W33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AA33" s="48"/>
       <c r="AD33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AH33" s="48"/>
       <c r="AK33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO33" s="48"/>
       <c r="AR33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AV33" s="48"/>
       <c r="AY33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BC33" s="48"/>
       <c r="BF33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BJ33" s="48"/>
       <c r="BM33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BQ33" s="48"/>
       <c r="BT33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BX33" s="48"/>
       <c r="CA33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="CE33" s="48"/>
       <c r="CH33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="CL33" s="48"/>
       <c r="CO33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="CS33" s="48"/>
       <c r="CV33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="CZ33" s="48"/>
       <c r="DC33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="DG33" s="48"/>
       <c r="DJ33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="DN33" s="48"/>
       <c r="DQ33" s="153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="DU33" s="48"/>
     </row>
     <row r="34">
       <c r="B34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C34" s="129">
         <v>325000</v>
@@ -13560,7 +13568,7 @@
       </c>
       <c r="F34" s="48"/>
       <c r="I34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J34" s="129">
         <v>375000</v>
@@ -13570,7 +13578,7 @@
       </c>
       <c r="M34" s="48"/>
       <c r="P34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q34" s="129"/>
       <c r="R34" s="130" t="str">
@@ -13578,7 +13586,7 @@
       </c>
       <c r="T34" s="48"/>
       <c r="W34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X34" s="129"/>
       <c r="Y34" s="130" t="str">
@@ -13586,7 +13594,7 @@
       </c>
       <c r="AA34" s="48"/>
       <c r="AD34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AE34" s="129"/>
       <c r="AF34" s="130" t="str">
@@ -13594,7 +13602,7 @@
       </c>
       <c r="AH34" s="48"/>
       <c r="AK34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL34" s="129"/>
       <c r="AM34" s="130" t="str">
@@ -13602,7 +13610,7 @@
       </c>
       <c r="AO34" s="48"/>
       <c r="AR34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AS34" s="129"/>
       <c r="AT34" s="130" t="str">
@@ -13610,7 +13618,7 @@
       </c>
       <c r="AV34" s="48"/>
       <c r="AY34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AZ34" s="129"/>
       <c r="BA34" s="130" t="str">
@@ -13618,7 +13626,7 @@
       </c>
       <c r="BC34" s="48"/>
       <c r="BF34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="BG34" s="129"/>
       <c r="BH34" s="130" t="str">
@@ -13626,7 +13634,7 @@
       </c>
       <c r="BJ34" s="48"/>
       <c r="BM34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="BN34" s="129"/>
       <c r="BO34" s="130" t="str">
@@ -13634,7 +13642,7 @@
       </c>
       <c r="BQ34" s="48"/>
       <c r="BT34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="BU34" s="129"/>
       <c r="BV34" s="130" t="str">
@@ -13642,7 +13650,7 @@
       </c>
       <c r="BX34" s="48"/>
       <c r="CA34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="CB34" s="129"/>
       <c r="CC34" s="130" t="str">
@@ -13650,7 +13658,7 @@
       </c>
       <c r="CE34" s="48"/>
       <c r="CH34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="CI34" s="129"/>
       <c r="CJ34" s="130" t="str">
@@ -13658,7 +13666,7 @@
       </c>
       <c r="CL34" s="48"/>
       <c r="CO34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="CP34" s="129"/>
       <c r="CQ34" s="130" t="str">
@@ -13666,7 +13674,7 @@
       </c>
       <c r="CS34" s="48"/>
       <c r="CV34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="CW34" s="129"/>
       <c r="CX34" s="130" t="str">
@@ -13674,7 +13682,7 @@
       </c>
       <c r="CZ34" s="48"/>
       <c r="DC34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="DD34" s="129"/>
       <c r="DE34" s="130" t="str">
@@ -13682,7 +13690,7 @@
       </c>
       <c r="DG34" s="48"/>
       <c r="DJ34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="DK34" s="129"/>
       <c r="DL34" s="130" t="str">
@@ -13690,7 +13698,7 @@
       </c>
       <c r="DN34" s="48"/>
       <c r="DQ34" s="154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="DR34" s="129"/>
       <c r="DS34" s="130" t="str">
@@ -13700,7 +13708,7 @@
     </row>
     <row r="35">
       <c r="B35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C35" s="129"/>
       <c r="D35" s="130" t="str">
@@ -13708,7 +13716,7 @@
       </c>
       <c r="F35" s="48"/>
       <c r="I35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J35" s="129"/>
       <c r="K35" s="130" t="str">
@@ -13716,7 +13724,7 @@
       </c>
       <c r="M35" s="48"/>
       <c r="P35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q35" s="129"/>
       <c r="R35" s="130" t="str">
@@ -13724,7 +13732,7 @@
       </c>
       <c r="T35" s="48"/>
       <c r="W35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="X35" s="129"/>
       <c r="Y35" s="130" t="str">
@@ -13732,7 +13740,7 @@
       </c>
       <c r="AA35" s="48"/>
       <c r="AD35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AE35" s="129"/>
       <c r="AF35" s="130" t="str">
@@ -13740,7 +13748,7 @@
       </c>
       <c r="AH35" s="48"/>
       <c r="AK35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL35" s="129"/>
       <c r="AM35" s="130" t="str">
@@ -13748,7 +13756,7 @@
       </c>
       <c r="AO35" s="48"/>
       <c r="AR35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AS35" s="129"/>
       <c r="AT35" s="130" t="str">
@@ -13756,7 +13764,7 @@
       </c>
       <c r="AV35" s="48"/>
       <c r="AY35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AZ35" s="129"/>
       <c r="BA35" s="130" t="str">
@@ -13764,7 +13772,7 @@
       </c>
       <c r="BC35" s="48"/>
       <c r="BF35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="BG35" s="129"/>
       <c r="BH35" s="130" t="str">
@@ -13772,7 +13780,7 @@
       </c>
       <c r="BJ35" s="48"/>
       <c r="BM35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="BN35" s="129"/>
       <c r="BO35" s="130" t="str">
@@ -13780,7 +13788,7 @@
       </c>
       <c r="BQ35" s="48"/>
       <c r="BT35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="BU35" s="129"/>
       <c r="BV35" s="130" t="str">
@@ -13788,7 +13796,7 @@
       </c>
       <c r="BX35" s="48"/>
       <c r="CA35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="CB35" s="129"/>
       <c r="CC35" s="130" t="str">
@@ -13796,7 +13804,7 @@
       </c>
       <c r="CE35" s="48"/>
       <c r="CH35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="CI35" s="129"/>
       <c r="CJ35" s="130" t="str">
@@ -13804,7 +13812,7 @@
       </c>
       <c r="CL35" s="48"/>
       <c r="CO35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="CP35" s="129"/>
       <c r="CQ35" s="130" t="str">
@@ -13812,7 +13820,7 @@
       </c>
       <c r="CS35" s="48"/>
       <c r="CV35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="CW35" s="129"/>
       <c r="CX35" s="130" t="str">
@@ -13820,7 +13828,7 @@
       </c>
       <c r="CZ35" s="48"/>
       <c r="DC35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="DD35" s="129"/>
       <c r="DE35" s="130" t="str">
@@ -13828,7 +13836,7 @@
       </c>
       <c r="DG35" s="48"/>
       <c r="DJ35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="DK35" s="129"/>
       <c r="DL35" s="130" t="str">
@@ -13836,7 +13844,7 @@
       </c>
       <c r="DN35" s="48"/>
       <c r="DQ35" s="154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="DR35" s="129"/>
       <c r="DS35" s="130" t="str">
@@ -13846,7 +13854,7 @@
     </row>
     <row r="36">
       <c r="B36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C36" s="129"/>
       <c r="D36" s="130" t="str">
@@ -13854,7 +13862,7 @@
       </c>
       <c r="F36" s="48"/>
       <c r="I36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J36" s="129"/>
       <c r="K36" s="130" t="str">
@@ -13862,7 +13870,7 @@
       </c>
       <c r="M36" s="48"/>
       <c r="P36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q36" s="129"/>
       <c r="R36" s="130" t="str">
@@ -13870,7 +13878,7 @@
       </c>
       <c r="T36" s="48"/>
       <c r="W36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X36" s="129"/>
       <c r="Y36" s="130" t="str">
@@ -13878,7 +13886,7 @@
       </c>
       <c r="AA36" s="48"/>
       <c r="AD36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AE36" s="129"/>
       <c r="AF36" s="130" t="str">
@@ -13886,7 +13894,7 @@
       </c>
       <c r="AH36" s="48"/>
       <c r="AK36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL36" s="129"/>
       <c r="AM36" s="130" t="str">
@@ -13894,7 +13902,7 @@
       </c>
       <c r="AO36" s="48"/>
       <c r="AR36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AS36" s="129"/>
       <c r="AT36" s="130" t="str">
@@ -13902,7 +13910,7 @@
       </c>
       <c r="AV36" s="48"/>
       <c r="AY36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AZ36" s="129"/>
       <c r="BA36" s="130" t="str">
@@ -13910,7 +13918,7 @@
       </c>
       <c r="BC36" s="48"/>
       <c r="BF36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="BG36" s="129"/>
       <c r="BH36" s="130" t="str">
@@ -13918,7 +13926,7 @@
       </c>
       <c r="BJ36" s="48"/>
       <c r="BM36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="BN36" s="129"/>
       <c r="BO36" s="130" t="str">
@@ -13926,7 +13934,7 @@
       </c>
       <c r="BQ36" s="48"/>
       <c r="BT36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="BU36" s="129"/>
       <c r="BV36" s="130" t="str">
@@ -13934,7 +13942,7 @@
       </c>
       <c r="BX36" s="48"/>
       <c r="CA36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="CB36" s="129"/>
       <c r="CC36" s="130" t="str">
@@ -13942,7 +13950,7 @@
       </c>
       <c r="CE36" s="48"/>
       <c r="CH36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="CI36" s="129"/>
       <c r="CJ36" s="130" t="str">
@@ -13950,7 +13958,7 @@
       </c>
       <c r="CL36" s="48"/>
       <c r="CO36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="CP36" s="129"/>
       <c r="CQ36" s="130" t="str">
@@ -13958,7 +13966,7 @@
       </c>
       <c r="CS36" s="48"/>
       <c r="CV36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="CW36" s="129"/>
       <c r="CX36" s="130" t="str">
@@ -13966,7 +13974,7 @@
       </c>
       <c r="CZ36" s="48"/>
       <c r="DC36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="DD36" s="129"/>
       <c r="DE36" s="130" t="str">
@@ -13974,7 +13982,7 @@
       </c>
       <c r="DG36" s="48"/>
       <c r="DJ36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="DK36" s="129"/>
       <c r="DL36" s="130" t="str">
@@ -13982,7 +13990,7 @@
       </c>
       <c r="DN36" s="48"/>
       <c r="DQ36" s="154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="DR36" s="129"/>
       <c r="DS36" s="130" t="str">
@@ -14030,7 +14038,7 @@
     </row>
     <row r="38">
       <c r="B38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C38" s="156" t="str">
         <f>=ROUND(IFERROR(C31-SUM(C34:C36),""),2)</f>
@@ -14041,7 +14049,7 @@
       <c r="E38" s="158"/>
       <c r="F38" s="159"/>
       <c r="I38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J38" s="156" t="str">
         <f>=ROUND(IFERROR(J31-SUM(J34:J36),""),2)</f>
@@ -14052,7 +14060,7 @@
       <c r="L38" s="158"/>
       <c r="M38" s="159"/>
       <c r="P38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q38" s="156" t="str">
         <f>=ROUND(IFERROR(Q31-SUM(Q34:Q36),""),2)</f>
@@ -14063,7 +14071,7 @@
       <c r="S38" s="158"/>
       <c r="T38" s="159"/>
       <c r="W38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="X38" s="156" t="str">
         <f>=ROUND(IFERROR(X31-SUM(X34:X36),""),2)</f>
@@ -14074,7 +14082,7 @@
       <c r="Z38" s="158"/>
       <c r="AA38" s="159"/>
       <c r="AD38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AE38" s="156" t="str">
         <f>=ROUND(IFERROR(AE31-SUM(AE34:AE36),""),2)</f>
@@ -14085,7 +14093,7 @@
       <c r="AG38" s="158"/>
       <c r="AH38" s="159"/>
       <c r="AK38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL38" s="156" t="str">
         <f>=ROUND(IFERROR(AL31-SUM(AL34:AL36),""),2)</f>
@@ -14096,7 +14104,7 @@
       <c r="AN38" s="158"/>
       <c r="AO38" s="159"/>
       <c r="AR38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AS38" s="156" t="str">
         <f>=ROUND(IFERROR(AS31-SUM(AS34:AS36),""),2)</f>
@@ -14107,7 +14115,7 @@
       <c r="AU38" s="158"/>
       <c r="AV38" s="159"/>
       <c r="AY38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AZ38" s="156" t="str">
         <f>=ROUND(IFERROR(AZ31-SUM(AZ34:AZ36),""),2)</f>
@@ -14118,7 +14126,7 @@
       <c r="BB38" s="158"/>
       <c r="BC38" s="159"/>
       <c r="BF38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="BG38" s="156" t="str">
         <f>=ROUND(IFERROR(BG31-SUM(BG34:BG36),""),2)</f>
@@ -14129,7 +14137,7 @@
       <c r="BI38" s="158"/>
       <c r="BJ38" s="159"/>
       <c r="BM38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="BN38" s="156" t="str">
         <f>=ROUND(IFERROR(BN31-SUM(BN34:BN36),""),2)</f>
@@ -14140,7 +14148,7 @@
       <c r="BP38" s="158"/>
       <c r="BQ38" s="159"/>
       <c r="BT38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="BU38" s="156" t="str">
         <f>=ROUND(IFERROR(BU31-SUM(BU34:BU36),""),2)</f>
@@ -14151,7 +14159,7 @@
       <c r="BW38" s="158"/>
       <c r="BX38" s="159"/>
       <c r="CA38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="CB38" s="156" t="str">
         <f>=ROUND(IFERROR(CB31-SUM(CB34:CB36),""),2)</f>
@@ -14162,7 +14170,7 @@
       <c r="CD38" s="158"/>
       <c r="CE38" s="159"/>
       <c r="CH38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="CI38" s="156" t="str">
         <f>=ROUND(IFERROR(CI31-SUM(CI34:CI36),""),2)</f>
@@ -14173,7 +14181,7 @@
       <c r="CK38" s="158"/>
       <c r="CL38" s="159"/>
       <c r="CO38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="CP38" s="156" t="str">
         <f>=ROUND(IFERROR(CP31-SUM(CP34:CP36),""),2)</f>
@@ -14184,7 +14192,7 @@
       <c r="CR38" s="158"/>
       <c r="CS38" s="159"/>
       <c r="CV38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="CW38" s="156" t="str">
         <f>=ROUND(IFERROR(CW31-SUM(CW34:CW36),""),2)</f>
@@ -14195,7 +14203,7 @@
       <c r="CY38" s="158"/>
       <c r="CZ38" s="159"/>
       <c r="DC38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="DD38" s="156" t="str">
         <f>=ROUND(IFERROR(DD31-SUM(DD34:DD36),""),2)</f>
@@ -14206,7 +14214,7 @@
       <c r="DF38" s="158"/>
       <c r="DG38" s="159"/>
       <c r="DJ38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="DK38" s="156" t="str">
         <f>=ROUND(IFERROR(DK31-SUM(DK34:DK36),""),2)</f>
@@ -14217,7 +14225,7 @@
       <c r="DM38" s="158"/>
       <c r="DN38" s="159"/>
       <c r="DQ38" s="155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="DR38" s="156" t="str">
         <f>=ROUND(IFERROR(DR31-SUM(DR34:DR36),""),2)</f>
@@ -14230,335 +14238,335 @@
     </row>
     <row r="41">
       <c r="B41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="W41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AD41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AK41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AR41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AY41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="BF41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="BM41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="BT41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="CA41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="CH41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="CO41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="CV41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="DC41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="DJ41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="DQ41" s="105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="121" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="D42" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="E42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="F42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="I42" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="D42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="E42" s="121" t="s">
+      <c r="J42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="K42" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="F42" s="121" t="s">
+      <c r="L42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="M42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="P42" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q42" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="I42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="J42" s="121" t="s">
+      <c r="R42" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="S42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="T42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="W42" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="K42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="L42" s="121" t="s">
+      <c r="X42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="Y42" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="M42" s="121" t="s">
+      <c r="Z42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="AD42" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="AE42" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="P42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q42" s="121" t="s">
+      <c r="AF42" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="AG42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="AH42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="AK42" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="R42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="S42" s="121" t="s">
+      <c r="AL42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM42" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="T42" s="121" t="s">
+      <c r="AN42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="AR42" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="AS42" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="W42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="X42" s="121" t="s">
+      <c r="AT42" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="AU42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="AV42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="AY42" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="Y42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="Z42" s="121" t="s">
+      <c r="AZ42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="BA42" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="AA42" s="121" t="s">
+      <c r="BB42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="BC42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF42" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="BG42" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="AD42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="AE42" s="121" t="s">
+      <c r="BH42" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="BI42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="BJ42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="BM42" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="AF42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="AG42" s="121" t="s">
+      <c r="BN42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="BO42" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="AH42" s="121" t="s">
+      <c r="BP42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="BQ42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="BT42" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="BU42" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="AK42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="AL42" s="121" t="s">
+      <c r="BV42" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="BW42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="BX42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="CA42" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="AM42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="AN42" s="121" t="s">
+      <c r="CB42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="CC42" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="AO42" s="121" t="s">
+      <c r="CD42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="CE42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="CH42" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="CI42" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="AR42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="AS42" s="121" t="s">
+      <c r="CJ42" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="CK42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="CL42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="CO42" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="AT42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="AU42" s="121" t="s">
+      <c r="CP42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="CQ42" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="AV42" s="121" t="s">
+      <c r="CR42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="CS42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="CV42" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="CW42" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="AY42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="AZ42" s="121" t="s">
+      <c r="CX42" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="CY42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="CZ42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="DC42" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="BA42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="BB42" s="121" t="s">
+      <c r="DD42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="DE42" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="BC42" s="121" t="s">
+      <c r="DF42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="DG42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="DJ42" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="DK42" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="BF42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="BG42" s="121" t="s">
+      <c r="DL42" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="DM42" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="DN42" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="DQ42" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="BH42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="BI42" s="121" t="s">
+      <c r="DR42" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="DS42" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="BJ42" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="BM42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="BN42" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="BO42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="BP42" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="BQ42" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="BT42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="BU42" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="BV42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="BW42" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="BX42" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="CA42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="CB42" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="CC42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="CD42" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="CE42" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="CH42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="CI42" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="CJ42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="CK42" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="CL42" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="CO42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="CP42" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="CQ42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="CR42" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="CS42" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="CV42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="CW42" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="CX42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="CY42" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="CZ42" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="DC42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="DD42" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="DE42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="DF42" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="DG42" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="DJ42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="DK42" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="DL42" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="DM42" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="DN42" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="DQ42" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="DR42" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="DS42" s="121" t="s">
-        <v>297</v>
-      </c>
       <c r="DT42" s="121" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="DU42" s="121" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="160" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C43" s="161" t="s">
         <v>158</v>
@@ -14573,7 +14581,7 @@
         <f>=ROUND(IFERROR(D43/E43,0),6)</f>
       </c>
       <c r="I43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J43" s="161" t="s">
         <v>158</v>
@@ -14588,7 +14596,7 @@
         <f>=ROUND(IFERROR(K43/L43,0),6)</f>
       </c>
       <c r="P43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q43" s="161" t="s">
         <v>158</v>
@@ -14603,7 +14611,7 @@
         <f>=ROUND(IFERROR(R43/S43,0),6)</f>
       </c>
       <c r="W43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X43" s="161" t="s">
         <v>158</v>
@@ -14618,7 +14626,7 @@
         <f>=ROUND(IFERROR(Y43/Z43,0),6)</f>
       </c>
       <c r="AD43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AE43" s="161" t="s">
         <v>158</v>
@@ -14633,7 +14641,7 @@
         <f>=ROUND(IFERROR(AF43/AG43,0),6)</f>
       </c>
       <c r="AK43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL43" s="161" t="s">
         <v>158</v>
@@ -14648,7 +14656,7 @@
         <f>=ROUND(IFERROR(AM43/AN43,0),6)</f>
       </c>
       <c r="AR43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AS43" s="161" t="s">
         <v>158</v>
@@ -14663,7 +14671,7 @@
         <f>=ROUND(IFERROR(AT43/AU43,0),6)</f>
       </c>
       <c r="AY43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AZ43" s="161" t="s">
         <v>158</v>
@@ -14678,7 +14686,7 @@
         <f>=ROUND(IFERROR(BA43/BB43,0),6)</f>
       </c>
       <c r="BF43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="BG43" s="161" t="s">
         <v>158</v>
@@ -14693,7 +14701,7 @@
         <f>=ROUND(IFERROR(BH43/BI43,0),6)</f>
       </c>
       <c r="BM43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="BN43" s="161" t="s">
         <v>158</v>
@@ -14708,7 +14716,7 @@
         <f>=ROUND(IFERROR(BO43/BP43,0),6)</f>
       </c>
       <c r="BT43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="BU43" s="161" t="s">
         <v>158</v>
@@ -14723,7 +14731,7 @@
         <f>=ROUND(IFERROR(BV43/BW43,0),6)</f>
       </c>
       <c r="CA43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="CB43" s="161" t="s">
         <v>158</v>
@@ -14738,7 +14746,7 @@
         <f>=ROUND(IFERROR(CC43/CD43,0),6)</f>
       </c>
       <c r="CH43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="CI43" s="161" t="s">
         <v>158</v>
@@ -14753,7 +14761,7 @@
         <f>=ROUND(IFERROR(CJ43/CK43,0),6)</f>
       </c>
       <c r="CO43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="CP43" s="161" t="s">
         <v>158</v>
@@ -14768,7 +14776,7 @@
         <f>=ROUND(IFERROR(CQ43/CR43,0),6)</f>
       </c>
       <c r="CV43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="CW43" s="161" t="s">
         <v>158</v>
@@ -14783,7 +14791,7 @@
         <f>=ROUND(IFERROR(CX43/CY43,0),6)</f>
       </c>
       <c r="DC43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="DD43" s="161" t="s">
         <v>158</v>
@@ -14798,7 +14806,7 @@
         <f>=ROUND(IFERROR(DE43/DF43,0),6)</f>
       </c>
       <c r="DJ43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="DK43" s="161" t="s">
         <v>158</v>
@@ -14813,7 +14821,7 @@
         <f>=ROUND(IFERROR(DL43/DM43,0),6)</f>
       </c>
       <c r="DQ43" s="160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="DR43" s="161" t="s">
         <v>158</v>
@@ -15638,10 +15646,10 @@
     </row>
     <row r="48">
       <c r="B48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$D$43:$D$47),2)</f>
@@ -15653,10 +15661,10 @@
         <f>=ROUND(IFERROR(D48/E48,0),6)</f>
       </c>
       <c r="I48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$K$43:$K$47),2)</f>
@@ -15668,10 +15676,10 @@
         <f>=ROUND(IFERROR(K48/L48,0),6)</f>
       </c>
       <c r="P48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$R$43:$R$47),2)</f>
@@ -15683,10 +15691,10 @@
         <f>=ROUND(IFERROR(R48/S48,0),6)</f>
       </c>
       <c r="W48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="X48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$Y$43:$Y$47),2)</f>
@@ -15698,10 +15706,10 @@
         <f>=ROUND(IFERROR(Y48/Z48,0),6)</f>
       </c>
       <c r="AD48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AE48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AF48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$AF$43:$AF$47),2)</f>
@@ -15713,10 +15721,10 @@
         <f>=ROUND(IFERROR(AF48/AG48,0),6)</f>
       </c>
       <c r="AK48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$AM$43:$AM$47),2)</f>
@@ -15728,10 +15736,10 @@
         <f>=ROUND(IFERROR(AM48/AN48,0),6)</f>
       </c>
       <c r="AR48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AS48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AT48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$AT$43:$AT$47),2)</f>
@@ -15743,10 +15751,10 @@
         <f>=ROUND(IFERROR(AT48/AU48,0),6)</f>
       </c>
       <c r="AY48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AZ48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BA48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$BA$43:$BA$47),2)</f>
@@ -15758,10 +15766,10 @@
         <f>=ROUND(IFERROR(BA48/BB48,0),6)</f>
       </c>
       <c r="BF48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="BG48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BH48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$BH$43:$BH$47),2)</f>
@@ -15773,10 +15781,10 @@
         <f>=ROUND(IFERROR(BH48/BI48,0),6)</f>
       </c>
       <c r="BM48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="BN48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BO48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$BO$43:$BO$47),2)</f>
@@ -15788,10 +15796,10 @@
         <f>=ROUND(IFERROR(BO48/BP48,0),6)</f>
       </c>
       <c r="BT48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="BU48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BV48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$BV$43:$BV$47),2)</f>
@@ -15803,10 +15811,10 @@
         <f>=ROUND(IFERROR(BV48/BW48,0),6)</f>
       </c>
       <c r="CA48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="CB48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CC48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$CC$43:$CC$47),2)</f>
@@ -15818,10 +15826,10 @@
         <f>=ROUND(IFERROR(CC48/CD48,0),6)</f>
       </c>
       <c r="CH48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="CI48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CJ48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$CJ$43:$CJ$47),2)</f>
@@ -15833,10 +15841,10 @@
         <f>=ROUND(IFERROR(CJ48/CK48,0),6)</f>
       </c>
       <c r="CO48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="CP48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CQ48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$CQ$43:$CQ$47),2)</f>
@@ -15848,10 +15856,10 @@
         <f>=ROUND(IFERROR(CQ48/CR48,0),6)</f>
       </c>
       <c r="CV48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="CW48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CX48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$CX$43:$CX$47),2)</f>
@@ -15863,10 +15871,10 @@
         <f>=ROUND(IFERROR(CX48/CY48,0),6)</f>
       </c>
       <c r="DC48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="DD48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DE48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$DE$43:$DE$47),2)</f>
@@ -15878,10 +15886,10 @@
         <f>=ROUND(IFERROR(DE48/DF48,0),6)</f>
       </c>
       <c r="DJ48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="DK48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DL48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$DL$43:$DL$47),2)</f>
@@ -15893,10 +15901,10 @@
         <f>=ROUND(IFERROR(DL48/DM48,0),6)</f>
       </c>
       <c r="DQ48" s="170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="DR48" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DS48" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$DS$43:$DS$47),2)</f>
@@ -15910,330 +15918,330 @@
     </row>
     <row r="50">
       <c r="B50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="W50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AD50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AK50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AR50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AY50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="BF50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="BM50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="BT50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="CA50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="CH50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="CO50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="CV50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="DC50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="DJ50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="DQ50" s="105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="121" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="D51" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="E51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="F51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="I51" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="D51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="E51" s="121" t="s">
+      <c r="J51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="K51" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="F51" s="121" t="s">
+      <c r="L51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="M51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="P51" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q51" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="I51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="J51" s="121" t="s">
+      <c r="R51" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="S51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="T51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="W51" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="K51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="L51" s="121" t="s">
+      <c r="X51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="Y51" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="M51" s="121" t="s">
+      <c r="Z51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="AD51" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="AE51" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="P51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q51" s="121" t="s">
+      <c r="AF51" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="AG51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="AH51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="AK51" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="R51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="S51" s="121" t="s">
+      <c r="AL51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM51" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="T51" s="121" t="s">
+      <c r="AN51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="AR51" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="AS51" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="W51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="X51" s="121" t="s">
+      <c r="AT51" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="AU51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="AV51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="AY51" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="Y51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="Z51" s="121" t="s">
+      <c r="AZ51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="BA51" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="AA51" s="121" t="s">
+      <c r="BB51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="BC51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF51" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="BG51" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="AD51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="AE51" s="121" t="s">
+      <c r="BH51" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="BI51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="BJ51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="BM51" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="AF51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="AG51" s="121" t="s">
+      <c r="BN51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="BO51" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="AH51" s="121" t="s">
+      <c r="BP51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="BQ51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="BT51" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="BU51" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="AK51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="AL51" s="121" t="s">
+      <c r="BV51" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="BW51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="BX51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="CA51" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="AM51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="AN51" s="121" t="s">
+      <c r="CB51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="CC51" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="AO51" s="121" t="s">
+      <c r="CD51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="CE51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="CH51" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="CI51" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="AR51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="AS51" s="121" t="s">
+      <c r="CJ51" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="CK51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="CL51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="CO51" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="AT51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="AU51" s="121" t="s">
+      <c r="CP51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="CQ51" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="AV51" s="121" t="s">
+      <c r="CR51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="CS51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="CV51" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="CW51" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="AY51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="AZ51" s="121" t="s">
+      <c r="CX51" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="CY51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="CZ51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="DC51" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="BA51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="BB51" s="121" t="s">
+      <c r="DD51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="DE51" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="BC51" s="121" t="s">
+      <c r="DF51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="DG51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="DJ51" s="121" t="s">
+        <v>319</v>
+      </c>
+      <c r="DK51" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="BF51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="BG51" s="121" t="s">
+      <c r="DL51" s="121" t="s">
+        <v>298</v>
+      </c>
+      <c r="DM51" s="121" t="s">
+        <v>299</v>
+      </c>
+      <c r="DN51" s="121" t="s">
+        <v>321</v>
+      </c>
+      <c r="DQ51" s="121" t="s">
         <v>319</v>
       </c>
-      <c r="BH51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="BI51" s="121" t="s">
+      <c r="DR51" s="121" t="s">
+        <v>320</v>
+      </c>
+      <c r="DS51" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="BJ51" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="BM51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="BN51" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="BO51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="BP51" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="BQ51" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="BT51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="BU51" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="BV51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="BW51" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="BX51" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="CA51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="CB51" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="CC51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="CD51" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="CE51" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="CH51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="CI51" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="CJ51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="CK51" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="CL51" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="CO51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="CP51" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="CQ51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="CR51" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="CS51" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="CV51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="CW51" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="CX51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="CY51" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="CZ51" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="DC51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="DD51" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="DE51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="DF51" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="DG51" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="DJ51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="DK51" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="DL51" s="121" t="s">
-        <v>297</v>
-      </c>
-      <c r="DM51" s="121" t="s">
-        <v>298</v>
-      </c>
-      <c r="DN51" s="121" t="s">
-        <v>320</v>
-      </c>
-      <c r="DQ51" s="121" t="s">
-        <v>318</v>
-      </c>
-      <c r="DR51" s="121" t="s">
-        <v>319</v>
-      </c>
-      <c r="DS51" s="121" t="s">
-        <v>297</v>
-      </c>
       <c r="DT51" s="121" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="DU51" s="121" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52">
@@ -16478,7 +16486,7 @@
     </row>
     <row r="53">
       <c r="B53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C53" s="166" t="s">
         <v>158</v>
@@ -16493,7 +16501,7 @@
         <f>=ROUND(IFERROR(D53/E53,0),6)</f>
       </c>
       <c r="I53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J53" s="166" t="s">
         <v>158</v>
@@ -16508,7 +16516,7 @@
         <f>=ROUND(IFERROR(K53/L53,0),6)</f>
       </c>
       <c r="P53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q53" s="166" t="s">
         <v>158</v>
@@ -16521,7 +16529,7 @@
         <f>=ROUND(IFERROR(R53/S53,0),6)</f>
       </c>
       <c r="W53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="X53" s="166" t="s">
         <v>158</v>
@@ -16534,7 +16542,7 @@
         <f>=ROUND(IFERROR(Y53/Z53,0),6)</f>
       </c>
       <c r="AD53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AE53" s="166" t="s">
         <v>158</v>
@@ -16547,7 +16555,7 @@
         <f>=ROUND(IFERROR(AF53/AG53,0),6)</f>
       </c>
       <c r="AK53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL53" s="166" t="s">
         <v>158</v>
@@ -16560,7 +16568,7 @@
         <f>=ROUND(IFERROR(AM53/AN53,0),6)</f>
       </c>
       <c r="AR53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AS53" s="166" t="s">
         <v>158</v>
@@ -16573,7 +16581,7 @@
         <f>=ROUND(IFERROR(AT53/AU53,0),6)</f>
       </c>
       <c r="AY53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AZ53" s="166" t="s">
         <v>158</v>
@@ -16586,7 +16594,7 @@
         <f>=ROUND(IFERROR(BA53/BB53,0),6)</f>
       </c>
       <c r="BF53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BG53" s="166" t="s">
         <v>158</v>
@@ -16599,7 +16607,7 @@
         <f>=ROUND(IFERROR(BH53/BI53,0),6)</f>
       </c>
       <c r="BM53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BN53" s="166" t="s">
         <v>158</v>
@@ -16612,7 +16620,7 @@
         <f>=ROUND(IFERROR(BO53/BP53,0),6)</f>
       </c>
       <c r="BT53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU53" s="166" t="s">
         <v>158</v>
@@ -16625,7 +16633,7 @@
         <f>=ROUND(IFERROR(BV53/BW53,0),6)</f>
       </c>
       <c r="CA53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="CB53" s="166" t="s">
         <v>158</v>
@@ -16638,7 +16646,7 @@
         <f>=ROUND(IFERROR(CC53/CD53,0),6)</f>
       </c>
       <c r="CH53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="CI53" s="166" t="s">
         <v>158</v>
@@ -16651,7 +16659,7 @@
         <f>=ROUND(IFERROR(CJ53/CK53,0),6)</f>
       </c>
       <c r="CO53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="CP53" s="166" t="s">
         <v>158</v>
@@ -16664,7 +16672,7 @@
         <f>=ROUND(IFERROR(CQ53/CR53,0),6)</f>
       </c>
       <c r="CV53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="CW53" s="166" t="s">
         <v>158</v>
@@ -16677,7 +16685,7 @@
         <f>=ROUND(IFERROR(CX53/CY53,0),6)</f>
       </c>
       <c r="DC53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="DD53" s="166" t="s">
         <v>158</v>
@@ -16690,7 +16698,7 @@
         <f>=ROUND(IFERROR(DE53/DF53,0),6)</f>
       </c>
       <c r="DJ53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="DK53" s="166" t="s">
         <v>158</v>
@@ -16703,7 +16711,7 @@
         <f>=ROUND(IFERROR(DL53/DM53,0),6)</f>
       </c>
       <c r="DQ53" s="165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="DR53" s="166" t="s">
         <v>158</v>
@@ -16718,7 +16726,7 @@
     </row>
     <row r="54">
       <c r="B54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C54" s="166" t="s">
         <v>158</v>
@@ -16731,7 +16739,7 @@
         <f>=ROUND(IFERROR(D54/E54,0),6)</f>
       </c>
       <c r="I54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J54" s="166" t="s">
         <v>158</v>
@@ -16744,7 +16752,7 @@
         <f>=ROUND(IFERROR(K54/L54,0),6)</f>
       </c>
       <c r="P54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q54" s="166" t="s">
         <v>158</v>
@@ -16757,7 +16765,7 @@
         <f>=ROUND(IFERROR(R54/S54,0),6)</f>
       </c>
       <c r="W54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="X54" s="166" t="s">
         <v>158</v>
@@ -16770,7 +16778,7 @@
         <f>=ROUND(IFERROR(Y54/Z54,0),6)</f>
       </c>
       <c r="AD54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AE54" s="166" t="s">
         <v>158</v>
@@ -16783,7 +16791,7 @@
         <f>=ROUND(IFERROR(AF54/AG54,0),6)</f>
       </c>
       <c r="AK54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL54" s="166" t="s">
         <v>158</v>
@@ -16796,7 +16804,7 @@
         <f>=ROUND(IFERROR(AM54/AN54,0),6)</f>
       </c>
       <c r="AR54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AS54" s="166" t="s">
         <v>158</v>
@@ -16809,7 +16817,7 @@
         <f>=ROUND(IFERROR(AT54/AU54,0),6)</f>
       </c>
       <c r="AY54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AZ54" s="166" t="s">
         <v>158</v>
@@ -16822,7 +16830,7 @@
         <f>=ROUND(IFERROR(BA54/BB54,0),6)</f>
       </c>
       <c r="BF54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BG54" s="166" t="s">
         <v>158</v>
@@ -16835,7 +16843,7 @@
         <f>=ROUND(IFERROR(BH54/BI54,0),6)</f>
       </c>
       <c r="BM54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BN54" s="166" t="s">
         <v>158</v>
@@ -16848,7 +16856,7 @@
         <f>=ROUND(IFERROR(BO54/BP54,0),6)</f>
       </c>
       <c r="BT54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BU54" s="166" t="s">
         <v>158</v>
@@ -16861,7 +16869,7 @@
         <f>=ROUND(IFERROR(BV54/BW54,0),6)</f>
       </c>
       <c r="CA54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="CB54" s="166" t="s">
         <v>158</v>
@@ -16874,7 +16882,7 @@
         <f>=ROUND(IFERROR(CC54/CD54,0),6)</f>
       </c>
       <c r="CH54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="CI54" s="166" t="s">
         <v>158</v>
@@ -16887,7 +16895,7 @@
         <f>=ROUND(IFERROR(CJ54/CK54,0),6)</f>
       </c>
       <c r="CO54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="CP54" s="166" t="s">
         <v>158</v>
@@ -16900,7 +16908,7 @@
         <f>=ROUND(IFERROR(CQ54/CR54,0),6)</f>
       </c>
       <c r="CV54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="CW54" s="166" t="s">
         <v>158</v>
@@ -16913,7 +16921,7 @@
         <f>=ROUND(IFERROR(CX54/CY54,0),6)</f>
       </c>
       <c r="DC54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="DD54" s="166" t="s">
         <v>158</v>
@@ -16926,7 +16934,7 @@
         <f>=ROUND(IFERROR(DE54/DF54,0),6)</f>
       </c>
       <c r="DJ54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="DK54" s="166" t="s">
         <v>158</v>
@@ -16939,7 +16947,7 @@
         <f>=ROUND(IFERROR(DL54/DM54,0),6)</f>
       </c>
       <c r="DQ54" s="165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="DR54" s="166" t="s">
         <v>158</v>
@@ -17662,10 +17670,10 @@
     </row>
     <row r="58">
       <c r="B58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$D$52:$D$57),2)</f>
@@ -17677,10 +17685,10 @@
         <f>=ROUND(IFERROR(D58/E58,0),6)</f>
       </c>
       <c r="I58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$K$52:$K$57),2)</f>
@@ -17692,10 +17700,10 @@
         <f>=ROUND(IFERROR(K58/L58,0),6)</f>
       </c>
       <c r="P58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$R$52:$R$57),2)</f>
@@ -17707,10 +17715,10 @@
         <f>=ROUND(IFERROR(R58/S58,0),6)</f>
       </c>
       <c r="W58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="X58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$Y$52:$Y$57),2)</f>
@@ -17722,10 +17730,10 @@
         <f>=ROUND(IFERROR(Y58/Z58,0),6)</f>
       </c>
       <c r="AD58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AE58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AF58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$AF$52:$AF$57),2)</f>
@@ -17737,10 +17745,10 @@
         <f>=ROUND(IFERROR(AF58/AG58,0),6)</f>
       </c>
       <c r="AK58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$AM$52:$AM$57),2)</f>
@@ -17752,10 +17760,10 @@
         <f>=ROUND(IFERROR(AM58/AN58,0),6)</f>
       </c>
       <c r="AR58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AS58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AT58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$AT$52:$AT$57),2)</f>
@@ -17767,10 +17775,10 @@
         <f>=ROUND(IFERROR(AT58/AU58,0),6)</f>
       </c>
       <c r="AY58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AZ58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BA58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$BA$52:$BA$57),2)</f>
@@ -17782,10 +17790,10 @@
         <f>=ROUND(IFERROR(BA58/BB58,0),6)</f>
       </c>
       <c r="BF58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="BG58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BH58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$BH$52:$BH$57),2)</f>
@@ -17797,10 +17805,10 @@
         <f>=ROUND(IFERROR(BH58/BI58,0),6)</f>
       </c>
       <c r="BM58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="BN58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BO58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$BO$52:$BO$57),2)</f>
@@ -17812,10 +17820,10 @@
         <f>=ROUND(IFERROR(BO58/BP58,0),6)</f>
       </c>
       <c r="BT58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="BU58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="BV58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$BV$52:$BV$57),2)</f>
@@ -17827,10 +17835,10 @@
         <f>=ROUND(IFERROR(BV58/BW58,0),6)</f>
       </c>
       <c r="CA58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="CB58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CC58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$CC$52:$CC$57),2)</f>
@@ -17842,10 +17850,10 @@
         <f>=ROUND(IFERROR(CC58/CD58,0),6)</f>
       </c>
       <c r="CH58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="CI58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CJ58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$CJ$52:$CJ$57),2)</f>
@@ -17857,10 +17865,10 @@
         <f>=ROUND(IFERROR(CJ58/CK58,0),6)</f>
       </c>
       <c r="CO58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="CP58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CQ58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$CQ$52:$CQ$57),2)</f>
@@ -17872,10 +17880,10 @@
         <f>=ROUND(IFERROR(CQ58/CR58,0),6)</f>
       </c>
       <c r="CV58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="CW58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CX58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$CX$52:$CX$57),2)</f>
@@ -17887,10 +17895,10 @@
         <f>=ROUND(IFERROR(CX58/CY58,0),6)</f>
       </c>
       <c r="DC58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="DD58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DE58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$DE$52:$DE$57),2)</f>
@@ -17902,10 +17910,10 @@
         <f>=ROUND(IFERROR(DE58/DF58,0),6)</f>
       </c>
       <c r="DJ58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="DK58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DL58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$DL$52:$DL$57),2)</f>
@@ -17917,10 +17925,10 @@
         <f>=ROUND(IFERROR(DL58/DM58,0),6)</f>
       </c>
       <c r="DQ58" s="170" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="DR58" s="171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DS58" s="172" t="str">
         <f>=ROUND(SUBTOTAL(109,$DS$52:$DS$57),2)</f>
@@ -18548,499 +18556,499 @@
   <sheetData>
     <row r="3">
       <c r="E3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="U3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AC3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AS3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AW3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BA3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BE3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BI3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BM3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BQ3" s="176" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C4" s="177" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D4" s="177"/>
       <c r="F4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G4" s="177" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H4" s="177"/>
       <c r="J4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K4" s="177" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L4" s="177"/>
       <c r="N4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O4" s="177" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P4" s="177"/>
       <c r="R4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S4" s="177" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T4" s="177"/>
       <c r="V4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="W4" s="177" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="X4" s="177"/>
       <c r="Z4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA4" s="177" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AB4" s="177"/>
       <c r="AD4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AE4" s="177" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AF4" s="177"/>
       <c r="AH4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI4" s="177" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AJ4" s="177"/>
       <c r="AL4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM4" s="177" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN4" s="177"/>
       <c r="AP4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ4" s="177" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AR4" s="177"/>
       <c r="AT4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AU4" s="177" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AV4" s="177"/>
       <c r="AX4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AY4" s="177" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AZ4" s="177"/>
       <c r="BB4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BC4" s="177" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BD4" s="177"/>
       <c r="BF4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BG4" s="177" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="BH4" s="177"/>
       <c r="BJ4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BK4" s="177" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="BL4" s="177"/>
       <c r="BN4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BO4" s="177" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="BP4" s="177"/>
       <c r="BR4" s="105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="BS4" s="177" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="BT4" s="177"/>
     </row>
     <row r="5">
       <c r="B5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C5" s="108">
         <v>45658</v>
       </c>
       <c r="D5" s="108"/>
       <c r="F5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G5" s="108">
         <v>45839</v>
       </c>
       <c r="H5" s="108"/>
       <c r="J5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K5" s="108"/>
       <c r="L5" s="108"/>
       <c r="N5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O5" s="108"/>
       <c r="P5" s="108"/>
       <c r="R5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="S5" s="108"/>
       <c r="T5" s="108"/>
       <c r="V5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="W5" s="108"/>
       <c r="X5" s="108"/>
       <c r="Z5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA5" s="108"/>
       <c r="AB5" s="108"/>
       <c r="AD5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AE5" s="108"/>
       <c r="AF5" s="108"/>
       <c r="AH5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI5" s="108"/>
       <c r="AJ5" s="108"/>
       <c r="AL5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM5" s="108"/>
       <c r="AN5" s="108"/>
       <c r="AP5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ5" s="108"/>
       <c r="AR5" s="108"/>
       <c r="AT5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AU5" s="108"/>
       <c r="AV5" s="108"/>
       <c r="AX5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AY5" s="108"/>
       <c r="AZ5" s="108"/>
       <c r="BB5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BC5" s="108"/>
       <c r="BD5" s="108"/>
       <c r="BF5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BG5" s="108"/>
       <c r="BH5" s="108"/>
       <c r="BJ5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BK5" s="108"/>
       <c r="BL5" s="108"/>
       <c r="BN5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BO5" s="108"/>
       <c r="BP5" s="108"/>
       <c r="BR5" s="105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="BS5" s="108"/>
       <c r="BT5" s="108"/>
     </row>
     <row r="6">
       <c r="B6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C6" s="108">
         <v>45838</v>
       </c>
       <c r="D6" s="108"/>
       <c r="F6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G6" s="108">
         <v>46022</v>
       </c>
       <c r="H6" s="108"/>
       <c r="J6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K6" s="108"/>
       <c r="L6" s="108"/>
       <c r="N6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O6" s="108"/>
       <c r="P6" s="108"/>
       <c r="R6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S6" s="108"/>
       <c r="T6" s="108"/>
       <c r="V6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="W6" s="108"/>
       <c r="X6" s="108"/>
       <c r="Z6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA6" s="108"/>
       <c r="AB6" s="108"/>
       <c r="AD6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AE6" s="108"/>
       <c r="AF6" s="108"/>
       <c r="AH6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AI6" s="108"/>
       <c r="AJ6" s="108"/>
       <c r="AL6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM6" s="108"/>
       <c r="AN6" s="108"/>
       <c r="AP6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ6" s="108"/>
       <c r="AR6" s="108"/>
       <c r="AT6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AU6" s="108"/>
       <c r="AV6" s="108"/>
       <c r="AX6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AY6" s="108"/>
       <c r="AZ6" s="108"/>
       <c r="BB6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BC6" s="108"/>
       <c r="BD6" s="108"/>
       <c r="BF6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BG6" s="108"/>
       <c r="BH6" s="108"/>
       <c r="BJ6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BK6" s="108"/>
       <c r="BL6" s="108"/>
       <c r="BN6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BO6" s="108"/>
       <c r="BP6" s="108"/>
       <c r="BR6" s="105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BS6" s="108"/>
       <c r="BT6" s="108"/>
     </row>
     <row r="7">
       <c r="B7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C7" s="178" t="str">
         <f>=IF(OR(C5="",C6=""),"",DATEDIF(C5,C6,"m")+1)</f>
       </c>
       <c r="D7" s="178"/>
       <c r="F7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G7" s="178" t="str">
         <f>=IF(OR(G5="",G6=""),"",DATEDIF(G5,G6,"m")+1)</f>
       </c>
       <c r="H7" s="178"/>
       <c r="J7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K7" s="178" t="str">
         <f>=IF(OR(K5="",K6=""),"",DATEDIF(K5,K6,"m")+1)</f>
       </c>
       <c r="L7" s="178"/>
       <c r="N7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O7" s="178" t="str">
         <f>=IF(OR(O5="",O6=""),"",DATEDIF(O5,O6,"m")+1)</f>
       </c>
       <c r="P7" s="178"/>
       <c r="R7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="S7" s="178" t="str">
         <f>=IF(OR(S5="",S6=""),"",DATEDIF(S5,S6,"m")+1)</f>
       </c>
       <c r="T7" s="178"/>
       <c r="V7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W7" s="178" t="str">
         <f>=IF(OR(W5="",W6=""),"",DATEDIF(W5,W6,"m")+1)</f>
       </c>
       <c r="X7" s="178"/>
       <c r="Z7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA7" s="178" t="str">
         <f>=IF(OR(AA5="",AA6=""),"",DATEDIF(AA5,AA6,"m")+1)</f>
       </c>
       <c r="AB7" s="178"/>
       <c r="AD7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AE7" s="178" t="str">
         <f>=IF(OR(AE5="",AE6=""),"",DATEDIF(AE5,AE6,"m")+1)</f>
       </c>
       <c r="AF7" s="178"/>
       <c r="AH7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AI7" s="178" t="str">
         <f>=IF(OR(AI5="",AI6=""),"",DATEDIF(AI5,AI6,"m")+1)</f>
       </c>
       <c r="AJ7" s="178"/>
       <c r="AL7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM7" s="178" t="str">
         <f>=IF(OR(AM5="",AM6=""),"",DATEDIF(AM5,AM6,"m")+1)</f>
       </c>
       <c r="AN7" s="178"/>
       <c r="AP7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AQ7" s="178" t="str">
         <f>=IF(OR(AQ5="",AQ6=""),"",DATEDIF(AQ5,AQ6,"m")+1)</f>
       </c>
       <c r="AR7" s="178"/>
       <c r="AT7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AU7" s="178" t="str">
         <f>=IF(OR(AU5="",AU6=""),"",DATEDIF(AU5,AU6,"m")+1)</f>
       </c>
       <c r="AV7" s="178"/>
       <c r="AX7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AY7" s="178" t="str">
         <f>=IF(OR(AY5="",AY6=""),"",DATEDIF(AY5,AY6,"m")+1)</f>
       </c>
       <c r="AZ7" s="178"/>
       <c r="BB7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BC7" s="178" t="str">
         <f>=IF(OR(BC5="",BC6=""),"",DATEDIF(BC5,BC6,"m")+1)</f>
       </c>
       <c r="BD7" s="178"/>
       <c r="BF7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BG7" s="178" t="str">
         <f>=IF(OR(BG5="",BG6=""),"",DATEDIF(BG5,BG6,"m")+1)</f>
       </c>
       <c r="BH7" s="178"/>
       <c r="BJ7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BK7" s="178" t="str">
         <f>=IF(OR(BK5="",BK6=""),"",DATEDIF(BK5,BK6,"m")+1)</f>
       </c>
       <c r="BL7" s="178"/>
       <c r="BN7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BO7" s="178" t="str">
         <f>=IF(OR(BO5="",BO6=""),"",DATEDIF(BO5,BO6,"m")+1)</f>
       </c>
       <c r="BP7" s="178"/>
       <c r="BR7" s="105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BS7" s="178" t="str">
         <f>=IF(OR(BS5="",BS6=""),"",DATEDIF(BS5,BS6,"m")+1)</f>
@@ -19049,96 +19057,96 @@
     </row>
     <row r="8">
       <c r="B8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C8" s="179">
         <v>125</v>
       </c>
       <c r="D8" s="179"/>
       <c r="F8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G8" s="179">
         <v>125</v>
       </c>
       <c r="H8" s="179"/>
       <c r="J8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K8" s="179"/>
       <c r="L8" s="179"/>
       <c r="N8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O8" s="179"/>
       <c r="P8" s="179"/>
       <c r="R8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S8" s="179"/>
       <c r="T8" s="179"/>
       <c r="V8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="W8" s="179"/>
       <c r="X8" s="179"/>
       <c r="Z8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA8" s="179"/>
       <c r="AB8" s="179"/>
       <c r="AD8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AE8" s="179"/>
       <c r="AF8" s="179"/>
       <c r="AH8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AI8" s="179"/>
       <c r="AJ8" s="179"/>
       <c r="AL8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM8" s="179"/>
       <c r="AN8" s="179"/>
       <c r="AP8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AQ8" s="179"/>
       <c r="AR8" s="179"/>
       <c r="AT8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AU8" s="179"/>
       <c r="AV8" s="179"/>
       <c r="AX8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AY8" s="179"/>
       <c r="AZ8" s="179"/>
       <c r="BB8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="BC8" s="179"/>
       <c r="BD8" s="179"/>
       <c r="BF8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="BG8" s="179"/>
       <c r="BH8" s="179"/>
       <c r="BJ8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="BK8" s="179"/>
       <c r="BL8" s="179"/>
       <c r="BN8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="BO8" s="179"/>
       <c r="BP8" s="179"/>
       <c r="BR8" s="105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="BS8" s="179"/>
       <c r="BT8" s="179"/>
@@ -19148,163 +19156,163 @@
         <v>204</v>
       </c>
       <c r="C9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="G9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="K9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="O9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="S9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="T9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="V9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="W9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="X9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="AA9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AB9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AD9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="AE9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AF9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AH9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="AI9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AJ9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="AM9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AP9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="AQ9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AR9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AT9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="AU9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AV9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AX9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="AY9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AZ9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="BB9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="BC9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="BD9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="BF9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="BG9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="BH9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="BJ9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="BK9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="BL9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="BN9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="BO9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="BP9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="BR9" s="180" t="s">
         <v>204</v>
       </c>
       <c r="BS9" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="BT9" s="180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -20355,7 +20363,7 @@
     </row>
     <row r="18">
       <c r="B18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_1[Angefordert (LC)]),2)</f>
@@ -20364,7 +20372,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_1[Angefordert (EUR)]),2)</f>
       </c>
       <c r="F18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_2[Angefordert (LC)]),2)</f>
@@ -20373,7 +20381,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_2[Angefordert (EUR)]),2)</f>
       </c>
       <c r="J18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_3[Angefordert (LC)]),2)</f>
@@ -20382,7 +20390,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_3[Angefordert (EUR)]),2)</f>
       </c>
       <c r="N18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_4[Angefordert (LC)]),2)</f>
@@ -20391,7 +20399,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_4[Angefordert (EUR)]),2)</f>
       </c>
       <c r="R18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_5[Angefordert (LC)]),2)</f>
@@ -20400,7 +20408,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_5[Angefordert (EUR)]),2)</f>
       </c>
       <c r="V18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="W18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_6[Angefordert (LC)]),2)</f>
@@ -20409,7 +20417,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_6[Angefordert (EUR)]),2)</f>
       </c>
       <c r="Z18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_7[Angefordert (LC)]),2)</f>
@@ -20418,7 +20426,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_7[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AD18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AE18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_8[Angefordert (LC)]),2)</f>
@@ -20427,7 +20435,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_8[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AH18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AI18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_9[Angefordert (LC)]),2)</f>
@@ -20436,7 +20444,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_9[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AL18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_10[Angefordert (LC)]),2)</f>
@@ -20445,7 +20453,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_10[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AP18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AQ18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_11[Angefordert (LC)]),2)</f>
@@ -20454,7 +20462,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_11[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AT18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AU18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_12[Angefordert (LC)]),2)</f>
@@ -20463,7 +20471,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_12[Angefordert (EUR)]),2)</f>
       </c>
       <c r="AX18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AY18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_13[Angefordert (LC)]),2)</f>
@@ -20472,7 +20480,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_13[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BB18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="BC18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_14[Angefordert (LC)]),2)</f>
@@ -20481,7 +20489,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_14[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BF18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="BG18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_15[Angefordert (LC)]),2)</f>
@@ -20490,7 +20498,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_15[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BJ18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="BK18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_16[Angefordert (LC)]),2)</f>
@@ -20499,7 +20507,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_16[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BN18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="BO18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_17[Angefordert (LC)]),2)</f>
@@ -20508,7 +20516,7 @@
         <f>=ROUND(SUBTOTAL(109,MA_17[Angefordert (EUR)]),2)</f>
       </c>
       <c r="BR18" s="183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="BS18" s="184" t="str">
         <f>=ROUND(SUBTOTAL(109,MA_18[Angefordert (LC)]),2)</f>
@@ -20519,7 +20527,7 @@
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C20" s="186" t="str">
         <f>=ROUND($C$18,2)</f>
@@ -20528,7 +20536,7 @@
         <f>=ROUND($D$18,2)</f>
       </c>
       <c r="F20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G20" s="186" t="str">
         <f>=ROUND($G$18,2)</f>
@@ -20537,7 +20545,7 @@
         <f>=ROUND($H$18,2)</f>
       </c>
       <c r="J20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K20" s="186" t="str">
         <f>=ROUND($K$18,2)</f>
@@ -20546,7 +20554,7 @@
         <f>=ROUND($L$18,2)</f>
       </c>
       <c r="N20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O20" s="186" t="str">
         <f>=ROUND($O$18,2)</f>
@@ -20555,7 +20563,7 @@
         <f>=ROUND($P$18,2)</f>
       </c>
       <c r="R20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="S20" s="186" t="str">
         <f>=ROUND($S$18,2)</f>
@@ -20564,7 +20572,7 @@
         <f>=ROUND($T$18,2)</f>
       </c>
       <c r="V20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="W20" s="186" t="str">
         <f>=ROUND($W$18,2)</f>
@@ -20573,7 +20581,7 @@
         <f>=ROUND($X$18,2)</f>
       </c>
       <c r="Z20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AA20" s="186" t="str">
         <f>=ROUND($AA$18,2)</f>
@@ -20582,7 +20590,7 @@
         <f>=ROUND($AB$18,2)</f>
       </c>
       <c r="AD20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AE20" s="186" t="str">
         <f>=ROUND($AE$18,2)</f>
@@ -20591,7 +20599,7 @@
         <f>=ROUND($AF$18,2)</f>
       </c>
       <c r="AH20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AI20" s="186" t="str">
         <f>=ROUND($AI$18,2)</f>
@@ -20600,7 +20608,7 @@
         <f>=ROUND($AJ$18,2)</f>
       </c>
       <c r="AL20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM20" s="186" t="str">
         <f>=ROUND($AM$18,2)</f>
@@ -20609,7 +20617,7 @@
         <f>=ROUND($AN$18,2)</f>
       </c>
       <c r="AP20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ20" s="186" t="str">
         <f>=ROUND($AQ$18,2)</f>
@@ -20618,7 +20626,7 @@
         <f>=ROUND($AR$18,2)</f>
       </c>
       <c r="AT20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AU20" s="186" t="str">
         <f>=ROUND($AU$18,2)</f>
@@ -20627,7 +20635,7 @@
         <f>=ROUND($AV$18,2)</f>
       </c>
       <c r="AX20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AY20" s="186" t="str">
         <f>=ROUND($AY$18,2)</f>
@@ -20636,7 +20644,7 @@
         <f>=ROUND($AZ$18,2)</f>
       </c>
       <c r="BB20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="BC20" s="186" t="str">
         <f>=ROUND($BC$18,2)</f>
@@ -20645,7 +20653,7 @@
         <f>=ROUND($BD$18,2)</f>
       </c>
       <c r="BF20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="BG20" s="186" t="str">
         <f>=ROUND($BG$18,2)</f>
@@ -20654,7 +20662,7 @@
         <f>=ROUND($BH$18,2)</f>
       </c>
       <c r="BJ20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="BK20" s="186" t="str">
         <f>=ROUND($BK$18,2)</f>
@@ -20663,7 +20671,7 @@
         <f>=ROUND($BL$18,2)</f>
       </c>
       <c r="BN20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="BO20" s="186" t="str">
         <f>=ROUND($BO$18,2)</f>
@@ -20672,7 +20680,7 @@
         <f>=ROUND($BP$18,2)</f>
       </c>
       <c r="BR20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="BS20" s="186" t="str">
         <f>=ROUND($BS$18,2)</f>
@@ -20683,7 +20691,7 @@
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C21" s="24">
         <v>250000</v>
@@ -20692,7 +20700,7 @@
         <f>=IFERROR(ROUND($C$21/$C$8,2),0)</f>
       </c>
       <c r="F21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G21" s="24">
         <v>200000</v>
@@ -20701,112 +20709,112 @@
         <f>=IFERROR(ROUND($G$21/$G$8,2),0)</f>
       </c>
       <c r="J21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K21" s="24"/>
       <c r="L21" s="182" t="str">
         <f>=IFERROR(ROUND($K$21/$K$8,2),0)</f>
       </c>
       <c r="N21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O21" s="24"/>
       <c r="P21" s="182" t="str">
         <f>=IFERROR(ROUND($O$21/$O$8,2),0)</f>
       </c>
       <c r="R21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="S21" s="24"/>
       <c r="T21" s="182" t="str">
         <f>=IFERROR(ROUND($S$21/$S$8,2),0)</f>
       </c>
       <c r="V21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="W21" s="24"/>
       <c r="X21" s="182" t="str">
         <f>=IFERROR(ROUND($W$21/$W$8,2),0)</f>
       </c>
       <c r="Z21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA21" s="24"/>
       <c r="AB21" s="182" t="str">
         <f>=IFERROR(ROUND($AA$21/$AA$8,2),0)</f>
       </c>
       <c r="AD21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AE21" s="24"/>
       <c r="AF21" s="182" t="str">
         <f>=IFERROR(ROUND($AE$21/$AE$8,2),0)</f>
       </c>
       <c r="AH21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AI21" s="24"/>
       <c r="AJ21" s="182" t="str">
         <f>=IFERROR(ROUND($AI$21/$AI$8,2),0)</f>
       </c>
       <c r="AL21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM21" s="24"/>
       <c r="AN21" s="182" t="str">
         <f>=IFERROR(ROUND($AM$21/$AM$8,2),0)</f>
       </c>
       <c r="AP21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AQ21" s="24"/>
       <c r="AR21" s="182" t="str">
         <f>=IFERROR(ROUND($AQ$21/$AQ$8,2),0)</f>
       </c>
       <c r="AT21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AU21" s="24"/>
       <c r="AV21" s="182" t="str">
         <f>=IFERROR(ROUND($AU$21/$AU$8,2),0)</f>
       </c>
       <c r="AX21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AY21" s="24"/>
       <c r="AZ21" s="182" t="str">
         <f>=IFERROR(ROUND($AY$21/$AY$8,2),0)</f>
       </c>
       <c r="BB21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="BC21" s="24"/>
       <c r="BD21" s="182" t="str">
         <f>=IFERROR(ROUND($BC$21/$BC$8,2),0)</f>
       </c>
       <c r="BF21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="BG21" s="24"/>
       <c r="BH21" s="182" t="str">
         <f>=IFERROR(ROUND($BG$21/$BG$8,2),0)</f>
       </c>
       <c r="BJ21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="BK21" s="24"/>
       <c r="BL21" s="182" t="str">
         <f>=IFERROR(ROUND($BK$21/$BK$8,2),0)</f>
       </c>
       <c r="BN21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="BO21" s="24"/>
       <c r="BP21" s="182" t="str">
         <f>=IFERROR(ROUND($BO$21/$BO$8,2),0)</f>
       </c>
       <c r="BR21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="BS21" s="24"/>
       <c r="BT21" s="182" t="str">
@@ -20815,7 +20823,7 @@
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C22" s="24">
         <v>125000</v>
@@ -20824,7 +20832,7 @@
         <f>=IFERROR(ROUND($C$22/$C$8,2),0)</f>
       </c>
       <c r="F22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G22" s="24">
         <v>100000</v>
@@ -20833,112 +20841,112 @@
         <f>=IFERROR(ROUND($G$22/$G$8,2),0)</f>
       </c>
       <c r="J22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K22" s="24"/>
       <c r="L22" s="182" t="str">
         <f>=IFERROR(ROUND($K$22/$K$8,2),0)</f>
       </c>
       <c r="N22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O22" s="24"/>
       <c r="P22" s="182" t="str">
         <f>=IFERROR(ROUND($O$22/$O$8,2),0)</f>
       </c>
       <c r="R22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S22" s="24"/>
       <c r="T22" s="182" t="str">
         <f>=IFERROR(ROUND($S$22/$S$8,2),0)</f>
       </c>
       <c r="V22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="W22" s="24"/>
       <c r="X22" s="182" t="str">
         <f>=IFERROR(ROUND($W$22/$W$8,2),0)</f>
       </c>
       <c r="Z22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA22" s="24"/>
       <c r="AB22" s="182" t="str">
         <f>=IFERROR(ROUND($AA$22/$AA$8,2),0)</f>
       </c>
       <c r="AD22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AE22" s="24"/>
       <c r="AF22" s="182" t="str">
         <f>=IFERROR(ROUND($AE$22/$AE$8,2),0)</f>
       </c>
       <c r="AH22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AI22" s="24"/>
       <c r="AJ22" s="182" t="str">
         <f>=IFERROR(ROUND($AI$22/$AI$8,2),0)</f>
       </c>
       <c r="AL22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM22" s="24"/>
       <c r="AN22" s="182" t="str">
         <f>=IFERROR(ROUND($AM$22/$AM$8,2),0)</f>
       </c>
       <c r="AP22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AQ22" s="24"/>
       <c r="AR22" s="182" t="str">
         <f>=IFERROR(ROUND($AQ$22/$AQ$8,2),0)</f>
       </c>
       <c r="AT22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AU22" s="24"/>
       <c r="AV22" s="182" t="str">
         <f>=IFERROR(ROUND($AU$22/$AU$8,2),0)</f>
       </c>
       <c r="AX22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AY22" s="24"/>
       <c r="AZ22" s="182" t="str">
         <f>=IFERROR(ROUND($AY$22/$AY$8,2),0)</f>
       </c>
       <c r="BB22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="BC22" s="24"/>
       <c r="BD22" s="182" t="str">
         <f>=IFERROR(ROUND($BC$22/$BC$8,2),0)</f>
       </c>
       <c r="BF22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="BG22" s="24"/>
       <c r="BH22" s="182" t="str">
         <f>=IFERROR(ROUND($BG$22/$BG$8,2),0)</f>
       </c>
       <c r="BJ22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="BK22" s="24"/>
       <c r="BL22" s="182" t="str">
         <f>=IFERROR(ROUND($BK$22/$BK$8,2),0)</f>
       </c>
       <c r="BN22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="BO22" s="24"/>
       <c r="BP22" s="182" t="str">
         <f>=IFERROR(ROUND($BO$22/$BO$8,2),0)</f>
       </c>
       <c r="BR22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="BS22" s="24"/>
       <c r="BT22" s="182" t="str">
@@ -20947,7 +20955,7 @@
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C23" s="188" t="str">
         <f>=ROUND(IF(Saldovortrag_LW="",0,Saldovortrag_LW),2)</f>
@@ -20956,7 +20964,7 @@
         <f>=IFERROR(ROUND($C$23/$C$8,2),0)</f>
       </c>
       <c r="F23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_1,0),2)</f>
@@ -20965,7 +20973,7 @@
         <f>=IFERROR(ROUND($G$23/$G$8,2),0)</f>
       </c>
       <c r="J23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_2,0),2)</f>
@@ -20974,7 +20982,7 @@
         <f>=IFERROR(ROUND($K$23/$K$8,2),0)</f>
       </c>
       <c r="N23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_3,0),2)</f>
@@ -20983,7 +20991,7 @@
         <f>=IFERROR(ROUND($O$23/$O$8,2),0)</f>
       </c>
       <c r="R23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_4,0),2)</f>
@@ -20992,7 +21000,7 @@
         <f>=IFERROR(ROUND($S$23/$S$8,2),0)</f>
       </c>
       <c r="V23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="W23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_5,0),2)</f>
@@ -21001,7 +21009,7 @@
         <f>=IFERROR(ROUND($W$23/$W$8,2),0)</f>
       </c>
       <c r="Z23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_6,0),2)</f>
@@ -21010,7 +21018,7 @@
         <f>=IFERROR(ROUND($AA$23/$AA$8,2),0)</f>
       </c>
       <c r="AD23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AE23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_7,0),2)</f>
@@ -21019,7 +21027,7 @@
         <f>=IFERROR(ROUND($AE$23/$AE$8,2),0)</f>
       </c>
       <c r="AH23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AI23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_8,0),2)</f>
@@ -21028,7 +21036,7 @@
         <f>=IFERROR(ROUND($AI$23/$AI$8,2),0)</f>
       </c>
       <c r="AL23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_9,0),2)</f>
@@ -21037,7 +21045,7 @@
         <f>=IFERROR(ROUND($AM$23/$AM$8,2),0)</f>
       </c>
       <c r="AP23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AQ23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_10,0),2)</f>
@@ -21046,7 +21054,7 @@
         <f>=IFERROR(ROUND($AQ$23/$AQ$8,2),0)</f>
       </c>
       <c r="AT23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AU23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_11,0),2)</f>
@@ -21055,7 +21063,7 @@
         <f>=IFERROR(ROUND($AU$23/$AU$8,2),0)</f>
       </c>
       <c r="AX23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AY23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_12,0),2)</f>
@@ -21064,7 +21072,7 @@
         <f>=IFERROR(ROUND($AY$23/$AY$8,2),0)</f>
       </c>
       <c r="BB23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="BC23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_13,0),2)</f>
@@ -21073,7 +21081,7 @@
         <f>=IFERROR(ROUND($BC$23/$BC$8,2),0)</f>
       </c>
       <c r="BF23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="BG23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_14,0),2)</f>
@@ -21082,7 +21090,7 @@
         <f>=IFERROR(ROUND($BG$23/$BG$8,2),0)</f>
       </c>
       <c r="BJ23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="BK23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_15,0),2)</f>
@@ -21091,7 +21099,7 @@
         <f>=IFERROR(ROUND($BK$23/$BK$8,2),0)</f>
       </c>
       <c r="BN23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="BO23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_16,0),2)</f>
@@ -21100,7 +21108,7 @@
         <f>=IFERROR(ROUND($BO$23/$BO$8,2),0)</f>
       </c>
       <c r="BR23" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="BS23" s="188" t="str">
         <f>=ROUND(IFERROR(FB_SaldoLC_17,0),2)</f>
@@ -21111,7 +21119,7 @@
     </row>
     <row r="25">
       <c r="B25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C25" s="190" t="str">
         <f>=IFERROR(ROUND($C$18-$C$21-$C$22-$C$23,2),0)</f>
@@ -21120,7 +21128,7 @@
         <f>=IFERROR(ROUND($D$18-$D$21-$D$22-$D$23,2),0)</f>
       </c>
       <c r="F25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G25" s="190" t="str">
         <f>=IFERROR(ROUND($G$18-$G$21-$G$22-$G$23,2),0)</f>
@@ -21129,7 +21137,7 @@
         <f>=IFERROR(ROUND($H$18-$H$21-$H$22-$H$23,2),0)</f>
       </c>
       <c r="J25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K25" s="190" t="str">
         <f>=IFERROR(ROUND($K$18-$K$21-$K$22-$K$23,2),0)</f>
@@ -21138,7 +21146,7 @@
         <f>=IFERROR(ROUND($L$18-$L$21-$L$22-$L$23,2),0)</f>
       </c>
       <c r="N25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O25" s="190" t="str">
         <f>=IFERROR(ROUND($O$18-$O$21-$O$22-$O$23,2),0)</f>
@@ -21147,7 +21155,7 @@
         <f>=IFERROR(ROUND($P$18-$P$21-$P$22-$P$23,2),0)</f>
       </c>
       <c r="R25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S25" s="190" t="str">
         <f>=IFERROR(ROUND($S$18-$S$21-$S$22-$S$23,2),0)</f>
@@ -21156,7 +21164,7 @@
         <f>=IFERROR(ROUND($T$18-$T$21-$T$22-$T$23,2),0)</f>
       </c>
       <c r="V25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="W25" s="190" t="str">
         <f>=IFERROR(ROUND($W$18-$W$21-$W$22-$W$23,2),0)</f>
@@ -21165,7 +21173,7 @@
         <f>=IFERROR(ROUND($X$18-$X$21-$X$22-$X$23,2),0)</f>
       </c>
       <c r="Z25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA25" s="190" t="str">
         <f>=IFERROR(ROUND($AA$18-$AA$21-$AA$22-$AA$23,2),0)</f>
@@ -21174,7 +21182,7 @@
         <f>=IFERROR(ROUND($AB$18-$AB$21-$AB$22-$AB$23,2),0)</f>
       </c>
       <c r="AD25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AE25" s="190" t="str">
         <f>=IFERROR(ROUND($AE$18-$AE$21-$AE$22-$AE$23,2),0)</f>
@@ -21183,7 +21191,7 @@
         <f>=IFERROR(ROUND($AF$18-$AF$21-$AF$22-$AF$23,2),0)</f>
       </c>
       <c r="AH25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AI25" s="190" t="str">
         <f>=IFERROR(ROUND($AI$18-$AI$21-$AI$22-$AI$23,2),0)</f>
@@ -21192,7 +21200,7 @@
         <f>=IFERROR(ROUND($AJ$18-$AJ$21-$AJ$22-$AJ$23,2),0)</f>
       </c>
       <c r="AL25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM25" s="190" t="str">
         <f>=IFERROR(ROUND($AM$18-$AM$21-$AM$22-$AM$23,2),0)</f>
@@ -21201,7 +21209,7 @@
         <f>=IFERROR(ROUND($AN$18-$AN$21-$AN$22-$AN$23,2),0)</f>
       </c>
       <c r="AP25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AQ25" s="190" t="str">
         <f>=IFERROR(ROUND($AQ$18-$AQ$21-$AQ$22-$AQ$23,2),0)</f>
@@ -21210,7 +21218,7 @@
         <f>=IFERROR(ROUND($AR$18-$AR$21-$AR$22-$AR$23,2),0)</f>
       </c>
       <c r="AT25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AU25" s="190" t="str">
         <f>=IFERROR(ROUND($AU$18-$AU$21-$AU$22-$AU$23,2),0)</f>
@@ -21219,7 +21227,7 @@
         <f>=IFERROR(ROUND($AV$18-$AV$21-$AV$22-$AV$23,2),0)</f>
       </c>
       <c r="AX25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AY25" s="190" t="str">
         <f>=IFERROR(ROUND($AY$18-$AY$21-$AY$22-$AY$23,2),0)</f>
@@ -21228,7 +21236,7 @@
         <f>=IFERROR(ROUND($AZ$18-$AZ$21-$AZ$22-$AZ$23,2),0)</f>
       </c>
       <c r="BB25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BC25" s="190" t="str">
         <f>=IFERROR(ROUND($BC$18-$BC$21-$BC$22-$BC$23,2),0)</f>
@@ -21237,7 +21245,7 @@
         <f>=IFERROR(ROUND($BD$18-$BD$21-$BD$22-$BD$23,2),0)</f>
       </c>
       <c r="BF25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BG25" s="190" t="str">
         <f>=IFERROR(ROUND($BG$18-$BG$21-$BG$22-$BG$23,2),0)</f>
@@ -21246,7 +21254,7 @@
         <f>=IFERROR(ROUND($BH$18-$BH$21-$BH$22-$BH$23,2),0)</f>
       </c>
       <c r="BJ25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BK25" s="190" t="str">
         <f>=IFERROR(ROUND($BK$18-$BK$21-$BK$22-$BK$23,2),0)</f>
@@ -21255,7 +21263,7 @@
         <f>=IFERROR(ROUND($BL$18-$BL$21-$BL$22-$BL$23,2),0)</f>
       </c>
       <c r="BN25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BO25" s="190" t="str">
         <f>=IFERROR(ROUND($BO$18-$BO$21-$BO$22-$BO$23,2),0)</f>
@@ -21264,7 +21272,7 @@
         <f>=IFERROR(ROUND($BP$18-$BP$21-$BP$22-$BP$23,2),0)</f>
       </c>
       <c r="BR25" s="189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BS25" s="190" t="str">
         <f>=IFERROR(ROUND($BS$18-$BS$21-$BS$22-$BS$23,2),0)</f>
@@ -21275,92 +21283,92 @@
     </row>
     <row r="27">
       <c r="B27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C27" s="181"/>
       <c r="D27" s="25"/>
       <c r="F27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G27" s="181"/>
       <c r="H27" s="25"/>
       <c r="J27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K27" s="181"/>
       <c r="L27" s="25"/>
       <c r="N27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O27" s="181"/>
       <c r="P27" s="25"/>
       <c r="R27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S27" s="181"/>
       <c r="T27" s="25"/>
       <c r="V27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="W27" s="181"/>
       <c r="X27" s="25"/>
       <c r="Z27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA27" s="181"/>
       <c r="AB27" s="25"/>
       <c r="AD27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AE27" s="181"/>
       <c r="AF27" s="25"/>
       <c r="AH27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AI27" s="181"/>
       <c r="AJ27" s="25"/>
       <c r="AL27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM27" s="181"/>
       <c r="AN27" s="25"/>
       <c r="AP27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ27" s="181"/>
       <c r="AR27" s="25"/>
       <c r="AT27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AU27" s="181"/>
       <c r="AV27" s="25"/>
       <c r="AX27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AY27" s="181"/>
       <c r="AZ27" s="25"/>
       <c r="BB27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BC27" s="181"/>
       <c r="BD27" s="25"/>
       <c r="BF27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BG27" s="181"/>
       <c r="BH27" s="25"/>
       <c r="BJ27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BK27" s="181"/>
       <c r="BL27" s="25"/>
       <c r="BN27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BO27" s="181"/>
       <c r="BP27" s="25"/>
       <c r="BR27" s="181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BS27" s="181"/>
       <c r="BT27" s="25"/>
@@ -21574,7 +21582,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="true">
       <c r="B2" s="192" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C2" s="192"/>
       <c r="D2" s="192"/>
@@ -21587,7 +21595,7 @@
     </row>
     <row r="3" ht="18" customHeight="true">
       <c r="B3" s="193" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C3" s="193"/>
       <c r="D3" s="193"/>
@@ -21600,7 +21608,7 @@
     </row>
     <row r="5" ht="22" customHeight="true">
       <c r="B5" s="194" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C5" s="194"/>
       <c r="D5" s="194"/>
@@ -21621,7 +21629,7 @@
     </row>
     <row r="6">
       <c r="B6" s="195" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C6" s="195"/>
       <c r="D6" s="195"/>
@@ -21632,7 +21640,7 @@
       <c r="I6" s="195"/>
       <c r="J6" s="195"/>
       <c r="L6" s="315" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M6" s="307" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$4,'IV. MA'!$G$4,'IV. MA'!$K$4,'IV. MA'!$O$4,'IV. MA'!$S$4,'IV. MA'!$W$4,'IV. MA'!$AA$4,'IV. MA'!$AE$4,'IV. MA'!$AI$4,'IV. MA'!$AM$4,'IV. MA'!$AQ$4,'IV. MA'!$AU$4,'IV. MA'!$AY$4,'IV. MA'!$BC$4,'IV. MA'!$BG$4,'IV. MA'!$BK$4,'IV. MA'!$BO$4,'IV. MA'!$BS$4),"")</f>
@@ -21641,7 +21649,7 @@
     </row>
     <row r="7">
       <c r="L7" s="315" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M7" s="308" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$5,'IV. MA'!$G$5,'IV. MA'!$K$5,'IV. MA'!$O$5,'IV. MA'!$S$5,'IV. MA'!$W$5,'IV. MA'!$AA$5,'IV. MA'!$AE$5,'IV. MA'!$AI$5,'IV. MA'!$AM$5,'IV. MA'!$AQ$5,'IV. MA'!$AU$5,'IV. MA'!$AY$5,'IV. MA'!$BC$5,'IV. MA'!$BG$5,'IV. MA'!$BK$5,'IV. MA'!$BO$5,'IV. MA'!$BS$5),"")</f>
@@ -21650,14 +21658,14 @@
     </row>
     <row r="8" ht="22" customHeight="true">
       <c r="C8" s="202" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D8" s="203"/>
       <c r="E8" s="203"/>
       <c r="F8" s="203"/>
       <c r="G8" s="204"/>
       <c r="L8" s="315" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M8" s="308" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$6,'IV. MA'!$G$6,'IV. MA'!$K$6,'IV. MA'!$O$6,'IV. MA'!$S$6,'IV. MA'!$W$6,'IV. MA'!$AA$6,'IV. MA'!$AE$6,'IV. MA'!$AI$6,'IV. MA'!$AM$6,'IV. MA'!$AQ$6,'IV. MA'!$AU$6,'IV. MA'!$AY$6,'IV. MA'!$BC$6,'IV. MA'!$BG$6,'IV. MA'!$BK$6,'IV. MA'!$BO$6,'IV. MA'!$BS$6),"")</f>
@@ -21666,16 +21674,16 @@
     </row>
     <row r="9">
       <c r="C9" s="205" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D9" s="197"/>
       <c r="E9" s="63" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F9" s="63"/>
       <c r="G9" s="206"/>
       <c r="L9" s="315" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M9" s="309" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$7,'IV. MA'!$G$7,'IV. MA'!$K$7,'IV. MA'!$O$7,'IV. MA'!$S$7,'IV. MA'!$W$7,'IV. MA'!$AA$7,'IV. MA'!$AE$7,'IV. MA'!$AI$7,'IV. MA'!$AM$7,'IV. MA'!$AQ$7,'IV. MA'!$AU$7,'IV. MA'!$AY$7,'IV. MA'!$BC$7,'IV. MA'!$BG$7,'IV. MA'!$BK$7,'IV. MA'!$BO$7,'IV. MA'!$BS$7),"")</f>
@@ -21684,7 +21692,7 @@
     </row>
     <row r="10">
       <c r="C10" s="205" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D10" s="197"/>
       <c r="E10" s="198" t="str">
@@ -21694,7 +21702,7 @@
       <c r="F10" s="198"/>
       <c r="G10" s="207"/>
       <c r="L10" s="315" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M10" s="310" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$8,'IV. MA'!$G$8,'IV. MA'!$K$8,'IV. MA'!$O$8,'IV. MA'!$S$8,'IV. MA'!$W$8,'IV. MA'!$AA$8,'IV. MA'!$AE$8,'IV. MA'!$AI$8,'IV. MA'!$AM$8,'IV. MA'!$AQ$8,'IV. MA'!$AU$8,'IV. MA'!$AY$8,'IV. MA'!$BC$8,'IV. MA'!$BG$8,'IV. MA'!$BK$8,'IV. MA'!$BO$8,'IV. MA'!$BS$8),"")</f>
@@ -21703,7 +21711,7 @@
     </row>
     <row r="11">
       <c r="C11" s="205" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D11" s="197"/>
       <c r="E11" s="198" t="str">
@@ -21716,7 +21724,7 @@
     </row>
     <row r="12">
       <c r="C12" s="209" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D12" s="199"/>
       <c r="E12" s="199"/>
@@ -21726,10 +21734,10 @@
         <v>204</v>
       </c>
       <c r="M12" s="180" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N12" s="321" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13">
@@ -21877,7 +21885,7 @@
     </row>
     <row r="20" ht="22" customHeight="true">
       <c r="B20" s="18" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -21899,7 +21907,7 @@
     </row>
     <row r="21">
       <c r="L21" s="322" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M21" s="243" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$18,'IV. MA'!$G$18,'IV. MA'!$K$18,'IV. MA'!$O$18,'IV. MA'!$S$18,'IV. MA'!$W$18,'IV. MA'!$AA$18,'IV. MA'!$AE$18,'IV. MA'!$AI$18,'IV. MA'!$AM$18,'IV. MA'!$AQ$18,'IV. MA'!$AU$18,'IV. MA'!$AY$18,'IV. MA'!$BC$18,'IV. MA'!$BG$18,'IV. MA'!$BK$18,'IV. MA'!$BO$18,'IV. MA'!$BS$18),"")</f>
@@ -21910,14 +21918,14 @@
     </row>
     <row r="22">
       <c r="B22" s="223" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C22" s="224"/>
       <c r="D22" s="225" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
       <c r="F22" s="230" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G22" s="231"/>
       <c r="H22" s="231"/>
@@ -21927,24 +21935,24 @@
     </row>
     <row r="23">
       <c r="B23" s="205" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C23" s="197"/>
       <c r="D23" s="226" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
       <c r="F23" s="233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G23" s="197" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H23" s="197"/>
       <c r="I23" s="234" t="str">
         <f>=IFERROR(ROUND(Saldovortrag_EUR,2),0)</f>
       </c>
       <c r="L23" s="143" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M23" s="116" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$20,'IV. MA'!$G$20,'IV. MA'!$K$20,'IV. MA'!$O$20,'IV. MA'!$S$20,'IV. MA'!$W$20,'IV. MA'!$AA$20,'IV. MA'!$AE$20,'IV. MA'!$AI$20,'IV. MA'!$AM$20,'IV. MA'!$AQ$20,'IV. MA'!$AU$20,'IV. MA'!$AY$20,'IV. MA'!$BC$20,'IV. MA'!$BG$20,'IV. MA'!$BK$20,'IV. MA'!$BO$20,'IV. MA'!$BS$20),"")</f>
@@ -21962,10 +21970,10 @@
         <f>=IF(Reserve_Freigabe="Ja",ROUND($D$22,2),ROUND($D$22-$D$23,2))</f>
       </c>
       <c r="F24" s="233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G24" s="197" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H24" s="197"/>
       <c r="I24" s="234" t="str">
@@ -21973,7 +21981,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="143" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M24" s="116" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$21,'IV. MA'!$G$21,'IV. MA'!$K$21,'IV. MA'!$O$21,'IV. MA'!$S$21,'IV. MA'!$W$21,'IV. MA'!$AA$21,'IV. MA'!$AE$21,'IV. MA'!$AI$21,'IV. MA'!$AM$21,'IV. MA'!$AQ$21,'IV. MA'!$AU$21,'IV. MA'!$AY$21,'IV. MA'!$BC$21,'IV. MA'!$BG$21,'IV. MA'!$BK$21,'IV. MA'!$BO$21,'IV. MA'!$BS$21),"")</f>
@@ -21984,17 +21992,17 @@
     </row>
     <row r="25">
       <c r="B25" s="205" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C25" s="197"/>
       <c r="D25" s="226" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblKMWMittel[Betrag]),2),0)</f>
       </c>
       <c r="F25" s="233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G25" s="197" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H25" s="197"/>
       <c r="I25" s="234" t="str">
@@ -22002,7 +22010,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="143" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M25" s="116" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$22,'IV. MA'!$G$22,'IV. MA'!$K$22,'IV. MA'!$O$22,'IV. MA'!$S$22,'IV. MA'!$W$22,'IV. MA'!$AA$22,'IV. MA'!$AE$22,'IV. MA'!$AI$22,'IV. MA'!$AM$22,'IV. MA'!$AQ$22,'IV. MA'!$AU$22,'IV. MA'!$AY$22,'IV. MA'!$BC$22,'IV. MA'!$BG$22,'IV. MA'!$BK$22,'IV. MA'!$BO$22,'IV. MA'!$BS$22),"")</f>
@@ -22013,7 +22021,7 @@
     </row>
     <row r="26">
       <c r="B26" s="227" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C26" s="228"/>
       <c r="D26" s="229" t="str">
@@ -22021,7 +22029,7 @@
       </c>
       <c r="F26" s="47"/>
       <c r="G26" s="218" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H26" s="218"/>
       <c r="I26" s="235" t="str">
@@ -22040,7 +22048,7 @@
     <row r="27">
       <c r="F27" s="236"/>
       <c r="G27" s="228" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H27" s="228"/>
       <c r="I27" s="229" t="str">
@@ -22051,7 +22059,7 @@
     </row>
     <row r="28">
       <c r="L28" s="323" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M28" s="324" t="str">
         <f>=IFERROR(CHOOSE($AD$5,'IV. MA'!$C$25,'IV. MA'!$G$25,'IV. MA'!$K$25,'IV. MA'!$O$25,'IV. MA'!$S$25,'IV. MA'!$W$25,'IV. MA'!$AA$25,'IV. MA'!$AE$25,'IV. MA'!$AI$25,'IV. MA'!$AM$25,'IV. MA'!$AQ$25,'IV. MA'!$AU$25,'IV. MA'!$AY$25,'IV. MA'!$BC$25,'IV. MA'!$BG$25,'IV. MA'!$BK$25,'IV. MA'!$BO$25,'IV. MA'!$BS$25),"")</f>
@@ -22062,14 +22070,14 @@
     </row>
     <row r="29">
       <c r="B29" s="223" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C29" s="224"/>
       <c r="D29" s="225" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BV$1:$BV$198,'Daten'!$BT$1:$BT$198,"KMW-Mittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,E11),2),0)</f>
       </c>
       <c r="F29" s="223" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G29" s="224"/>
       <c r="H29" s="224"/>
@@ -22079,14 +22087,14 @@
     </row>
     <row r="30">
       <c r="B30" s="227" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C30" s="228"/>
       <c r="D30" s="229" t="str">
         <f>=ROUND($D$26-MAX(0,$D$29),2)</f>
       </c>
       <c r="F30" s="227" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G30" s="228"/>
       <c r="H30" s="228"/>
@@ -22096,14 +22104,14 @@
     </row>
     <row r="32">
       <c r="B32" s="223" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C32" s="224"/>
       <c r="D32" s="237" t="str">
         <f>=IFERROR(CHOOSE(E10,MA_ManBetrag_1,MA_ManBetrag_2,MA_ManBetrag_3,MA_ManBetrag_4,MA_ManBetrag_5,MA_ManBetrag_6,MA_ManBetrag_7,MA_ManBetrag_8,MA_ManBetrag_9,MA_ManBetrag_10,MA_ManBetrag_11,MA_ManBetrag_12,MA_ManBetrag_13,MA_ManBetrag_14,MA_ManBetrag_15,MA_ManBetrag_16,MA_ManBetrag_17,MA_ManBetrag_18),0)</f>
       </c>
       <c r="F32" s="223" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G32" s="224"/>
       <c r="H32" s="224"/>
@@ -22113,14 +22121,14 @@
     </row>
     <row r="33">
       <c r="B33" s="227" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C33" s="228"/>
       <c r="D33" s="229" t="str">
         <f>=ROUND(MAX(0,$D$26-MAX(0,$D$32)),2)</f>
       </c>
       <c r="F33" s="227" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G33" s="228"/>
       <c r="H33" s="228"/>
@@ -22130,7 +22138,7 @@
     </row>
     <row r="36" ht="22" customHeight="true">
       <c r="B36" s="18" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
@@ -22146,18 +22154,18 @@
         <v>158</v>
       </c>
       <c r="C38" s="247" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D38" s="247" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E38" s="248" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="205" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C39" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BF$1:$BF$18,'Daten'!$BB$1:$BB$18,E10,'Daten'!$BD$1:$BD$18,"&lt;="&amp;E11,'Daten'!$BD$1:$BD$18,"&gt;=1"),2),0)</f>
@@ -22169,7 +22177,7 @@
     </row>
     <row r="40">
       <c r="B40" s="205" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C40" s="239" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 1]),2),0)</f>
@@ -22183,7 +22191,7 @@
     </row>
     <row r="41">
       <c r="B41" s="205" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C41" s="239" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 2]),2),0)</f>
@@ -22197,7 +22205,7 @@
     </row>
     <row r="42">
       <c r="B42" s="205" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C42" s="239" t="str">
         <f>=IFERROR(ROUND(SUBTOTAL(109,TblBudgetAusgaben[Jahr 3]),2),0)</f>
@@ -22211,7 +22219,7 @@
     </row>
     <row r="43">
       <c r="B43" s="205" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C43" s="242" t="str">
         <f>=$D$40+$D$41+$D$42</f>
@@ -22221,7 +22229,7 @@
     </row>
     <row r="44">
       <c r="B44" s="205" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C44" s="242" t="str">
         <f>=IFERROR(CHOOSE(IFERROR(SUMPRODUCT('Daten'!$BA$1:$BA$18,('Daten'!$BB$1:$BB$18=E10)*('Daten'!$BD$1:$BD$18=E11)),0),'IV. MA'!$C$7,'IV. MA'!$G$7,'IV. MA'!$K$7,'IV. MA'!$O$7,'IV. MA'!$S$7,'IV. MA'!$W$7,'IV. MA'!$AA$7,'IV. MA'!$AE$7,'IV. MA'!$AI$7,'IV. MA'!$AM$7,'IV. MA'!$AQ$7,'IV. MA'!$AU$7,'IV. MA'!$AY$7,'IV. MA'!$BC$7,'IV. MA'!$BG$7,'IV. MA'!$BK$7,'IV. MA'!$BO$7,'IV. MA'!$BS$7),0)</f>
@@ -22231,7 +22239,7 @@
     </row>
     <row r="45">
       <c r="B45" s="251" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C45" s="243" t="str">
         <f>=IFERROR(ROUND($C$40*$D$40/12+$C$41*$D$41/12+$C$42*$D$42/12,2),0)</f>
@@ -22243,7 +22251,7 @@
     </row>
     <row r="46">
       <c r="B46" s="251" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C46" s="244" t="str">
         <f>=IF($C$39&lt;=$C$45,"OK","ÜBERSCHRITTEN")</f>
@@ -22255,7 +22263,7 @@
     </row>
     <row r="47">
       <c r="B47" s="205" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C47" s="239" t="str">
         <f>=ROUND(MAX(0,$C$39-$C$45),2)</f>
@@ -22267,7 +22275,7 @@
     </row>
     <row r="48">
       <c r="B48" s="253" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C48" s="254" t="str">
         <f>=IFERROR($C$39/$C$45,0)</f>
@@ -22279,7 +22287,7 @@
     </row>
     <row r="50" ht="22" customHeight="true">
       <c r="B50" s="18" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
@@ -22292,31 +22300,31 @@
     </row>
     <row r="52" ht="28" customHeight="true">
       <c r="B52" s="263" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C52" s="264" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D52" s="264" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E52" s="264" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F52" s="264" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G52" s="264" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H52" s="264" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I52" s="264" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J52" s="265" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="53">
@@ -22350,7 +22358,7 @@
     </row>
     <row r="54">
       <c r="B54" s="266" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C54" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Drittmittel",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
@@ -22408,7 +22416,7 @@
     </row>
     <row r="56">
       <c r="B56" s="266" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C56" s="239" t="str">
         <f>=IFERROR(ROUND(SUMIFS('Daten'!$BU$1:$BU$198,'Daten'!$BT$1:$BT$198,"Zinsertraege",'Daten'!$BR$1:$BR$198,E10,'Daten'!$BS$1:$BS$198,"&lt;="&amp;E11,'Daten'!$BS$1:$BS$198,"&gt;=1"),2),0)</f>
@@ -22437,7 +22445,7 @@
     </row>
     <row r="57" ht="20" customHeight="true">
       <c r="B57" s="271" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C57" s="272" t="str">
         <f>=ROUND(SUM($C$53:$C$56),2)</f>
@@ -22466,7 +22474,7 @@
     </row>
     <row r="59" ht="22" customHeight="true">
       <c r="B59" s="18" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
@@ -22479,31 +22487,31 @@
     </row>
     <row r="61" ht="28" customHeight="true">
       <c r="B61" s="263" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C61" s="264" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D61" s="264" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E61" s="264" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F61" s="264" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G61" s="264" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H61" s="264" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I61" s="264" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J61" s="265" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="62">
@@ -22740,7 +22748,7 @@
     </row>
     <row r="70" ht="20" customHeight="true">
       <c r="B70" s="271" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C70" s="272" t="str">
         <f>=ROUND(SUM($C$62:$C$69),2)</f>
@@ -22769,7 +22777,7 @@
     </row>
     <row r="76" ht="22" customHeight="true">
       <c r="B76" s="194" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C76" s="194"/>
       <c r="D76" s="194"/>
@@ -22789,7 +22797,7 @@
     </row>
     <row r="77">
       <c r="B77" s="195" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C77" s="195"/>
       <c r="D77" s="195"/>
@@ -22800,7 +22808,7 @@
       <c r="I77" s="195"/>
       <c r="J77" s="195"/>
       <c r="L77" s="315" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M77" s="326" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$4,'III. Finanzberichte'!$J$4,'III. Finanzberichte'!$Q$4,'III. Finanzberichte'!$X$4,'III. Finanzberichte'!$AE$4,'III. Finanzberichte'!$AL$4,'III. Finanzberichte'!$AS$4,'III. Finanzberichte'!$AZ$4,'III. Finanzberichte'!$BG$4,'III. Finanzberichte'!$BN$4,'III. Finanzberichte'!$BU$4,'III. Finanzberichte'!$CB$4,'III. Finanzberichte'!$CI$4,'III. Finanzberichte'!$CP$4,'III. Finanzberichte'!$CW$4,'III. Finanzberichte'!$DD$4,'III. Finanzberichte'!$DK$4,'III. Finanzberichte'!$DR$4),"")</f>
@@ -22811,7 +22819,7 @@
     </row>
     <row r="78">
       <c r="L78" s="315" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M78" s="327" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$5,'III. Finanzberichte'!$J$5,'III. Finanzberichte'!$Q$5,'III. Finanzberichte'!$X$5,'III. Finanzberichte'!$AE$5,'III. Finanzberichte'!$AL$5,'III. Finanzberichte'!$AS$5,'III. Finanzberichte'!$AZ$5,'III. Finanzberichte'!$BG$5,'III. Finanzberichte'!$BN$5,'III. Finanzberichte'!$BU$5,'III. Finanzberichte'!$CB$5,'III. Finanzberichte'!$CI$5,'III. Finanzberichte'!$CP$5,'III. Finanzberichte'!$CW$5,'III. Finanzberichte'!$DD$5,'III. Finanzberichte'!$DK$5,'III. Finanzberichte'!$DR$5),"")</f>
@@ -22822,14 +22830,14 @@
     </row>
     <row r="79" ht="22" customHeight="true">
       <c r="C79" s="202" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D79" s="203"/>
       <c r="E79" s="203"/>
       <c r="F79" s="203"/>
       <c r="G79" s="204"/>
       <c r="L79" s="315" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M79" s="327" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$6,'III. Finanzberichte'!$J$6,'III. Finanzberichte'!$Q$6,'III. Finanzberichte'!$X$6,'III. Finanzberichte'!$AE$6,'III. Finanzberichte'!$AL$6,'III. Finanzberichte'!$AS$6,'III. Finanzberichte'!$AZ$6,'III. Finanzberichte'!$BG$6,'III. Finanzberichte'!$BN$6,'III. Finanzberichte'!$BU$6,'III. Finanzberichte'!$CB$6,'III. Finanzberichte'!$CI$6,'III. Finanzberichte'!$CP$6,'III. Finanzberichte'!$CW$6,'III. Finanzberichte'!$DD$6,'III. Finanzberichte'!$DK$6,'III. Finanzberichte'!$DR$6),"")</f>
@@ -22840,16 +22848,16 @@
     </row>
     <row r="80">
       <c r="C80" s="205" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D80" s="197"/>
       <c r="E80" s="63" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F80" s="63"/>
       <c r="G80" s="206"/>
       <c r="L80" s="315" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M80" s="328" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$7,'III. Finanzberichte'!$J$7,'III. Finanzberichte'!$Q$7,'III. Finanzberichte'!$X$7,'III. Finanzberichte'!$AE$7,'III. Finanzberichte'!$AL$7,'III. Finanzberichte'!$AS$7,'III. Finanzberichte'!$AZ$7,'III. Finanzberichte'!$BG$7,'III. Finanzberichte'!$BN$7,'III. Finanzberichte'!$BU$7,'III. Finanzberichte'!$CB$7,'III. Finanzberichte'!$CI$7,'III. Finanzberichte'!$CP$7,'III. Finanzberichte'!$CW$7,'III. Finanzberichte'!$DD$7,'III. Finanzberichte'!$DK$7,'III. Finanzberichte'!$DR$7),"")</f>
@@ -22860,7 +22868,7 @@
     </row>
     <row r="81">
       <c r="C81" s="253" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D81" s="286"/>
       <c r="E81" s="287" t="str">
@@ -22869,7 +22877,7 @@
       <c r="F81" s="288"/>
       <c r="G81" s="289"/>
       <c r="L81" s="315" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M81" s="329" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$8,'III. Finanzberichte'!$J$8,'III. Finanzberichte'!$Q$8,'III. Finanzberichte'!$X$8,'III. Finanzberichte'!$AE$8,'III. Finanzberichte'!$AL$8,'III. Finanzberichte'!$AS$8,'III. Finanzberichte'!$AZ$8,'III. Finanzberichte'!$BG$8,'III. Finanzberichte'!$BN$8,'III. Finanzberichte'!$BU$8,'III. Finanzberichte'!$CB$8,'III. Finanzberichte'!$CI$8,'III. Finanzberichte'!$CP$8,'III. Finanzberichte'!$CW$8,'III. Finanzberichte'!$DD$8,'III. Finanzberichte'!$DK$8,'III. Finanzberichte'!$DR$8),"")</f>
@@ -22884,7 +22892,7 @@
     </row>
     <row r="83" ht="22" customHeight="true">
       <c r="B83" s="18" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C83" s="18"/>
       <c r="D83" s="18"/>
@@ -22895,7 +22903,7 @@
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
       <c r="L83" s="341" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M83" s="330"/>
       <c r="N83" s="330"/>
@@ -22904,31 +22912,31 @@
     </row>
     <row r="84" ht="26" customHeight="true">
       <c r="L84" s="343" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M84" s="331" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N84" s="331" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O84" s="331" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P84" s="344" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="223" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C85" s="224"/>
       <c r="D85" s="225" t="str">
         <f>=IFERROR(ROUND(KMW_Mittel_EUR,2),0)</f>
       </c>
       <c r="F85" s="230" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G85" s="231"/>
       <c r="H85" s="231"/>
@@ -22951,17 +22959,17 @@
     </row>
     <row r="86">
       <c r="B86" s="205" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C86" s="197"/>
       <c r="D86" s="226" t="str">
         <f>=IFERROR(ROUND(Kosten_Reserve_EUR,2),0)</f>
       </c>
       <c r="F86" s="233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G86" s="197" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H86" s="197"/>
       <c r="I86" s="234" t="str">
@@ -22992,10 +23000,10 @@
         <f>=IF(Reserve_Freigabe="Ja",ROUND($D$85,2),ROUND($D$85-$D$86,2))</f>
       </c>
       <c r="F87" s="233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G87" s="197" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H87" s="197"/>
       <c r="I87" s="234" t="str">
@@ -23003,7 +23011,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="143" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M87" s="116" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$13,'III. Finanzberichte'!$J$13,'III. Finanzberichte'!$Q$13,'III. Finanzberichte'!$X$13,'III. Finanzberichte'!$AE$13,'III. Finanzberichte'!$AL$13,'III. Finanzberichte'!$AS$13,'III. Finanzberichte'!$AZ$13,'III. Finanzberichte'!$BG$13,'III. Finanzberichte'!$BN$13,'III. Finanzberichte'!$BU$13,'III. Finanzberichte'!$CB$13,'III. Finanzberichte'!$CI$13,'III. Finanzberichte'!$CP$13,'III. Finanzberichte'!$CW$13,'III. Finanzberichte'!$DD$13,'III. Finanzberichte'!$DK$13,'III. Finanzberichte'!$DR$13),"")</f>
@@ -23020,7 +23028,7 @@
     </row>
     <row r="88">
       <c r="B88" s="205" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C88" s="197"/>
       <c r="D88" s="226" t="str">
@@ -23028,7 +23036,7 @@
       </c>
       <c r="F88" s="47"/>
       <c r="G88" s="218" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H88" s="218"/>
       <c r="I88" s="235" t="str">
@@ -23052,7 +23060,7 @@
     </row>
     <row r="89">
       <c r="B89" s="227" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C89" s="228"/>
       <c r="D89" s="229" t="str">
@@ -23060,14 +23068,14 @@
       </c>
       <c r="F89" s="236"/>
       <c r="G89" s="228" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H89" s="228"/>
       <c r="I89" s="229" t="str">
         <f>=ROUND($D$89-$I$88,2)</f>
       </c>
       <c r="L89" s="143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M89" s="116" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$15,'III. Finanzberichte'!$J$15,'III. Finanzberichte'!$Q$15,'III. Finanzberichte'!$X$15,'III. Finanzberichte'!$AE$15,'III. Finanzberichte'!$AL$15,'III. Finanzberichte'!$AS$15,'III. Finanzberichte'!$AZ$15,'III. Finanzberichte'!$BG$15,'III. Finanzberichte'!$BN$15,'III. Finanzberichte'!$BU$15,'III. Finanzberichte'!$CB$15,'III. Finanzberichte'!$CI$15,'III. Finanzberichte'!$CP$15,'III. Finanzberichte'!$CW$15,'III. Finanzberichte'!$DD$15,'III. Finanzberichte'!$DK$15,'III. Finanzberichte'!$DR$15),"")</f>
@@ -23084,7 +23092,7 @@
     </row>
     <row r="90">
       <c r="L90" s="345" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M90" s="333" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$16,'III. Finanzberichte'!$J$16,'III. Finanzberichte'!$Q$16,'III. Finanzberichte'!$X$16,'III. Finanzberichte'!$AE$16,'III. Finanzberichte'!$AL$16,'III. Finanzberichte'!$AS$16,'III. Finanzberichte'!$AZ$16,'III. Finanzberichte'!$BG$16,'III. Finanzberichte'!$BN$16,'III. Finanzberichte'!$BU$16,'III. Finanzberichte'!$CB$16,'III. Finanzberichte'!$CI$16,'III. Finanzberichte'!$CP$16,'III. Finanzberichte'!$CW$16,'III. Finanzberichte'!$DD$16,'III. Finanzberichte'!$DK$16,'III. Finanzberichte'!$DR$16),"")</f>
@@ -23101,7 +23109,7 @@
     </row>
     <row r="91">
       <c r="L91" s="341" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M91" s="330"/>
       <c r="N91" s="330"/>
@@ -23113,21 +23121,21 @@
         <v>205</v>
       </c>
       <c r="M92" s="331" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N92" s="331" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O92" s="331" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P92" s="344" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="true">
       <c r="B93" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C93" s="18"/>
       <c r="D93" s="18"/>
@@ -23172,31 +23180,31 @@
     </row>
     <row r="95" ht="28" customHeight="true">
       <c r="B95" s="263" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C95" s="264" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D95" s="264" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E95" s="264" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F95" s="264" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G95" s="264" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H95" s="264" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I95" s="264" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J95" s="265" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L95" s="143" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$B$21,'III. Finanzberichte'!$I$21,'III. Finanzberichte'!$P$21,'III. Finanzberichte'!$W$21,'III. Finanzberichte'!$AD$21,'III. Finanzberichte'!$AK$21,'III. Finanzberichte'!$AR$21,'III. Finanzberichte'!$AY$21,'III. Finanzberichte'!$BF$21,'III. Finanzberichte'!$BM$21,'III. Finanzberichte'!$BT$21,'III. Finanzberichte'!$CA$21,'III. Finanzberichte'!$CH$21,'III. Finanzberichte'!$CO$21,'III. Finanzberichte'!$CV$21,'III. Finanzberichte'!$DC$21,'III. Finanzberichte'!$DJ$21,'III. Finanzberichte'!$DQ$21),"")</f>
@@ -23260,7 +23268,7 @@
     </row>
     <row r="97">
       <c r="B97" s="266" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C97" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$13,'III. Finanzberichte'!$L$13,'III. Finanzberichte'!$S$13,'III. Finanzberichte'!$Z$13,'III. Finanzberichte'!$AG$13,'III. Finanzberichte'!$AN$13,'III. Finanzberichte'!$AU$13,'III. Finanzberichte'!$BB$13,'III. Finanzberichte'!$BI$13,'III. Finanzberichte'!$BP$13,'III. Finanzberichte'!$BW$13,'III. Finanzberichte'!$CD$13,'III. Finanzberichte'!$CK$13,'III. Finanzberichte'!$CR$13,'III. Finanzberichte'!$CY$13,'III. Finanzberichte'!$DF$13,'III. Finanzberichte'!$DM$13,'III. Finanzberichte'!$DT$13),2),0)</f>
@@ -23348,7 +23356,7 @@
     </row>
     <row r="99">
       <c r="B99" s="266" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C99" s="239" t="str">
         <f>=IFERROR(ROUND(CHOOSE(E81,'III. Finanzberichte'!$E$15,'III. Finanzberichte'!$L$15,'III. Finanzberichte'!$S$15,'III. Finanzberichte'!$Z$15,'III. Finanzberichte'!$AG$15,'III. Finanzberichte'!$AN$15,'III. Finanzberichte'!$AU$15,'III. Finanzberichte'!$BB$15,'III. Finanzberichte'!$BI$15,'III. Finanzberichte'!$BP$15,'III. Finanzberichte'!$BW$15,'III. Finanzberichte'!$CD$15,'III. Finanzberichte'!$CK$15,'III. Finanzberichte'!$CR$15,'III. Finanzberichte'!$CY$15,'III. Finanzberichte'!$DF$15,'III. Finanzberichte'!$DM$15,'III. Finanzberichte'!$DT$15),2),0)</f>
@@ -23392,7 +23400,7 @@
     </row>
     <row r="100" ht="20" customHeight="true">
       <c r="B100" s="271" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C100" s="272" t="str">
         <f>=ROUND(SUM($C$96:$C$99),2)</f>
@@ -23453,7 +23461,7 @@
     </row>
     <row r="102" ht="22" customHeight="true">
       <c r="B102" s="18" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C102" s="18"/>
       <c r="D102" s="18"/>
@@ -23481,7 +23489,7 @@
     </row>
     <row r="103">
       <c r="L103" s="345" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M103" s="333" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$29,'III. Finanzberichte'!$J$29,'III. Finanzberichte'!$Q$29,'III. Finanzberichte'!$X$29,'III. Finanzberichte'!$AE$29,'III. Finanzberichte'!$AL$29,'III. Finanzberichte'!$AS$29,'III. Finanzberichte'!$AZ$29,'III. Finanzberichte'!$BG$29,'III. Finanzberichte'!$BN$29,'III. Finanzberichte'!$BU$29,'III. Finanzberichte'!$CB$29,'III. Finanzberichte'!$CI$29,'III. Finanzberichte'!$CP$29,'III. Finanzberichte'!$CW$29,'III. Finanzberichte'!$DD$29,'III. Finanzberichte'!$DK$29,'III. Finanzberichte'!$DR$29),"")</f>
@@ -23498,31 +23506,31 @@
     </row>
     <row r="104" ht="28" customHeight="true">
       <c r="B104" s="263" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C104" s="264" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D104" s="264" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E104" s="264" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F104" s="264" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G104" s="264" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H104" s="264" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I104" s="264" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J104" s="265" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L104" s="47"/>
       <c r="P104" s="48"/>
@@ -23556,7 +23564,7 @@
         <f>=ROUND(IFERROR(($G$105/$H$105)-1,0),4)</f>
       </c>
       <c r="L105" s="347" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M105" s="348" t="str">
         <f>=IFERROR(CHOOSE(E81,'III. Finanzberichte'!$C$31,'III. Finanzberichte'!$J$31,'III. Finanzberichte'!$Q$31,'III. Finanzberichte'!$X$31,'III. Finanzberichte'!$AE$31,'III. Finanzberichte'!$AL$31,'III. Finanzberichte'!$AS$31,'III. Finanzberichte'!$AZ$31,'III. Finanzberichte'!$BG$31,'III. Finanzberichte'!$BN$31,'III. Finanzberichte'!$BU$31,'III. Finanzberichte'!$CB$31,'III. Finanzberichte'!$CI$31,'III. Finanzberichte'!$CP$31,'III. Finanzberichte'!$CW$31,'III. Finanzberichte'!$DD$31,'III. Finanzberichte'!$DK$31,'III. Finanzberichte'!$DR$31),"")</f>
@@ -23776,7 +23784,7 @@
     </row>
     <row r="113" ht="20" customHeight="true">
       <c r="B113" s="271" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C113" s="272" t="str">
         <f>=ROUND(SUM($C$105:$C$112),2)</f>
@@ -24192,19 +24200,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C1" s="351" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I1" s="351" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O1" s="351" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="U1" s="351" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="BA1">
         <v>1</v>
@@ -24265,7 +24273,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C2" cm="1" s="3">
         <f t="array" ref="C2">_xlfn._xlws.FILTER(_xlfn.ANCHORARRAY(AA2), (_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(AA2),3)&lt;&gt;0)+(_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(AA2),4)&lt;&gt;0), "")</f>
@@ -24350,7 +24358,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="BA3">
         <v>3</v>
@@ -24403,7 +24411,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="BA4">
         <v>4</v>
@@ -24456,7 +24464,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -24509,7 +24517,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="BA6">
         <v>6</v>
@@ -24562,7 +24570,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="BA7">
         <v>7</v>
@@ -24615,7 +24623,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="BA8">
         <v>8</v>
@@ -24668,7 +24676,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="BA9">
         <v>9</v>
@@ -24721,7 +24729,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BA10">
         <v>10</v>
@@ -24763,7 +24771,7 @@
         <f>=$BD$1</f>
       </c>
       <c r="BT10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU10" t="str">
         <f>=IFERROR('IV. MA'!C22,0)</f>
@@ -24774,7 +24782,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BA11">
         <v>11</v>
@@ -24827,7 +24835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BA12">
         <v>12</v>
@@ -24880,7 +24888,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="BA13">
         <v>13</v>
@@ -24933,7 +24941,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BA14">
         <v>14</v>
@@ -24986,7 +24994,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="BA15">
         <v>15</v>
@@ -25039,7 +25047,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="BA16">
         <v>16</v>
@@ -25092,7 +25100,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="BA17">
         <v>17</v>
@@ -25145,7 +25153,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="BA18">
         <v>18</v>
@@ -25238,7 +25246,7 @@
         <f>=$BD$2</f>
       </c>
       <c r="BT21" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU21" t="str">
         <f>=IFERROR('IV. MA'!G22,0)</f>
@@ -25425,7 +25433,7 @@
         <f>=$BD$3</f>
       </c>
       <c r="BT32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU32" t="str">
         <f>=IFERROR('IV. MA'!K22,0)</f>
@@ -25612,7 +25620,7 @@
         <f>=$BD$4</f>
       </c>
       <c r="BT43" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU43" t="str">
         <f>=IFERROR('IV. MA'!O22,0)</f>
@@ -25799,7 +25807,7 @@
         <f>=$BD$5</f>
       </c>
       <c r="BT54" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU54" t="str">
         <f>=IFERROR('IV. MA'!S22,0)</f>
@@ -25986,7 +25994,7 @@
         <f>=$BD$6</f>
       </c>
       <c r="BT65" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU65" t="str">
         <f>=IFERROR('IV. MA'!W22,0)</f>
@@ -26173,7 +26181,7 @@
         <f>=$BD$7</f>
       </c>
       <c r="BT76" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU76" t="str">
         <f>=IFERROR('IV. MA'!AA22,0)</f>
@@ -26360,7 +26368,7 @@
         <f>=$BD$8</f>
       </c>
       <c r="BT87" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU87" t="str">
         <f>=IFERROR('IV. MA'!AE22,0)</f>
@@ -26547,7 +26555,7 @@
         <f>=$BD$9</f>
       </c>
       <c r="BT98" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU98" t="str">
         <f>=IFERROR('IV. MA'!AI22,0)</f>
@@ -26734,7 +26742,7 @@
         <f>=$BD$10</f>
       </c>
       <c r="BT109" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU109" t="str">
         <f>=IFERROR('IV. MA'!AM22,0)</f>
@@ -26921,7 +26929,7 @@
         <f>=$BD$11</f>
       </c>
       <c r="BT120" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU120" t="str">
         <f>=IFERROR('IV. MA'!AQ22,0)</f>
@@ -27108,7 +27116,7 @@
         <f>=$BD$12</f>
       </c>
       <c r="BT131" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU131" t="str">
         <f>=IFERROR('IV. MA'!AU22,0)</f>
@@ -27295,7 +27303,7 @@
         <f>=$BD$13</f>
       </c>
       <c r="BT142" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU142" t="str">
         <f>=IFERROR('IV. MA'!AY22,0)</f>
@@ -27482,7 +27490,7 @@
         <f>=$BD$14</f>
       </c>
       <c r="BT153" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU153" t="str">
         <f>=IFERROR('IV. MA'!BC22,0)</f>
@@ -27669,7 +27677,7 @@
         <f>=$BD$15</f>
       </c>
       <c r="BT164" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU164" t="str">
         <f>=IFERROR('IV. MA'!BG22,0)</f>
@@ -27856,7 +27864,7 @@
         <f>=$BD$16</f>
       </c>
       <c r="BT175" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU175" t="str">
         <f>=IFERROR('IV. MA'!BK22,0)</f>
@@ -28043,7 +28051,7 @@
         <f>=$BD$17</f>
       </c>
       <c r="BT186" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU186" t="str">
         <f>=IFERROR('IV. MA'!BO22,0)</f>
@@ -28230,7 +28238,7 @@
         <f>=$BD$18</f>
       </c>
       <c r="BT197" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BU197" t="str">
         <f>=IFERROR('IV. MA'!BS22,0)</f>
